--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF53"/>
+  <dimension ref="A1:AF103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,8 +604,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>N</t>
@@ -701,7 +699,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
           <t>(사업관련) 심천비즈니스센터 +86-755-2692-0717, rainbowlu@kocca.kr / (웰콘관련) WelCon Help Desk 1566-9984, welcon@kocca.kr</t>
@@ -712,7 +709,6 @@
           <t>rainbowlu@kocca.kr</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -750,7 +746,6 @@
           <t>□ 지원규모 : 충북 소재 수출(희망) 중소기업 50개사 내외</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>50개</t>
@@ -916,7 +911,6 @@
           <t>1675백만원</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>N</t>
@@ -1012,13 +1006,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
           <t>한국환경산업기술원 녹색투자지원실 02-2284-1989, 1974</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
           <t>02-2284-1989</t>
@@ -1066,7 +1058,6 @@
           <t>40백만원</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1225,7 +1216,6 @@
           <t>2백만원</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>N</t>
@@ -1321,13 +1311,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
           <t>경기신용보험센터 031-230-1581 및 서울, 인천권역 신용보험센터 공고문 참조</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
           <t>031-230-1581</t>
@@ -1375,7 +1363,6 @@
           <t>40백만원</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1533,7 +1520,6 @@
           <t>2억원</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1691,7 +1677,6 @@
           <t>200만원</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1849,7 +1834,6 @@
           <t>1억원</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2002,8 +1986,6 @@
           <t>지원 지원금액 기업부담</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2161,7 +2143,6 @@
           <t>5백만원</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2319,7 +2300,6 @@
           <t>48백만원</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>N</t>
@@ -2415,13 +2395,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr">
         <is>
           <t>광주경제진흥상생일자리재단 소상공인디지털전환실 062-960-2635</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
           <t>062-960-2635</t>
@@ -2469,7 +2447,6 @@
           <t>200만원</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2727,7 +2704,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr">
         <is>
           <t>한국출판문화산업진흥원 케이북세계로팀 063-219-2867, hyemm@kpipa.or.kr</t>
@@ -2781,8 +2757,6 @@
           <t>지원내용: 해외 바이어 수출상담을 통한 글로벌 온·오프라인 시장 진출 지원</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2940,7 +2914,6 @@
           <t>100백만원</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3098,7 +3071,6 @@
           <t>750만원</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3253,8 +3225,6 @@
           <t>2 지원규모 및 지원내용</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3576,7 +3546,6 @@
           <t>1천만원</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3901,7 +3870,6 @@
           <t>3억원</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4007,7 +3975,6 @@
           <t>경상북도경제진흥원 민생경제지원팀 1800-8730 경산시 소상공인연합회 053-814-0405</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
           <t>053-814-0405</t>
@@ -4053,8 +4020,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>N</t>
@@ -4150,7 +4115,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr">
         <is>
           <t>청주상공회의소 충북지식재산센터 043-229-2734, ooppy7093@korcham.net</t>
@@ -4310,13 +4274,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr">
         <is>
           <t>경기테크노파크 기술사업화팀 031-500-3017</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
           <t>031-500-3017</t>
@@ -4364,7 +4326,6 @@
           <t>180만원</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4460,7 +4421,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr">
         <is>
           <t>부산정보산업진흥원 051-749-9154, organix@bipa.kr</t>
@@ -4514,8 +4474,6 @@
           <t>❍ 지원내용 : 2026년 아시아 기계 &amp; 제조 산업전 AMXPO 소공인 공동관 운영</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>N</t>
@@ -4678,7 +4636,6 @@
           <t>3억원</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4784,7 +4741,6 @@
           <t>경상북도경제진흥원 민생경제지원팀 1800-8730 / 경상북도소상공인연합회 054-772-7008</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
           <t>054-772-7008</t>
@@ -4994,7 +4950,6 @@
           <t>1억원</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5152,7 +5107,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>N</t>
@@ -5310,7 +5264,6 @@
           <t>20만원</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5468,7 +5421,6 @@
           <t>90만원</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>N</t>
@@ -5574,7 +5526,6 @@
           <t>강원특별자치도 소상공인과 상생경제팀 033-249-3226 사회적기업통합사업관리시스템 고객센터 1661-4006 및 각 시군별 사회적기업 담당부서 문의처 공고문 10p 참조</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
           <t>033-249-3226</t>
@@ -5622,7 +5573,6 @@
           <t>85백만원</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5775,8 +5725,6 @@
           <t>□ 지원규모</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5936,7 +5884,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6099,7 +6046,6 @@
           <t>2000만원</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6257,7 +6203,6 @@
           <t>7천만원</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6572,8 +6517,6 @@
           <t>□ 지원내용 : 안테나숍 입점 및 판매 지원</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6732,7 +6675,6 @@
           <t>2096270원</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6838,7 +6780,6 @@
           <t>전북특별자치도 금융사회적경제과 063-280-3781 전북사회연대경제(전북 사회적기업ㆍ협동조합 통합지원센터) 063-213-2244 및 기타 시군별 문의처 공고문 12p 참조 (시스템 문의안내) 사회적기업포털 031-697-7700</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr">
         <is>
           <t>031-697-7700</t>
@@ -6881,8 +6822,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>N</t>
@@ -6978,13 +6917,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr">
         <is>
           <t>(신청·접수 관련 문의) 부산광역시 중소상공인지원과 051-888-4764 및 구ㆍ군별 문의처 공고문 참조 (사회적기업 포털 이용 문의) 한국사회적기업진흥원 1661-4006</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr">
         <is>
           <t>051-888-4764</t>
@@ -7032,7 +6969,6 @@
           <t>1억원</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>N</t>
@@ -7128,7 +7064,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr">
         <is>
           <t>대한무역투자진흥공사 한류소비재팀 02-3460-7747, 7737 / ge_cgsk@kotra.or.kr 및 기타 문의처 공고문 참조</t>
@@ -7286,7 +7221,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr">
         <is>
           <t>대한무역투자진흥공사 한류소비재팀 02-3460-7747, 7737 / ge_cgsk@kotra.or.kr</t>
@@ -7344,7 +7278,6 @@
           <t>250만원</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>N</t>
@@ -7440,7 +7373,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr">
         <is>
           <t>KOTRA 물류지원실 02-3460-7433, 7428 KOTRA 상하이무역관 +86-21-5108-8771-108, lujingsh@kotra.or.kr</t>
@@ -7493,8 +7425,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>N</t>
@@ -7590,7 +7520,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr">
         <is>
           <t>KOTRA 톈진무역관 youngyoung@kotra.or.kr, castletiger@kotra.or.kr</t>
@@ -7601,7 +7530,6 @@
           <t>castletiger@kotra.or.kr</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -7639,8 +7567,6 @@
           <t>모집규모</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7793,8 +7719,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>N</t>
@@ -7900,7 +7824,6 @@
           <t>대한무역투자진흥공사 중소혁신기업팀 02-3460-7545</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="inlineStr">
         <is>
           <t>02-3460-7545</t>
@@ -7948,7 +7871,6 @@
           <t>5억원</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8270,7 +8192,6 @@
           <t>15백만원</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8376,7 +8297,6 @@
           <t>성남시청 기업혁신과 기업고도화팀 031-729-2583</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr">
         <is>
           <t>031-729-2583</t>
@@ -8419,7 +8339,6 @@
           <t>○ 모집규모: 10개사 내외</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>10개</t>
@@ -8584,8 +8503,6 @@
           <t>지원내용&gt;&lt;&gt;</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>N</t>
@@ -8681,13 +8598,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr">
         <is>
           <t>충남대학교 창업보육센터 042-933-7181 및 센터별 문의처 공고문 참조</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr"/>
       <c r="AD53" t="inlineStr">
         <is>
           <t>042-933-7181</t>
@@ -8701,6 +8616,7777 @@
       <c r="AF53" t="inlineStr">
         <is>
           <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125031</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026년 빅웨이브 글로벌(일본5차)참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>인천창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-08-04 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>이메일 접수 (global@biigwave.org)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>○ 모집대상 및 지원규모 : 총3개사 내외(공고일 기준 설립 7년이내)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>[필수] 신청서, 개인정보제공동의서, 티저, IR자료, 주주명부 등, [선택], 이외의 글로벌 관련 소개자료, (해외경진대회수상증명</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>인천창조경제혁신센터 글로벌오픈이노베이션팀 032-458-5026, sskim@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sskim@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>032-458-5026</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125195</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 2차 미취업청년 취업연계 일경험 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>충청북도기업진흥원</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>방문 또는 우편, 이메일 접수
+- 접수처 : (28542) 충북 청주시 상당구 사북로 164(우민타워), 5층 충북청년희망센터 일경험 지원 담당자 앞
+- 이메일 : cba9783@naver.com</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>- 일경험 청년 인건비 월 최대 180만원 지원(3개월)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>180만원</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>의 접수처 도착 기준으로 접수마감, 충북청년희망센터 일경험 지원 담당자 앞, (이메일 : cba9783@naver.com), 신청서 및, 는 충북기업진흥원 홈페이지(www.cba.ne.kr), 지원사업 안내(사업공고/신청) 공고문 붙임 서식 참조,  유의사항, 우선 판단하여 접수 바라며</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>충청북도기업진흥원 청년고용지원팀 043-270-0262, cba9783@naver.com</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>cba9783@naver.com</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>043-270-0262</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125194</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 독일 뒤셀도르프 의료기기 전시회(MEDICA) 단체참가 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-07-30 ~ 2026-08-13</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>온라인 접수 (대전비즈 홈페이지)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>❍ 지원내용: 단체참가 비용(부스임차료, 장치비, 통역비 등) 12백만원 한도 내외</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>12백만원</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>【신청절차】, 신청 해당사업 접속 → 지원 사업신청 및, 압축 후 업로드, 【필수, 영문 모두 제출), ④ 제품소개서(붙임1), ⑤ 참여기업 성과 조사지(붙임2), ⑥ 참가기업 서약서(붙임3)</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원 기업통상지원팀 042-380-3042, djtrade@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>djtrade@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>042-380-3042</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125193</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026년 중국 섬서성 환경보호산업 시장진출 지원사업 연장 공고</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-07-23 ~ 2026-08-13</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>온라인 접수(무역투자24)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>◇ 가격단가 : 1개사당 한화 50만원(출장자 1인 기준)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사 시안무역관 86-29-88831060(106), wangyang@kotra.or.kr 한국환경산업기술원 중국사무소 86-10-85910997, cms0522@keiti.re.kr</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>cms0522@keiti.re.kr</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125192</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 3차 해외규격인증 획득지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>선착순 접수</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>온라인 접수 (대전비즈홈페이지)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 10개사 내외</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원 기업통상지원팀 담당자 042-380-3045, djtrade@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>djtrade@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>042-380-3045</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125190</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>[경북] 영천시 2026년 해외(태국ㆍ말레이시아) 무역사절단 참가기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>모집 완료시까지</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>이메일 접수 (summerseol@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>※1개사 당 항공료 및 숙박비 135만원 한도 내 지원, 기타 출장비 지원사업 중복 수혜 불가</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>135만원</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>비고, 사업 참가 신청서 · [양식1] 참조, · 소재지 및 제조 기업 확인용, 건축물 관리대장 상 주, 용도가 ‘공장’ 또는 ‘제조업소’ 일 경우 신청 가능, 기업 및 제품 카탈로그, 년 수출 실적 증명 서류, 외국어 카탈로그 · 해당기업만 제출</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 동부지소 054-612-2971, summerseol@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>summerseol@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>054-612-2971</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125189</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>[경북] 김천시 2026년 해외무역사절단 파견 지원 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>이메일 접수 (dkkim00700@daum.net)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>□ (모집규모) 10개사 정도</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>순번, 비고, · 신청서, 제품(상품) 소개서, 개인(기업)정보 이용 등에 관한 동의서 각 1부 붙임, · 수출실적증명서(2024년, 년), 각 1부</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 ESGㆍ기업지원팀 054-470-8559</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>dkkim00700@daum.net</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>054-470-8559</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125188</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>[경북] 김천시ㆍ칠곡군 2026년 6차 시군 특화 맞춤형 일자리 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>구미전자정보기술원</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-07-29 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>온라인 접수 (구미시 창업지원 통합안내사이트)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>□ 모집규모 : 8개 사(김천 4, 칠곡 4)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>8개</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>가 미비하거나 채용 요건 미 충족 시, 차순위 기업 기회 부여, 시군특화 참여기업 청년 참여기업 R&amp;D 과제 및, 참여기업 모집 인력 신규 채용 최종 선정 및 도제식, 및 1차 선정 및 고용계약 체결 협약체결 교육훈련 지원, 지원 내용, ① (프로젝트 과제비 지원), ◦ 기업이 추진하고 있는 R&amp;D 프로젝트의 기획</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>구미전자정보기술원 창업성장지원센터 054-479-2054</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>054-479-2054</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125186</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>[강원] 2026년 하반기 중소기업 밀집지역 위기대응 체계 구축사업 Stand-up 맞춤지원 모집 공고</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>강원테크노파크</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>이메일 또는 우편 접수
+- 이메일 : leesy@gwtp.or.kr
+- 접수처 : 강원 지역중소기업 위기지원센터(강원테크노파크)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>97백만원</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>97백만원</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>포워딩 인보이스, 비용지급 관련 송금영수증(지원기업→물류업체), 비용지급 관련 세금계산서(물류업체→지원기업), 국내운임, 취급수수료, 도착국 발생비용, 세금은 제외, 최대 5백만원</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>강원 지역중소기업 위기지원센터(강원테크노파크) 033-248-5696, leesy@gwtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>leesy@gwtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>033-248-5696</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125185</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 사회연대경제박람회 판매ㆍ체험 부스 참여기업 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>광주사회적경제지원센터</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-11</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>이메일 접수 (gjsec_m@gjsec.kr)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>※ 적격성 검토 결과에 따라 선착순 접수 기업이더라도 최종 선정에서 제외될 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>연번, 서식 구분, 신청서 서식 1 필수 공통, 정보제공동의서 서식 2 필수 공통, 사회연대경제기업 인증(지정)서 - 필수 공통, 상품·체험 사진 - 필수 참여기업, 식품제조가공업, 즉석판매제조가공업</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>광주사회적경제지원센터 기업성장팀 062-531-6667(내선 2번), 070-7707-3156, 6836</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>gjsec_m@gjsec.kr</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>062-531-6667</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125184</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>[충남] 예산군 2026년 3차 뿌리산업 고도화를 통한 전후방산업 동반성장 모델 구축 사업 모집 공고(시군구 연고산업 육성사업)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>충남테크노파크</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>온라인 접수 (중소기업 기술개발사업 종합관리시스템)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>지원규모 : 76273천원</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>의 미비 또는, 가 사실과 다른 경우,  본 사업에 적정하지 않다고 판단되는 경우, 지원규모 : 76, 천원, (지원규모) 총 약 백만원, (지원범위) 기업별 총 한도 천만원 이내에서 지원, (지원범위 및 프로그램)</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>(사업공고 문의) 선문대학교 041-530-8486, kej20@sunmoon.ac.kr, 한국지역특화산업협회 041-583-1326, kria77@nate.com / (온라인접수 시스템문의) SMTECH중소기업 통합콜센터 1357(국번없이)</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>kej20@sunmoon.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>041-530-8486</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125183</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>[인천] 2026년 공공구매(조달) 상담회 참가기업 모집 공고(지역상품 공공 조달정보 지원사업)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>인천상공회의소</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-09-14</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>온라인 접수(Biz-OK)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>m 공공기관과 공급 희망 기업 간 만남의 장 마련 m 모집규모 : 인천 관내 소재 기업 50개사 내외</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>50개</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>관 등 15개소 내외, 서류 제출 시, 모든 서류 파일명에 순번 표기하여 zip 파일로 제출, 최종, 구 분, ※ 제품 사진 포함 서식 작성 필수, 수요자 중심 매칭 방식으로 운영됨, ④ [서식4] 정보활용동의서</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>인천상공회의소 경제진흥실 032-810-2865 shkang@incham.net</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>shkang@incham.net</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>032-810-2865</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125182</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026년 민관협력 오픈이노베이션 지원 성과기업 후속 지원 창업기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>창업진흥원</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>온라인 접수 (K-Startup누리집)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>□ 지원내용 : 창업기업 대상 사업화 자금(최대 2억원) 및 후속 연계 지원</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2억원</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>중 일부를 별도로 발급받지 않아도, 자동 연동하여 제출 가능합니다. * 4. 접수 방법-, 참고, 모집 개요, 창업기업의 지속 성장을 위해 PoV 등 후속 협업 지원, 공고문 내 신청자격 및 요건을 충족하는 기업, 선정규모 : 창업기업 80개사 내외, 모집유형 : ➊ 성과 우수형</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>(사업문의) 창업진흥원 민관협력실 044-410-1720, 1767, 1764 / (시스템문의) 중소기업통합콜센터 국번없이 1357</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>044-410-1720</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125181</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026년 부산국제수산EXPO(BISFE) 연계 상담회 참가업체 모집 공고</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>수협중앙회</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-07-29 ~ 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>온라인 신청(K-씨푸드 온라인 사업신청 통합시스템)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>&lt;신청기한&gt;&lt;○ 2026. 9. 18(금) 23:00&gt;, 온라인 신청서 및 첨부파일의 엑셀 양식 작성 필수, 참가조건, 바이어와의 상담에서 수출형태, 가격, 결제방법 등을 포함한</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>수협중앙회 무역사업부 02-2240-5604, inapark@suhyup.co.kr</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>inapark@suhyup.co.kr</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>02-2240-5604</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125180</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>[부산] 2026년 국제게임전시회 지스타 BTBㆍBTC 부산공동관 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>부산정보산업진흥원</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>이메일 접수(jhj0813@bipa.kr)
+※ BTBㆍBTC 동시 신청 가능</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>- 지원규모 : 20개사 내외</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20개</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>부산정보산업진흥원 신기술게임단 게임산업팀 051-749-9140, jhj0813@bipa.kr</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>jhj0813@bipa.kr</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>051-749-9140</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125179</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026년 2차 ICT 비즈니스 파트너십(일본) 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>정보통신산업진흥원</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-09-02</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>이메일 접수 (sohee7278@nipa.kr)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>(공식일정), 참가기업별 1인 출장비용(최대 200만원)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>200만원</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>양식1) 참가신청서, 양식2) 기업 소개 자료, 양식3) 개인정보 수집·이용·제공 동의서, 양식4) 참가서약서, ※ 마감시간(14시) 이후 접수 무효이므로 시간 엄수, 박소희 책임 (043-931-5522</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>정보통신산업진흥원 글로벌본부 글로벌협력팀 043-931-5522, sohee7278@nipa.kr</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>sohee7278@nipa.kr</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>043-931-5522</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125178</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026년 제26회 올해의 여성과학기술인상 선정계획 공고</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>한국여성과학기술인육성재단</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-07-28 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>온라인 접수 (한국여성과학기술인육성재단)
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ㅇ 포상 내용 : 부총리 겸 과학기술정보통신부장관 상장 및 상금 각 1천만 원</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1천만원</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>① [개인추천] 추천서 또는 [단체추천] 추천공문, ② 공적조서, ③ 개인정보 수집·이용 및 제공 동의서, ➃ 실적 증빙자료, [산업]_추천기관명(혹은 추천인)_후보자 이름, [진흥]_추천기관명(혹은 추천인)_후보자 이름, 별 사용 양식 및 작성 안내&gt;, 명 사용 양식 작성 안내</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>한국여성과학기술인육성재단 사업운영실 사업전략팀 02-6411-1063, hhkim@wiset.or.kr</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>hhkim@wiset.or.kr</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>02-6411-1063</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125177</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026년 문화체육관광 연구개발사업 기술사업화 및 글로벌 전시 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>한국콘텐츠진흥원</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-17</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>온라인 접수 (한국콘텐츠진흥원 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>&lt;지원규모&gt;&lt;ㅇ 연구개발기관(기술) 총 10개 내외   &gt;</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>한국콘텐츠진흥원 연구개발성과팀 042-330-6647, 6653 / kjh5315@kocca.kr, shinkim@kocca.kr</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>kjh5315@kocca.kr</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>042-330-6647</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125176</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 모빌리티 부품 제조AI 확산센터 구축 사업 기업지원 수혜기업 모집 통합 공고</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>지능형자동차부품진흥원</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-07-27 ~ 2026-08-17</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>이메일 접수
+- 지원프로그램에 따라 해당 기관 접수처로 이메일 접수
+ㆍ 제조 AI 기술도입을 위한 기술지원 : 지능형자동차부품진흥원 gamja38@kiapi.or.kr
+ㆍ 차량 SW 설계ㆍ특화ㆍ검증 및 기술지원 : 한국전자기술연구원 youngbo.shim@keti.re.kr
+ㆍ 제조공정 혁신 및 공정지원 특화 기술지원 : 대구경북과학기술원 kjp@dgist.ac.kr</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>프로그램별 상세 지원내용은 상세안내문 첨부 파일 참고</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>지원신청서 및 프로그램별 상세사업계획서 등 아래표 참조, 필요 시, 외 기업 확인을 위한 기타 서류 요청 가능, 󰊳 신청방법 및 지원절차, 기관 접수처로 이메일 접수, 선정 및 지원절차, 󰊴 평가방법 및 기준, 평가방법 선정평가 서류평가</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>지능형자동차부품진흥원 053-615-7606 / 한국전자기술연구원 031-739-7454 / 대구경북과학기술원 053-785-6314</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>031-739-7454</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125175</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>[울산] 2026년 방폭안전 강화사업 지원기업 모집 추가 공고</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>울산테크노파크</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>온라인 접수 (U Biz Platform)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ㅇ 지원규모 : 총 17개사 내외(사업장 상황을 고려하여 조정 가능)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>17개</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>첨단화학 기술지원단 052-216-9402, juna0072@utp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>juna0072@utp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>052-216-9402</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125174</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>[경기] 안산시 2026년 해외지사화 지원사업 참가기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>방문 또는 우편 접수
+- 접수처 : (15396) 안산시 단원구 중앙대로 685(초지동) 산업지원본부 기업지원과 해외지사화사업 담당자 앞
+※ 각종 증빙서류 사본 제출 시, 원본대조필 및 직인 날인 필요</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>(잔여예산 범위 내, 업체당 최대 300만원 이내)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>300만원</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>가. 신청방법 : 직접 방문 또는 우편, ∙우편 접수 :, 마감일 당일 18시, 도착분, 까지 인정, 나., 참가신청서, 참가 추진계획서</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>안산시 산업지원본부 기업지원과 해외지사화사업 담당자 031-481-2093</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>031-481-2093</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125173</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>[경기] 부천시 2026년 부천상권페스타 맞춤형 마케팅 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>부천산업진흥원</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>온라인, 이메일 접수
+- 온라인 : 부천산업진흥원
+- 이메일 : (전통시장) mjy@bizbc.or.kr (골목상권) leehy@bizbc.or.kr</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>- 골목상권 : 최대 1100만원  ※ 모집 결과에 따라 지원금액이 조정 될 수 있음</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1100만원</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>부천산업진흥원 (전통시장) 032-716-6144 (골목상권) 032-716-6143</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>032-716-6143</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125172</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>[경남] 2026년 3차 사회연대경제 청년 일경험사업 참여 기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>경남투자경제진흥원</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-10</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>이메일 또는 팩스 접수
+- 이메일 : sm1126@giba.or.kr
+- 팩스 : 055-230-2995 (팩스 발송 후 담당자 연락 요망)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1) 참여청년 임금 : 월 최대 234만원* , 5개월간 지급</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>234만원</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>및 상세내용 반드시 확인 (p.7), 【붙임 1】 사회연대경제 청년 일경험 참여기업 신청서, 【붙임 2】 참여기업 운영계획서, 【붙임 3】 참여기업 확인서, 【붙임 4】 참여기업 서약서, 참여자격 확인 서류, 고용보험 자격취득자 명부, 마을기업</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>경남투자경제진흥원 055-230-2943, 2912</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>sm1126@giba.or.kr</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>055-230-2943</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125171</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026년 스마트도시 특화단지 조성사업 스마트도시 알파-부스트 지원사업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>대구테크노파크</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>온라인 접수 (대구테크노파크)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t> 지원규모 : 14건 내외, 지원기업 별 최대 66000천원</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>14건</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>지능도시본부 지속가능도시센터 053-795-9766, iyh@dgtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>iyh@dgtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>053-795-9766</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125170</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026년 인간-AI 협업형 LAM 개발ㆍ글로벌 실증 사업 재공고</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>정보통신산업진흥원</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-10</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>온라인 접수(범부처통합연구지원시스템)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>68억원(48.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>68억원</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>검토 질의응답 종합심의, ㅇ 평가방법 및 기준, 평가위원 : 산·학·연 전문가 7인내외 구성, ☐ 평가항목(안), 평가항목 세부 평가항목(안) 배점(100), ㆍ연구개발 목표의 명확성, 연구개발, 연구개발의 이해도 및 목표의 명확성</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>(과제관련 문의) 정보통신산업진흥원 지역AX본부 지역AX거점팀 043-931-5947, 5929 / wsj0417@nipa.kr, csj@nipa.kr (시스템 관련 문의) 범부처통합연구지원시스템(IRIS) 콜센터 1877-2041, 042-862-1500</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>csj@nipa.kr</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>042-862-1500</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125169</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>[강원] 2026년 비관세장벽 대응 지원사업(미국FDA 식품등록) 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>강원지방중소벤처기업청</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jmkim1121@korea.kr)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>□ 지원규모 : 총 10개사 내외, 기업당 최대 100만원(부가세 포함) 지원</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>(필수 및 해당자료) 기한 내 제출, 구분 연번, 비 고, 사업신청서 및 수출계획서 [붙임1] 및 [붙임3], 개인 및 기업정보 수집 동의서 [붙임4], 수행기관(KTR) 견적서 KTR 김현호 수석연구원, 품목 제조 보고서, 영양성분 성적서</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>강원지방중소벤처기업청 수출지원센터 033-260-1675 / 한국화학융합시험연구원 글로벌소비재센터 02-2164-0043</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>jmkim1121@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>02-2164-0043</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125168</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>[경북] 연구장비 활용 수수료 지원사업 수혜기업 모집 공고(경북산업기술단지 거점기능강화사업)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>경북테크노파크</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경북테크노파크)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t> 지원금액 : 기업당 최대 3백만원</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>3백만원</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>(신청서 등) 미비기업 ③ 단순 유통업</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>경북테크노파크 기업지원단 기업육성지원실 053-819-3054, 053-819-3055 / skyhong@gbtp.or.kr, gmj@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>gmj@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>053-819-3054</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125167</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026년 디지털커머스 전문기관(소담스퀘어 in 경북) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>한국중소벤처기업유통원</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-10-30</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>온라인 접수 (판판대로)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>지원규모   100개사</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>100개</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>정보, 진행절차 정보, 진행절차 Step 1 판판대로 회원가입, Step3 신청서 등록, Step5 대상선정 및 지원, 문의처, 소담스퀘어 경북, [문의처 054-475-5003</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>소담스퀘어 경북 054-475-5003, gbsodam@sebiz.or.kr</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>gbsodam@sebiz.or.kr</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>054-475-5003</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125166</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>[경남] 양산시 2026년 중소 제조기업 맞춤형 시뮬레이션 지원사업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>한국생산기술연구원</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-11</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>이메일 접수 (hsb85@kitech.re.kr)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>&lt;3&gt;&lt;&gt;&lt;지원규모 및 지원내용&gt;</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>한국생산기술연구원 055-367-9405</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>055-367-9405</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125165</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>[강원] 중국 국제 중소기업 박람회 한국관 및 전시상담회 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-11</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>온라인 접수 (무역투자24)
+※ 사이트 접속이 어려운 경우 ESG경영혁신실 담당자에게 메일로 신청 (jwjeong@kotra.or.kr)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>부스 공동참가, 강원도와 상생으로 사업 규모화 및 홍보 극대화</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>ESG경영혁신실 86-20-2208-1603, cu@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>cu@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125164</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>[경남] 2026년 2차 소재부품 성장 잠재기업 육성사업 및 양산지역 중소기업 디지털 전환 공정 최적화 지원사업 수요기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>한국생산기술연구원</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-11</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>이메일 접수 (hsb85@kitech.re.kr)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>&lt;3&gt;&lt;&gt;&lt;지원규모 및 지원내용&gt;</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>한국생산기술연구원 055-367-9405</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>055-367-9405</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125163</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026년 해외 온라인 플랫폼 입점지원 사업 참여 소상공인 모집 공고</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>소상공인시장진흥공단</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-04 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>온라인 접수(소상공인24)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ㅇ 최종 선정된 소상공인은 수행기관과 계약 체결(선정 후 2주)하고, 자부담금과 부가세를 전문기관으로 납부해야 하며, 기한(계약 후 2주) 내 미납부 시 선정 취소될 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>(사업문의) 전문기관 1551-4536 스마트지원실 온라인판로팀 042-363-7825, 7826 (소상공인 24 시스템 문의) 1644-5302 (중소기업확인서(소상공인) 발급 문의) 1357</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>042-363-7825</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125162</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>패션 브랜드 협업활성화 원단지원 기업 모집 공고(원단 제공기업 대상 디자인 협업 및 홍보ㆍ마케팅 지원)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DYETEC연구원</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>이메일, 팩스, 방문 접수
+- 이메일 : fabricdive@dyetec.or.kr
+- 팩스 : 053-350-3887
+- 접수처 : (41706) 대구광역시 서구 달서천로 92 DYETEC연구원 섬유패션AX센터
+※ 발송 후 전화 연락 바랍니다</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>□ 모집규모 : 20개사 내외</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>20개</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>DYETEC연구원 섬유패션AX센터 053-350-3908</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>053-350-3908</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125161</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 우수 수산물 육성사업 대만 해외시장개척단 참가기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-07 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>이메일 접수 (osmasis@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>매출액 10억원 이상 5억원 이상 3억원 이상 1억원 이상 1억원 미만</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>10억원</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>신청서식 붙임 1참조, ◦ 기타 증빙자료 등 모든 제출자료는 PDF파일로 제출, ◦ 서류 제출 시, 순서에 맞게 하여 하나의 파일로 제출하거나 제출, 순서에 맞추어 파일명을 번호화 하여 작성·제출, ※예시) 1. 신청서, 체크리스트, 선정방법</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 동부지소 054-612-2967, osmasis@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>osmasis@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>054-612-2967</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125160</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 5차 글로벌 IP스타기업 육성 해외출원비용지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>전북지식재산센터</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>온라인 접수(RIPC사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>지원내용 : 해외 특허, 상표, 디자인 출원에 소요되는 비용 중 일부를 지원하며, 전북지식재산센터 컨설턴트의 컨설팅 병행 제공</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>전북지식재산센터 글로벌 IP스타기업 담당자 (대표) 063-252-9301, (직통) 070-7775-2623 / djdyc122@kipa.org</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>djdyc122@kipa.org</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>063-252-9301</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125159</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 2차 기능성식품 규제자유특구 규제자유특구혁신사업육성  사업화지원 사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>한국식품산업클러스터진흥원</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-08-04 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>이메일 접수(ryu2616@foodpolis.kr)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>□ 지원규모 및 비율</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>접수, (메일), (화), (월), 특구사업자, → 식품진흥원, 사전검토, 자격요건</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>한국식품산업클러스터진흥원 규제자유특구 사업화지원 담당자 063-720-0641 ryu2616@foodpolis.kr</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>ryu2616@foodpolis.kr</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>063-720-0641</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125158</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>[인천] 제물포구 2026년 하반기 착한가격업소 신규 지정 모집 공고</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>방문, 우편, 팩스 및 이메일 접수
+- 접수처 : 인천광역시 제물포구 신포로27번길 80, 서별관 1층 일자리경제과
+- 팩스 : 032-745-3119
+- 이메일 : smileyul@korea.kr
+※ 팩스나 이메일 신청 시 반드시 담당자에게 연락해주시기 바랍니다. (032-745-3103)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>▪ 지방세를 3회 이상 및 100만원 이상 체납하고 있는 업소</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>착한가격업소 지정 신청서, [공고문 하단 서식1], 개인정보 수집 및 이용 제공 동의서, [공고문 하단 서식2], 대표자 신분증 사본, 위생등급제 결과서(해당하는 경우만 제출), 착한가격업소 표찰 지원, 업소별 인센티브 지원</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>제물포구청 일자리경제과 032-745-3103</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>smileyul@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>032-745-3103</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125157</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026년 로봇 기반 공간컴퓨팅 창업지원 예비창업자(팀) 모집 추가공고</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>대구테크노파크</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-08-04 ~ 2026-08-19</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>이메일 접수 (petra@dgtp.or.kr)
+※ 접수 후 유선 확인 필수</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 90백만원</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>90백만원</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>접수 및 문의처, :00까지, ※ 접수 후 유선 확인 필수, 연번, 비고, ∘ 신청서 및 수행계획서 지정양식, ∘ 중복지원금지 확약서 지정양식, ∘ 청렴 이행 각서 지정양식</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>대구테크노파크 053-756-9126, petra@dgtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>petra@dgtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>053-756-9126</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125156</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026년 경북 K-뷰티산업 국내외 마케팅 지원사업 모집 공고(말레이시아ㆍ우즈베키스탄 공동관)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>경북IT융합산업기술원</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-12</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>방문 또는 우편 접수
+- 접수처 : 경북 경산시 삼성현로 738(유곡동 294-39), 글로벌 코스메틱 비즈니스센터 105호</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>기업부담금 : 100만원(VAT포함) 이상의 부스 그래픽, 제품 디스플레이</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>등을 확인하여 신청자격 등 검토, 후보기업: 선정취소ㆍ포기 기업 발생 시, 점 이상인 차순위 기업순으로 선정, ③ 결과발표 : 평가결과는 공개하지 않으며, 선정결과는 개별 통보, 평가항목, 평가항목 평가내용 배점 비고, 기업 제품의 품질 및 기술성</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>경북IT융합산업기술원 053-812-0276, cos@gitc.or.kr 및 기타 문의처 출처바로가기 내 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>cos@gitc.or.kr</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>053-812-0276</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125155</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>[경기] 성남시 2026년 산업기술보호 컨설팅 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>한국산업기술보호협회</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>이메일 접수 (security@kaits.or.kr)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>□ 지원내용 : 보안관리체계 전반 진단 및 개선방안 컨설팅, 정보시스템 취약점</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>한국산업기술보호협회 02-3489-7022, security@kaits.or.kr</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>security@kaits.or.kr</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>02-3489-7022</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125154</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>[제주] 2026년 아세안+α 시장 개척을 위한  바이어 초청 수출상담회 참가업체 모집 공고</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>직접수행</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-07-30 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>온라인 접수 (전자무역시스템)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>※ 모집규모 초과 시 선착순 마감(신청서류 접수순)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>접수순), 행사규모, 아세안+α 국가 바이어 5개사 이내, 도내 수출기업 20개사 이내, ※ 농수축산물, 가공식품, 화장품 등 수출 가능 상품 생산 및 수출업체, 프로그램</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>제주특별자치도 통상물류과 통상정책팀 064-710-3063, gh2kang@korea.kr</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>gh2kang@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>064-710-3063</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125153</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 반도체 공정기반 나노메디컬 기술상용화 지원 사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>나노종합기술원</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-07-31 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>이메일 접수 (hkyoun@nnfc.re.kr)
+※ 원본 1부 현장 방문 제출</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2천만원 이내 지원    - 기술지도를 위한 전문가 인건비 현물 지원   - 기술지도를 위한 재료구매를 포함한 외부시설사용비 지원   - 1.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2천만원</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>나노종합기술원 나노바이오센서ㆍ칩 기술상용화지원센터 042-366-1650</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr"/>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>042-366-1650</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125152</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026년 딥테크 창업기업 기술지원사업 LAB TO CITY (L2C)ㆍ반도체 공고</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>나노종합기술원</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-08-07 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>이메일 접수 (woojinyun@nnfc.re.kr)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>○ (지원규모) 총 5개 기업 선발/기업당 2000만원 기술원장비사용료 지원</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2000만원</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>나노종합기술원 042-366-1733</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr"/>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>042-366-1733</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125151</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>제24회 전주국제발효식품엑스포 참가기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>전북바이오융합산업진흥원</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>이메일 접수 (iffe@iffe.or.kr) 
+※ 서류제출 후 접수여부 확인 필수(063-210-6590)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>4M 1980000원/1부스 국내기업관 실내</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1980000원</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>(서류 4종), ① 참가지원 신청서 1부 (양식첨부), ② 전시품목 내역서 1부 (양식첨부), ③ 개인정보동의서 1부 (양식첨부), 모집기간 및 신청방법, ◦신청방법 : 서류 구비 후 e-mail 접수, 접수기업이 많아 간혹 누락건이 발생하고 있습니다., 접수여부 유선확인을 하지 않아 누락된 경우</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>전북바이오융합산업진흥원 기업육성팀 063-210-6590</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>iffe@iffe.or.kr</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>063-210-6590</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125150</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 경북세일페스타 유통사 입점 마케팅 데이 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>선착순 접수</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>온라인 접수 (라라랩)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 054-470-8577, 8572, gepa.commerce26@gmail.com / 운영사무국 02-1588-4550, gepa.commerce26@gmail.com</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>gepa.commerce26@gmail.com</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>02-1588-4550</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125149</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026년 북미 자동차 부품 전략 상담회 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>온라인 접수 (무역투자24)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>신청 시 하기의 제출 필수자료 첨부, 제출된 자료는, 바이어게 직접 전달 및 수출상담회에서 배포될 예정, ② 영문 기업 소개서/카탈로그, 전체 첨부 요망, ◦ 참가기업 선정, ◦ 문의처, 추진호 사원(jinho.choo@kotra.or.kr)</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>(사업 문의) KOTRA 디트로이트무역관 mjpark@kotra.or.kr (신청 문의) KOTRA 소재부품장비팀 mwjie@kotra.or.kr, jinho.choo@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>jinho.choo@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr"/>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125148</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>[인천] 계양구 2026년 하반기 착한가격업소 신규지정 모집 공고</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>방문, 팩스, 이메일 접수
+- 접수처 : 계양구청 5층 지역경제과(평일 09:00~18:00) 
+- 팩스 : 032-551-5746
+- 이메일 : kar9533@korea.kr
+※ 팩스나 이메일 신청시 반드시 담당자에게 연락해주시기 바랍니다.(032-450-5484)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>지방세를 3회 이상 또는 100만원 이상 체납하고 있는 경우(신청일 기준)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>착한가격업소 신규지정 신청서(붙임1), 위생등급제 결과서(해당하는 경우만 제출), 선정기준 :, 평점 총합이 40점 이상인 업소 중 선정, 점검기준, 배점, 세부기준, 가격</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구청 지역경제과 032-450-5484</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>kar9533@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>032-450-5484</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125147</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026년 ILS(Innovation Leaders Summit) 연계 한일 오픈이노베이션 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-19</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>온라인 접수 (무역투자24)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>◦ 모집규모 : 국내 유망 스타트업 O개사 (발표시간 5분)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>양식에 맞지 않을 경우 선정 대상에서 제외, 신청 마감 후 추가 접수 관련 문의 불가, [ 사업신청 세부절차 ], ① KOTRA 기업회원 가입 (※필수), 이노베이션 사업' 검색, ③ 사업신청 페이지에서 양식 다운로드 및 작성 후 제출, 문 1부 제출 필수, 일문 혹은 영어 자료 1부) 각 1부</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>KOTRA 도쿄무역관 +81-3-3214-6951, startup_japan@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>startup_japan@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr"/>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125146</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>[인천] 미추홀구 2026년 하반기 착한가격업소 신규 모집 공고</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>팩스 또는 이메일 접수
+- 팩스 : 032-880-4872
+- 이메일 : zeze1011@korea.kr</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>▪ 지방세를 3회 이상 또는 100만원 이상 체납하고 있는 업소(신청일 기준)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구청 경제지원과 032-880-4385</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>zeze1011@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>032-880-4385</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125145</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>[경기] 2026년 에너지기술공유대학(ETU) 산업체 연계 인턴십 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>경기산학융합원</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>이메일 접수 (chjm@giuci.or.kr)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>ㅇ 지원규모 : 총 8개사(기업당 1000000원) 예정</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1000000원</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>8개</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>(필수) 참여신청서 및 채용 계획서, (선택) 기업 소개자료 등, ㅇ 접수 및 문의 : (사)경기산학융합원 산학협력본부, 전화 : 031-8041-0178</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>경기산학융합원 산학협력본부 031-8041-0178, chjm@giuci.or.kr</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>chjm@giuci.or.kr</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>031-8041-0178</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125144</t>
         </is>
       </c>
     </row>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF103"/>
+  <dimension ref="A1:AF151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8645,7 +8645,6 @@
           <t>○ 모집대상 및 지원규모 : 총3개사 내외(공고일 기준 설립 7년이내)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>3개</t>
@@ -8972,7 +8971,6 @@
           <t>12백만원</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9230,7 +9228,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr">
         <is>
           <t>대한무역투자진흥공사 시안무역관 86-29-88831060(106), wangyang@kotra.or.kr 한국환경산업기술원 중국사무소 86-10-85910997, cms0522@keiti.re.kr</t>
@@ -9241,7 +9238,6 @@
           <t>cms0522@keiti.re.kr</t>
         </is>
       </c>
-      <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -9279,7 +9275,6 @@
           <t>❍ 지원규모 : 10개사 내외</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>10개</t>
@@ -9380,7 +9375,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr">
         <is>
           <t>대전일자리경제진흥원 기업통상지원팀 담당자 042-380-3045, djtrade@djbea.or.kr</t>
@@ -9595,7 +9589,6 @@
           <t>□ (모집규모) 10개사 정도</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>10개</t>
@@ -9753,7 +9746,6 @@
           <t>□ 모집규모 : 8개 사(김천 4, 칠곡 4)</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>8개</t>
@@ -9864,7 +9856,6 @@
           <t>구미전자정보기술원 창업성장지원센터 054-479-2054</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr"/>
       <c r="AD61" t="inlineStr">
         <is>
           <t>054-479-2054</t>
@@ -9914,7 +9905,6 @@
           <t>97백만원</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10067,8 +10057,6 @@
           <t>※ 적격성 검토 결과에 따라 선착순 접수 기업이더라도 최종 선정에서 제외될 수 있습니다.</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10221,8 +10209,6 @@
           <t>지원규모 : 76273천원</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10375,7 +10361,6 @@
           <t>m 공공기관과 공급 희망 기업 간 만남의 장 마련 m 모집규모 : 인천 관내 소재 기업 50개사 내외</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>50개</t>
@@ -10538,7 +10523,6 @@
           <t>2억원</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10644,7 +10628,6 @@
           <t>(사업문의) 창업진흥원 민관협력실 044-410-1720, 1767, 1764 / (시스템문의) 중소기업통합콜센터 국번없이 1357</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr"/>
       <c r="AD66" t="inlineStr">
         <is>
           <t>044-410-1720</t>
@@ -10687,8 +10670,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10842,7 +10823,6 @@
           <t>- 지원규모 : 20개사 내외</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>20개</t>
@@ -10943,7 +10923,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr">
         <is>
           <t>부산정보산업진흥원 신기술게임단 게임산업팀 051-749-9140, jhj0813@bipa.kr</t>
@@ -11001,7 +10980,6 @@
           <t>200만원</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>N</t>
@@ -11160,7 +11138,6 @@
           <t>1천만원</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>N</t>
@@ -11313,7 +11290,6 @@
           <t>&lt;지원규모&gt;&lt;ㅇ 연구개발기관(기술) 총 10개 내외   &gt;</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>10개</t>
@@ -11414,7 +11390,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr"/>
       <c r="AB71" t="inlineStr">
         <is>
           <t>한국콘텐츠진흥원 연구개발성과팀 042-330-6647, 6653 / kjh5315@kocca.kr, shinkim@kocca.kr</t>
@@ -11471,8 +11446,6 @@
           <t>프로그램별 상세 지원내용은 상세안내문 첨부 파일 참고</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>N</t>
@@ -11578,7 +11551,6 @@
           <t>지능형자동차부품진흥원 053-615-7606 / 한국전자기술연구원 031-739-7454 / 대구경북과학기술원 053-785-6314</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr">
         <is>
           <t>031-739-7454</t>
@@ -11621,7 +11593,6 @@
           <t>ㅇ 지원규모 : 총 17개사 내외(사업장 상황을 고려하여 조정 가능)</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>17개</t>
@@ -11722,7 +11693,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr"/>
       <c r="AB73" t="inlineStr">
         <is>
           <t>첨단화학 기술지원단 052-216-9402, juna0072@utp.or.kr</t>
@@ -11782,7 +11752,6 @@
           <t>300만원</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11888,7 +11857,6 @@
           <t>안산시 산업지원본부 기업지원과 해외지사화사업 담당자 031-481-2093</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr"/>
       <c r="AD74" t="inlineStr">
         <is>
           <t>031-481-2093</t>
@@ -11938,7 +11906,6 @@
           <t>1100만원</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>N</t>
@@ -12034,13 +12001,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr">
         <is>
           <t>부천산업진흥원 (전통시장) 032-716-6144 (골목상권) 032-716-6143</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr"/>
       <c r="AD75" t="inlineStr">
         <is>
           <t>032-716-6143</t>
@@ -12247,7 +12212,6 @@
           <t> 지원규모 : 14건 내외, 지원기업 별 최대 66000천원</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>14건</t>
@@ -12348,7 +12312,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr">
         <is>
           <t>지능도시본부 지속가능도시센터 053-795-9766, iyh@dgtp.or.kr</t>
@@ -12406,7 +12369,6 @@
           <t>68억원</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12726,7 +12688,6 @@
           <t>3백만원</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>N</t>
@@ -12879,7 +12840,6 @@
           <t>지원규모   100개사</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>100개</t>
@@ -13037,8 +12997,6 @@
           <t>&lt;3&gt;&lt;&gt;&lt;지원규모 및 지원내용&gt;</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>N</t>
@@ -13134,13 +13092,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr">
         <is>
           <t>한국생산기술연구원 055-367-9405</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr"/>
       <c r="AD82" t="inlineStr">
         <is>
           <t>055-367-9405</t>
@@ -13184,8 +13140,6 @@
           <t>부스 공동참가, 강원도와 상생으로 사업 규모화 및 홍보 극대화</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>N</t>
@@ -13281,7 +13235,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="inlineStr">
         <is>
           <t>ESG경영혁신실 86-20-2208-1603, cu@kotra.or.kr</t>
@@ -13292,7 +13245,6 @@
           <t>cu@kotra.or.kr</t>
         </is>
       </c>
-      <c r="AD83" t="inlineStr"/>
       <c r="AE83" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -13330,8 +13282,6 @@
           <t>&lt;3&gt;&lt;&gt;&lt;지원규모 및 지원내용&gt;</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>N</t>
@@ -13427,13 +13377,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr">
         <is>
           <t>한국생산기술연구원 055-367-9405</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr"/>
       <c r="AD84" t="inlineStr">
         <is>
           <t>055-367-9405</t>
@@ -13476,8 +13424,6 @@
           <t>ㅇ 최종 선정된 소상공인은 수행기관과 계약 체결(선정 후 2주)하고, 자부담금과 부가세를 전문기관으로 납부해야 하며, 기한(계약 후 2주) 내 미납부 시 선정 취소될 수 있습니다.</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>N</t>
@@ -13573,13 +13519,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA85" t="inlineStr"/>
       <c r="AB85" t="inlineStr">
         <is>
           <t>(사업문의) 전문기관 1551-4536 스마트지원실 온라인판로팀 042-363-7825, 7826 (소상공인 24 시스템 문의) 1644-5302 (중소기업확인서(소상공인) 발급 문의) 1357</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr"/>
       <c r="AD85" t="inlineStr">
         <is>
           <t>042-363-7825</t>
@@ -13626,7 +13570,6 @@
           <t>□ 모집규모 : 20개사 내외</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>20개</t>
@@ -13727,13 +13670,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr">
         <is>
           <t>DYETEC연구원 섬유패션AX센터 053-350-3908</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr"/>
       <c r="AD86" t="inlineStr">
         <is>
           <t>053-350-3908</t>
@@ -13781,7 +13722,6 @@
           <t>10억원</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>N</t>
@@ -13934,8 +13874,6 @@
           <t>지원내용 : 해외 특허, 상표, 디자인 출원에 소요되는 비용 중 일부를 지원하며, 전북지식재산센터 컨설턴트의 컨설팅 병행 제공</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>N</t>
@@ -14031,7 +13969,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr"/>
       <c r="AB88" t="inlineStr">
         <is>
           <t>전북지식재산센터 글로벌 IP스타기업 담당자 (대표) 063-252-9301, (직통) 070-7775-2623 / djdyc122@kipa.org</t>
@@ -14084,8 +14021,6 @@
           <t>□ 지원규모 및 비율</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14247,7 +14182,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14406,7 +14340,6 @@
           <t>90백만원</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>N</t>
@@ -14565,7 +14498,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14718,8 +14650,6 @@
           <t>□ 지원내용 : 보안관리체계 전반 진단 및 개선방안 컨설팅, 정보시스템 취약점</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14815,7 +14745,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA93" t="inlineStr"/>
       <c r="AB93" t="inlineStr">
         <is>
           <t>한국산업기술보호협회 02-3489-7022, security@kaits.or.kr</t>
@@ -14868,8 +14797,6 @@
           <t>※ 모집규모 초과 시 선착순 마감(신청서류 접수순)</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15028,7 +14955,6 @@
           <t>2천만원</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15124,13 +15050,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA95" t="inlineStr"/>
       <c r="AB95" t="inlineStr">
         <is>
           <t>나노종합기술원 나노바이오센서ㆍ칩 기술상용화지원센터 042-366-1650</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr"/>
       <c r="AD95" t="inlineStr">
         <is>
           <t>042-366-1650</t>
@@ -15278,13 +15202,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA96" t="inlineStr"/>
       <c r="AB96" t="inlineStr">
         <is>
           <t>나노종합기술원 042-366-1733</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr"/>
       <c r="AD96" t="inlineStr">
         <is>
           <t>042-366-1733</t>
@@ -15333,7 +15255,6 @@
           <t>1980000원</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15486,8 +15407,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15583,7 +15502,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr">
         <is>
           <t>경상북도경제진흥원 054-470-8577, 8572, gepa.commerce26@gmail.com / 운영사무국 02-1588-4550, gepa.commerce26@gmail.com</t>
@@ -15636,8 +15554,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>N</t>
@@ -15748,7 +15664,6 @@
           <t>jinho.choo@kotra.or.kr</t>
         </is>
       </c>
-      <c r="AD99" t="inlineStr"/>
       <c r="AE99" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -15795,7 +15710,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15948,8 +15862,6 @@
           <t>◦ 모집규모 : 국내 유망 스타트업 O개사 (발표시간 5분)</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>N</t>
@@ -16060,7 +15972,6 @@
           <t>startup_japan@kotra.or.kr</t>
         </is>
       </c>
-      <c r="AD101" t="inlineStr"/>
       <c r="AE101" t="inlineStr">
         <is>
           <t>창업벤처</t>
@@ -16105,7 +16016,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16201,7 +16111,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA102" t="inlineStr"/>
       <c r="AB102" t="inlineStr">
         <is>
           <t>인천광역시 미추홀구청 경제지원과 032-880-4385</t>
@@ -16387,6 +16296,7498 @@
       <c r="AF103" t="inlineStr">
         <is>
           <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125144</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026년 창업진흥원 대전 팁스타운 일본 파트너 초청 상담회 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>창업진흥원</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-08-07 ~ 2026-08-12</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>온라인 접수 (K-Startup)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>□ 지원규모 : 창업기업 총 20개사 내외</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>20개</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>중 일부를 별도로 발급받지 않아도 자동, 연동하여 제출 가능합니다. * 4. 접수방법-, 참고, 상담회 개요, 통해 해외 시장 진출 기반 마련, 일자 및 장소 : ’26.9.1.(화)~9.2.(수), 창업진흥원 대전 팁스타운 1층, &lt; 세부 일정(안) &gt;</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>창업진흥원 대전팁스팀 042-720-4561, 4562, 4563</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>042-720-4561</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125243</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>[경기] 시흥시 2026년 스타트업 투자유치 지원 참여기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>시흥산업진흥원</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-08-07 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>온라인 접수
+- 시흥산업홈페이지, 시흥창업센터(startup.sida.kr) 홈페이지 中 택 1
+※ 자세한 신청방법 공고문 참조
+※ 1, 2의 홈페이지(온라인) 제출시, 전산 오류에 따른 기업 피해 최소화를 위해 서류 제출(업로드) 후 문의처(031-497-6246)를 통한 정상 등록 여부 확인 요망</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>❍ 지원한도 : 기업당 소요비용(공급가액 기준, VAT 제외)의 80%, 최대 500만원 한도</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>시흥산업진흥원 시흥창업센터 사업담당자 031-497-6246, hw.kim@sida.kr</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>hw.kim@sida.kr</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>031-497-6246</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125242</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026년 K-브랜드 챌린지 참여기업 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>중소벤처기업진흥공단</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-07-27 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>온라인 접수 (고비즈코리아)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>(총 9개사) ➂ [온라인마케팅] 기업당 500만원 상당의 마케팅 패키지 지원</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>9개</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t> 서류 보완을 요구하지 않으며, 공고 기간 내 미제출 시 평가대상에서 제외, ] 제품 및 마케팅 전략서 등, 연번 구분, 제출 방식, · 참여기업 신청서 온라인 작성, · 제품 및 마케팅 전략서 (예선 평가 자료), PDF 파일로 변환하여 제출</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>(사업 전반 문의) 중소벤처기업진흥공단 온라인수출처 055-751-9777, 9768, young1211@kosmes.or.kr / (신청 시스템 문의) 고비즈코리아 고객지원센터 1588-6234, gobiz@kosmeskorea.or.kr</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>gobiz@kosmeskorea.or.kr</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>055-751-9777</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125241</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026년 농식품 중소기업 기술보호 컨설팅 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>농림식품기술기획평가원</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>온라인 접수(상생누리플랫폼)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>❍ 접수결과 지원규모 초과시 ①농식품 R&amp;D 수행기업(평가원 소관 R&amp;D)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>참여 신청서(별첨1), 기업(개인) 정보활용 동의서(별첨2), Ⅱ. 선정방법, 인증기술 및, 《 컨설팅 지원사업 추진 세부절차 》, 구분 수행내용, 신청, 업체선정 ✔ 지원규모(7개사</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>농림식품기술기획평가원 기획조정실 061-338-9718, ksh5360@ipet.re.kr</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>ksh5360@ipet.re.kr</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>061-338-9718</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125240</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 자동차 부품기업 국내외 마케팅 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>충북과학기술혁신원</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-08-07 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>온라인 접수 (충북과학기술혁신원 과제관리시스템 비즈온)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>충북과학기술혁신원 AI융합혁신본부 디지털산업부 산업육성팀 043-210-0848, dyra@cbist.or.kr</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>dyra@cbist.or.kr</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>043-210-0848</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125239</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>최초 수출기업의 해외인증 취득 사전 검증 지원 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>한국기계전기전자시험연구원</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>이메일접수 (precert2026@ktc.re.kr)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>◦ 지원 금액: 기업당 최대 500만원 (기술지도, 검증 및 시험비)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>한국기계전기전자시험연구원 글로벌사업본부 031-428-8449, precert2026@ktc.re.kr</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>precert2026@ktc.re.kr</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>031-428-8449</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125238</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026년 2차 해외산림자원개발 이차보전 사업 공고</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>산림조합중앙회</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>우편 또는 방문 접수
+- 접수처 : (우편번호 07570) 서울특별시 강서구 공항대로 475 한국임업진흥원 산림산업지원본부 국제산림협력실</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>신규 대출규모: 3664백만원</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>3664백만원</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>신청서(별도서식), 해외산림자원개발 사업계획 신고수리서(사본), 사업계획서, 관련계약서․투자대상국 투자승인서 또는 인가서 등(사본), 법인 인감증명서, 기업신용평가서, 사실관계조사확인서* 등, 서명 또는 날인) 등 첨부</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>한국임업진흥원 산업지원본부 해외산림협력실 02-6393-2703 / (대출 및 담보관련 문의) 산림조합중앙회 상호금융여신부 02-3434-7236</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr"/>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>02-3434-7236</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125237</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 해양 콘텐츠 제작 지원사업 모집 공고(경북콘텐츠기업지원센터)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>경북문화재단 콘텐츠진흥원</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>온라인 접수 (e나라도움)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>완료 후 잔고가 ‘0원’인 상태에서 운용)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>는 본 공고문 2-5~6, 등 참고, 나. 발표평가, 평가기준 : 평가항목의 각 항목별 점수를 합산, 평균하여 100점 만점 기준, 점 이상 기업 중 고득점 순으로 선정, 평가내용 : 사업수행신청서 및 계획서 등, 전반</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>경북콘텐츠기업지원센터 담당자 054-256-3809, 3802</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr"/>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>054-256-3809</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125236</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026년 농식품 중소기업 ESG 경영 도입 및 국제표준 인증 취득 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>농림식품기술기획평가원</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>온라인 접수(상생누리플랫폼)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>❍ 접수결과 지원규모 초과시 ①농식품 R&amp;D 수행기업(평가원 소관 R&amp;D)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>참여 신청서(별첨1), 기업(개인) 정보활용 동의서(별첨2), Ⅱ. 선정방법, 인증기술 및, 《 컨설팅 지원사업 추진 세부절차 》, 구분 수행내용, 신청, 업체선정 ✔ 지원규모(12개사)를 고</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>농림식품기술기획평가원 기획조정실 061-338-9718, ksh5360@ipet.re.kr</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>ksh5360@ipet.re.kr</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>061-338-9718</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125235</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026년 하반기 지식재산처 우수특허기반 혁신제품 추가등록 공고</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>한국발명진흥회</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>온라인 접수 (한국발명진흥회)
+※ 물품식별번호 등록 완료 후 신청 서류 구비하여 평가기관(한국발명진흥회) 홈페이지를 통해 접수
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>◦(예상가격) 예: 000만원/시스템 또는 대당</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>0만원</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>작성 서류, 연번 서류 항목 서식 파일형태 비고, 혁신제품 신청서(추가등록) 붙임1 PDF 필수, 혁신제품 설명서(추가등록) 붙임2 한글 필수, 혁신제품 규격목록(추가등록) 붙임4 PDF, Excel 필수, 추가등록 제품규격서 붙임5-1, 한글 필수</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>한국발명진흥회 02-3459-2929, fast@kipa.org / 접수시스템 관련 문의 070-7703-6365</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>fast@kipa.org</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>02-3459-2929</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125234</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>[경북] 메가 이벤트 연계 제작 지원사업 모집 공고(경북콘텐츠기업지원센터)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>경북문화재단 콘텐츠진흥원</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>온라인 접수 (e나라도움)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>지원규모: 과제당 45000000원 × 3개 과제 (총 135000천원)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>45000000원</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>는 본 공고문 2-5~6(자격), 등 참고, 나. 발표평가, 평가기준 : 평가항목의 각 항목별 점수를 합산, 평균하여 100점 만점 기준, 점 이상 기업 중 고득점 순으로 선정, 평가내용 : 사업수행신청서 및 계획서 등, 전반</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>경북콘텐츠기업지원센터 담당자 054-256-3804, 3802</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr"/>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>054-256-3804</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125233</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026년 하반기 지식재산처 우수특허기반 혁신제품 신규지정 공고</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>한국발명진흥회</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>온라인 접수 (한국발명진흥회)
+※ 물품식별번호 등록 완료 후 신청 서류 구비하여 평가기관(한국발명진흥회) 홈페이지를 통해 접수
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>◦(예상가격) 예: 000만원/시스템 또는 대당</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>0만원</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>증빙 서류, 연번 서류 항목 세부내용 비고, 선정 공문 등), 신청, 분야, 증빙, (분야2: 우수발명품), 우수발명품</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>한국발명진흥회 02-3459-2929, fast@kipa.org / 접수시스템 관련 문의 070-7703-6365</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>fast@kipa.org</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>02-3459-2929</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125232</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 하반기 중소기업 밀집지역 위기대응 체계 구축사업 Stand-up 맞춤지원 모집 공고</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>충북테크노파크</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>온라인 접수 (기업지원종합정보망 컨택센터) 
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>◦ (2026년 하반기 지원규모) 50백만원(5개사 내외)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>50백만원</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>포워딩 인보이스, 비용지급 관련, 물류비 지원 송금영수증(지원기업→물류업체), 비용지급 관련 최대 5백만원, 세금계산서(물류업체→지원기업), 국내운임, 취급수수료, 도착국 발생비용</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>충북 지역중소기업 위기지원센터(충북테크노파크) 043-270-2234, 2236 / dhkim@cbtp.or.kr, yhlee@cbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>dhkim@cbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>043-270-2234</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125231</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>[경남] 2026년 2차 R&amp;D기획 지원 신청기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>경남테크노파크</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경남테크노파크 홈페이지)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>◦ (지원규모) 2개사 내외 / 기업당 4백만원 이내 지원(기업부담금 10% 이상)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>4백만원</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>신청 자격 등에 대한 평가 시행, ◦ (평가항목), &lt;평가 항목&gt;, 사업신청서 평가항목 평가지표, 신청기업 현황, (10점), 타당성 기술개발 추진의 타당성, 기술개발</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>경남테크노파크 기업지원단 055-259-3614, kkkhm@gntp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>kkkhm@gntp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>055-259-3614</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125230</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026년 이차전지 소재부품 기업대상 시제품 제작 지원프로그램 참여기업 추가 상시모집 공고</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>구미전자정보기술원</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>상시 접수</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>이메일 접수 (tnd02204@geri.re.kr)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ㅇ 지원 규모 : 5개사</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>구미전자정보기술원 054-479-2237, tnd02204@geri.re.kr</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>tnd02204@geri.re.kr</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>054-479-2237</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125229</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026년 6차 해외지식재산센터 법률서비스 지원사업 정기 공고</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>한국지식재산보호원</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>세부사업별 상이</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>온라인 및 유선 접수
+- 정기모집 : 온라인 접수(해외지식재산센터 법률서비스지원시스템)
+- 수시접수 : 해외지식재산협력실(1600-9099), 해외지식재산센터(붙임2참조)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>지원 내용</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>등록 후 [다음] 버튼 클릭 시, 지정한 수행대리인에게 자동으로, ㅇ 정기모집, 수행동의 요청 메일이 발송됨, 마감 기한 내, ③ 지원유형선택, ㅇ 수시모집(분쟁ㆍ침해 초기대응유형만 신청가능), ① 지원기업의 [지원사업유형</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>한국지식재산보호원 1600-9099, ipcenter_help@koipa.re.kr 및 해외지식재산센터 10개소 문의처는 공고문 ‘붙임2’ 참조</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>ipcenter_help@koipa.re.kr</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>00 070-5150</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125228</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026년 예술기업 상생혁신(오픈이노베이션) 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>예술경영지원센터</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>온라인 접수 (e나라도움)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>ㅇ (지원규모) 총 5개사, 선정기업별 40백만원</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>40백만원</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>※ e나라도움을 통한 온라인 제출 외 e메일, 우편, 방문 접수·제출 불가, ※ 모든, 는 e나라도움 시스템 내 첨부 필수, (필수, 총 4종, 파일형식</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>예술경영지원센터 070-4135-5511, 26kams.startup@gmail.com / e나라도움사용자 지원센터 1670-9595</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>26kams.startup@gmail.com</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>070-4135-5511</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125227</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>[전남광주ㆍ충남] 2026년 인공지능 맞춤형 뷰티기기 고도화 글로벌화 지원사업 기업지원 통합 모집 공고(바이오산업 개방형 생태계 조성 촉진 사업)</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>광주테크노파크</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-19</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>이메일 접수
+※ 지원프로그램 별 이메일 상이, 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>(지원규모) 총 200280천원</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>일체를 스캔·PDF로 변환하여 각 지원기, 관 담당자 메일주소로 제출, 각 지원기관이 제시하는 서류 일체, 평가방법 및 기준, (평가주체) 본 공고는 통합모집공고로, 선정평가는 프로그램별 지원, 기관이 각각 자체 시행함, (평가절차)</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>광주테크노파크 062-602-7277 외 기관별 문의처 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>csh@gjtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>062-602-7277</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125226</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>[울산] 2026년 5차 사회연대경제 청년 일경험 시범사업 참여기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>울산경제일자리진흥원</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>모집 완료시</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>이메일 접수 (swork@ubpi.or.kr)
+※ 제출서류를 1개의 파일로 만들어 제출</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>※ 보조금 산정 기준 : 월234만원 X 5개월 X 11.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>234만원</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>를 1개의 파일로 만들어 제출, (담당자 연락처 ☎052-283-7190), 신청 시 신청서에 아래 해당 유형 선택, 유형 내용, 팀단위(2~4명) 배정, 일자리창조형, 지역 수요와 공동체 가치에 맞게 새로운 일자리로 확장, 재설계 하는 것</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>울산경제일자리진흥원 일자리지원부 사업 담당자 052-283-7190, swork@ubpi.or.kr</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>swork@ubpi.or.kr</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>052-283-7190</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125225</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>[충남] 2026년 3차 소기업형 스마트공장 구축 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>충남테크노파크</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>온라인 접수(스마트공장 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>지원내용</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>다운로드, 및 작성 → 온라인 신청(, 업로드, 도입기업 아이디로 신청), 구분 온라인 등록 서류, 사업계획서, 고용보험사업장 취득자 명부 증명원(‘24년, ’25년)</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>충남테크노파크 041-336-9031, bgh82@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>bgh82@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>041-336-9031</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125224</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>[서울] 강남구 2026년 LA K-프리미엄 소비재전 참가기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-10</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>온라인 접수 (구글폼)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>일괄 업로드, 신청방법, 참가 신청서 (서식 1), 제품설명서 (서식 2), 참가 서약서 (서식 3), (보유시) ○ 기술 특허증(상표, 디자인 등 불인정) 및 해외규격인증서(MoCRA, CE 등)</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>강남구청 지역경제과 02-3423-5502 / 한국무역협회 마케팅전략실 02-6000-5228</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr"/>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>02-3423-5502</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125223</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 2차 특화형 공공조달 연계 군수품 상용화 지원사업(교육 및 컨설팅 분야) 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>경북테크노파크</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경북테크노파크 홈페이지)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>○ 지원내용 : ①군수물자 납품 모의평가, ②교육, ③컨설팅, ④기술교류회</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>번호 서 류 명 비 고, 문의처, 구분 연락처, 경북테크노파크 박정수 선임연구원, 신청방법 문의, 한국조달연구원 황선오 선임연구원, 내선 603), 작성문의</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>(신청방법 문의) 경북테크노파크 항공방위산업육성실 053-819-3094, jungsu@gbtp.or.kr / (신청서류 작성문의) 한국조달연구원 국방조달연구부 02-796-8234(내선 603, 605), yellowsun0@kip.re.kr, hjk01@kip.re.kr</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>hjk01@kip.re.kr</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>02-796-8234</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125222</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026년 K-브랜드 해외 상표권 보호ㆍ라이선싱 전략 지원(시범)사업 공고</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>한국지식재산보호원</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>온라인 접수(국제 지재권분쟁 대응전략 지원사업 지원기업 서비스)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>□ 지원규모: 기업별 최대 3천만원(총사업비) 이내</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>3천만원</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>제출(온라인 신청만 가능하며, 방문·우편 접수 불가), 온라인 사업신청 사용자 매뉴얼 [붙임7] 참조, 다수, 제출 및 작성서류 목록, ㅇ 신청기업, 【신청기업 제출 및 작성서류 목록】, 일반 신청 간소화 신청</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>한국지식재산보호원 상표디자인분쟁대응실 (사업내용 문의) 02-2183-5894, 02-6196-2016 (이메일 문의) kbrand@koipa.re.kr 및 기타 문의처 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>kbrand@koipa.re.kr</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>02-2183-5894</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125221</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026년 산림분야 지식재산권 우수기술 사업화 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>한국임업진흥원</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-23</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jjangu@kofpi.or.kr)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>ㆍ시제품, 실증, 인허가, 판로개척등소요비용* 1000만원</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1000만원</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>대상별, 상세, 제출대상, 제출시기 제출방식, ◦ 수행 계획서 [서식 1, ◦ 개인정보 수집 및 활용 동의서 서식 2, 접수 마감일, 신청자 ◦ 임산업체 증빙서류 전자우편</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>(수행기관) 아이피온 070-5038-3372, 042-719-1415</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>jjangu@kofpi.or.kr</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>042-719-1415</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125220</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026년 산림분야 지식재산권 출원 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>한국임업진흥원</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-23</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jjangu@kofpi.or.kr)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>ㆍ보유기술의권리화를위해 국내특허·실용신안 100만원 이내/건</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>대상별, 상세, 제출대상, 제출시기 제출방식, ◦ 신청기술 설명서 [서식 2], 접수 마감일, ∼23:00까지, ◦ 출원 명세서(기 출원한 기술에 한함)</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>(수행기관) 아이피온 070-5038-3372, 042-719-1415</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>jjangu@kofpi.or.kr</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>042-719-1415</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125219</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026년 2차 바이오헬스산업 기술평가-사업화 연계 지원사업 참여기관(업) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>한국보건산업진흥원</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>이메일 접수 (hanui4@khidi.or.kr)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>□ 지원규모 : 15건 내외 기술</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>15건</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>구분, (일체 서류 pdf 변환하여 별도의 파일로 제출), 필수, ∎ [별첨3] 개인정보 수집 및 이용에 관한 동의서, 국세완납증명서(기업만 해당), ∎ 출원번호통지서 및 명세서(미공개특허인 경우), 선택, ∎ 기타 참고자료</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>한국보건산업진흥원 보건산업육성단 기술평가컨설팅팀 043-713-8595, hanui4@khidi.or.kr</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>hanui4@khidi.or.kr</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>043-713-8595</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125218</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026년 민관 공동 전략형 상생협력사업 (창의트랙사업) 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>대중소기업농어업협력재단</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-07-30 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>온라인 접수 (국고보조금통합관리시스템)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>&lt;총괄기관 (중기부)&gt;&lt;‣ 사업 기본계획 수립, 국고보조금 교부, 사업 및 전담기관 관리 등&gt;</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>대ㆍ중소기업ㆍ농어업협력재단 상생협력지원부 02-368-8971, 8746 / winwinct@win-win.or.kr</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>winwinct@win-win.or.kr</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>02-368-8971</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125217</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>[인천] 2027년 방산 중소기업 생산성향상 지원사업 수혜기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>인천테크노파크</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>온라인 접수(비즈오케이)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>❍ 2027년도 예정 사업비 : 390백만원</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>390백만원</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>인천테크노파크 기업지원본부 제조혁신센터 032-260-0622, 0625 / yeobi@itp.or.kr, yhchoi@itp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>yeobi@itp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>032-260-0622</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125216</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026년 순환경제 상생라운지 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>한국생산기술연구원</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-07-29 ~ 2026-08-12</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jaeho1130@kncpc.re.kr)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ㅇ (모집규모) 분야별 다수 기업을 모집하며, 신청내용의 적합성·수요</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>다음 서류를 구비하여 신청기간 내 제출, － (필수) 참가신청서 1부[붙임1], 수요기업 선정 및 비즈니스 매칭 절차, 구분 주요내용 일정, 참여기업 모집 공고 및 신청 접수 7월 말~8월 2주, 발표기업 선정 신청서·소개자료 서면검토, 필요 시 추가자료 요청 8월 2주, 홍보자료 선정된 발표기업 중 홍보자료(홍보용 쇼츠</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>한국생산기술연구원 02-2183-1538, 1521 / jaeho1130@kncpc.re.kr, lgyng@kncpc.re.kr</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>jaeho1130@kncpc.re.kr</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>02-2183-1538</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125215</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>[인천] 2026년 스마트공장 DX견학공장 기업 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>인천테크노파크</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-08-07 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>이메일 접수(yhchoi@itp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>□ 지원내용</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>인천테크노파크 제조혁신센터 032-260-0625, yhchoi@itp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>yhchoi@itp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>032-260-0625</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125214</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>국내 게임산업 해외 진출 아세안 최대규모 2026 Gamescom Asia x Thailand Game Show 전시 공동관 및  현지 네트워킹 행사 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>한국인공지능소프트웨어산업협회</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-08-07 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>온라인 접수 (구글폼) 
+※ 제반서류 등록 시 반드시 PDF로 변환하여 업로드 필수</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>지원내용</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>가 미비한 경우, 대중소 동반진출사업 유형별(산업재, 소비재) 연간 2회 초과 참여한 경우, 산업재(현지화)의 경우, 회만 참여 가능(타 과제 참여여부 확인 필수), 참여기업 제한 요건, 화의, 법정관리 등 정상적으로</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>한국인공지능ㆍ소프트웨어산업협회 글로벌협력팀 02-2188-2449, 6918 / mj0403@sw.or.kr, syn@sw.or.kr</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>mj0403@sw.or.kr</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>02-2188-2449</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125213</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026년 2차 마케팅 역량강화 매칭 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>한국중소벤처기업유통원</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>온라인 접수 (판판대로)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>□ 모집규모 : 18개사 내외</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>18개</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>②중소기업확인서, ⑤참여신청서, ⑥가점서류(해당시), 구분, 발급처 비고, 중소기업확인서 중소기업현황정보시스템 판판대로 시스템 내, 참여신청서 서식에 맞춰 직접 작성 첨부양식 참조, 가점서류 가점 증빙서류 해당시 제출</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>한국중소벤처기업유통원 마케팅기획팀 02-6678-9345, 9346</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr"/>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>02-6678-9345</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125212</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026년 3차 기술개발제품 시범구매 지원계획 공고</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>한국중소벤처기업유통원</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>온라인 접수 (공공구매종합정보망(SMPP))</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>* 공공기관 계약실적 5억원 이하 기업</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>5억원</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>검토방법 중 ‘공공기관 계약실적’ 확인, 적 아래 요건 중 어느 하나에 해당하는 기업, 교통 통합교통체계법 제102조 국토교통부 ㅇ ㅇ ㅇ, 용 기업 구분, ① 설립 7년 이하 창업기업, ② 공공기관 계약실적 5억원 이하 첫걸음 기업, ❶구매조건부 신제품개발 구매연계형(공공부문), 수요처가 지정된 제품 구분</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>한국중소벤처기업유통원 제도운영팀 02-6678-9173</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr"/>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>02-6678-9173</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125211</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026년 현장실습 훈련(시니어 인턴십) 지원사업 참여 기업 모집 공고(차오름)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>한국노인인력개발원</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>유선, 이메일, 온라인 접수
+- 유선 : 0502-6683-3111
+- 이메일 : fdcrewhh@naver.com
+- 온라인：네이버폼</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>* 123개월 : 각 40만원씩 최대 120만원</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>120만원</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>123개</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr"/>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>(주)차오름 일자리지원팀 0502-6683-3111</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr"/>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>02-6683-3111</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125210</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026년 1차 하반기 나라장터 상생세일 참여업체 모집 공고</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>직접수행</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-09-02</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>온라인 접수 (나라장터 종합쇼핑몰)
+※ 조달업체 로그인 &gt; 마이페이지 &gt; 사후/상품관리 &gt; 할인행사/기획전 &gt; 할인상품 기획전(상생세일) 신청 목록</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr"/>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>(MAS 문의) 042-724-7546 (우수제품 문의) 042-724-7241 / 조달청 구매총괄과 070-4056-7546</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr"/>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>042-724-7241</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125209</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026년 산업융합 혁신품목 및 산업융합 선도기업 선정 계획 공고</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>국가산업융합센터</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-09-02</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>온라인, 우편 접수
+- 온라인 : 국가산업융합센터
+- 우편 : (우)15588 경기도 안산시 상록구 항가울로 143(사동 1271-18번지)한국생산기술연구원 융복합동(D동) 국가산업융합센터 210호
+※ 전산접수 후 관련자료 우편 제출
+※ 우편물 표지에 전산 접수번호 및 기업명 필히 기재</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>당해연도 직전 분기까지 1년간 매출액이 10억 원 이상이고, 재무건전성과 사업</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>10억원</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>제출이 모두 완료되어야 정상 접수로 인정, &lt; (신규) 산업융합 혁신품목, ① 산업융합 혁신품목 신청서 원본 1부, ② 산업융합 혁신품목 신청양식 원본 1부, ④ 신청 제품의 검사, 검증 절차를 거쳤음을 증명하는 자료 (보유時, (예) 시험성적서 등), ⑤ 기타 평가 관련 증빙자료(지식재산권 출원 등록증</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>국가산업융합센터 산업융합정책실 산업융합 혁신품목ㆍ선도기업 담당자 031-8040-6789, 6797 / amber11@kitech.re.kr</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>amber11@kitech.re.kr</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>031-8040-6789</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125208</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026년 소재ㆍ부품ㆍ장비 기업 해외 공급망 ESG 요구대응 맞춤형 컨설팅 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-07-23 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>온라인 접수(무역투자24)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>[중소기업] 최근 3년간 50억원 이상 10억원 미만</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>50억원</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>신청 시 제출 필수자료 첨부, 제출된 자료를 바탕으로, 참가기업 선정 예정, &lt;제출 필수자료&gt;, ① 참가기업 신청서 *제공된 양식(첨부2) 활용, ③ 중소·중견기업 확인서, ④ 회사소개서, 제품소개서</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>KOTRA 소재부품장비팀 02-3460-7641, mwjie@kotra.or.kr KOTRA ESG경영혁신실 02-3460-3492, choiye@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>choiye@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>02-3460-3492</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125207</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>[경기] 성남시 2026년 유관기관 협력 지원(오아시스마켓) 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>성남산업진흥원</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>온라인 접수 (성남산업진흥원)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>○ 지원규모 : 10개사 내외</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>사업신청서 및 필수, ※ 필수, 는 사업신청서 참조, 참가문의, 성 남 산 업 진 흥 원</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>성남산업진흥원 혁신성장부 031-782-3056</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr"/>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>031-782-3056</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125206</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>[경기] 성남시 찾아가는 스마트 경영 컨설팅 참가기업 모집 공고(성남 섬유제조 소공인특화지원센터)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>성남산업진흥원</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-10-30</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>온라인 접수 (소상공인24)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>□ 지원규모 : 30개사 내외(기업당 최대 4회 / 회당 4시간)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>30개</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>성남산업진흥원 (성남 섬유제조 소공인특화지원센터) 031-750-2917</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr"/>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>031-750-2917</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125205</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026년 하반기 고양 IR데이 참가기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-30</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>온라인 접수 (구글폼)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>(회차별 IR우수기업 7개사 중 창업보육센터 선정기업 3개사 총 600만원 지원)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>600만원</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>7개</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>제출, 창업기업 창업예정자, 참가 신청서&lt;붙임1&gt; ○ ○, 개인정보 동의서&lt;붙임2&gt; ○ ○, 서약서&lt;붙임3&gt; ○ ○, 확약서&lt;붙임4&gt; ○ ○, 기업 소개자료(IR 발표자료) ○ ○, (최근 3개년</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>탭엔젤파트너스 IR데이 운영사무국 02-6246-6858, info@tapaps.com / 고양시청 기업지원과 031-8075-3573</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>info@tapaps.com</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>02-6246-6858</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125204</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>[경기] 안양시 2026년 안양춤축제 연계 안양 중소기업 홍보관 참가 기업모집 공고</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>안양산업진흥원</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>온라인 및 이메일 접수
+- 온라인 : 네이버 폼
+- 이메일 : treasure@aba.or.kr
+※ 온라인 접수 후 담당자 이메일로 서류 발송
+※ 자세한 지원내용 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>참가부문 내 용 지원내용 모집업체수</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>참가신청서 1부, 전시․판매 제품 설명서 1부, 개인 기업 정보 이용 및 제공 동의서 1부, 아. 접수기한 : 2026.08.31(월), :00까지, 주의 사항 및 기타 안내 사항, 해야합니다., 중소기업</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>안양산업진흥원 사업담당자 treasure@aba.or.kr</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>treasure@aba.or.kr</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr"/>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125203</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>[경남] 거제시 2026년 3차 노동자 휴게시설 지원사업 재공고</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>온라인 및 방문 또는 우편 접수
+- 접수처 : 거제시청 조선지원과 노동자지원팀
+- 온라인 : 보탬e</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>A사업체가 총사업비 8백만 원으로 휴게시설을 조성하려는 경우</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>8백만원</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>구분, 부수, 비고(서식), 지원신청서, 붙임1, 사업계획서, 붙임2, 단체소개서</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>거제시청 조선지원과 노동자지원팀 055-639-4454</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr"/>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>055-639-4454</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125202</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026년 창업혁신공간(동부권) 하남시 스타트업 발굴 및 육성 지원사업 이루다+ 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>경기도경제과학진흥원</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-07-23 ~ 2026-08-17</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경기스타트업플랫폼 및 구글폼)
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>- 우수기업 전문운영사 직접투자 연계(1개사 내외 / 총 1억원 이상)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1억원</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>오리엔테이션 및, 신청서 접수 발표평가 결과통보, 검토· 심사 프로그램 진행, 일정은 사업 진행 상황에 따라 변동될 수 있음, (신청제한), ‣ 접수기간 내에 신청서 및, 를 제출하지 아니하였거나, 가 허위인 경우</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>킹고스프링 031-5171-5851, kwoncw@kingospring.com / 경기도경제과학진흥원 동부창업허브팀 031-830-8547, gb4285@gbsa.or.kr</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>gb4285@gbsa.or.kr</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>031-5171-5851</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125201</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026년 수출시장 확장하기 온라인 통합 사절단(CIS) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>온라인 접수 (무역투자24)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>◦ 지원내용</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>첨부, 신청서, 외국어 카탈로그, ◦ 선정기준 : ① 신청서 및 외국어 카탈로그 충실도, ◦ 우대조건 : ① 내수기업 및 수출초보기업, ②수도권 외 지방 소재기업, 내수기업 : ‘25년도 관세청 수출실적 1, 달러 미만</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>KOTRA 중소혁신기업팀 02-3460-7328, 7545 / export@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>export@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>02-3460-7328</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125200</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026년 지역SW산업발전 유공자 및 공모전 공고</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>정보통신산업진흥원</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-09-30</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>이메일 접수 (swtest@rsw.or.kr)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>- (최우수) 과학기술정보통신부 부총리상(4) 각 100만원</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>를 총 1개의 파일로 취합하여 제출함을 원칙으로 함, 총 2개의 파일이 제출되어야 함, 제출 파일명은‘, 명 신청서_소속_성명’으로 작성함, 예시) 지역SW산업발전 유공자 신청서_소속_성명, 지역SW산업발전 우수사례 공모전 신청서_소속_성명, 지역SW산업발전 유공자 및 우수사례, 지역SW산업발전 유공자 지역SW산업발전 우수사례 공모전</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>지역SW산업발전협의회 정책사업팀 02-2132-2133~6, swtest@rsw.or.kr</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>swtest@rsw.or.kr</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>02-2132-2133</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125199</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 3차 BIT융합캠퍼스(의료ㆍ헬스ㆍ바이오) 지원사업 기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>경북대학교 첨단정보통신융합산업기술원</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>세부사업별 상이</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>온라인 접수 및 이메일 접수
+- 온라인 : 지산학연협력기술연구소 홈페이지
+※ 지원분야별 신청방법 상이하므로 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>▢ 지원한도 : 과제당 최대 75백만원</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>75백만원</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>적합성, 신청자격, 의 누락 및 부실* 여부, 신청자격 적합성 지원 및 제외 대상 해당 여부, 누락, 계획서는 정성적 판단을 통해 탈락 처리), (2차 발표평가) 과제수행 타당성, 수행계획 우수성을 종합적으로 평가하여</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>경북대학교 첨단정보통신융합산업기술원 053-219-0348, mskim1011@knu.ac.kr</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>mskim1011@knu.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>053-219-0348</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125198</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026년 민관협력 K-뷰티 중소벤처기업 일본 데뷔 프로그램 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>중소벤처기업진흥공단</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>이메일 접수 (kosmetokyo@kosmes.or.kr, kdh21@kosmes.or.kr)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>□ 모집규모 및 대상</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>구 분 필요 서류, ① 참가신청서(붙임1, 전자파일 원본과 날인 스캔본), ② 신용정보/기업정보 제공 및 활용동의서(붙임3~4, 날인 스캔본), ③ 청렴수행 이행서약서(붙임5, 대표이사 모두, 공고일 이후 발급분)</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>도쿄 글로벌비지니스센터 +81-3-6273-3694 / kosmetokyo@kosmes.or.kr, kdh21@kosmes.or.kr</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>kdh21@kosmes.or.kr</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr"/>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125197</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 기후테크 특화 오픈이노베이션 참여기업 추가모집 연장 재공고(기후테크 창업기업 성장지원사업)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>전북테크노파크</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>이메일 접수(hsyoo@jbtp.or.kr)
+※ 제출 후 접수 확인 필수(063-219-2128)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>㈜엔알비 미선정 과제당 최대 3천만원</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>3천만원</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>번호, (필수) 비고, 신청서 [양식] 필수, 과제 계획서(제안서) [붙임 1] 필수, 는 PDF 파일로 일괄 제출, 기타, 유의사항, 제출된 서류는 반환하지 않음</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>전북테크노파크 기업지원단 지역균형사업팀 063-219-2128, hsyoo@jbtp.or.kr (과제 문의) 엔알비 기업부설연구소 070-8801-2019</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>hsyoo@jbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>063-219-2128</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125196</t>
         </is>
       </c>
     </row>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -16325,7 +16325,6 @@
           <t>□ 지원규모 : 창업기업 총 20개사 내외</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>20개</t>
@@ -16436,7 +16435,6 @@
           <t>창업진흥원 대전팁스팀 042-720-4561, 4562, 4563</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr"/>
       <c r="AD104" t="inlineStr">
         <is>
           <t>042-720-4561</t>
@@ -16487,7 +16485,6 @@
           <t>500만원</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>N</t>
@@ -16583,7 +16580,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA105" t="inlineStr"/>
       <c r="AB105" t="inlineStr">
         <is>
           <t>시흥산업진흥원 시흥창업센터 사업담당자 031-497-6246, hw.kim@sida.kr</t>
@@ -16798,8 +16794,6 @@
           <t>❍ 접수결과 지원규모 초과시 ①농식품 R&amp;D 수행기업(평가원 소관 R&amp;D)</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>N</t>
@@ -16952,8 +16946,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>N</t>
@@ -17049,7 +17041,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA108" t="inlineStr"/>
       <c r="AB108" t="inlineStr">
         <is>
           <t>충북과학기술혁신원 AI융합혁신본부 디지털산업부 산업육성팀 043-210-0848, dyra@cbist.or.kr</t>
@@ -17107,7 +17098,6 @@
           <t>500만원</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>N</t>
@@ -17203,7 +17193,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA109" t="inlineStr"/>
       <c r="AB109" t="inlineStr">
         <is>
           <t>한국기계전기전자시험연구원 글로벌사업본부 031-428-8449, precert2026@ktc.re.kr</t>
@@ -17262,7 +17251,6 @@
           <t>3664백만원</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>N</t>
@@ -17368,7 +17356,6 @@
           <t>한국임업진흥원 산업지원본부 해외산림협력실 02-6393-2703 / (대출 및 담보관련 문의) 산림조합중앙회 상호금융여신부 02-3434-7236</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr"/>
       <c r="AD110" t="inlineStr">
         <is>
           <t>02-3434-7236</t>
@@ -17416,7 +17403,6 @@
           <t>0원</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17522,7 +17508,6 @@
           <t>경북콘텐츠기업지원센터 담당자 054-256-3809, 3802</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr"/>
       <c r="AD111" t="inlineStr">
         <is>
           <t>054-256-3809</t>
@@ -17565,8 +17550,6 @@
           <t>❍ 접수결과 지원규모 초과시 ①농식품 R&amp;D 수행기업(평가원 소관 R&amp;D)</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>N</t>
@@ -17726,7 +17709,6 @@
           <t>0만원</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17994,7 +17976,6 @@
           <t>경북콘텐츠기업지원센터 담당자 054-256-3804, 3802</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr"/>
       <c r="AD114" t="inlineStr">
         <is>
           <t>054-256-3804</t>
@@ -18044,7 +18025,6 @@
           <t>0만원</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18522,7 +18502,6 @@
           <t>ㅇ 지원 규모 : 5개사</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>5개</t>
@@ -18623,7 +18602,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA118" t="inlineStr"/>
       <c r="AB118" t="inlineStr">
         <is>
           <t>구미전자정보기술원 054-479-2237, tnd02204@geri.re.kr</t>
@@ -18678,8 +18656,6 @@
           <t>지원 내용</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18995,8 +18971,6 @@
           <t>(지원규모) 총 200280천원</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>N</t>
@@ -19312,8 +19286,6 @@
           <t>지원내용</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19466,8 +19438,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19573,7 +19543,6 @@
           <t>강남구청 지역경제과 02-3423-5502 / 한국무역협회 마케팅전략실 02-6000-5228</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr"/>
       <c r="AD124" t="inlineStr">
         <is>
           <t>02-3423-5502</t>
@@ -19616,8 +19585,6 @@
           <t>○ 지원내용 : ①군수물자 납품 모의평가, ②교육, ③컨설팅, ④기술교류회</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19775,7 +19742,6 @@
           <t>3천만원</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19933,7 +19899,6 @@
           <t>1000만원</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20091,7 +20056,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20244,7 +20208,6 @@
           <t>□ 지원규모 : 15건 내외 기술</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
           <t>15건</t>
@@ -20402,8 +20365,6 @@
           <t>&lt;총괄기관 (중기부)&gt;&lt;‣ 사업 기본계획 수립, 국고보조금 교부, 사업 및 전담기관 관리 등&gt;</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>N</t>
@@ -20499,7 +20460,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA130" t="inlineStr"/>
       <c r="AB130" t="inlineStr">
         <is>
           <t>대ㆍ중소기업ㆍ농어업협력재단 상생협력지원부 02-368-8971, 8746 / winwinct@win-win.or.kr</t>
@@ -20557,7 +20517,6 @@
           <t>390백만원</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>N</t>
@@ -20653,7 +20612,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA131" t="inlineStr"/>
       <c r="AB131" t="inlineStr">
         <is>
           <t>인천테크노파크 기업지원본부 제조혁신센터 032-260-0622, 0625 / yeobi@itp.or.kr, yhchoi@itp.or.kr</t>
@@ -20706,8 +20664,6 @@
           <t>ㅇ (모집규모) 분야별 다수 기업을 모집하며, 신청내용의 적합성·수요</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>Y</t>
@@ -20860,8 +20816,6 @@
           <t>□ 지원내용</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>N</t>
@@ -20957,7 +20911,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA133" t="inlineStr"/>
       <c r="AB133" t="inlineStr">
         <is>
           <t>인천테크노파크 제조혁신센터 032-260-0625, yhchoi@itp.or.kr</t>
@@ -21011,8 +20964,6 @@
           <t>지원내용</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>Y</t>
@@ -21165,7 +21116,6 @@
           <t>□ 모집규모 : 18개사 내외</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>18개</t>
@@ -21276,7 +21226,6 @@
           <t>한국중소벤처기업유통원 마케팅기획팀 02-6678-9345, 9346</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr"/>
       <c r="AD135" t="inlineStr">
         <is>
           <t>02-6678-9345</t>
@@ -21324,7 +21273,6 @@
           <t>5억원</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>Y</t>
@@ -21430,7 +21378,6 @@
           <t>한국중소벤처기업유통원 제도운영팀 02-6678-9173</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr"/>
       <c r="AD136" t="inlineStr">
         <is>
           <t>02-6678-9173</t>
@@ -21581,13 +21528,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr">
         <is>
           <t>(주)차오름 일자리지원팀 0502-6683-3111</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr"/>
       <c r="AD137" t="inlineStr">
         <is>
           <t>02-6683-3111</t>
@@ -21631,8 +21576,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>N</t>
@@ -21728,13 +21671,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA138" t="inlineStr"/>
       <c r="AB138" t="inlineStr">
         <is>
           <t>(MAS 문의) 042-724-7546 (우수제품 문의) 042-724-7241 / 조달청 구매총괄과 070-4056-7546</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr"/>
       <c r="AD138" t="inlineStr">
         <is>
           <t>042-724-7241</t>
@@ -21786,7 +21727,6 @@
           <t>10억원</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
           <t>Y</t>
@@ -21944,7 +21884,6 @@
           <t>50억원</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>Y</t>
@@ -22097,7 +22036,6 @@
           <t>○ 지원규모 : 10개사 내외</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>10개</t>
@@ -22208,7 +22146,6 @@
           <t>성남산업진흥원 혁신성장부 031-782-3056</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr"/>
       <c r="AD141" t="inlineStr">
         <is>
           <t>031-782-3056</t>
@@ -22251,7 +22188,6 @@
           <t>□ 지원규모 : 30개사 내외(기업당 최대 4회 / 회당 4시간)</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
           <t>30개</t>
@@ -22352,13 +22288,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr">
         <is>
           <t>성남산업진흥원 (성남 섬유제조 소공인특화지원센터) 031-750-2917</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr">
         <is>
           <t>031-750-2917</t>
@@ -22567,8 +22501,6 @@
           <t>참가부문 내 용 지원내용 모집업체수</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>Y</t>
@@ -22679,7 +22611,6 @@
           <t>treasure@aba.or.kr</t>
         </is>
       </c>
-      <c r="AD144" t="inlineStr"/>
       <c r="AE144" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -22724,7 +22655,6 @@
           <t>8백만원</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>Y</t>
@@ -22830,7 +22760,6 @@
           <t>거제시청 조선지원과 노동자지원팀 055-639-4454</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr"/>
       <c r="AD145" t="inlineStr">
         <is>
           <t>055-639-4454</t>
@@ -23036,8 +22965,6 @@
           <t>◦ 지원내용</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
           <t>N</t>
@@ -23195,7 +23122,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>N</t>
@@ -23355,7 +23281,6 @@
           <t>75백만원</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>Y</t>
@@ -23508,8 +23433,6 @@
           <t>□ 모집규모 및 대상</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>Y</t>
@@ -23620,7 +23543,6 @@
           <t>kdh21@kosmes.or.kr</t>
         </is>
       </c>
-      <c r="AD150" t="inlineStr"/>
       <c r="AE150" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -23664,7 +23586,6 @@
           <t>3천만원</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>Y</t>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF151"/>
+  <dimension ref="A1:AF204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23712,6 +23712,8220 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>[경남] 2026년 하반기 식품진흥기금 융자금 지원계획 공고</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 영업장 소재지 관할 시ㆍ군 식품위생부서</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>9억 원(시설개선자금)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>9억원</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>융자신청서, 사업계획서(견적서 및 시설 사진 포함), 이행확약서, 개인정보수집·이용 및 제공동의서, ※ 경남은행 여신관리규정에 따른, 는 은행에 별도 제출,  처리절차, 융자 신청인</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>경상남도 식품위생과 055-211-5014 및 각 시ㆍ군 식품위생부서 문의처 공고문 4p 참조</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr"/>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>055-211-5014</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125352</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>[서울] 강남구 2026년 중국 무역사절단 참가기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>한국무역협회</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-17</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>온라인 접수(구글폼)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>일괄 업로드:, 참가 신청서 (서식 1), 제품설명서 (서식 2), 참가 서약서 (서식 3), '24년), 수출실적증명서 ('24년, '25년) ※ 무역협회/무역통계진흥원 발급, CE 등)</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>한국무역협회 마케팅전략실 02-6000-5371 / 강남구청 지역경제과 02-3423-5502</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr"/>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>02-3423-5502</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125351</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026년 관광기업 베트남 오픈 이노베이션 참가기업 공고</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>한국관광공사</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-07-30 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>온라인 접수 (신청링크)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>ㅇ 우수기업(5개사): PoC 사업화 자금 최대 2천만원</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2천만원</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>온라인 제출 ※ 전자우편 및 방문제출 불가, 확장자 제출자료 파일명, PDF (양식1) 참가신청서 기업명_신청서, PDF (자유양식) 사업계획서 기업명_사업계획서, (해당시) 해외 실증사업 수행이력 혹은 해외, PDF 기업명_자격요건증빙, 거래처와의 계약실적 증빙, ※ 모든</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>2026년 관광기업 베트남 오픈 이노베이션 운영사무국 yesol.park@brinc.io / 한국관광공사 관광기업육성팀 02-729-9552, joocho@knto.or.kr</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>joocho@knto.or.kr</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>02-729-9552</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125350</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 하반기 전북해양수산창업투자지원센터 국내박람회 참여기업 통합 모집 공고</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>전북바이오융합산업진흥원</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>이메일 접수(nof914@jif.re.kr, dew0120@jif.re.kr)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>□ 모집규모</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>&gt;&lt;① 참가 신청서&gt;</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>전북바이오융합산업진흥원 063-210-6594, 5395</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>dew0120@jif.re.kr</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>063-210-6594</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125348</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026년 K-관광 비즈니스데이 in 나고야 참가기관 모집 공고</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>한국관광공사</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>온라인 접수 (한국관광산업포털(투어라즈))</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>참가신청서 제출(붙임 참조), 투어라즈 신청 시 기업 회원가입 필수, ㅇ 진행절차(안), (~ 8. 24.) 투어라즈 사이트 내 참가신청 접수, (~ 9. 11.) 참가기관 대상 1차 안내문 발송, 이후 절차 추후안내 예정, ㅇ 공사 지원사항, 통역 아르바이트 수배</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>(신청 문의) 한국관광공사 오사카지사 +81-6-6450-5641, 5698, aisj19@knto.or.kr, k_kawaguchi.kto@outlook.jp / (시스템문의) 한국관광공사 투어라즈 지원센터 070-8667-4511</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>aisj19@knto.or.kr</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>070-8667-4511</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125347</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>[충남] 2026년 그린스타트업타운 오픈이노베이션 사업화 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>충남콘텐츠진흥원</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>이메일 접수(by1419@ccon.kr)
+※ 신청서 이메일 제출 후, 유선문의를 통해 최종접수 여부 확인 요망</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>□ 지원예산 : 총45백만원(총사천오백만원)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>45백만원</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>구분, 제출안내 제출형식, 과제신청서(수행계획서), 개인정보, 수집·이용·제공동의서, 참여제한 체크리스트, 안내 자료 참고, 중복지원 여부 확인서</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>충남콘텐츠진흥원 벤처창업본부 041-589-7102, by1419@ccon.kr</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>by1419@ccon.kr</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>041-589-7102</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125346</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 전남형 신중년 사회연대경제 노동통합 모델 구축사업 참여기업 상시 모집 공고</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>전남사회적경제통합지원센터</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>상시 접수</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>이메일 접수 (secenter@jnsec.kr)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>○ 모집규모 : 사회연대경제기업 80개소</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>80개</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr"/>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>전남사회적경제통합지원센터 사회적경제팀 061-276-1336</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr"/>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>061-276-1336</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125345</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 KOREA BUSINESS EXPO SHENZHEN 충북관 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>한국무역협회</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-08-07 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>온라인 접수(충북글로벌마케팅시스템)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>- 전시회 참가비(500만원)의 80%</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr"/>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>한국무역협회 충북본부 043-716-2084 / 충청북도 국제통상과 043-220-3464</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr"/>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>043-220-3464</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125344</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>[서울] 2026년 콘텐츠 투자협의체 투자상담회 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>서울경제진흥원</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>온라인 접수 (서울경제진흥원)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>○ 지원내용</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>제출물 내역 양 식 제출방식, 투자상담회 참가신청서, [서울 콘텐츠 투자협의체] 투자상담회 신청서, 제공양식, 개인정보 수집 및 이용 동의서 (날인 후 스캔), (한글 hwp), 기업정보 제공 동의서 (날인 후 스캔), [별도 부가자료</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>서울경제진흥원 콘텐츠마케팅팀 02-3455-8323, jaehee@sba.seoul.kr</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>jaehee@sba.seoul.kr</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>02-3455-8323</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125343</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>[경북] 북부권 2026년 구인ㆍ구직 만남의 날 채용 행사 일자리 잡(JOB)는 날 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>이메일 또는 팩스 접수
+- 이메일 : jobgo@gepa.kr
+- 팩스 : 054-470-8569
+※ 신청 후 접수 여부 확인 필수</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>구인신청서 1부(붙임 참조), 신청문의, ❍ 전 화 : 054-470-8588</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 일자리종합지원팀 054-470-8588, 1544-8819</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>jobgo@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>054-470-8588</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125342</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026년 2차 국토교통연구기획 사업 시행 공고</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>국토교통과학기술진흥원</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>온라인 접수 (범부처통합연구지원시스템)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>지원내용</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>교부 및 접수, 접수 일정, 공고기간 인터넷(전산) 입력 및 신청서 접수, (33일) (8일), 문의 및 기타, ￭ 문의 : 국토교통과학기술진흥원, 담당자, 연번 연구개발과제명 담당부서</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>국토교통과학기술진흥원 031-389-6358 / 범부처통합연구지원시스템 고객센터 1877-2041</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr"/>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>031-389-6358</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125341</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026년 ATF 연계 방송콘텐츠 해외유통 지원 사업 공고</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>한국방송통신전파진흥원</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-09-08</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>이메일 접수(content@kca.kr)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>ㅇ (지원규모) 총 11편 이내</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>공통, ① 지원 신청서 1부., 필수, ② 저작권 보유현황 공개 동의서 1부., 콘텐츠 이용 동의 필요 시, 해외유통 저작권사의 서명 후 제출, ③ 개인정보 수집·이용·제공 동의서 1부., 해당 시</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>KCA 방송콘텐츠진흥팀 061-350-1403, mgs@kca.kr</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>mgs@kca.kr</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>061-350-1403</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125340</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026년 고신뢰 반도체 상용화를 위한 검증ㆍ확인 지원사업 기업 지원 프로그램 모집 공고</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>한국산업기술시험원</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jeong1009@ktl.re.kr)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>&lt;반도체 검증⋅확인(V&amp;V) 지원&gt;&lt;• 기능안전 인증 및 기술 대응을 위한 핵심 산출물(Work Product) 생성 지원  • FMEDA (Failure Modes, Effects, and Diagnostic Analysis) 분석 및 시뮬레이션 지원  • FTA (Fault Tree Analysis) 등 정량적 ·정성적 안전성 분석 지원  • 차량용 반도체(ISO 26262) 등 글로벌 표준에 부합하는 프로세스 구축 및 검증 확인   ※ 상기 명시된 항목은 대표적인 예시이며, 수요기업의 개발 단계 및 필요에 따라 협의를 통한 기타 ISO 26262 관련 산출물 생성 지원 가능&gt;&lt;2000만원&gt;&lt;기업부담금  10% 이상&gt;</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2000만원</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr"/>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>한국산업기술시험원 jeong1009@ktl.re.kr</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>jeong1009@ktl.re.kr</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr"/>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125339</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 경북PRIDE기업 수요 연계형 전주기 신기술 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>이메일 접수 (lhwokok@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>□ (지원금액) 기업당 최대 2000만원 한도(공급가액의 70% 지원, 부가세 제외)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2000만원</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>(스캔본 지양), 문의, 사업 및 신청서 작성 문의:, ESG·기업지원팀 ☎ 054-470-8565, 선정결과 통보, 개별통보(필요시 접수 홈페이지 공고), 사업개요, 사 업 내 용 : 신기술 기획</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 ESGㆍ기업지원팀 054-470-8565, lhwokok@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>lhwokok@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>054-470-8565</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125338</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026년 목재 수출 지원사업(바우처) 준비기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>한국임업진흥원</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-19</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>이메일 접수(hsb1217@kofpi.or.kr)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>1000만 원</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>1000만원</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>◦ 참가신청서, 목재 바우처 사업 참가계획서 등, ①참가신청서 ②바우처 사업 참가계획서, ⑦목재생산업등록증 사본 ⑧수출 증빙서류, ▶보유(해당) 시, ⑨보유 인증 및 특허, 선정기준, 평가표 상세내역 [붙임 2] 참조</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>한국임업진흥원 목재산업실 02-6393-2636</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>hsb1217@kofpi.or.kr</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>02-6393-2636</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125337</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026년 3분기 국내 저온 저장시설 보관 지원업체 모집 공고</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>한국수산무역협회</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>온라인 접수 (온라인 사업 신청 통합시스템)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>지원한도 ○ 업체당 최대 20백만원(1, 2분기 지원액 포함 연간 총액 기준)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>20백만원</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>임대인(소유주)정보, 목적물(면적, 주소, 저온창고 여부), 임대조건 및 임대료, 시설 보관내역 기재, 이용내역서(세금계산서 또는 거래명세서(표)) 제출, 저온 저장시설명</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>한국수산무역협회 수출지원부 02-6300-8704, 8706 / kfta@kfta.net</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>kfta@kfta.net</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>02-6300-8704</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125336</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>[제주] 2026년 중소기업육성자금 융자지원계획 변경 공고</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>제주특별자치도경제통상진흥원</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>접수처
+- 제주시 : 제주시 연삼로 473 경제통상진흥원 지하1층
+- 서귀포시 : 서귀포시 일주동로 8532 축산업협동조합 3층</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>최대 35억원</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>35억원</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>구 분, ‧ 시설투자자금 융자신청서(제조업․비제조업), 사업계획서, ‧ 개인(기업)정보의 수집‧이용‧제공 동의서, 행정정보공동이용 사전동의서, ‧ (해당업체), (최근 3개월이내 원본), 법인인감증명서</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>제주특별자치도 소상공인과 064-710-3905~6 / 제주특별자치도경제통상진흥원 자금지원팀 (제주시) 064-805-3370 (서귀포시) 064-805-3380</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr"/>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>064-710-3905</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125335</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>[부산] 경력단절예방 지원사업 기업환경개선 참여 기업체 모집 공고</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>부산광역여성새로일하기센터</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>방문 또는 이메일 접수
+- 접수처 : 사상구 학감대로 95(학장동, 여성문화회관)
+- 이메일 : whth334@korea.kr</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>총 사업비의 70%까지 지원(최대 5백만원 한도, 자부담 30% 이상)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>5백만원</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>나. 접수장소 : 부산광역여성새로일하기센터, 접수기관, 주 소, 전화번호, 부산광역여성새로일하기센터, (부산광역시여성문화회관), 사상구 학감대로 95(학장동, 여성문화회관)</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>부산광역여성새로일하기센터 051-320-8331</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>whth334@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>051-320-8331</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125334</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026년 국제방송영상마켓(BCWW 2026) X FOX K-포맷 쇼케이스 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>한국콘텐츠진흥원</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-07-23 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>이메일 접수 (showcase@bcww.kr)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>①참가신청서 및 참가 작품소개서(pdf), ②추가자료(트레일러, 티저 등), –19 시즌 미국 신규 예능 중 시청률 1위를 기록.</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>(참가신청 절차 및 지원내용 세부 문의) BCWW 운영사무국 02-6000-8571, showcase@bcww.kr</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>showcase@bcww.kr</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>02-6000-8571</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125333</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>[부산] 2026년 소셜 비즈니스 육성 지원 사업 기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>부산경제진흥원</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-08-07 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>이메일 접수 (yeoyk612@bepa.kr)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>- 판별 완료 기업 당 5백만원 이내 사업지원금 지급 ※사후정산</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>5백만원</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr"/>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>부산경제진흥원 동반성장팀 051-600-1396, yeoyk612@bepa.kr</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>yeoyk612@bepa.kr</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>051-600-1396</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125332</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026년 2차 더현대글로벌×더셀렉츠 글로벌 팝업스토어(일본 도쿄) 참가 브랜드 모집 공고</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>한국콘텐츠진흥원</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>온라인 접수 (한국콘텐츠진흥원 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>ㅇ 같은 회계연도 중 교부받은 지원금, 보조금 또는 간접보조금 총액이 10억원 이상인 수행기관은 「주식</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>10억원</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>번호, 구분 작성방법 주의사항, 한글파일(hwp) 또는, 사업신청서 필수 양식1, PDF파일 제출, 엑셀 파일 제출, 있는 브랜드 상품 리스트 작성, 직접참여인력 및 엑셀파일 제출</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>(사업 문의) 콘텐츠IP전략팀 061-900-6231, sstar5@kocca.kr / (사업관리시스템 문의) IDC 담당자 061-900-9089</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>sstar5@kocca.kr</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>061-900-6231</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125331</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>[울산] 2026년 말레이시아-인도 조선해양 무역사절단 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>KOTRA울산지원본부</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>온라인 접수 (울산통상지원시스템)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>- 편도 항공료 및 보험료 지원(기업당 1인, 이코노미석 기준, 최대 150만원혹은 공식일정 항공임 지원금 중 적은 금액 한도로 지원)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>150만원</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr"/>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>KOTRA울산지원본부 052-289-8056, jwshin@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>jwshin@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>052-289-8056</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125330</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>UNFCCC COP31 한국홍보관 부대행사 참여 모집 공고</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>한국환경산업기술원</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-30</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>이메일 접수 (unfccccopkorea@gmail.com)</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr"/>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>한국환경산업기술원 국제환경협력센터 032-540-2236, 2242, 2245</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr"/>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>032-540-2236</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125329</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026년 하반기 7차 IP-R&amp;D 전략지원 사업 시행 계획 공고(자유공모)</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>한국특허전략개발원</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>온라인 접수 (IP-R&amp;D 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>신청이 제한되며, 최종 선정 이후라도 어느 하나에 해당됨이 확인</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>를 미제출한 경우, 에서 추진하는 사업에 참여 제한 중인 경우, 직전 4개년 간 5회 이상 본 사업에 참여한 경우(단, 졸업제도 예외규정, 참여제한 여부, 해당 시 사업 참여 가능, p.9 유의사항 참고), ※ 상기 참여제한 사항은 사업 공고 마감일 기준으로 함</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>한국특허전략개발원 특허전략사업실 02-3287-4218, 4233, 4234 / ippro@kista.re.kr</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>ippro@kista.re.kr</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>02-3287-4218</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125328</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>[부산] 2026년 제2회 부산진구ㆍ부산상공회의소 채용박람회 참가기업 모집 공고(관광ㆍ마이스 특별관 운영)</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>부산상공회의소</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>이메일 및 팩스 접수
+(관광ㆍMICE 특별관) 부산상공회의소 이메일 yubinkang@korcham.net / 팩스 051-711-7414
+(기업 채용관) 부산진구청 이메일 busanjinjob@korea.kr / 팩스 051-605-6429</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr"/>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>(관광ㆍMICE 특별관) 부산상공회의소 051-990-7085, 7134 (기업 채용관) 부산진구청 051-605-6401, 6405~6409</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>yubinkang@korcham.net</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>051-605-6401</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125327</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026년 3차 방산 중소기업 컨설팅 지원사업 지원대상기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>한국방위산업진흥회</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>이메일 접수 (consul@kdia.or.kr)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>15억원)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>15억원</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>접수), 전자우편, (이메일), 제출, 서명/날인한 서류는 스캔본을 제출하며, 파일들은 1개의 압축파일(zip파일)로 모아서 제출, 아래, ②는 반드시 아래한글 파일로 제출</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>(신청 및 사업운영 관련 문의) 한국방위산업진흥회 방산지원팀 02-3270-6098, 6012, consul@kdia.or.kr / (지원사업 규정 관련 문의) 국방기술진흥연구소 방산성장지원팀 055-751-4863</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>consul@kdia.or.kr</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>02-3270-6098</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125326</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>UNFCCC COP31 한국홍보관 기술전시 참여 모집 공고</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>한국환경산업기술원</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-30</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>이메일 접수 (unfccccopkorea@gmail.com)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>ㅇ (지원내용) 기업별 전시 공간 제공&lt;구분&gt;&lt;주요 내용&gt;</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr"/>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>한국환경산업기술원 국제환경협력센터 032-540-2236, 2242, 2245</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr"/>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>032-540-2236</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125325</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026년 판로확대 지원 참여 소상공인 모집(쇼핑몰 통합관리ㆍ입점ㆍ판매대행 지원(셀러허브)) 공고</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>중소상공인희망재단</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-08-04 ~ 2026-08-30</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>온라인 접수 (중소상공인희망재단)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>5만원 부과</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>5만원</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>하단 서류 각 1부 (별첨 양식 참조), 연번 서류명 주요내용 부수 제출형식, 참여신청서 ⦁ 사업체 정보, 현황, 판매 제품 소개, 참여 목적 등 EXEL, 동의서 ⦁ 개인·기업 정보 수집 및 제3자 제공 동의서, 부 PDF</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>중소상공인희망재단 디지털혁신사업부 070-4267-8256, pjh@heemangfdn.or.kr</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>pjh@heemangfdn.or.kr</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>070-4267-8256</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125324</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>[강원] 2026년 2차 제조ㆍ창업 맞춤형 지원 프로그램 지원기업 통합 모집 공고</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>강원정보문화산업진흥원</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>이메일 접수 (stbc@gica.or.kr)
+※ 발송 후 확인 전화 필수</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>지원프로그램 및 모집 규모&gt;&lt;&gt;&lt;&gt;</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr"/>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>강원정보문화산업진흥원 033-245-6538, 6530, 6531, 6532, 6534, stbc@gica.or.kr / 주식회사 아이비스퀘어 033-264-1133</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>stbc@gica.or.kr</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>033-245-6538</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125323</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026년 제조AI 기술지도 프로그램 참가기업 모집 공고(산업통상부 제조AI 솔루션 개발 지원센터 사업)</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>KAIST</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-08-04 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>온라인 접수 (구글 폼)</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>지원 내용 KAIST 교수진 및 제조/|| 전문가로 구성된 자문단을 기업과 1: 매칭하며</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>검로</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>KAIST 성남연구센터 aramseo@kaist.ac.kr</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>aramseo@kaist.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr"/>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125322</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026년 강원특별자치도 첨단바이오 Pre-Open innovation((재)스크립스코리아항체연구원) 지원 기업 모집 재공고</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>강원테크노파크</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>온라인 접수 (강원특별자치도 연구개발사업관리시스템)
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>- 연간 5천만원 상당(최대 3년) (재)스크립스코리아항체연구원의 기술지원</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>5천만원</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>미제출, 제출양식 미준수인 경우, · 허위 또는 그 밖의 부정한 방법으로, 를 제출한 경우, ＊2년간 수행 후, 평가에 따라 1년 추가 연장 가능하며, 사업수행 결과 불량 또는 지자체 예산 상황에, 따라 조기 종료 가능</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>(강원테크노파크 미래사업단 바이오융합팀) 033-435-8463, 8471/ syjang@gwtp.or.kr, hyemi5@gwtp.or.kr (스크립스코리아항체연구원) songyb@skai.or.kr 및 문의처 출처바로가기 내 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>hyemi5@gwtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>033-435-8463</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125321</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>[충남] 2026년 지역 거점 정보보호 클러스터 구축 사업 정보보호 비즈니스 모델 발굴 및 유망기업 지원 모집 재공고</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>충남테크노파크</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>이메일 접수(sjw@ctp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>□ 지원규모 : 총77000천원(비즈니스 모델 발굴 지원 25000천원, 유망기업</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>서식 구분, 지원신청서 서식1 필수, 사업계획서 서식2 필수, 중복지원 금지확약서 서식3 필수, 개인정보이용동의서 서식4 필수, 대보험 가입자명부 - 필수, 년) - 필수, 창업기업 확인서 또는 벤처기업 확인서 - 필수</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>충남테크노파크 디지털혁신단 디지털진흥센터 041-336-9024, 9027 / sjw@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>sjw@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>041-336-9024</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125320</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>[충남] 2026년 정보보호 기업 성장(특화산업 사업화) 지원사업 모집 공고(지역 거점 정보보호 클러스터 구축사업)</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>충남테크노파크</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>이메일 접수(sjw@ctp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>지원예산 50백만원(정부지원금)</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>50백만원</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>구분 1. 신청 시, 부수 비고, 사업계획서 1부 CTP 제공 서식, 발행기관 서식, 신청기업 중소(중견)기업 확인서 1부, (중소기업현황정보시스템 등), 신청자격 적정성 자기진단서 1부 CTP 제공 서식, CTP 제공 서식</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>충남테크노파크 디지털혁신단 디지털진흥센터 041-336-9027</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>sjw@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>041-336-9027</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125319</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026년 2차 아트코리아랩 AI+기술융합 오픈이노베이션 공모</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>예술경영지원센터</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>온라인 접수 (e나라도움)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>- 과제별 협업 지원금 50백만원(총사업비의 자부담 10% 필수)</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>50백만원</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>구분, 제출방법, ➁ 지원신청서(한글파일 지정양식, 날인필수) 1부, 필수제출 ➂ 통합서식(확약서, 개인정보제공동의서, 성희롱성폭력 예방 등 서약서) 1부, e나라도움 내</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>(신청 문의) 예술경영지원센터 예술기술사업화팀 02-2098-2963 (e나라도움 사용 문의) e나라도움 사용자 지원센터 1670-9595, 02-2006-0200</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>artsfinance@gokams.or.kr</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>02-2006-0200</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125318</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 사회적경제기업 온라인판로 기초 지원사업 참여기업 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>대구광역시사회적경제지원센터</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-19</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>이메일 접수 (dgsecenter@daum.net)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 지원내용:온라인판로진입전·초기기업의판매준비도향상을위해'온라인판로</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>선정제외,  심사기준:심사기준에적합한과제가없는경우, 선발하지않을수있으며, 합계, 평균점수60점이상기업중고득점순으로선정, 심사항목 세부내용 배점, 적합성및, 지원필요성</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>대구광역시 사회적경제지원센터 성장지원팀 070-4450-7990</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>dgsecenter@daum.net</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>070-4450-7990</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125317</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>[충남] 2026년 2차 예비수소전문기업지원사업 수소산업분야 기술사업화(비R&amp;D) 수혜기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>충남테크노파크</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>우편 또는 방문 접수
+- 접수처 : 충청남도 예산군 예산읍 수철길 10(미래자동차센터 202호)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>m 지원규모 : 기업 당 최대 67000천원 이내(부가가치세 제외)</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>우편 및 방문접수, m 문의사항, 소 속 이 름 연락처 이메일, 미래자동차센터, 지원내용, m 지원분야, 지원 프로그램 및 내용, 구 분 분 야 내 용 지원금액 비 고</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>미래자동차센터 041-331-8013, 8021 / coinss@ctp.or.kr, lvme112@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>coinss@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>041-331-8013</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125316</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>[경기] 화성시 2026년 하반기 공급망 확대 사업화 기술컨설팅 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>화성산업진흥원</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>온라인 접수(화성시기업지원플랫폼)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>❏ 지원규모: 총 32개사 내외(분야별 8개사 목표, 예산 범위내 지원)</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>32개</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>업로드, ❏ 신청주체: 참여기업이 신청하며, 신청 전 컨설턴트와 컨설팅 내용, 일정, 횟수 등을 협의, 신청자격 및 지원 제외, ❏ 신청자격, m 공고일 현재 화성시 관내에 본사</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>화성산업진흥원 산업전략본부 공급망지원팀 031-278-4093, ihseo@hsbiz.or.kr</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>ihseo@hsbiz.or.kr</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>031-278-4093</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125315</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>[경기] 화성시 2026년 하반기 국내전시회 단체관 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>화성산업진흥원</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>온라인 접수(화성산업진흥원 기업지원플랫폼)</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>□ (지원내용) 국내 전시회 단체관 구축 및 참가 지원</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>를 통한 기술평가 등, 정량 평가 합을 산출하여 고득점순으로 선정, ※ 동점자 발생 시, ①통상지원사업 수혜실적 적은 기업, ②기업업력 낮은 기업, ③고용안정성 높은 기업 순으로 선정, ※ [붙임1]의 신청서 (서식4), 목록 확인표 참고</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>화성산업진흥원 기업성장팀 031-378-6095, kjh15@hsbiz.or.kr / 화성시청 기업지원과 기업통상지원팀 031-5189-2872</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>kjh15@hsbiz.or.kr</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>031-378-6095</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125314</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 지역 중소기업 우수IP 투자역량 강화 지원사업 기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>경북테크노파크</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경북테크노파크)
+※ 순서대로 작성하여 PDF/HPW로 두 가지 버전으로 제출</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>❍ IP투자연계 기술가치평가 비용 지원(기업당 최대 1500만원 이내)</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>1500만원</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>양식 비고, ➀ 사업신청서 1부 (첨부된 사업신청서 작성) 붙임1, 신청기업, 기본서류 4대보험 사업장 가입자 명부, 필수, 투자유치용 기업 IR자료, ➁ 신청 자격 및 적정성 확인서 붙임2, ➂ 개인정보 수집·이용 및 제 3자 제공 동의서 붙임3</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>경북테크노파크 기업지원단 053-819-3065, jwh333@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>jwh333@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>053-819-3065</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125313</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>경남 정보보호 기업 육성 창업ㆍ벤처 기업모집 재공고</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>경남테크노파크</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경남테크노파크)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>000만원 (자부담금 20% 현물 가능)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>0만원</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr"/>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>경남테크노파크 055-294-2404, jmy@gntp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>jmy@gntp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>055-294-2404</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125312</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>[부산] 2026년 하반기 중소기업 밀집지역 위기대응 체계 구축사업 Stand-up 맞춤지원 모집 공고</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>부산테크노파크</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>온라인 접수 (부산테크노파크 전자평가시스템)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>110백만원(11개사 내외)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>110백만원</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>11개</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>포워딩 인보이스, 비용지급 관련 송금영수증(지원기업→물류업체), 비용지급 관련 세금계산서(물류업체→지원기업), 국내운임, 취급수수료, 도착국 발생비용, 세금은 제외, 최대 5백만원</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>부산 중소기업 위기지원센터(부산테크노파크) 051-320-3532, jskim12@btp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>jskim12@btp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>051-320-3532</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125311</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>[경북] 영천시 2026년 5차 지방소멸 대응을 위한 모빌리티 가공부품산업 제조전환 및 구조 효율화 지원사업 공고(시군구연고산업육성 협업프로젝트)</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>경북테크노파크</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>온라인 접수 (기업지원사업 관리시스템)</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>◦ (지원규모) 총 약 35백만원</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>35백만원</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>가 허위, 중복인 경우 지원취소 및 지원금을 환수할 수 있음, 통한 전산 접수로만 시행되므로, 반드시 접수방법 사전 숙지 및 접수시간 준수, 서류 및 내용을 꼭 확인 후 “신청완료” 하여야 하며, 지원기관, 담당자와 사전 협의 후 프로그램 신청요망,  평가방법 및 기준</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>경북테크노파크 054-450-0552, sulee@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>sulee@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>054-450-0552</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125310</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[부산] 일본 MEDICAL JAPAN 수출상담회 지원사업 공고(2025년도 시군구연고산업육성사업 2차년도) </t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>부산테크노파크</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>온라인 접수(기업지원사업 관리시스템)</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 4건 지원 *자세한 사항은 지원대상 및 내용 참조</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>4건</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>(공통), 구분 제 출 서 류 서식, 사업신청서 서식1~3, 첨부1~5, 대차대조표), 우대사항을 확인할수 있는 서류 -, 각종 인증, 지식재산권 증서</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>부산테크노파크 바이오헬스센터 051-320-3524, rhythm@btp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>rhythm@btp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>051-320-3524</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125309</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [부산] 3차 기업성장기반 글로벌 하이메디 허브 특구 상생협력사업 지원프로그램 기업지원 모집공고(2025년 시군구연고산업육성 협업프로젝트 2차년도)</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>부산테크노파크</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>온라인 접수(기업지원사업 관리시스템)</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>- 기업 자부담 매칭 예시 : 지원금 30백만원 + 자부담(10%) 3백만원 = 총 사업비 33백만원(부가세 제외)</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>33백만원</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>(공통), 구분 제 출 서 류 서식여부, (서식1) 사업신청서 ◯, (서식2) 기업관리카드 ◯, (서식3) 수행계획서 ◯, (첨부2) 신청자격 적정성 확인서 ◯, 필수, (첨부5) 정부사업 참여이력 ◯</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>부산테크노파크 바이오헬스센터 051-320-3524, rhythm@btp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>rhythm@btp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>051-320-3524</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125308</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026년 2차 기계장비산업기술개발사업(AI팩토리) 신규지원 대상과제 공고</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>한국산업기술기획평가원</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>온라인 접수 (범부처통합연구지원시스템)</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>공고예산 198억원 25억원</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>198억원</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>사항, 기타 유의 사항, 문의처, 사업개요, 사업목적, 국내 기계장비기업의 글로벌 경쟁력 강화, 연구개발비 지원 규모 및 기간, 세부사업 기계장비산업기술개발 기계장비산업기술개발</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>한국산업기술기획평가원 AI기계로봇실 (선정평가 일정 및 절차 문의) 053-718-8276, 8477, 8727, 8747, 8748 (기획의도 문의) 피지컬AI PD 053-718-8381, dongwank@keit.re.kr</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>dongwank@keit.re.kr</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>053-718-8276</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125307</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 제2회 공영홈쇼핑 혁신기업 제품 코칭 상담회 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>지방중소벤처기업청</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-09-06</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>온라인 접수 (판판대로)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>② 마케팅 지원 : TV홈쇼핑 영상 제작비 최대 350만원 지원</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>350만원</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>(자격심사) 기업 기본서류, OEM 등 원산지증명서 서류, 가점서류 등 제출 및 진위여부 검토(정책개발팀), 구분 세 부 내 용, 나. 2차 코칭·상담회 평가 : 9월 15일(화), 일간, 사업자 확인, ② 중소기업확인서</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>공영홈쇼핑 정책개발팀 02-6350-8019 / 전북지방중소벤처기업청 지역정책과 063-210-6483</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr"/>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>02-6350-8019</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125306</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 하반기 지역형 예비사회적기업 지정 계획 공고</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>직접수행</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>온라인 접수 (사회적기업 포털)
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>□ 지원내용</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>검토 및 현지실사, 검토보고서 작성, (금) 대전지방고용노동청, 월 중, 심사위원회 개최 대전광역시, (일정 추후 통보), 월 한 지정서 교부 자치구→선정기업, 진행되며</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>대전광역시 일자리경제정책과 042-270-4581, sunchip@korea.kr 및 관할 구청 사회적기업 담당 부서 등 문의처 공고문 12p 참조</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>sunchip@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>042-270-4581</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125305</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026년 2차 기술개발제품 공공기관 실증지원 사업 공고</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>한국중소벤처기업유통원</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>온라인 접수 (공공구매종합정보망(SMPP))</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>□ 지원 규모 : 12개 과제 내외(한 과제당 3000만원 이내 지원)</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>3000만원</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>12개</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>검토⸱접수, 현장설치 공공기관, 현장검증제품 확인 심의위원회 평가위원회, 실증지원 의견확인, 현장검증 성공제품 공공기관 사업, 제품 설치 또는 지원 대상 사업계획서 기반, 확인 및 구매유도 참여 의견 최종 검토, 성능검증 최종선정 신청기업 대면평가</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>한국중소벤처기업유통원 제도운영팀 02-6678-9171,9174</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr"/>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>02-6678-9171</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125304</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>[경기] 2026년 친환경차 전환 진단 컨설팅 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>경기도 노사민정협의회</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>모집 완료시</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>이메일 접수 (mscs8808@gyef.or.kr)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr"/>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>경기도 노사민정협의회 031-289-3496, 3498</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>mscs8808@gyef.or.kr</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>031-289-3496</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125303</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>[충북] 북부 2026년 4차 지식재산 긴급지원 사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>충북북부지식재산센터</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>온라인 접수 (지원기업 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>신청서‧사업추진(활용)계획서 및 필수(선택), 지원절차, o 신청·접수 → 서류</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>충북북부지식재산센터 043-843-7005(내선 5번)</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr"/>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>043-843-7005</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125302</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 3차 사회연대경제 청년 일경험사업 시범사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>전남사회적경제통합지원센터</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>이메일 접수(cbcenter@jnsec.kr)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>□ 지원내용 : 참여청년 인건비*, 참여청년 1인당 운영비월 20만원,</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>20만원</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>제출&gt;</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>전남사회적경제통합지원센터 마을기업팀 061-285-7180, 7181, 7182, 7183</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr"/>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>061-285-7180</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125301</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026년 제4차 기업부설창작연구소(전담부서) 인정신청 공고</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>한국콘텐츠진흥원</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-09-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>온라인 접수 (기업부설창작연구소 시스템)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>세액공제 내역, 창작개발활동 조사표, 운영현황제출동의서, 개인정보, 수집이용동의서, Ⅱ. 상세요건, 대상, 요건</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>(제출서류 작성) 한국문화기술기획평가원 전략혁신연구팀 042-330-6623 / (신청시스템(홈페이지)) 한국콘텐츠진흥원 IDC 042-330-6682</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr"/>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>042-330-6623</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125300</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 하반기 중소기업 밀집지역 위기대응 체계 구축사업 Stand-up 맞춤지원 모집 공고</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>대구테크노파크</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>이메일 접수 (hibig51@dgtp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>◦ (2026년 하반기 지원규모) 70백만원(7개사)</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>70백만원</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>7개</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>포워딩 인보이스, 비용지급 관련, 물류비 지원 송금영수증(지원기업→물류업체), 비용지급 관련 최대 5백만원, 세금계산서(물류업체→지원기업), 국내운임, 취급수수료, 도착국 발생비용</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>대구시 지역중소기업 위기지원센터(대구테크노파크) 053-757-3708, 3704, 3701 / hibig51@dgtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>hibig51@dgtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>053-757-3708</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125299</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -23744,7 +23744,6 @@
           <t>9억원</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>N</t>
@@ -23850,7 +23849,6 @@
           <t>경상남도 식품위생과 055-211-5014 및 각 시ㆍ군 식품위생부서 문의처 공고문 4p 참조</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="inlineStr">
         <is>
           <t>055-211-5014</t>
@@ -23893,8 +23891,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>Y</t>
@@ -24000,7 +23996,6 @@
           <t>한국무역협회 마케팅전략실 02-6000-5371 / 강남구청 지역경제과 02-3423-5502</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr"/>
       <c r="AD153" t="inlineStr">
         <is>
           <t>02-3423-5502</t>
@@ -24205,8 +24200,6 @@
           <t>□ 모집규모</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>N</t>
@@ -24359,8 +24352,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
           <t>N</t>
@@ -24519,7 +24510,6 @@
           <t>45백만원</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>Y</t>
@@ -24672,7 +24662,6 @@
           <t>○ 모집규모 : 사회연대경제기업 80개소</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>80개</t>
@@ -24773,13 +24762,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA158" t="inlineStr"/>
       <c r="AB158" t="inlineStr">
         <is>
           <t>전남사회적경제통합지원센터 사회적경제팀 061-276-1336</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr"/>
       <c r="AD158" t="inlineStr">
         <is>
           <t>061-276-1336</t>
@@ -24827,7 +24814,6 @@
           <t>500만원</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>Y</t>
@@ -24923,13 +24909,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA159" t="inlineStr"/>
       <c r="AB159" t="inlineStr">
         <is>
           <t>한국무역협회 충북본부 043-716-2084 / 충청북도 국제통상과 043-220-3464</t>
         </is>
       </c>
-      <c r="AC159" t="inlineStr"/>
       <c r="AD159" t="inlineStr">
         <is>
           <t>043-220-3464</t>
@@ -24972,8 +24956,6 @@
           <t>○ 지원내용</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
           <t>N</t>
@@ -25129,8 +25111,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
           <t>Y</t>
@@ -25283,8 +25263,6 @@
           <t>지원내용</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
           <t>N</t>
@@ -25390,7 +25368,6 @@
           <t>국토교통과학기술진흥원 031-389-6358 / 범부처통합연구지원시스템 고객센터 1877-2041</t>
         </is>
       </c>
-      <c r="AC162" t="inlineStr"/>
       <c r="AD162" t="inlineStr">
         <is>
           <t>031-389-6358</t>
@@ -25433,8 +25410,6 @@
           <t>ㅇ (지원규모) 총 11편 이내</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>Y</t>
@@ -25592,7 +25567,6 @@
           <t>2000만원</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
           <t>N</t>
@@ -25688,7 +25662,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA164" t="inlineStr"/>
       <c r="AB164" t="inlineStr">
         <is>
           <t>한국산업기술시험원 jeong1009@ktl.re.kr</t>
@@ -25699,7 +25672,6 @@
           <t>jeong1009@ktl.re.kr</t>
         </is>
       </c>
-      <c r="AD164" t="inlineStr"/>
       <c r="AE164" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -25742,7 +25714,6 @@
           <t>2000만원</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
           <t>N</t>
@@ -25900,7 +25871,6 @@
           <t>1000만원</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
           <t>Y</t>
@@ -26058,7 +26028,6 @@
           <t>20백만원</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
           <t>Y</t>
@@ -26218,7 +26187,6 @@
           <t>35억원</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
           <t>Y</t>
@@ -26324,7 +26292,6 @@
           <t>제주특별자치도 소상공인과 064-710-3905~6 / 제주특별자치도경제통상진흥원 자금지원팀 (제주시) 064-805-3370 (서귀포시) 064-805-3380</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr"/>
       <c r="AD168" t="inlineStr">
         <is>
           <t>064-710-3905</t>
@@ -26374,7 +26341,6 @@
           <t>5백만원</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
           <t>Y</t>
@@ -26527,8 +26493,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>N</t>
@@ -26686,7 +26650,6 @@
           <t>5백만원</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>N</t>
@@ -26782,7 +26745,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA171" t="inlineStr"/>
       <c r="AB171" t="inlineStr">
         <is>
           <t>부산경제진흥원 동반성장팀 051-600-1396, yeoyk612@bepa.kr</t>
@@ -26840,7 +26802,6 @@
           <t>10억원</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
           <t>Y</t>
@@ -26998,7 +26959,6 @@
           <t>150만원</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
           <t>N</t>
@@ -27094,7 +27054,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA173" t="inlineStr"/>
       <c r="AB173" t="inlineStr">
         <is>
           <t>KOTRA울산지원본부 052-289-8056, jwshin@kotra.or.kr</t>
@@ -27147,8 +27106,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
           <t>N</t>
@@ -27244,13 +27201,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA174" t="inlineStr"/>
       <c r="AB174" t="inlineStr">
         <is>
           <t>한국환경산업기술원 국제환경협력센터 032-540-2236, 2242, 2245</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr"/>
       <c r="AD174" t="inlineStr">
         <is>
           <t>032-540-2236</t>
@@ -27293,8 +27248,6 @@
           <t>신청이 제한되며, 최종 선정 이후라도 어느 하나에 해당됨이 확인</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
           <t>Y</t>
@@ -27449,8 +27402,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
           <t>N</t>
@@ -27546,7 +27497,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA176" t="inlineStr"/>
       <c r="AB176" t="inlineStr">
         <is>
           <t>(관광ㆍMICE 특별관) 부산상공회의소 051-990-7085, 7134 (기업 채용관) 부산진구청 051-605-6401, 6405~6409</t>
@@ -27604,7 +27554,6 @@
           <t>15억원</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
           <t>Y</t>
@@ -27757,8 +27706,6 @@
           <t>ㅇ (지원내용) 기업별 전시 공간 제공&lt;구분&gt;&lt;주요 내용&gt;</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
           <t>N</t>
@@ -27854,13 +27801,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="inlineStr">
         <is>
           <t>한국환경산업기술원 국제환경협력센터 032-540-2236, 2242, 2245</t>
         </is>
       </c>
-      <c r="AC178" t="inlineStr"/>
       <c r="AD178" t="inlineStr">
         <is>
           <t>032-540-2236</t>
@@ -27908,7 +27853,6 @@
           <t>5만원</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
           <t>Y</t>
@@ -28062,8 +28006,6 @@
           <t>지원프로그램 및 모집 규모&gt;&lt;&gt;&lt;&gt;</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
           <t>N</t>
@@ -28159,7 +28101,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA180" t="inlineStr"/>
       <c r="AB180" t="inlineStr">
         <is>
           <t>강원정보문화산업진흥원 033-245-6538, 6530, 6531, 6532, 6534, stbc@gica.or.kr / 주식회사 아이비스퀘어 033-264-1133</t>
@@ -28212,8 +28153,6 @@
           <t>지원 내용 KAIST 교수진 및 제조/|| 전문가로 구성된 자문단을 기업과 1: 매칭하며</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
           <t>N</t>
@@ -28324,7 +28263,6 @@
           <t>aramseo@kaist.ac.kr</t>
         </is>
       </c>
-      <c r="AD181" t="inlineStr"/>
       <c r="AE181" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -28368,7 +28306,6 @@
           <t>5천만원</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
           <t>Y</t>
@@ -28521,8 +28458,6 @@
           <t>□ 지원규모 : 총77000천원(비즈니스 모델 발굴 지원 25000천원, 유망기업</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
           <t>Y</t>
@@ -28680,7 +28615,6 @@
           <t>50백만원</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
           <t>Y</t>
@@ -28838,7 +28772,6 @@
           <t>50백만원</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
           <t>Y</t>
@@ -28991,8 +28924,6 @@
           <t xml:space="preserve"> 지원내용:온라인판로진입전·초기기업의판매준비도향상을위해'온라인판로</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
           <t>Y</t>
@@ -29146,8 +29077,6 @@
           <t>m 지원규모 : 기업 당 최대 67000천원 이내(부가가치세 제외)</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
           <t>Y</t>
@@ -29300,7 +29229,6 @@
           <t>❏ 지원규모: 총 32개사 내외(분야별 8개사 목표, 예산 범위내 지원)</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
           <t>32개</t>
@@ -29458,8 +29386,6 @@
           <t>□ (지원내용) 국내 전시회 단체관 구축 및 참가 지원</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
           <t>Y</t>
@@ -29618,7 +29544,6 @@
           <t>1500만원</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
           <t>Y</t>
@@ -29776,7 +29701,6 @@
           <t>0만원</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
           <t>N</t>
@@ -29872,7 +29796,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA191" t="inlineStr"/>
       <c r="AB191" t="inlineStr">
         <is>
           <t>경남테크노파크 055-294-2404, jmy@gntp.or.kr</t>
@@ -30092,7 +30015,6 @@
           <t>35백만원</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
           <t>Y</t>
@@ -30245,7 +30167,6 @@
           <t>❍ 지원규모 : 4건 지원 *자세한 사항은 지원대상 및 내용 참조</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
           <t>4건</t>
@@ -30408,7 +30329,6 @@
           <t>33백만원</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
           <t>Y</t>
@@ -30566,7 +30486,6 @@
           <t>198억원</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
           <t>N</t>
@@ -30724,7 +30643,6 @@
           <t>350만원</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
           <t>Y</t>
@@ -30830,7 +30748,6 @@
           <t>공영홈쇼핑 정책개발팀 02-6350-8019 / 전북지방중소벤처기업청 지역정책과 063-210-6483</t>
         </is>
       </c>
-      <c r="AC197" t="inlineStr"/>
       <c r="AD197" t="inlineStr">
         <is>
           <t>02-6350-8019</t>
@@ -30874,8 +30791,6 @@
           <t>□ 지원내용</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
           <t>Y</t>
@@ -31143,7 +31058,6 @@
           <t>한국중소벤처기업유통원 제도운영팀 02-6678-9171,9174</t>
         </is>
       </c>
-      <c r="AC199" t="inlineStr"/>
       <c r="AD199" t="inlineStr">
         <is>
           <t>02-6678-9171</t>
@@ -31186,8 +31100,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
           <t>N</t>
@@ -31283,7 +31195,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA200" t="inlineStr"/>
       <c r="AB200" t="inlineStr">
         <is>
           <t>경기도 노사민정협의회 031-289-3496, 3498</t>
@@ -31336,8 +31247,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
           <t>N</t>
@@ -31443,7 +31352,6 @@
           <t>충북북부지식재산센터 043-843-7005(내선 5번)</t>
         </is>
       </c>
-      <c r="AC201" t="inlineStr"/>
       <c r="AD201" t="inlineStr">
         <is>
           <t>043-843-7005</t>
@@ -31491,7 +31399,6 @@
           <t>20만원</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
           <t>N</t>
@@ -31597,7 +31504,6 @@
           <t>전남사회적경제통합지원센터 마을기업팀 061-285-7180, 7181, 7182, 7183</t>
         </is>
       </c>
-      <c r="AC202" t="inlineStr"/>
       <c r="AD202" t="inlineStr">
         <is>
           <t>061-285-7180</t>
@@ -31640,8 +31546,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
           <t>Y</t>
@@ -31747,7 +31651,6 @@
           <t>(제출서류 작성) 한국문화기술기획평가원 전략혁신연구팀 042-330-6623 / (신청시스템(홈페이지)) 한국콘텐츠진흥원 IDC 042-330-6682</t>
         </is>
       </c>
-      <c r="AC203" t="inlineStr"/>
       <c r="AD203" t="inlineStr">
         <is>
           <t>042-330-6623</t>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF204"/>
+  <dimension ref="A1:AF254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31829,6 +31829,7770 @@
         </is>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>[경기] 가평군 2027년 기업환경 개선사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>방문 접수 및 이메일 접수
+- 접수처 : 가평군청 일자리정책 기업지원팀
+※ 사업계획서 한글 파일도 함께 이메일로 제출 (dlwltnek123@korea.kr)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>(총사업비 7억원 이내)</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>7억원</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>지참 후 방문접수, 접수장소: 가평군청 일자리정책, 기업지원팀(580-2277), 방문 접수, 필 수, 해당분야 사업계획서 1부(현장사진 포함), 자부담 확약서 1부, [서식 1]</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>가평군청 일자리청잭 기업지원팀 031-580-2277</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>dlwltnek123@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>031-580-2277</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125402</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>[경기] 2026년 무역위기 대응 K-FOOD 싱가포르 통상촉진단 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>경기도경제과학진흥원</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경기기업비서)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>단체 이동 차량 제공, 항공료 50% 지원(1사 1인에 한함, 최대 40만원 이내)</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>40만원</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>가. 신청방법 : 경기기업비서를 통한 온라인 접수, ③ 신청서 작성 및 ‘, 정보’, ‘인증서정보’에 서류 등록(‘나의서류함’에 해당 파일, 등록 후 선택), 알림수신 동의 후 지원사업 접수, 나., 필수제출</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>(사업문의) 경기도경제과학진흥원 수출마케팅팀 031-259-6143, minzz@gbsa.or.kr / (경기기업비서 시스템 문의) 전산운영실 031-259-6299</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>minzz@gbsa.or.kr</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>031-259-6143</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125401</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>[경기] 여주시 2026년 중화권 시장개척단 참가기업 모집 재공고</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>경기도경제과학진흥원</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-07-20 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>방문 또는 우편 접수
+- 접수처 : 여주시 세종로 10, 영무빌딩 3층 여주시청 일자리경제과 기업지원팀
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>- 항공비 지원(1사 1인 항공비의 50%, 최대 36만원)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>36만원</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>모집규모 : 5개사, 신청자격 :, 여주시, 중소 제조기업(단순 무역업체 제외)으로서 공장, 등록한 기업, 또는, 신청방법 :, 방문 신청 및 우편 신청(우편은 마감일 도착분까지 유효</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>여주시 일자리경제과 기업지원팀 031-887-3033 / 경기도경제과학진흥원 수출지원팀 031-259-6147</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>nyeong0110@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>031-259-6147</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125400</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>[경기] 광주시 2027년 기업환경 개선사업 신청 공고</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>우편 또는 방문 접수
+- 접수처 : 광주시 행정타운로 50, 3층 기업지원과</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>가. 사업계획서(견적서, 인감증명서 포함), ※ 세부 MAS 첨부파일 참고, ※ 기반시설 개선사업은 사업계획서만 제출, 나. 국세, 라. 재무재표(2023년~2025년, 년분), 마. 4대보험 가입자명부</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>광주시 기업지원과 031-760-3787</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr"/>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>031-760-3787</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125399</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>[경기] 김포시 중소기업 국도비 유치 지원사업 참여기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>김포산업지원센터</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-08-04 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>이메일 또는 우편 접수
+- 접수처 : 김포시 양촌읍 황금1로 122 5층
+- 이메일 : iglee@gopa.or.kr</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>○ 지원규모 : 1개사 내외, 최대 900만원 한도(부가가치세 제외)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>900만원</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr"/>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>김포산업지원센터 기업육성팀 031-981-1329</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr"/>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>031-981-1329</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125398</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>[경기] 용인시 2026년 우수기업 선정계획 공고</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>온라인 접수 (용인기업지원시스템)</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>10개 기업 선정</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>[필 수], 용인시, 우수기업, 인증 신청서, 【별지 제1호 서식】, 평가표, 【별지 제2호 서식】, 목록표</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>용인시 기업지원과 기업지원팀 031-6193-2856</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr"/>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>031-6193-2856</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125397</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>[경남] 2026년 4차 사회연대경제 청년 일경험사업 참여 기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>경남투자경제진흥원</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>모집 완료시</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>이메일 또는 팩스 접수
+- 이메일 : hyejj0128@giba.or.kr
+- 팩스 : 055-230-2995 (팩스 발송 후 담당자 연락 요망)</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>1) 참여청년 임금 : 월 최대 234만원* , 5개월간 지급</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>234만원</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>및 상세내용 반드시 확인 (p.7), 【붙임 1】 사회연대경제 청년 일경험 참여기업 신청서, 【붙임 2】 참여기업 운영계획서, 【붙임 3】 참여기업 확인서, 【붙임 4】 참여기업 서약서, 참여자격 확인 서류, 고용보험 자격취득자 명부, 마을기업</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>경남투자경제진흥원 055-230-2927, 2912</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>hyejj0128@giba.or.kr</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>055-230-2927</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125396</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 경북세일페스타 인플루언서 협업 홍보 지원사업 참여기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>이메일 접수(salefesta054@gmail.com)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr"/>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 마케팅팀 054-470-8577, 8572</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>salefesta054@gmail.com</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>054-470-8577</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125395</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>[경기] 용인시 2027년 기업환경 개선사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>방문 또는 우편 접수
+- 접수처 : 용인시 처인구 중부대로 1199, 9층(용인시청 기업지원과)
+※ 신청서류는 기한[2026. 9. 4.(금) 18시] 내 도착분에 한하여 유효하며, 우편 신청 시 반드시 전화(031-6193-2286)로 접수여부 확인</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>사업비 2천만원(VAT 제외) 이상이고, 자부담율 50% 미만인 경우는 지방계약법령에</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2천만원</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>신청, 방법 : 방문 또는 우편 신청, 용인시 처인구 중부대로 1199, 층(용인시청 기업지원과), 하며, 사업계획서(, ※사업비 산출내역서 및 세부 견적서 포함, 부.</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>용인시청 기업지원과 031-6193-2286</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr"/>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>031-6193-2286</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125394</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>[경남] 김해시 2026년 메가쇼 시즌2 단체관 참가 지원사업 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>김해의생명산업진흥원</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>접수방법별 마감일 상이</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>우편 및 이메일 접수
+- 접수처 : 김해시 주촌면 골든루트로 80-16, 3층 김해의생명ㆍ산업진흥원
+- 이메일 : pjwon05@naver.com</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 메가쇼 프리미엄 부스 지원(10개사 내외)</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>구분, 비고, 필수, 제출, ➃ [붙임4] 서약서 ➇ 제품소개자료 제출, 공장등록증※, 제출 ➁ 각종 인증서 및 지정서 사본 활용, ※ 증빙서류 사본에 원본대조필 날인 필수</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>김해의생명산업진흥원 소상공인지원팀 055-310-9241</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>pjwon05@naver.com</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>055-310-9241</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125393</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>[경남] 하남시 2026년 제2회 청년 채용 ZONE 참여기업 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026-07-06 ~ 2026-09-07</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>이메일 접수 (no2random@korea.kr)</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>따라 5년 이하의 징역 또는 5천만원 이하의 벌금에 처할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>5천만원</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>개인정보 이용에 대한 동의서, 구인신청서, 채용담당자 신분증, (주민번호 뒷자리 없이), 및 재직증명서 또는 사원증, 나. 접수방법 : 이메일 접수, 담당자 이메일 :, [하남시 청년일자리과 청년일자리팀]</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>하남시 청년일자리과 청년일자리팀 031-790-5248</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>no2random@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>031-790-5248</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125392</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>[전남광주] 목포시 중동사태 어업용 면세유 유가연동보조금 지원사업 신청 공고</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 주소지 관할 시ㆍ군청</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>3원 /ℓ (수협중앙회 월별 면세유 공급가격에 따라 변동)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>3원</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>사업 신청서 1부(붙임), 신분증 및 통장사본 각 1부., 면세유류카드 사본, 접수장소 및 문의처, 지급시기, 예산확정 후 지급 (※ 별도 문자 안내), 유의사항, 에 허위의 사실을 기재하거나 기타 부정한 방법으로 지원</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>목포시청 수산산업과 어업지원팀 061-270-3411</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr"/>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>061-270-3411</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125391</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>[경기] 시흥시 2026년 3차 현장노동자 휴게시설 개선사업 추가 공고</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>방문 또는 우편 접수
+- 접수처 : 우편번호 14998, 경기도 시흥시 시청로 20, 시흥시청 본관 4층 시흥시 노동지원과, 휴게시설 개선사업 담당자 앞
+※ 위 서류 원본과 동일한 전자파일을 2026. 8. 28.(금) 18:00까지 이메일(yujin0122@korea.kr)로 제출해야 함</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>○ 최소 지원요건 : 총사업비(보조금+자부담) 300만원 이상</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>300만원</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>아래 서류 각 2부 및 그와 동일한 전자파일, ① 사업신청서 ② 사업계획서(현장사진, 견적서 등 계획에 필요한 자료 포함), 고유번호증, 최근 3년간), ⑦ 기타 증빙서류(생활임금 서약제 참여 증빙서류, 기타 신청 관련 서류 등 해당시 제출), 제출방법 : 직접방문(평일 09:00~18:00 내)</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>시흥시 노동지원과 휴게시설 개선사업 담당자 031-310-3946</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>yujin0122@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>031-310-3946</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125390</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 농식품 해외 무역사절단 파견(호주) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>충청북도기업진흥원</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>온라인 접수 (충북글로벌마케팅시스템)</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>＊이코노미 기준, 1사 1인 50만원 이내</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr"/>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>충청북도기업진흥원 농식품유통본부 043-270-0214</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr"/>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>043-270-0214</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125389</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026년 BOUNCE 2026 스타트업 오픈이노베이션 페스타 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>부산창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-09-02</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>온라인 접수 (구글폼)</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t> 모집규모 : 파트너사별 상이 (파트너사당 4 ~ 8개사 내외)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>8개</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr"/>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>부산창조경제혁신센터 글로벌 오픈이노베이션팀 051-749-8931, ymlee1106@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>ymlee1106@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>051-749-8931</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125388</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>[경기] 시흥시 2026년 명품점포 지원사업 모집 공고(소상공인 지원사업)</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 시흥시청 4층 소상공인과 골목상권팀</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>❍ (지원내용) 영업장 시설개선 비용 지원(최대 300만원) 및 인증현판 수여</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>300만원</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>상시근로자, 수 확인을 위한 증빙서류를 추가로 제출하시기 바랍니다., 시 흥 시 장, 사업개요, ❍ (지원규모) 20개소, 지원대상, 신청자격, 도소매업</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>시흥시 소상공인과 031-310-2609</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr"/>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>031-310-2609</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125387</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 해양기업 맞춤형 역량강화 컨설팅 프로그램 지원기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>포항테크노파크</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-17</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>온라인 접수(포항테크노파크)</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>○ 지원내용</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>구분 연번, 비고, ▹참가신청서, ‘붙임’ 참조, 개인(기업)정보 수집·이용제공 동의서 포함, 제출, 서류, ▹회사/제품(기술) 소개자료(자유양식)</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>포항테크노파크 바이오사업본부 054-255-2601, subin0427@ptp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>subin0427@ptp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>054-255-2601</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125386</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>[대구ㆍ경북] 2026년 하반기 대구경북 공공구매상담회 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>대구경북지방중소벤처기업청</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-09-03</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jsoball9@korea.kr)</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>소프트웨어를 제외한 110만원 이하의 컴퓨터 본체</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>110만원</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr"/>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>대구ㆍ경북지방중소벤처기업청 성장지원과 053-659-2237</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>jsoball9@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>053-659-2237</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125385</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026년 시흥바이오 소부장 캡스톤 경진대회 참여기업 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>시흥산업진흥원</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>온라인 접수 (시흥산업진흥원)</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr"/>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>시흥산업진흥원 바이오산업실 070-4265-1526, jhkim@sida.kr</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>jhkim@sida.kr</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>070-4265-1526</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125384</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>[경기] 남양주시 2026년 2차 식품안심업소(위생등급제) 청소비 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>방문 또는 이메일 접수
+- 접수처 : 남양주시청 위생과 (남양주시청 제1청사 신관 1층)
+- 이메일 : hihi605@korea.kr</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>영업장 내부 청소비 지원 8개소 업소당 70만원 이내</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>70만원</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>8개</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>] 신청서 1부, 청소 전 사진 1부, 재지정 신청 동의서 1부, 식품안심업소 지정서 사본 1부, 청소업체 견적서 1부, 마. 문의사항, 남양주시 위생과 위생기획팀(☎031-590-3975), &lt; 신청 시 유의 사항&gt;</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>남양주시 위생과 위생기획팀 031-590-3975</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>hihi605@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>031-590-3975</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125383</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 베트남 D-Global 유망기업 기술교류회 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>대전테크노파크</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-09-02</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>온라인 접수(DIPS 대전기업정보포털)</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>5백만원 이내)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>5백만원</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>접수서류 순서대로 압축(zip)하여 첨부파일 등록, 최종선정, 기업대상 필요서류 별도 제출(안내) 예정, 구분 등록서류 비고, 신청서(사업계획서, 신용정보 조회동의서 등 포함) 날인 必, ’25년), 원클릭 제출 활용</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>대전테크노파크 기업성장본부 기업투자ㆍ유치팀 042-930-4872, hc4550@djtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>hc4550@djtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>042-930-4872</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125382</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>[경기] 고양시 2026년 현장노동자 휴게시설 개선사업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>온라인 접수 (지방보조금관리시스템(보탬e))</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>○ 지원요건 : 총사업비 3백만원 이상 사업</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>3백만원</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>① 사업신청서, ② 사업계획서(휴게시설 현장사진, 견적서 등 포함), 고유번호증, ⑥ 기타 증빙서류(생활임금 서약서, 대보험 납부증빙서류, 매출액 증빙서류 등 해당하는 경우에 한해 제출), &amp;lt; 공동휴게시설 개선 신청 시&amp;gt;</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>고양시 일자리정책과 노사협력팀 031-8075-3563</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr"/>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>031-8075-3563</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125381</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>[경북] 양산시 2026년 해외무역관 지사화 지원사업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경상남도 해외마케팅 사업지원시스템)
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2 지원규모 : 양산시에 본사 또는 STS 둔, 수출 희망하는 중소기업 10개사 내외 (업체별 최대 300만원</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>300만원</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr"/>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>KOTRA 경남지역본부 055-290-0624 / 양산시 기업지원과 055-392-2313</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr"/>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>055-290-0624</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125380</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>[충남] 2026년 해양수산 창업투자지원사업 육성기업 상품홍보 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>충남테크노파크</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>이메일 접수(sj5@ctp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>- 아시아, 러시아, 몽골: 최대 50만 원(1인, 이코노미 기준)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>양식은 공고문 참조 요망, 는 합본이 아닌 항목별로 제출하며, 가 미비할 경우 접수 진행 불가), 기업, 항목 서식, (사업자 보유), 지원신청서1)(1부) 붙임1 필수, 참여확약서(1부) 붙임2 필수</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>충남 해양수산 창업투자지원센터 041-330-0512, 041-957-9602 / sj5@ctp.or.kr, ksy@ctp.or.kr / fax. 041-330-0518</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>ksy@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>041-330-0512</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125379</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>[울산] 2026년 일자리창출 우수 강소기업 선정사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>울산경제일자리진흥원</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>이메일 접수 (yunman2000@ubpi.or.kr)</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>&lt; ▪ 금융기관과 정상적인 거래를 할 수 없는 기업  ▪ 공고일 현재 국세 및 지방세 체납 기업  ▪ 임금체불기업, 민원야기, 환경오염, 불법공장 등 사회적 물의를 일으킨 기업  ▪ 최근 2년간 2회 이상 근로기준법 위반으로 300만원 이상 벌금 또는 과태료를 부과 받은 기업  ▪ 도박성 게임, 유흥 등 사행성 불건전 소비 업종의 기업  ▪ 관련 회사의 인수·합병·통폐합으로 인해 근로자 수 증가가 발생한 기업 &gt;</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>300만원</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr"/>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>울산경제일자리진흥원 일자리지원부 고용개선팀 052-283-7192, yunman2000@ubpi.or.kr</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>yunman2000@ubpi.or.kr</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>052-283-7192</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125378</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026년 8차 미래환경산업육성융자(온실가스배출저감설비자금) 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>한국환경산업기술원</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>온라인 접수 (환경기술산업 원스톱 서비스)
+※ 우편 접수(서면) 및 이메일 접수 불가</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>○ (융자규모) 819억 원</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>819억원</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr"/>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>한국환경산업기술원 기업육성실 032-540-2220 / (시스템 문의(회원가입, 로그인 등) 02-2284-1486</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr"/>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>02-2284-1486</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125377</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026년 제1회 평창 그린바이오인의 밤 연계 그린바이오 연구협력 아이디어 발굴 모집 공고</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>강원테크노파크</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>이메일 접수 (kji@gwtp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t> 지원규모 우수 연구협력 아이디어 건 이내 총 지원규모 만원 이내</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>필수 연구협력 아이디어 제안서 부 정보활용 동의서 부,  신청양식 평창군청 강원 홈페이지, 모집공고 첨부파일 참조,  접수처, 기관명 담당자명 이메일 전화번호 문의, 접수 및 사업, 문의, 추진 일정</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>강원테크노파크 033-435-8472, kji@gwtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>kji@gwtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>033-435-8472</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125376</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 광주권역 사회적경제기업 해외수출 지원사업 참여기업 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>광주사회적경제지원센터</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>이메일 접수 (gjsec_m@gjsec.kr)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>지원 300만원</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>300만원</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>② 신청기업 현황 [서식 2] 1부, ③ 신청기업 수요 상세기술서 [서식 3] 1부, ④ 개인정보 제공 및 이용 동의서 [서식 4] 1부, ⑤ 사회적경제기업 증빙서류(지정서, 인증서, 선정서 등) 1부, ⑦ 기업명의 통장사본 1부, ⑧ 전년도 수출실적 증빙자료(해당시) 각 1부</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>광주사회적경제지원센터 기업성장팀 062-531-6667, 내선2</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>gjsec_m@gjsec.kr</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>062-531-6667</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125375</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 중소기업 정부기술개발 공모사업 선정 지원사업 차년도 R&amp;D 컨설팅 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>경북테크노파크</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>온라인 접수(경북테크노파크)
+※신청서 및 서류 제출 후 반드시 담당자(053-819-3067)에게 접수여부 확인 必</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>□ 지원규모 : 15개사 내외 (기업당 최대 450만원)</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>450만원</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>15개</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr"/>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>경북테크노파크 기업지원단 기술사업화지원실 053-819-3067, 3062 / youngumm@gbtp.or.kr, lani@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>lani@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>053-819-3067</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125374</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>[경북] 상주시 2026년 하반기 중소기업 맞춤형 인재양성 지원사업  참여기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>경북테크노파크</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>온라인 접수(경북테크노파크)</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>- (지원규모) 4개사 내외, 기업당 최대 1000만원(부가세 포함)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>1000만원</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>4개</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>에 허위사실을 기재하거나 증빙자료를 조작한, 선정 취소 또는 지원금 환수 등의 제재를 취할 수 있음, ◦ 지원내용, 다양한 프로그램을 이수할 수 있는 교육 바우처 지급, (지원규모) 4개사 내외, 기업당 최대 1, 만원(부가세 포함), 바우처 지급</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>경북테크노파크 기업지원단 기업육성지원실 053-819-3053, kjs8768@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>kjs8768@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>053-819-3053</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125373</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026년 2차 대전 AI 영상콘텐츠 제작 지원사업(미디어파사드) 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>대전정보문화산업진흥원</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>온라인 접수 (e나라도움)</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>30000000원 30000000×10÷90 3400000원</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>30000000원</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>첨부 저장 완료 후 [신청서 제출] 탭의, [신청서 제출] 버튼을 눌러야 접수 완료됨, 제출, 서류 미비 시, 심사 제외, 필수, ※ 서류 제출 요령, 의 각 파일명을 ‘순서.</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>대전정보문화산업진흥원 콘텐츠기반사업단 영상산업육성팀 042-259-8605 / e나라도움 사용자 지원센터 1670-9595</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr"/>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>042-259-8605</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125372</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>[경기] 동두천시 2027년 기업환경 개선사업 접수 공고</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2026-08-07 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 동두천시 중앙로 268, 동두천어울림센터 5층 (동두천시 일자리경제과 기업지원팀)</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>공사비 15백만원(VAT제외) 이상 공사는 건축공사업 또는 해당 공종 전문건설업 등록</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>15백만원</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>사업계획서(자부담 확약서, 시설물 유지동의서 포함), 고용보험 가입자명부(고용인원 확인용), 국세 및 지방세 완납증명원, v 아래의 경우, 해당되는 경우에 한하여 제출, 공장등록 증명서(공장건축면적 500㎡이상), 여성기업 확인서(여성기업)</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>동두천시청 일자리경제과 기업지원팀 031-860-2281</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr"/>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>031-860-2281</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125371</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026년 한-독(2+2) 국제공동기술개발사업 공고</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>한국산업기술진흥원</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-11-04</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>온라인 접수(k-pass)</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>&lt;독일&gt;&lt;5억원 이내/년, 최대 15억원 이내&gt;&lt;3년 이내&gt;&lt;기업 + 대학/연구기관 형태로,  2개 이상의 기관으로 구성된 컨소시엄&gt;</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>15억원</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr"/>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>(한국 측) 한국산업기술진흥원 국제협력사업실 02-6009-3774, cih@kiat.or.kr (독일 측) DLR Projektträger c.lange@dlr.de, +49-228-38-21-1423 (온라인접수(K-PASS) 관련 문의) 한국산업기술진흥원 통합유지보수 02-6009-4319, 4320, 4321</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>c.lange@dlr.de</t>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>02-6009-3774</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125370</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>[경기] 2026년 4차 글로벌IP스타기업육성 특허기술 홍보영상제작 사업 공고</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>경기지식재산센터</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-19</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>온라인 접수 (RIPC 온라인 사업신청)</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>ㅁ 지원내용</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr"/>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>경기지식재산센터 (안산) 031-500-3046, 3041, 3047, 3032 (판교) 031-8016-9203 (용인) 031-321-0170 (세부지원사업 문의) 1661-1900</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr"/>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>031-321-0170</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125369</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>민관협력 오픈이노베이션 지원 공공데이터 활용 지원 공공기관 제안 협업 과제 (Top-Down) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>서울창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>온라인 접수 (K-Startup)</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>(과제별 최대 1억원)</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>1억원</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>필수, 자료 미제출 시 평가 대상에서 제외될 수 있음, 과제 신청 :, K-Startup 누리집, 온라인 신청, 온라인 사업 신청 관련 자세한 사항은 ‘, [별첨] 사업 신청 매뉴얼, ’ 참고</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>(사업 문의) 창업진흥원 민관협력실 044-410-1720, 1767, 1768, 1764 중소벤처기업부 신산업기술창업과 044-204-7643 (시스템 문의) 중소기업통합콜센터 국번없이 1357</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr"/>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>044-204-7643</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125368</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>민관협력 오픈이노베이션 지원 공공데이터 활용 지원 창업기업 제안 협업 과제 (Bottom-Up) 모집공고</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>서울창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>온라인 접수 (K-Startup)</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>사업비는 최대 1억원 이내로 작성</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>1억원</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>접수 방법-, 참고, 모집 개요, 사업목적 :, 모집대상 :, 공고일 기준으로「중소기업창업 지원법」의 창업에 해당, 하는, 기업으로 공고문 내 신청자격 및 요건을 충족하는 기업</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>(사업 문의) 서울창조경제혁신센터 02-739-7328, 7329, 9796 (시스템 문의) 중소기업통합콜센터 국번없이 1357</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr"/>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t>02-739-7328</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125367</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>[경기] 2026년 4차 글로벌IP스타기업육성 기업 IP경영 진단구축 사업 공고</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>경기지식재산센터</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-19</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>온라인 접수 (RIPC 온라인 사업신청)</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>ㅁ 지원내용</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr"/>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>경기지식재산센터 (안산) 031-500-3046, 3041, 3047, 3032 (판교) 031-8016-9203 (용인) 031-321-0170</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr"/>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>031-321-0170</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125366</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026년 하반기 온라인 K-SEAFOOD 판매 전용관 운영 사업 입점 제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>한국수산회</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2026-07-13 ~ 2026-10-30</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>온라인 접수(온라인 사업신청 통합시스템)</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>*** 최초 매입은 기업당 최대 100만 원까지 지원하며, 판매 실적이 우수한 제품은</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>제출, 문의처, 가. (사)한국수산회 수출기획마케팅팀 설재웅 대리, 나. (사)한국수산회 수출기획마케팅팀 정세호 주임</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>한국수산회 수출기획마케팅팀 02-898-0571, 0566 / sjw@kfish.kr, hdf1405@kfish.kr</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>hdf1405@kfish.kr</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>02-898-0571</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125365</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>[경기] 2026년 4차 글로벌IP스타기업육성 특허맵(해외) 사업 공고</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>경기지식재산센터</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-19</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>온라인 접수 (RIPC 온라인 사업신청)</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>ㅁ 지원내용</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr"/>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>경기지식재산센터 (안산) 031-500-3046, 3041, 3047, 3032 / (판교) 031-8016-9203 / (용인) 031-321-0170</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr"/>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>031-321-0170</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125364</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 4차 지식재산 긴급지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>전남지식재산센터</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>온라인 접수 (지역지식재산센터 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>o 기업 당 2000만원 이내(지원금 합산 기준, 자부담 제외)</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>2000만원</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>신청서‧사업추진(활용)계획서 및 필수(선택), 지원절차, 지원규모, o 기업 당 2, 만원 이내(지원금 합산 기준, 자부담 제외), 기업분담금, o 기업분단금 : 40%(현금40%)</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>지역지식재산센터 대표전화 1661-1900 전남지식재산센터 061-242-8587</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr"/>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>061-242-8587</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125363</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>제11회 소상공인 쇼케이스데이 발표 참가기업 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>중소상공인희망재단</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2026-07-13 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>온라인 접수 (중소상공인희망재단 홈페이지)</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>▪ 결선 우수기업 대상 사업화지원금 지급(총 3개사, 1000만원)</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>1000만원</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>바탕으로 세부 항목평가 및 발표평가 대상자 확정, 증빙제출 불필요), ③ 발표평가 : 발표 및 질의응답을 통해 제품경쟁력, 사업성 등을 심층 평가, 발표평가는 대면평가로 진행되며, 대표자 직접 발표 필수, 평가지표, ◦ 제품경쟁력</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>중소상공인희망재단 코업성장사업부 070-4458-2325, sh14@heemangfdn.or.kr</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>sh14@heemangfdn.or.kr</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>070-4458-2325</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125362</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026년 3분기 국내 활ㆍ신선 수조 보관 지원업체 모집 공고</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>한국수산무역협회</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>온라인 접수(온라인 사업신청 통합시스템)</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>(최대 11개월)  /  지원한도 : 업체당 65백만원&gt;</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>65백만원</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>11개</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr"/>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>한국수산무역협회 수출지원부 02-6300-8705, 8702 / kfta@kfta.net</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>kfta@kfta.net</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>02-6300-8705</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125361</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>[경기] 수원시 2026년 3차 지식재산 긴급지원(중소기업IP바로 지원) 사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>경기지식재산센터</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>온라인 접수 (지원사업 신청시스템)</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>o 기업 당 2000만원 이내(지원금 합산 기준, 자부담 제외)</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2000만원</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>신청서‧사업추진(활용)계획서 및 필수(선택), 지원절차, 지원규모, o 기업 당 2, 만원 이내(지원금 합산 기준, 자부담 제외), 기업분담금, o 기업분단금 : 40%(현금20%+현물20%)</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>경기남부지식재산센터 031-8000-9455, 031-244-8321</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr"/>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>031-244-8321</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125360</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026년 민관협력 오픈이노베이션 지원 성과기업 후속 지원 창업기업 모집 수정 공고</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>창업진흥원</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>온라인 접수 (K-Startup누리집)</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>□ 지원내용 : 창업기업 대상 사업화 자금(최대 2억원) 및 후속 연계 지원</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2억원</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>중 일부를 별도로 발급받지 않아도, 자동 연동하여 제출 가능합니다. * 4. 접수 방법-, 참고, 모집 개요, 창업기업의 지속 성장을 위해 PoV 등 후속 협업 지원, 공고문 내 신청자격 및 요건을 충족하는 기업, 선정규모 : 창업기업 80개사 내외, 모집유형 : ➊ 성과 우수형</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>(사업문의) 창업진흥원 민관협력실 044-410-1720, 1767, 1764 / (시스템문의) 중소기업통합콜센터 국번없이 1357</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr"/>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>044-410-1720</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125359</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>[경기] 안산시 2026년 수산식품 가공설비 지원사업 사업자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 안산시 대부해양본부 해양수산과(단원구 돈지섬1길 10)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>(5천만원이상)</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>5천만원</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>원가계산서, 규격·사양서, 수입물품원가계산서(수입물품의 경우) 등) 1부, ㅇ 임대차 관련 분쟁금지 확약서, 가공설비 지원사업 동의서 및 개인정보 수집 및, 이용동의서, 보조금 관련 법률 준수 서약서, 무역통계정보 제공 동의서 1부.</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>안산시 대부해양본부 해양수산과 031-481-3954</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr"/>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>031-481-3954</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125358</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>[부산] 2026년 식품ㆍ화장품 중국 안심수출 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>한국화학융합시험연구원</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2026-03-20 ~ 2026-12-31</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>이메일 접수(busan@busan-sh.com)</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>관련문의, 상해무역사무소 ☎., 중국지부 IP☎, 부산광역시 상해무역사무소</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>(상해무역사무소) 070-7077-6033, +86-21-6362-0018 / busan@busan-sh.com (한국화학융합시험연구원) 02-507-8078, shfood@ktr.co.kr</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>busan@busan-sh.com</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>02-507-8078</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125357</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>[부산] 2026년 수출원스톱센터 수출애로 컨설팅 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>부산경제진흥원</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2026-04-22 ~ 2026-12-31</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>온라인 접수(부산수출플랫폼)</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr"/>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>부산경제진흥원 글로벌사업추진단 051-600-1827, bri0324@bepa.kr</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>bri0324@bepa.kr</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>051-600-1827</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125356</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>[경기] 성남시 2026년 고용우수기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-14</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>이메일 접수(sh110061@korea.kr)</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>❍ 선정규모: 고용우수기업 30개사 내외</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>30개</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>❍ 고용우수기업 인증신청서 1부, ❍ 고용우수기업 평가세부내역 1부, ❍ 선정(심사) 배제대상 비대상 확인 확약서 1부, ❍ 중소기업확인서 1부, 공장등록증 사본(해당기업) 각 1부, ❍ 기업 신용평가서 1부, ❍ 최근 1년간 고용증가인원 및 고용증가율 증빙자료, 고용보험(사업장) 자격취득자 명부 제출</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>성남시 고용과 고용정책팀 031-729-8543</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>sh110061@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>031-729-8543</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125355</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 하반기 기업 직접물류비 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2026-10-01 ~ 2026-10-09</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>온라인 접수(대전일자리경제진흥원)</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>❍ 물류비 합산비용의 50%, 기업당 최대 200만원 한도 지원(VAT제외)</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>200만원</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr"/>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원 기업통상지원팀 042-380-3046, 1004@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>1004@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>042-380-3046</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125354</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026년 디지털콘텐츠 융합기업 글로벌 마켓 참가 사업(XR Fair Tokyo Autumn 2026) 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>정보통신산업진흥원</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-09-08</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>온라인 접수 (우리원 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>사업개요 및 지원내용</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>및 신청자격 사업추진을 위한, 등을 평가하여 우선 지원, 검토를 통한 평가대상 확정 협약체결, 대상 기업 선정, ※ 세부내용은 공고안내문 ‘평가절차 및 기준’ 등 참조, ■ 주요 추진일정, 프로그램 결과보고 및, 사업공고 선정평가 협약체결</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>(사업내용 문의) 정보통신산업진흥원 글로벌성장팀 043-931-5593, hsim@nipa.kr (전산접수 문의) 스마트시스템 유지보수팀 070-5151-8239, 8215 / smart@nipa.kr</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>hsim@nipa.kr</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>043-931-5593</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125353</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF254"/>
+  <dimension ref="A1:AF306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31862,7 +31862,6 @@
           <t>7억원</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
           <t>Y</t>
@@ -32020,7 +32019,6 @@
           <t>40만원</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
           <t>Y</t>
@@ -32180,7 +32178,6 @@
           <t>36만원</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
           <t>Y</t>
@@ -32334,8 +32331,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
           <t>Y</t>
@@ -32441,7 +32436,6 @@
           <t>광주시 기업지원과 031-760-3787</t>
         </is>
       </c>
-      <c r="AC208" t="inlineStr"/>
       <c r="AD208" t="inlineStr">
         <is>
           <t>031-760-3787</t>
@@ -32591,13 +32585,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA209" t="inlineStr"/>
       <c r="AB209" t="inlineStr">
         <is>
           <t>김포산업지원센터 기업육성팀 031-981-1329</t>
         </is>
       </c>
-      <c r="AC209" t="inlineStr"/>
       <c r="AD209" t="inlineStr">
         <is>
           <t>031-981-1329</t>
@@ -32640,7 +32632,6 @@
           <t>10개 기업 선정</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
           <t>10개</t>
@@ -32751,7 +32742,6 @@
           <t>용인시 기업지원과 기업지원팀 031-6193-2856</t>
         </is>
       </c>
-      <c r="AC210" t="inlineStr"/>
       <c r="AD210" t="inlineStr">
         <is>
           <t>031-6193-2856</t>
@@ -32958,8 +32948,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
           <t>N</t>
@@ -33055,7 +33043,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA212" t="inlineStr"/>
       <c r="AB212" t="inlineStr">
         <is>
           <t>경상북도경제진흥원 마케팅팀 054-470-8577, 8572</t>
@@ -33115,7 +33102,6 @@
           <t>2천만원</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
           <t>Y</t>
@@ -33221,7 +33207,6 @@
           <t>용인시청 기업지원과 031-6193-2286</t>
         </is>
       </c>
-      <c r="AC213" t="inlineStr"/>
       <c r="AD213" t="inlineStr">
         <is>
           <t>031-6193-2286</t>
@@ -33266,7 +33251,6 @@
           <t>❍ 지원규모 : 메가쇼 프리미엄 부스 지원(10개사 내외)</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
           <t>10개</t>
@@ -33429,7 +33413,6 @@
           <t>5천만원</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
         <is>
           <t>Y</t>
@@ -33588,7 +33571,6 @@
           <t>3원</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
           <t>N</t>
@@ -33694,7 +33676,6 @@
           <t>목포시청 수산산업과 어업지원팀 061-270-3411</t>
         </is>
       </c>
-      <c r="AC216" t="inlineStr"/>
       <c r="AD216" t="inlineStr">
         <is>
           <t>061-270-3411</t>
@@ -33744,7 +33725,6 @@
           <t>300만원</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
           <t>Y</t>
@@ -33902,7 +33882,6 @@
           <t>50만원</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
           <t>N</t>
@@ -33998,13 +33977,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA218" t="inlineStr"/>
       <c r="AB218" t="inlineStr">
         <is>
           <t>충청북도기업진흥원 농식품유통본부 043-270-0214</t>
         </is>
       </c>
-      <c r="AC218" t="inlineStr"/>
       <c r="AD218" t="inlineStr">
         <is>
           <t>043-270-0214</t>
@@ -34047,7 +34024,6 @@
           <t> 모집규모 : 파트너사별 상이 (파트너사당 4 ~ 8개사 내외)</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
           <t>8개</t>
@@ -34148,7 +34124,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA219" t="inlineStr"/>
       <c r="AB219" t="inlineStr">
         <is>
           <t>부산창조경제혁신센터 글로벌 오픈이노베이션팀 051-749-8931, ymlee1106@ccei.kr</t>
@@ -34207,7 +34182,6 @@
           <t>300만원</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr">
         <is>
           <t>Y</t>
@@ -34313,7 +34287,6 @@
           <t>시흥시 소상공인과 031-310-2609</t>
         </is>
       </c>
-      <c r="AC220" t="inlineStr"/>
       <c r="AD220" t="inlineStr">
         <is>
           <t>031-310-2609</t>
@@ -34356,8 +34329,6 @@
           <t>○ 지원내용</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr">
         <is>
           <t>Y</t>
@@ -34515,7 +34486,6 @@
           <t>110만원</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr">
         <is>
           <t>Y</t>
@@ -34611,7 +34581,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA222" t="inlineStr"/>
       <c r="AB222" t="inlineStr">
         <is>
           <t>대구ㆍ경북지방중소벤처기업청 성장지원과 053-659-2237</t>
@@ -34664,8 +34633,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr">
         <is>
           <t>N</t>
@@ -34761,7 +34728,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA223" t="inlineStr"/>
       <c r="AB223" t="inlineStr">
         <is>
           <t>시흥산업진흥원 바이오산업실 070-4265-1526, jhkim@sida.kr</t>
@@ -34983,7 +34949,6 @@
           <t>5백만원</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr">
         <is>
           <t>Y</t>
@@ -35141,7 +35106,6 @@
           <t>3백만원</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr">
         <is>
           <t>Y</t>
@@ -35247,7 +35211,6 @@
           <t>고양시 일자리정책과 노사협력팀 031-8075-3563</t>
         </is>
       </c>
-      <c r="AC226" t="inlineStr"/>
       <c r="AD226" t="inlineStr">
         <is>
           <t>031-8075-3563</t>
@@ -35396,13 +35359,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA227" t="inlineStr"/>
       <c r="AB227" t="inlineStr">
         <is>
           <t>KOTRA 경남지역본부 055-290-0624 / 양산시 기업지원과 055-392-2313</t>
         </is>
       </c>
-      <c r="AC227" t="inlineStr"/>
       <c r="AD227" t="inlineStr">
         <is>
           <t>055-290-0624</t>
@@ -35450,7 +35411,6 @@
           <t>50만원</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
         <is>
           <t>Y</t>
@@ -35608,7 +35568,6 @@
           <t>300만원</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
         <is>
           <t>N</t>
@@ -35704,7 +35663,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA229" t="inlineStr"/>
       <c r="AB229" t="inlineStr">
         <is>
           <t>울산경제일자리진흥원 일자리지원부 고용개선팀 052-283-7192, yunman2000@ubpi.or.kr</t>
@@ -35763,7 +35721,6 @@
           <t>819억원</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
           <t>N</t>
@@ -35859,13 +35816,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA230" t="inlineStr"/>
       <c r="AB230" t="inlineStr">
         <is>
           <t>한국환경산업기술원 기업육성실 032-540-2220 / (시스템 문의(회원가입, 로그인 등) 02-2284-1486</t>
         </is>
       </c>
-      <c r="AC230" t="inlineStr"/>
       <c r="AD230" t="inlineStr">
         <is>
           <t>02-2284-1486</t>
@@ -35908,8 +35863,6 @@
           <t> 지원규모 우수 연구협력 아이디어 건 이내 총 지원규모 만원 이내</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr">
         <is>
           <t>N</t>
@@ -36067,7 +36020,6 @@
           <t>300만원</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr">
         <is>
           <t>Y</t>
@@ -36326,7 +36278,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA233" t="inlineStr"/>
       <c r="AB233" t="inlineStr">
         <is>
           <t>경북테크노파크 기업지원단 기술사업화지원실 053-819-3067, 3062 / youngumm@gbtp.or.kr, lani@gbtp.or.kr</t>
@@ -36546,7 +36497,6 @@
           <t>30000000원</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr">
         <is>
           <t>Y</t>
@@ -36652,7 +36602,6 @@
           <t>대전정보문화산업진흥원 콘텐츠기반사업단 영상산업육성팀 042-259-8605 / e나라도움 사용자 지원센터 1670-9595</t>
         </is>
       </c>
-      <c r="AC235" t="inlineStr"/>
       <c r="AD235" t="inlineStr">
         <is>
           <t>042-259-8605</t>
@@ -36701,7 +36650,6 @@
           <t>15백만원</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr">
         <is>
           <t>Y</t>
@@ -36807,7 +36755,6 @@
           <t>동두천시청 일자리경제과 기업지원팀 031-860-2281</t>
         </is>
       </c>
-      <c r="AC236" t="inlineStr"/>
       <c r="AD236" t="inlineStr">
         <is>
           <t>031-860-2281</t>
@@ -36955,7 +36902,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA237" t="inlineStr"/>
       <c r="AB237" t="inlineStr">
         <is>
           <t>(한국 측) 한국산업기술진흥원 국제협력사업실 02-6009-3774, cih@kiat.or.kr (독일 측) DLR Projektträger c.lange@dlr.de, +49-228-38-21-1423 (온라인접수(K-PASS) 관련 문의) 한국산업기술진흥원 통합유지보수 02-6009-4319, 4320, 4321</t>
@@ -37008,8 +36954,6 @@
           <t>ㅁ 지원내용</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr">
         <is>
           <t>N</t>
@@ -37105,13 +37049,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA238" t="inlineStr"/>
       <c r="AB238" t="inlineStr">
         <is>
           <t>경기지식재산센터 (안산) 031-500-3046, 3041, 3047, 3032 (판교) 031-8016-9203 (용인) 031-321-0170 (세부지원사업 문의) 1661-1900</t>
         </is>
       </c>
-      <c r="AC238" t="inlineStr"/>
       <c r="AD238" t="inlineStr">
         <is>
           <t>031-321-0170</t>
@@ -37159,7 +37101,6 @@
           <t>1억원</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr">
         <is>
           <t>Y</t>
@@ -37265,7 +37206,6 @@
           <t>(사업 문의) 창업진흥원 민관협력실 044-410-1720, 1767, 1768, 1764 중소벤처기업부 신산업기술창업과 044-204-7643 (시스템 문의) 중소기업통합콜센터 국번없이 1357</t>
         </is>
       </c>
-      <c r="AC239" t="inlineStr"/>
       <c r="AD239" t="inlineStr">
         <is>
           <t>044-204-7643</t>
@@ -37313,7 +37253,6 @@
           <t>1억원</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr">
         <is>
           <t>Y</t>
@@ -37419,7 +37358,6 @@
           <t>(사업 문의) 서울창조경제혁신센터 02-739-7328, 7329, 9796 (시스템 문의) 중소기업통합콜센터 국번없이 1357</t>
         </is>
       </c>
-      <c r="AC240" t="inlineStr"/>
       <c r="AD240" t="inlineStr">
         <is>
           <t>02-739-7328</t>
@@ -37462,8 +37400,6 @@
           <t>ㅁ 지원내용</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr">
         <is>
           <t>N</t>
@@ -37559,13 +37495,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA241" t="inlineStr"/>
       <c r="AB241" t="inlineStr">
         <is>
           <t>경기지식재산센터 (안산) 031-500-3046, 3041, 3047, 3032 (판교) 031-8016-9203 (용인) 031-321-0170</t>
         </is>
       </c>
-      <c r="AC241" t="inlineStr"/>
       <c r="AD241" t="inlineStr">
         <is>
           <t>031-321-0170</t>
@@ -37613,7 +37547,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr">
         <is>
           <t>N</t>
@@ -37766,8 +37699,6 @@
           <t>ㅁ 지원내용</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr">
         <is>
           <t>N</t>
@@ -37863,13 +37794,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA243" t="inlineStr"/>
       <c r="AB243" t="inlineStr">
         <is>
           <t>경기지식재산센터 (안산) 031-500-3046, 3041, 3047, 3032 / (판교) 031-8016-9203 / (용인) 031-321-0170</t>
         </is>
       </c>
-      <c r="AC243" t="inlineStr"/>
       <c r="AD243" t="inlineStr">
         <is>
           <t>031-321-0170</t>
@@ -37917,7 +37846,6 @@
           <t>2000만원</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr">
         <is>
           <t>N</t>
@@ -38023,7 +37951,6 @@
           <t>지역지식재산센터 대표전화 1661-1900 전남지식재산센터 061-242-8587</t>
         </is>
       </c>
-      <c r="AC244" t="inlineStr"/>
       <c r="AD244" t="inlineStr">
         <is>
           <t>061-242-8587</t>
@@ -38333,7 +38260,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA246" t="inlineStr"/>
       <c r="AB246" t="inlineStr">
         <is>
           <t>한국수산무역협회 수출지원부 02-6300-8705, 8702 / kfta@kfta.net</t>
@@ -38391,7 +38317,6 @@
           <t>2000만원</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr">
         <is>
           <t>N</t>
@@ -38497,7 +38422,6 @@
           <t>경기남부지식재산센터 031-8000-9455, 031-244-8321</t>
         </is>
       </c>
-      <c r="AC247" t="inlineStr"/>
       <c r="AD247" t="inlineStr">
         <is>
           <t>031-244-8321</t>
@@ -38545,7 +38469,6 @@
           <t>2억원</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
           <t>Y</t>
@@ -38651,7 +38574,6 @@
           <t>(사업문의) 창업진흥원 민관협력실 044-410-1720, 1767, 1764 / (시스템문의) 중소기업통합콜센터 국번없이 1357</t>
         </is>
       </c>
-      <c r="AC248" t="inlineStr"/>
       <c r="AD248" t="inlineStr">
         <is>
           <t>044-410-1720</t>
@@ -38700,7 +38622,6 @@
           <t>5천만원</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
           <t>Y</t>
@@ -38806,7 +38727,6 @@
           <t>안산시 대부해양본부 해양수산과 031-481-3954</t>
         </is>
       </c>
-      <c r="AC249" t="inlineStr"/>
       <c r="AD249" t="inlineStr">
         <is>
           <t>031-481-3954</t>
@@ -38849,8 +38769,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
         <is>
           <t>Y</t>
@@ -39003,8 +38921,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
           <t>N</t>
@@ -39100,7 +39016,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA251" t="inlineStr"/>
       <c r="AB251" t="inlineStr">
         <is>
           <t>부산경제진흥원 글로벌사업추진단 051-600-1827, bri0324@bepa.kr</t>
@@ -39153,7 +39068,6 @@
           <t>❍ 선정규모: 고용우수기업 30개사 내외</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
           <t>30개</t>
@@ -39316,7 +39230,6 @@
           <t>200만원</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr">
         <is>
           <t>N</t>
@@ -39412,7 +39325,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA253" t="inlineStr"/>
       <c r="AB253" t="inlineStr">
         <is>
           <t>대전일자리경제진흥원 기업통상지원팀 042-380-3046, 1004@djbea.or.kr</t>
@@ -39465,8 +39377,6 @@
           <t>사업개요 및 지원내용</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr">
         <is>
           <t>N</t>
@@ -39590,6 +39500,8082 @@
       <c r="AF254" t="inlineStr">
         <is>
           <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125353</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>[충남] 금산군 2026년 미국 소비촉진 사업 참가기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>충남경제진흥원</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>온라인 접수(충남경제진흥원 통합지원시스템)</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 10개사 내외</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>구분, · (서식1)참가신청서, (서식2)품목설명서, (서식3)참가각서, (서식4)개인(신용)정보활용 · 중소기업, 지원사업 통합관리시스템 정보활용 동의서, (서식5)무역통계시스템 데이터 활용 동의서, ※ 공장등록증을 대체하여 제출 가능한 경우</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>충남경제진흥원 해외진출팀 041-404-1366, 1361 / sggwak@cepa.or.kr, shkim@cepa.or.kr</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>sggwak@cepa.or.kr</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>041-404-1366</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125456</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026년 우수인재 연계 기업인턴십 참여기업 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>한국콘텐츠진흥원</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-11-06</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>이메일 접수(startup@kocca.kr)</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr"/>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>한국콘텐츠진흥원 기업육성팀 061-900-6382, psj@kocca.kr</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>psj@kocca.kr</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>061-900-6382</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125455</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 R&amp;D 기반 혁신 실증스튜디오 운영사업 AIDX 스케일업 성장 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>광주정보문화산업진흥원</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>온라인 접수(e나라도움)</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>m 지원규모 : 약 3~4개사(지원규모에 따라 변동)</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>4개</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>의 내용이 허위이거나 사실과 다른 경우, 상시 점검하며, 지원내용 및 범위, m 기업당 최대 18, 천원 사업화 자금, 스케일업 프로그램 지원, 지원항목 지원내용, ·시제품·양산품제작비</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>광주정보문화산업진흥원 전략사업TF팀 062-610-2987, him2000@gicon.or.kr</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>him2000@gicon.or.kr</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>062-610-2987</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125454</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 패션뷰인대구 디지털마케팅 지원 D-Fashion Brand Content Lab 참가 디자이너 및 패션업체 모집 공고</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>대구경북패션사업협동조합</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>이메일 접수(jini83@fcdg.org)</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>참가비 200만원 VAT 미포함</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>200만원</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>신청서식1, 은 반드시 법인 도장 또는 개인 인감으로 제출, 세부내용 비고, 참가신청서 [신청서식 1] 작성, 시즌 기획(안) [신청서식 2] 작성, 개인정보수집·이용, [신청서식 3] 작성, 제3자 제공 동의서</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>대구경북패션사업협동조합 사무국 053-382-1211, 070-4680-1397 / jini83@fcdg.org</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>jini83@fcdg.org</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>053-382-1211</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125453</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>[충남] 아산시 2026년 2차 로컬푸드 직매장 포장재 지원 사업 공고</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>방문, 이메일 접수
+- 접수처 : 우 31512, 충청남도 아산시 염치읍 염성길 70-30, 아산시농업기술센터 농식품유통과 도농교류팀
+- 이메일 : rlacodms76@korea.kr</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>지원규모 : ￦20088200원(금이천팔만팔천이백원)</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>20088200원</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>사업신청서, 사업계획서 외 붙임 서류, 다운받을 수 있습니다., 심의기준 및 결과통보, 심의기관 : 아산시 지방보조금관리위원회, 심의기준 : 지방보조금 지원의 필요성, 타당성, 적법성 등 종합 고려</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>충청남도 아산시 농업기술센터 농식품유통과 041-537-3931</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr"/>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>041-537-3931</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125452</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>[경북] 칠곡군 2026년 소상공인 카드수수료 지원사업 참여점포 모집 변경 공고</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>온라인 접수 및 방문 접수
+- 온라인 : 행복카드.kr
+- 접수처
+ㆍ읍, 면, 동 행정복지센터
+ㆍ 경상북도경제진흥원 4층 민생경제지원팀(구미시 이계북로 7)
+ㆍ 칠곡군 소상공인연합회(칠곡군 왜관읍 석전로 157-2)</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>2025년 매출액 1억원 이하 업체 2025년 매출액 3억원 이하 업체</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>3억원</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>온라인 접수 시 방문 접수 시, 심사 및 선정, ㅇ 사업 신청 접수순으로 심사, 미비 시 접수순서는 유지하되, 보완 완료 후 심사 가능, ※ 서류 보완 안내 개인 연락처로 안내되오니, 연락처 정확히 기재 바랍니다, ㅇ 국세청 세무신고 여부</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 민생경제지원팀 1800-8730 / 칠곡군 소상공인연합회 문의처 출처 바로가기 내 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr"/>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>00000000000</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125451</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 2차 AX기업혁신센터 공동연구센터 시제품제작지원 사업 공고(지역혁신중심 대학지원체계(RISE))</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>건국대학교</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>온라인 접수 (지역산업진흥원 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>□ 지원규모 : 총 10백만원*</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>10백만원</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>를 제출하지 않거나, 제출양식을 준수하지 않은 경우, 기술료 납부, 정산금·환수금·제재부가금 납부 등 의무사항을 불이행, 하고 있는 경우, 해당 과제 대학, 연구책임자 및 참여기업은 참여 1년 제한. 단, 참여기업은 기술이전 완료</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>건국대학교 RISE사업단 RISE사업단 043-840-4914, sim1023@kku.ac.kr / 충북대학교 RISE사업단 지산학협력부 043-249-1279, hsi0788@cbnu.ac.kr</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>hsi0788@cbnu.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>043-249-1279</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125450</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>[경북] 김천시 2026년 소상공인 카드수수료 지원사업 참여점포 모집 변경 공고</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>온라인 접수 및 방문 접수
+- 온라인 : 행복카드.kr
+- 접수처
+ㆍ읍, 면, 동 행정복지센터
+ㆍ 경상북도경제진흥원 4층 민생경제지원팀(구미시 이계북로 7)
+ㆍ 경상북도소상공인연합회(경주시 동천로 24, 2층)</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>(지원내용) '25년도 카드 매출액의 04% 지원 (40만원 한도 내 지급</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>40만원</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>미비 시 점수, ※ 서류 보완 안내 개인, ㅇ 국세청 세무신고 여부, 카드 매출금액 등 확인(국세청 자료 기준), ㅇ 지원대상에 부합하고, 지원 제외 사유가 없을 시 선정, O 지원금 지급, 신청 과다로</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 민생경제지원팀 1800-8730 / 경상북도소상공인연합회 054-772-7008</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr"/>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>054-772-7008</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125449</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 시제품 제작 지원 참여기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>온라인 접수 (대전일자리경제진흥원 홈페이지)</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>□ 지원금액 : 기업당 최대 10000000원 이내※ 부가가치세는 지원금에서 제외하며 선정기업이 부담</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>10000000원</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>&lt;연번&gt;&lt;, &gt;&lt;발급기관&gt;&lt;비고&gt;, &lt;1&gt;&lt;&lt;양식1&gt; 참가신청서 1부&gt;&lt;&gt;&lt;필수&gt;, &lt;2&gt;&lt;&lt;양식2&gt; 사업계획서 1부&gt;&lt;&gt;, &lt;4&gt;&lt;&lt;양식4&gt; 확약서 1부&gt;&lt;&gt;, &lt;5&gt;&lt;지원기업, 제작기업 &gt;</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원 사회적경제지원팀 042-632-3735, yedalm12@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>yedalm12@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>042-632-3735</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125448</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 2차 푸드테크 이노베이션 공동연구센터 시제품제작지원 사업 공고(지역혁신중심 대학지원체계(RISE))</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>건국대학교</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>온라인 접수 (지역산업진흥원 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>□ 지원규모 : 총 30백만원*</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>30백만원</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>를 제출하지 않거나, 제출양식을 준수하지 않은 경우, 기술료 납부, 고 있는 경우, 주관대학, 특히, '기술이전'이 필수 성과인 대학 유형의 경우, 기한 내 기술이전 미</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>건국대학교 RISE사업단 푸드테크 이노베이션센터 043-840-4914, sim1023@kku.ac.kr 외 문의처 공고문 10p 참조 ※ 대원대학교 RISE사업단 문의처 출처바로가기 내 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>sim1023@kku.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>043-840-4914</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125447</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026년 2차 어린이제품 관련 영세기업 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>한국제품안전관리원</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>온라인 접수 (네이버 폼)</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>지원한도 150만원 100만원</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>150만원</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>연번 6 참조), 있는 자료 제출 필요(, ※ 잔여비용 이월 불가(사용기간: 선정일로부터 8주), ※ 지원금은 공급가액 기준으로 산정하며, 부가가치세(VAT) 등 세금성 비용 및 지원한도, 초과분은 기업 부담, ※ 지원비용 미사용 제재 안내 (신청 전 필독), 신청 및 선정 방법</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>한국제품안전관리원 제품안전지원실 070-5223-1388, kids@kips.kr</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>kids@kips.kr</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>070-5223-1388</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125446</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>[전남광주] 중국 현지 홍보부스 참여 농업경영체 모집 공고(전남광주통합특별시농업기술원 기술개발 우수 농식품)</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>전남광주통합특별시농업기술원</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>방문 또는 이메일 접수
+- 접수처 : 전남광주통합특별시 나주 산포면 세남로 1508, 3층 자원경영과
+- 이메일 : kmj1122@korea.kr</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>참가자 국외여비 1인당 200만원 정액 지급</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>200만원</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>를 제출하지 않은 경영체, 현지 일정에 참가할 수 없는 경영체, 신청안내, 가. 접수방법: 방문 또는 전자우편 신청, 주 소: 전남광주통합특별시 나주 산포면 세남로 1508, 층 자원경영과, 이메일: kmj1122@korea.kr, 나.</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>전남광주통합특별시농업기술원 자원경영과 061–330–2593</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>kmj1122@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD266" t="inlineStr"/>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125445</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>[강원ㆍ충청권] 2026년 5차 중소기업 R&amp;D 전담은행 투자지원 프로그램 신청기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>중소기업기술정보진흥원</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>온라인 접수 (중소기업 기술개발사업 종합관리시스템)</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>□ 지원 내용</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr"/>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>중소기업기술정보진흥원 성과확산실 044-300-0716</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr"/>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>044-300-0716</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125444</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 하반기 해외 전시박람회 단체참가 업체 모집 공고</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>이메일 접수(gepa2622@naver.com)</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 6개사 내외</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>6개</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr"/>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단 일자리경제실 062-956-2639</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr"/>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>062-956-2639</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125443</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 2차 지능형 시스템 반도체 공동연구센터 시제품제작지원 사업 공고(지역혁신중심 대학지원체계(RISE))</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>충북대학교</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>온라인 접수 (지역산업진흥원 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>□ 지원규모 : 총 30백만원</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>30백만원</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>를 제출하지 않거나, 제출양식을 준수하지 않은 경우, 기술료 납부, 정산금·환수금·제재부과금 납부 등 의무사항을 불이행, 하고 있는 경우, 해당 과제 대학, 연구책임자 및 참여기업은 참여 1년 제한. 단, 참여기업은 기술이전 완료</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>충북대학교 RISE사업단 지산학연협력부 043-249-1279, hsi0788@cbnu.ac.kr / 청주대학교 RISE사업단 dn330@cju.ac.kr ※ 청주대학교 RISE사업단 연락처 출처바로가기 내 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>dn330@cju.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>043-249-1279</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125442</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 일본 오사카 국제 로봇 전시회(RoboNext)  참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>대전테크노파크</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>온라인 접수 (대전기업정보포털)</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>2 지원내용</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>일체 온라인 접수, 해당내용 입력 è, 첨부 후 등록완료 è신청완료, ㅇ 주의사항, 순번, 양식제공 비고, 참가 신청서 [서식 제1호], 신청자격 적정성 확인서 [서식 제3호]</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>국방ㆍ로봇ㆍ첨단제조센터 042-930-4458, alsgur@djtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>alsgur@djtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>042-930-4458</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125441</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 지역특화형(고도화) 스마트공장 구축사업 공고</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>경북테크노파크</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>온라인 접수(스마트공장 사업관리 시스템)</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>5억원 내에서 2회(1회차고도화→2회차동일수준)까지 지원하되, 회당 최대 2억원 한도, 지원비율 50% 이내에서 지원가능</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>5억원</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr"/>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>(신청ㆍ접수, 사업계획서 작성, 선정평가, 유의사항 등 문의) 경북테크노파크 AI제조혁신실 053-819-7032, 7035 (사업기획 문의) 국번없이 1357 (사업시행 관련 문의) 044-300-0955</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr"/>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>044-300-0955</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125440</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>[충남] 2026년 제2회 유망기업 사업화경진대회 참가기업 모집 재공고(충남스타기업 CEO포럼)</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>충남테크노파크</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>우편 또는 방문 접수
+- 접수처 : (31035) 충남 천안시 서북구 직산읍 직산로 136 충남테크노파크 종합지원관 1201호 충남테크노파크 기업지원본부 사업화지원실
+※ 제출 완료후 최종본 이메일 제출</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>자격요건 및 지원내용&gt;&lt;&gt;</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr"/>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>충남테크노파크 기업지원본부 사업화지원실 041-589-0634, 041-589-0641 / fangse@ctp.or.kr, jepark@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>fangse@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>041-589-0634</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125439</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>[울산] 2026년 4차 울산 지역기업 성장사다리 지원사업 지원 연장 공고</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>울산테크노파크</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2026-07-24 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>온라인 접수(기업지원사업 관리시스템)
+※ 지원기업 선정 후 직접지원(주관기관 → 지원기업) 또는 간접지원(주관기관 → 공급기관(업) → 지원기업)의 방법으로 지원
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>※ 예) 총 사업비(공급가액) 1100만원 = 정부지원금(1000만원)+기업부담금(100만원)</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>1100만원</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>제출(업로드), 비고, 첨부 서식 및 증빙자료 제출 ※ 상세, 내용은 [붙임4] 참고, 구 분 지원내용 지원단가, • 주력산업 맞춤 BM 전략, 수요기업·적용산업 분석, 사업화 단계별</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>(지원프로그램 및 신청ㆍ접수 관련 문의) 울산테크노파크 052-219-8614, 8617, ekdud899@utp.or.kr, kpe3839@utp.or.kr / (RMS 시스템 관련 문의) 중소기업 통합콜센터 (국번없이) 1357</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>ekdud899@utp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>052-219-8614</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125437</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>[서남권] 2026년 3차 지역혁신클러스터육성(비R&amp;D) 기업지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>전남지역산업진흥원</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jhs@riia.or.kr)</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>지원내용  3.</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>&lt;&lt;Ⅰ&gt; 지원개요&gt;, 지원목적, 지원대상 및 지원자격, 지원분야: 에너지신산업, (전남)IOT 접목 지능형 전력시스템, 신재생 에너지 설비, 에너지 저장관리 시스템(ESS) 등, 사업기간 종료일까지 입주**를 완료해야함(</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>전남지역산업진흥원 061-339-9727</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr"/>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>061-339-9727</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125435</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>[경기] 군포시 2027년 기업환경 개선사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>방문 또는 우편 접수
+- 접수처 : 군포시 청백리길 6 (금정동) 별관 2층 기업정책과</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>매출액 200억원 이하중소기업</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>200억원</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>사업계획서 원본 1부, 자부담 확약서 1부, 시설물 유지동의서 1부, 사업비 산출 증빙서류(내역서 및 견적서) 1부, 건물주 및 임대인 동의서(해당할 경우) 1부, 대 사회보험 사업장 가입자 명부(26.8월 이후) 1부, 최근 3년(2023~2025년) 매출액 증빙서류, 중소기업 지원사업 통합관리시스템 정보활용동의서 1부</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>군포시청 기업정책과 기업정책팀 031-390-0817</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr"/>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>031-390-0817</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125434</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026년 홍보영상 제작 및 온라인 게시 지원 참여 희망 소상공인 모집 공고</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>부산경제진흥원</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-09-02</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>온라인 접수 ※ 2곳 모두 신청 완료해야함
+① 판판대로 홈페이지(https://fanfandaero.kr) 사업신청
+② 소담스퀘어 in 부산 홈페이지(https://bssodam.or.kr) 사업신청</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>❍ 지원내용</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>&lt;구분&gt;&lt;준비서류&gt;, &lt;필수&gt;</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>부산경제진흥원 소상공인지원단 051-600-1367, zmk81@bepa.kr</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>zmk81@bepa.kr</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>051-600-1367</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125433</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 장애인기업 육성지원 사업 연장 공고</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>장애인기업종합지원센터</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2026-07-20 ~ 2026-08-19</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jey@debc.or.kr)
+※ 메일 송신 후 유선상으로 수신 확인 요망(043-238-8243)</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>❍ 지원규모: 총 21개 기업(명)(컨설팅 3개사, AI교육 21개사(명))</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>21개</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr"/>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>장애인기업종합지원센터 충북지역센터 043-238-8243 충청북도 경제기업과 043-220-3226</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr"/>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>043-220-3226</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>장애인기업</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125432</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 2차 첨단로봇ㆍ제조 공동연구센터 시제품제작지원 사업 공고(지역혁신중심 대학지원체계(RISE))</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>청주대학교</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>온라인 접수 (지역산업진흥원 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>□ 지원규모 : 총 10백만원</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>10백만원</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>를 제출하지 않거나, 제출양식을 준수하지 않은 경우, 기술료 납부, 정산금·환수금·제재부가금 납부 등 의무사항을 불이행, 하고 있는 경우, 해당 과제 대학, 연구책임자 및 참여기업은 참여 1년 제한. 단, 참여기업은 기술이전 완료</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>건국대학교 글로컬캠퍼스 RISE사업단 공동연구센터 043-840-4914, sim1023@kku.ac.kr</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>sim1023@kku.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD278" t="inlineStr">
+        <is>
+          <t>043-840-4914</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF278" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125431</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>AI 기반 제주형 그린바이오 밸류체인 고도화 및 글로벌 돋움 프로젝트 지원 수혜기업 모집 공고(제주 지역성장 인재양성체계(앵커))</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>제주산학융합원</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>이메일 접수 (hjs@jejuiucc.or.kr)</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>(사업 종료 시까지 이루어지지 않을 경우, 사업비 환수 조치)</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>비고, ① 신청서 1부 별첨1, ② 참여의사 확인 및 개인정보 이용 동의서 1부 별첨2, ③ 자가진단표 1부 별첨3, 신청일, ⑤ 4대보험 사업장 가입자 명부 사본 1부, 기준 3개월, ⑦ 추가</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>제주산학융합원 070-4260-1145, hjs@jejuiucc.or.kr</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>hjs@jejuiucc.or.kr</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>070-4260-1145</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125430</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026년 MEDICAL JAPAN TOKYO 2026 전시회 부스 참여 기업 모집 공고(스마트 디지털헬스케어 제품 사업화 통합 지원)</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>범부처통합헬스케어협회</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>온라인 접수 (BSMS 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>4) 기업 지원 내용</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>제출된 자료는 신청서와 동일한 효력을 지님, 하여야 함, 협약 해지, 등의 필요한 조치를 취할 수 있음, 않는 경우 지원 제외될 수 있음, 선정기업의 귀책사유로 인해 지원사업이 중도 파기될 경우, 선정기업은 수행, 기관에게 적절한 피해보상의 의무가 있으며</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>범부처통합헬스케어협회 070-7710-5038, hiy9529@kothea.or.kr</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>hiy9529@kothea.or.kr</t>
+        </is>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>070-7710-5038</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125429</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026년 U-Global Connect x  Fincnatieri 프로그램 참여기업 모집 공고(울산창조경제혁신센터)</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>울산창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>온라인 접수 (울산 스타트업 허브)</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>연계 지원, 이탈리아 현지 조선소 방문, PoC 사업화 지원금(기업당 500만원)</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>의 내용이 허위이거나, 를 위·변조한 기업, • 타인의 기술, 운영 프로세스, 단계 운영절차 지원규모 운영일정, 참여기업 모집 ① 온라인 접수 - ~8/26(수), ② 요건검토 -, 월 말</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>울산창조경제혁신센터 글로벌전략팀 052-230-3408, april416@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>april416@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>052-230-3408</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125428</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>[충북] 충주시 2026년 우수상품 MD 구매상담회 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>- 접수처 : 주사무소 소재 읍ㆍ면ㆍ동 행정복지센터</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>참여신청서 등[붙임서식], 중소기업확인서, 제품 소개자료(카탈로그), 인증서 등, 접 수 처 :, 주사무소 소재 읍·면·동 행정복지센터, 참여기업 선정, 가. 신청기업의 상품 특성</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>충청북도 충주시 120(시민행복콜센터, 충주 2번) 및 주사무소 소재 읍ㆍ면ㆍ동 행정복지센터</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr"/>
+      <c r="AD282" t="inlineStr"/>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125427</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026년 미래내일 일경험(인턴형) 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>대한상공회의소</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-10-31</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>이메일 또는 유선 접수
+- 이메일 접수 : jugml82@kiwoom.or.kr
+- 유선 접수 : 070-7633-0055</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>1인당 주 5만원 1인당 주 3.</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>5만원</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr"/>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>중소기업키움센터 전략기획팀 070-7633-0055</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>jugml82@kiwoom.or.kr</t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>070-7633-0055</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125426</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>[서울] 강북구 2026년 창업경진대회 IMPACT ON 강북 아이디어와 투자로 만드는 강북의 창업 무대 참가자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>온라인, 이메일 접수
+- 온라인 : 구글폼
+- 이메일 : gb.maru22@gmail.com
+※ 제출서류는 구글폼 작성 후 반드시 메일에 참가기업명을 적어 제출</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>모의투자자 : 아이디어 발표자의 발표내용을 듣고 가상의 1억 원을 배분하여 모의투자</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>1억원</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>(해당자만 제출) ※, Ⅱ 사전 교육 안내, 날짜 시간 강의 주제, ※ 참가자는 해당 사전교육 이수 후 본 행사 참여 가능, 모의투자자 (교육장소 : 강북청년창업마루 4층 회의실), (목)</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>강북청년창업마루 02-908-8246, gb.maru22@gmail.com</t>
+        </is>
+      </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>gb.maru22@gmail.com</t>
+        </is>
+      </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>02-908-8246</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125425</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>[서울] 2026년 제3회 S.Challenge IR AXㆍDX 분야 창업기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>서울창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>이메일 접수(s.challengeir@ccei.kr)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>□ 선정규모</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>이메일(s.challengeir@ccei.kr)로 송부, ◆ 유의사항, 반드시, ◦ 개인정보 동의서 1부. [붙임2] 양식, 법인의 경우, 심사방법 및 심사기준, 심사방법, 신청자격 등 형식 요건에 대한 사전확인 후 서면심사</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>서울창조경제혁신센터 S.challenge IR 담당자 02-739-8170, s.challengeir@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>s.challengeir@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AD285" t="inlineStr">
+        <is>
+          <t>02-739-8170</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125424</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>[부산] 2026년 소셜 비즈니스 육성 지원 사업 기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>부산경제진흥원</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2026-08-07 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>이메일 접수 (yeoyk612@bepa.kr)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>- 판별 fe 기업 담 5백만원 이내 사업지원금 지급 *사후정산</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>5백만원</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr"/>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>부산광역시 사회적경제지원센터 051-600-1396</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>yeoyk612@bepa.kr</t>
+        </is>
+      </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>051-600-1396</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125423</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>[경남] 2026년 방산중소기업 말레이시아 수출상담회 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>한국방위산업진흥회</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>이메일 또는 우편 접수
+- 접수처 : 경남 창원시 성산구 창이대로 532번길 50(경남중소벤처기업청 수출팀 2층)
+- 이메일 : zeonyi@korea.kr, hmins@kdia.or.kr</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>□ 모집규모 : 경남도 소재 방산분야 제조·생산기업 10개사 내외</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>구 분 제 출 서 류 부수, 제출 5 특허·인증서 사본 및 기업소개자료 각 1부, 선정평가기준 : 붙임4. 평가표 참조, ① 품질·기술경쟁력(30점), ② 수출마케팅 노력도(20점), ③ 지원필요성(30점), ④ 추진계획·기대효과(20점), ⑤ 가산점(10점)</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>(한국방위산업진흥회 경남지사) 055-294-9397, hmins@kdia.or.kr (경남지방중소벤처기업청 수출지원팀) 055-268-2565, zeonyi@korea.kr</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>hmins@kdia.or.kr</t>
+        </is>
+      </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>055-268-2565</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125422</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026년 1회차 초기창업패키지 로켓십 IR 경진대회(AIㆍ빅데이터) 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>창업진흥원</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>이메일 접수 (ac4@cntt.co.kr)</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Ÿ 참여 혜택: 우수기업 대상 최대 5억 원 직접투자 검토</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>5억원</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>구분 서류 목록 내용, ① 참가신청서 Ÿ [붙임1] 지정 양식 준용, 필수, Ÿ 초기창업패키지 협약 증명서, 선발 절차, 진행 단계 세부 내용 일정, 선정평가 ž 사업계획서 기반 서류평가 8/28(금), 평가 항목 평가 내용 배점</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>초기창업패키지 운영사무국 02-3152-5824, 8660 / ac4@cntt.co.kr</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>ac4@cntt.co.kr</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>02-3152-5824</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125421</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 2차 자동차부품산업 경쟁력강화 지원사업 시행계획 재공고(관세피해기업 경쟁력강화 지원)</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>경북테크노파크</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>온라인 접수(경북테크노파크)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>지원내용</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z289" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr"/>
+      <c r="AB289" t="inlineStr">
+        <is>
+          <t>경북테크노파크 미래차부품진흥실 053-802-2411, mskim@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>mskim@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD289" t="inlineStr">
+        <is>
+          <t>053-802-2411</t>
+        </is>
+      </c>
+      <c r="AE289" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF289" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125420</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>[경기] 성남시 2026년 국제 바이오 헬스케어 컨벤션 (SBIC) 참가기업 모집(수출상담회, 전시부스) 공고</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>성남산업진흥원</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>선착순 접수</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>온라인 접수 (성남산업진흥원)</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>구분 지원내용 기업혜택</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>참가신청서, 개인정보동의서, 수출상담회 신청서, 제품 홍보자료 등, 신청기한 선착순 마감, 전시부스 운영 (수출상담회 필수), 모집규모 10개사 내외, 제품 실물</t>
+        </is>
+      </c>
+      <c r="AB290" t="inlineStr">
+        <is>
+          <t>성남산업진흥원 바이오산업부 031-782-3083, hjsi333@snip.or.kr</t>
+        </is>
+      </c>
+      <c r="AC290" t="inlineStr">
+        <is>
+          <t>hjsi333@snip.or.kr</t>
+        </is>
+      </c>
+      <c r="AD290" t="inlineStr">
+        <is>
+          <t>031-782-3083</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF290" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125419</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026년 하반기 온ㆍ오프라인 통합 품평회 모집 공고</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>중소기업중앙회</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>온라인 접수 (중소기업중앙회)</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr"/>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>중소기업중앙회 소상공인정책실 02-2124-3173</t>
+        </is>
+      </c>
+      <c r="AC291" t="inlineStr"/>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>02-2124-3173</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF291" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125418</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026년 2차 독자 AI 파운데이션 모델 프로젝트 공동활용 데이터 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>한국데이터산업진흥원</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-09-02</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>이메 접수 (ai_data@kdata.or.kr)</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>: 총 4350백만원</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>4350백만원</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z292" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>및 자격요건 사전검토, 자격요건 등을, 를 통해 사전검토하고 평가 대상 선정, 기준으로 실시, (사업수행계획서 평가), 평가위원회의 구성 및 운영은 한국지능정보, 사회진흥원, (이하 한국지능정보원)</t>
+        </is>
+      </c>
+      <c r="AB292" t="inlineStr">
+        <is>
+          <t>한국데이터산업진흥원 AI데이터지원팀 02-3708-5442</t>
+        </is>
+      </c>
+      <c r="AC292" t="inlineStr">
+        <is>
+          <t>ai_data@kdata.or.kr</t>
+        </is>
+      </c>
+      <c r="AD292" t="inlineStr">
+        <is>
+          <t>02-3708-5442</t>
+        </is>
+      </c>
+      <c r="AE292" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF292" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125417</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026년 중국 포산 수소전시회 연계 수소산업 수출상담회 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>온라인 및 이메일 접수
+① KOTRA 홈페이지(무역투자24)를 통한 온라인 접수
+② 첨부파일 작성 후, 이메일 발송(canton@kotra.or.kr)</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>◦ (사업규모) 국내 10개사</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>첨부, ② 첨부파일 작성 후, 이메일 송부(canton@kotra.or.kr), ◦ (참가비) 무료, ◦ (주요일정), ① 참가신청서 ② 영문 또는 중문회사소개서 및 카탈로그, 파일 첨부는 1개만 가능하므로 참가신청서, 카탈로그 및 회사소개서는 압축 후</t>
+        </is>
+      </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사 (본사) 기후에너지산업팀 green@kotra.or.kr (광저우 무역관) khd@kotra.or.kr, huizhen@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AC293" t="inlineStr">
+        <is>
+          <t>green@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AD293" t="inlineStr"/>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF293" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125416</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>24차 디자인전문기업 금융지원 희망기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>한국디자인진흥원</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>이메일 접수 (designfinance@kidp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>ㅇ 보증한도 : 기업별 1억원 이상 (1억원까지는 100% 보증)</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>1억원</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z294" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>ㅇ 신청서 1부 : 별첨 양식 참조, 지원 내용, 지원내용, 기술보증기금 심사에 따라 1억원 초과 지원 가능, 다만, ㅇ 기술평가료 : 20만원, (KIBO) 보증료율 0.2%p 감면, 지원조건</t>
+        </is>
+      </c>
+      <c r="AB294" t="inlineStr">
+        <is>
+          <t>한국디자인진흥원 산업육성실 031-780-2167, designfinance@kidp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC294" t="inlineStr">
+        <is>
+          <t>designfinance@kidp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD294" t="inlineStr">
+        <is>
+          <t>031-780-2167</t>
+        </is>
+      </c>
+      <c r="AE294" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF294" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125415</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 인도ㆍ태국 현지수출상담회 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>대구경북기계협동조합</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2026-08-07 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>온라인 접수 (대구광역시 수출지원시스템) 
+※ 첨부서류는 온라인 신청 시 첨부 또는 이메일(mondol@dgomc.org) 송부
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>참가신청서 및 확약서, 정보활용동의서, 참가기업 의향서, 최근 3년간(2023~2025) 수출실적, 외국어 카탈로그, 각종 인증서, 선정방법, 가. 참가기업의 제품 및 기술수준(산업재산권</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>대구경북기계협동조합 기업성장지원본부 053-248-8136, mondol@dgomc.org</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>mondol@dgomc.org</t>
+        </is>
+      </c>
+      <c r="AD295" t="inlineStr">
+        <is>
+          <t>053-248-8136</t>
+        </is>
+      </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF295" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125414</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 사회연대경제 추석 특별판매전 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>경상북도사회적경제지원센터</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>이메일 접수 (gbsecenter@daum.net)</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>선정규모: 총 12개사</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>12개</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>이메일 제출 (gbsecenter@daum.net), 연번, 비고, 공통, 또는 도청특판전 이메일에 첨부 요망, 신청시 주문시 입금받을 통장사본, ￭ 선정방법: 신청내용 기반 서면심사를 통한 선발, ※ 심사위원/심사기준 세부사항은 별도로 정함</t>
+        </is>
+      </c>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>경상북도 사회적경제지원센터 053-850-4805, 4807</t>
+        </is>
+      </c>
+      <c r="AC296" t="inlineStr">
+        <is>
+          <t>gbsecenter@daum.net</t>
+        </is>
+      </c>
+      <c r="AD296" t="inlineStr">
+        <is>
+          <t>053-850-4805</t>
+        </is>
+      </c>
+      <c r="AE296" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF296" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125413</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026년 물류로봇 특화거점 실증 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>인천테크노파크</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>온라인 접수 (비즈OK)</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>ㅇ (지원내용) 로봇랜드 실증인프라 활용, 물류(모빌리티)로봇의 데이터</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>구분, 비 고, 사업계획서 서식 1, 국세 및 지방세, 대보험 완납 증명서, 신청자격 적정성 확인서 서식 2, 참여의사 확약서 서식 3, 개인정보 이동 동의서 서식 4</t>
+        </is>
+      </c>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>인천테크노파크 모빌리티본부 로봇센터 032-727-5015, 5011 / jspark@itp.or.kr, sa01049@itp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC297" t="inlineStr">
+        <is>
+          <t>jspark@itp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD297" t="inlineStr">
+        <is>
+          <t>032-727-5015</t>
+        </is>
+      </c>
+      <c r="AE297" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF297" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125412</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>[강원] 양양군 2026년 2차 소상공인 특례보증수수료 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 양양군청 경제에너지과 소상공인지원팀</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>특례보증액 5천만원 이내, 보증기간 5년 이내에 대한 보증수수료 0.</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>5천만원</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>구분, 세부내용, 비고, 지원신청서 1부, 서식1, 개인정보 제공 동의서 1부, 서식2, 신용보증 수수료 납부영수증(원본) 1부.</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>양양군청 경제에너지과 소상공인지원팀 033-670-2957</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr"/>
+      <c r="AD298" t="inlineStr">
+        <is>
+          <t>033-670-2957</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF298" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125411</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>[강원] 양양군 2026년 2차 소상공인 특례보증 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>온라인, 방문 접수
+- 접수처 : 강원신용보증재단
+- 온라인 : 강원신용보증재단 보증드림(웹사이트, 앱)
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>5억원</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>5억원</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>확인, 전자약정 · 실사, ‧ 비대면 전자약정, QR코드 안내, 앱 접속, 신청방법 유튜브 영상, 회원가입, 신청방법</t>
+        </is>
+      </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>양양군청 경제에너지과 소상공인지원팀 033-670-2957 강원신용보증재단 속초지점 033-260-0071</t>
+        </is>
+      </c>
+      <c r="AC299" t="inlineStr"/>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>033-260-0071</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF299" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125410</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026년 인천 콘텐츠 스케일업 플러스 지원사업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>인천테크노파크</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2026-07-27 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>온라인 접수(biz OK)</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>❍ 지원내용</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr"/>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>인천테크노파크 콘텐츠기업지원센터 032-876-5073, dgffg14@itp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>dgffg14@itp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>032-876-5073</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF300" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125409</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>[울산] 2026년 2차 원천기술 상용화 플랫폼 구축사업 기술상용화 촉진 프로그램 지원기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>울산테크노파크</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>온라인 접수 (울산테크노파크 기업지원사업 관리시스템)
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>10백만원 이내</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>10백만원</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z301" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>확인 후, ⇒ ⇒ 신청서 및 서류 제출 업로드, 입력, 제출 관리자 승인, 울산 TP 시스템, 신청자 신청자, 관리자, 과제 신청을 위해 반드시 회원가입 후 승인 절차 필요</t>
+        </is>
+      </c>
+      <c r="AB301" t="inlineStr">
+        <is>
+          <t>울산테크노파크 사업담당자 052-219-8644, jeon6417@utp.or.kr / 기업지원사업 관리시스템 담당자 052-219-8678, hyeoun970920@utp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC301" t="inlineStr">
+        <is>
+          <t>hyeoun970920@utp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD301" t="inlineStr">
+        <is>
+          <t>052-219-8644</t>
+        </is>
+      </c>
+      <c r="AE301" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF301" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125408</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>[강원] 홍천군 2026년 청년 일경험 지원사업 참여 기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 홍천군청 경제진흥과 청년지원팀</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>기업이 청년을 채용(인턴)할 경우, 청년 인건비 및 교통비 월200만원을 4개월 지원</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>200만원</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>4개</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>신청, 방법 : 접수처에 직접 방문 접수, (10:00~18:00 가능, :00~13:00 제외), 접 수 처, 홍천군청 경제진흥과 청년지원팀, 방문 신청은 평일(휴일 제외) 근무시간, 내 가능</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>홍천군 경제진흥과 청년지원팀 033-430-2896</t>
+        </is>
+      </c>
+      <c r="AC302" t="inlineStr"/>
+      <c r="AD302" t="inlineStr">
+        <is>
+          <t>033-430-2896</t>
+        </is>
+      </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF302" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125407</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 2차 광주여자대학교 RISE사업단 코스메디케어 제품 실증 및 상용화 지원 용역 실증 및 상용화 지원 수혜기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>광주테크노파크</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-19</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>방문 또는 우편, 이메일 접수
+- 접수처 : (61003) 광주광역시 북구 추암로 249 광주테크노파크 2단지 생체의료소재부품센터 2층 201호
+- 이메일 : didwldnjs93@gjtp.or.kr
+※ 원본(방문 또는 우편)과 사본(이메일) 접수</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>※ 광주여자대학교와 연계하여 협의 후 지원 규모 결정 1천만원 상당</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>1천만원</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>지원 신청서 및, 각 1부, 접수, ㅇ (접수기한) 2026년 8월 12일 ~ 8월 19일, :00까지, ※ 우편접수의 경우 접수기한 내 도착분에 한함, 선정절차 및 기준, 선정절차 : 예비진단 → 면담/현장실태조사 → 선정평가</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>(사업신청 관련 문의) 광주테크노파크 메디헬스케어센터 062-602-0804, didwldnjs93@gjtp.or.kr / (제작 및 견적 관련 문의) 광주화장품생산시설 나인원코스메디 062-719-1001, po@91cosmedi.com</t>
+        </is>
+      </c>
+      <c r="AC303" t="inlineStr">
+        <is>
+          <t>didwldnjs93@gjtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD303" t="inlineStr">
+        <is>
+          <t>062-602-0804</t>
+        </is>
+      </c>
+      <c r="AE303" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF303" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125406</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026년 INKE 인도 시장진출 지원 프로그램  참가기업 모집 공고(뉴델리 현지 바이어 매칭 및 수출상담회)</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>벤처기업협회</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>이메일 접수 (min@kova.or.kr)</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>5개사 기준 총 2000만원 규모의 현지 공동 프로그램 지원</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>2000만원</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA304" t="inlineStr"/>
+      <c r="AB304" t="inlineStr">
+        <is>
+          <t>벤처기업협회 기업지원1본부 02-6331-7081, min@kova.or.kr</t>
+        </is>
+      </c>
+      <c r="AC304" t="inlineStr">
+        <is>
+          <t>min@kova.or.kr</t>
+        </is>
+      </c>
+      <c r="AD304" t="inlineStr">
+        <is>
+          <t>02-6331-7081</t>
+        </is>
+      </c>
+      <c r="AE304" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF304" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125405</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>[강원] 홍천군 2026년 3차 소상공인 시설개선 및 경영지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 홍천군 경제진흥과</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t> 총사업비: 84백만원(군비 42백만원, 자부담 42백만원)</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>84백만원</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>(공고일 이후 발급분에 한함), 항목, 필수, 사업신청서 1부, [붙임 1], ▶ 사업신청서상, “보조금”, 계산법[부가가치세 환급규정]</t>
+        </is>
+      </c>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>홍천군 경제진흥과 033-430-2807</t>
+        </is>
+      </c>
+      <c r="AC305" t="inlineStr"/>
+      <c r="AD305" t="inlineStr">
+        <is>
+          <t>033-430-2807</t>
+        </is>
+      </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF305" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125404</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>[강원] 강릉시 2026년 3차 해양수산사업 지원계획 및 사업자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>방문 및 우편 접수
+- 접수처 : 강릉시청 해양수산과, 주문진읍사무소</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>「해양수산부 국고보조금 관리에 관한 규정」및「강릉시 지방보조금 관리</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>사업신청서, 사업계획서 등, ※ 사업별 사업신청서 서식 참고하여, 포함하여 제출, q 신청자격, q 지원 제외대상, 【 공통사항 】, 사실이 있는 자(단체 포함)</t>
+        </is>
+      </c>
+      <c r="AB306" t="inlineStr">
+        <is>
+          <t>강릉시청 해양수산과 수산자원팀 033-640-5378</t>
+        </is>
+      </c>
+      <c r="AC306" t="inlineStr"/>
+      <c r="AD306" t="inlineStr">
+        <is>
+          <t>033-640-5378</t>
+        </is>
+      </c>
+      <c r="AE306" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF306" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125403</t>
         </is>
       </c>
     </row>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF306"/>
+  <dimension ref="A1:AF345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39529,7 +39529,6 @@
           <t>❍ 지원규모 : 10개사 내외</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
           <t>10개</t>
@@ -39687,8 +39686,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr">
         <is>
           <t>N</t>
@@ -39784,7 +39781,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA256" t="inlineStr"/>
       <c r="AB256" t="inlineStr">
         <is>
           <t>한국콘텐츠진흥원 기업육성팀 061-900-6382, psj@kocca.kr</t>
@@ -39837,7 +39833,6 @@
           <t>m 지원규모 : 약 3~4개사(지원규모에 따라 변동)</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
           <t>4개</t>
@@ -40000,7 +39995,6 @@
           <t>200만원</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
           <t>Y</t>
@@ -40160,7 +40154,6 @@
           <t>20088200원</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr">
         <is>
           <t>N</t>
@@ -40266,7 +40259,6 @@
           <t>충청남도 아산시 농업기술센터 농식품유통과 041-537-3931</t>
         </is>
       </c>
-      <c r="AC259" t="inlineStr"/>
       <c r="AD259" t="inlineStr">
         <is>
           <t>041-537-3931</t>
@@ -40319,7 +40311,6 @@
           <t>3억원</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr">
         <is>
           <t>Y</t>
@@ -40425,7 +40416,6 @@
           <t>경상북도경제진흥원 민생경제지원팀 1800-8730 / 칠곡군 소상공인연합회 문의처 출처 바로가기 내 공고문 참조</t>
         </is>
       </c>
-      <c r="AC260" t="inlineStr"/>
       <c r="AD260" t="inlineStr">
         <is>
           <t>00000000000</t>
@@ -40473,7 +40463,6 @@
           <t>10백만원</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
           <t>Y</t>
@@ -40636,7 +40625,6 @@
           <t>40만원</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
           <t>N</t>
@@ -40742,7 +40730,6 @@
           <t>경상북도경제진흥원 민생경제지원팀 1800-8730 / 경상북도소상공인연합회 054-772-7008</t>
         </is>
       </c>
-      <c r="AC262" t="inlineStr"/>
       <c r="AD262" t="inlineStr">
         <is>
           <t>054-772-7008</t>
@@ -40790,7 +40777,6 @@
           <t>10000000원</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr">
         <is>
           <t>N</t>
@@ -40948,7 +40934,6 @@
           <t>30백만원</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr">
         <is>
           <t>Y</t>
@@ -41106,7 +41091,6 @@
           <t>150만원</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr">
         <is>
           <t>Y</t>
@@ -41266,7 +41250,6 @@
           <t>200만원</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr">
         <is>
           <t>Y</t>
@@ -41377,7 +41360,6 @@
           <t>kmj1122@korea.kr</t>
         </is>
       </c>
-      <c r="AD266" t="inlineStr"/>
       <c r="AE266" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -41415,8 +41397,6 @@
           <t>□ 지원 내용</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr">
         <is>
           <t>N</t>
@@ -41512,13 +41492,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA267" t="inlineStr"/>
       <c r="AB267" t="inlineStr">
         <is>
           <t>중소기업기술정보진흥원 성과확산실 044-300-0716</t>
         </is>
       </c>
-      <c r="AC267" t="inlineStr"/>
       <c r="AD267" t="inlineStr">
         <is>
           <t>044-300-0716</t>
@@ -41561,7 +41539,6 @@
           <t>❍ 지원규모 : 6개사 내외</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
           <t>6개</t>
@@ -41662,13 +41639,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA268" t="inlineStr"/>
       <c r="AB268" t="inlineStr">
         <is>
           <t>광주경제진흥상생일자리재단 일자리경제실 062-956-2639</t>
         </is>
       </c>
-      <c r="AC268" t="inlineStr"/>
       <c r="AD268" t="inlineStr">
         <is>
           <t>062-956-2639</t>
@@ -41716,7 +41691,6 @@
           <t>30백만원</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr">
         <is>
           <t>Y</t>
@@ -41869,8 +41843,6 @@
           <t>2 지원내용</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr">
         <is>
           <t>Y</t>
@@ -42028,7 +42000,6 @@
           <t>5억원</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr">
         <is>
           <t>N</t>
@@ -42124,13 +42095,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA271" t="inlineStr"/>
       <c r="AB271" t="inlineStr">
         <is>
           <t>(신청ㆍ접수, 사업계획서 작성, 선정평가, 유의사항 등 문의) 경북테크노파크 AI제조혁신실 053-819-7032, 7035 (사업기획 문의) 국번없이 1357 (사업시행 관련 문의) 044-300-0955</t>
         </is>
       </c>
-      <c r="AC271" t="inlineStr"/>
       <c r="AD271" t="inlineStr">
         <is>
           <t>044-300-0955</t>
@@ -42175,8 +42144,6 @@
           <t>자격요건 및 지원내용&gt;&lt;&gt;</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr">
         <is>
           <t>N</t>
@@ -42272,7 +42239,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA272" t="inlineStr"/>
       <c r="AB272" t="inlineStr">
         <is>
           <t>충남테크노파크 기업지원본부 사업화지원실 041-589-0634, 041-589-0641 / fangse@ctp.or.kr, jepark@ctp.or.kr</t>
@@ -42332,7 +42298,6 @@
           <t>1100만원</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
         <is>
           <t>Y</t>
@@ -42485,8 +42450,6 @@
           <t>지원내용  3.</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr">
         <is>
           <t>N</t>
@@ -42592,7 +42555,6 @@
           <t>전남지역산업진흥원 061-339-9727</t>
         </is>
       </c>
-      <c r="AC274" t="inlineStr"/>
       <c r="AD274" t="inlineStr">
         <is>
           <t>061-339-9727</t>
@@ -42641,7 +42603,6 @@
           <t>200억원</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr">
         <is>
           <t>Y</t>
@@ -42747,7 +42708,6 @@
           <t>군포시청 기업정책과 기업정책팀 031-390-0817</t>
         </is>
       </c>
-      <c r="AC275" t="inlineStr"/>
       <c r="AD275" t="inlineStr">
         <is>
           <t>031-390-0817</t>
@@ -42792,8 +42752,6 @@
           <t>❍ 지원내용</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr">
         <is>
           <t>N</t>
@@ -42947,7 +42905,6 @@
           <t>❍ 지원규모: 총 21개 기업(명)(컨설팅 3개사, AI교육 21개사(명))</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
           <t>21개</t>
@@ -43048,13 +43005,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA277" t="inlineStr"/>
       <c r="AB277" t="inlineStr">
         <is>
           <t>장애인기업종합지원센터 충북지역센터 043-238-8243 충청북도 경제기업과 043-220-3226</t>
         </is>
       </c>
-      <c r="AC277" t="inlineStr"/>
       <c r="AD277" t="inlineStr">
         <is>
           <t>043-220-3226</t>
@@ -43102,7 +43057,6 @@
           <t>10백만원</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr">
         <is>
           <t>Y</t>
@@ -43255,8 +43209,6 @@
           <t>(사업 종료 시까지 이루어지지 않을 경우, 사업비 환수 조치)</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
           <t>Y</t>
@@ -43409,8 +43361,6 @@
           <t>4) 기업 지원 내용</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
           <t>Y</t>
@@ -43568,7 +43518,6 @@
           <t>500만원</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr">
         <is>
           <t>Y</t>
@@ -43721,8 +43670,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr">
         <is>
           <t>Y</t>
@@ -43828,8 +43775,6 @@
           <t>충청북도 충주시 120(시민행복콜센터, 충주 2번) 및 주사무소 소재 읍ㆍ면ㆍ동 행정복지센터</t>
         </is>
       </c>
-      <c r="AC282" t="inlineStr"/>
-      <c r="AD282" t="inlineStr"/>
       <c r="AE282" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -43874,7 +43819,6 @@
           <t>5만원</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr">
         <is>
           <t>N</t>
@@ -43970,7 +43914,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA283" t="inlineStr"/>
       <c r="AB283" t="inlineStr">
         <is>
           <t>중소기업키움센터 전략기획팀 070-7633-0055</t>
@@ -44031,7 +43974,6 @@
           <t>1억원</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr">
         <is>
           <t>Y</t>
@@ -44184,8 +44126,6 @@
           <t>□ 선정규모</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr">
         <is>
           <t>Y</t>
@@ -44343,7 +44283,6 @@
           <t>5백만원</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr">
         <is>
           <t>N</t>
@@ -44439,7 +44378,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA286" t="inlineStr"/>
       <c r="AB286" t="inlineStr">
         <is>
           <t>부산광역시 사회적경제지원센터 051-600-1396</t>
@@ -44494,7 +44432,6 @@
           <t>□ 모집규모 : 경남도 소재 방산분야 제조·생산기업 10개사 내외</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr">
         <is>
           <t>10개</t>
@@ -44657,7 +44594,6 @@
           <t>5억원</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr"/>
       <c r="H288" t="inlineStr">
         <is>
           <t>Y</t>
@@ -44810,8 +44746,6 @@
           <t>지원내용</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr">
         <is>
           <t>N</t>
@@ -44907,7 +44841,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA289" t="inlineStr"/>
       <c r="AB289" t="inlineStr">
         <is>
           <t>경북테크노파크 미래차부품진흥실 053-802-2411, mskim@gbtp.or.kr</t>
@@ -44960,8 +44893,6 @@
           <t>구분 지원내용 기업혜택</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr">
         <is>
           <t>Y</t>
@@ -45114,8 +45045,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr">
         <is>
           <t>N</t>
@@ -45211,13 +45140,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA291" t="inlineStr"/>
       <c r="AB291" t="inlineStr">
         <is>
           <t>중소기업중앙회 소상공인정책실 02-2124-3173</t>
         </is>
       </c>
-      <c r="AC291" t="inlineStr"/>
       <c r="AD291" t="inlineStr">
         <is>
           <t>02-2124-3173</t>
@@ -45265,7 +45192,6 @@
           <t>4350백만원</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr">
         <is>
           <t>Y</t>
@@ -45420,7 +45346,6 @@
           <t>◦ (사업규모) 국내 10개사</t>
         </is>
       </c>
-      <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr">
         <is>
           <t>10개</t>
@@ -45536,7 +45461,6 @@
           <t>green@kotra.or.kr</t>
         </is>
       </c>
-      <c r="AD293" t="inlineStr"/>
       <c r="AE293" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -45579,7 +45503,6 @@
           <t>1억원</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
           <t>Y</t>
@@ -45734,8 +45657,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr">
         <is>
           <t>Y</t>
@@ -45888,7 +45809,6 @@
           <t>선정규모: 총 12개사</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr">
         <is>
           <t>12개</t>
@@ -46046,8 +45966,6 @@
           <t>ㅇ (지원내용) 로봇랜드 실증인프라 활용, 물류(모빌리티)로봇의 데이터</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr">
         <is>
           <t>Y</t>
@@ -46206,7 +46124,6 @@
           <t>5천만원</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr">
         <is>
           <t>Y</t>
@@ -46312,7 +46229,6 @@
           <t>양양군청 경제에너지과 소상공인지원팀 033-670-2957</t>
         </is>
       </c>
-      <c r="AC298" t="inlineStr"/>
       <c r="AD298" t="inlineStr">
         <is>
           <t>033-670-2957</t>
@@ -46363,7 +46279,6 @@
           <t>5억원</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr">
         <is>
           <t>N</t>
@@ -46469,7 +46384,6 @@
           <t>양양군청 경제에너지과 소상공인지원팀 033-670-2957 강원신용보증재단 속초지점 033-260-0071</t>
         </is>
       </c>
-      <c r="AC299" t="inlineStr"/>
       <c r="AD299" t="inlineStr">
         <is>
           <t>033-260-0071</t>
@@ -46512,8 +46426,6 @@
           <t>❍ 지원내용</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr">
         <is>
           <t>N</t>
@@ -46609,7 +46521,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA300" t="inlineStr"/>
       <c r="AB300" t="inlineStr">
         <is>
           <t>인천테크노파크 콘텐츠기업지원센터 032-876-5073, dgffg14@itp.or.kr</t>
@@ -46668,7 +46579,6 @@
           <t>10백만원</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr">
         <is>
           <t>Y</t>
@@ -46937,7 +46847,6 @@
           <t>홍천군 경제진흥과 청년지원팀 033-430-2896</t>
         </is>
       </c>
-      <c r="AC302" t="inlineStr"/>
       <c r="AD302" t="inlineStr">
         <is>
           <t>033-430-2896</t>
@@ -46988,7 +46897,6 @@
           <t>1천만원</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr">
         <is>
           <t>N</t>
@@ -47246,7 +47154,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA304" t="inlineStr"/>
       <c r="AB304" t="inlineStr">
         <is>
           <t>벤처기업협회 기업지원1본부 02-6331-7081, min@kova.or.kr</t>
@@ -47305,7 +47212,6 @@
           <t>84백만원</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr">
         <is>
           <t>Y</t>
@@ -47411,7 +47317,6 @@
           <t>홍천군 경제진흥과 033-430-2807</t>
         </is>
       </c>
-      <c r="AC305" t="inlineStr"/>
       <c r="AD305" t="inlineStr">
         <is>
           <t>033-430-2807</t>
@@ -47455,8 +47360,6 @@
           <t>「해양수산부 국고보조금 관리에 관한 규정」및「강릉시 지방보조금 관리</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr">
         <is>
           <t>N</t>
@@ -47562,7 +47465,6 @@
           <t>강릉시청 해양수산과 수산자원팀 033-640-5378</t>
         </is>
       </c>
-      <c r="AC306" t="inlineStr"/>
       <c r="AD306" t="inlineStr">
         <is>
           <t>033-640-5378</t>
@@ -47576,6 +47478,6144 @@
       <c r="AF306" t="inlineStr">
         <is>
           <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125403</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>수성알파시티 기업 전용 5G 기반 통신망 서비스 지원 대상 기업 1차 모집 공고</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>대구테크노파크</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>이메일 접수 (smartcity@dgtp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>m 지원내용 : 기업 전용 5G 기반 통신망 지원</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>심의, 의 검토 및 심의를 통해 ‘지원대상’ 여부 판정, m 검토기준, 항 목 검토 기준 비 고, 기술성 기존 기술(서비스)과의 차별성, 항 목 별, 적정성 도입 기술의 성숙도 및 구현 가능성 세부검토, 활용성 서비스 확산 및 상용화 가능성 및</t>
+        </is>
+      </c>
+      <c r="AB307" t="inlineStr">
+        <is>
+          <t>대구테크노파크 지능도시본부 스마트시티센터 053-795-9764</t>
+        </is>
+      </c>
+      <c r="AC307" t="inlineStr">
+        <is>
+          <t>smartcity@dgtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD307" t="inlineStr">
+        <is>
+          <t>053-795-9764</t>
+        </is>
+      </c>
+      <c r="AE307" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF307" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125497</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>[제주] 제주우수제품품질인증(JQ) 인증기업 시험성적서 비용 지원 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>제주특별자치도경제통상진흥원</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>이메일 또는 방문 접수
+- 이메일 : gusdl9312@naver.com
+- 접수처 : 제주시 연삼로 473 지하1층 기업성장팀</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>m 지원내용: 기업당 최대 100만원 지원(품목당 50만원 한도)</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>검토, 신청기업 신청기업 → 진흥원 진흥원 진흥원 → 신청기업, 신청 및 접수, m 선정방법: 선착순 신청에 따라 지원금 지급, m 참가신청, 순번 서 류 명 비 고, 품질검사비 보조금 지원신청서 붙임 1, 개인정보 수집 이용 동의서 붙임 2</t>
+        </is>
+      </c>
+      <c r="AB308" t="inlineStr">
+        <is>
+          <t>제주특별자치도경제통상진흥원 기업성장팀 064-805-3397</t>
+        </is>
+      </c>
+      <c r="AC308" t="inlineStr">
+        <is>
+          <t>gusdl9312@naver.com</t>
+        </is>
+      </c>
+      <c r="AD308" t="inlineStr">
+        <is>
+          <t>064-805-3397</t>
+        </is>
+      </c>
+      <c r="AE308" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF308" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125496</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>[제주] 2026년 단시간 노동자 일자리 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>제주특별자치도경제통상진흥원</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>방문 또는 이메일 접수
+- 접수처 : 제주특별자치도 제주시 연삼로 473(이도이동) 제주경제통상진흥원 기업성장팀, 지하1층
+- 이메일 : xodnd255@jba.or.kr
+※ 이메일 제출 후, 확인전화 필수(064-800-7624)</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>알면서 지방보조금을 교부한 자는 10년 이하의 징역 또는 1억원 이하의 벌금에 처한다.</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>1억원</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>지하1층, 방문 접수 시 주말, 공휴일, 점심시간(12:00~13:00) 제외, ❍ 메일: xodnd255@jba.or.kr, 구 분 접수처, 이메일, ※ 이메일 제출 후</t>
+        </is>
+      </c>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>(참여 신청 접수 및 지원금 지원에 관한 사항) 제주특별자치도경제통상진흥원 기업육성처 기업성장팀 064-800-7624 / (단시간 청년노동자 일자리 지원사업 정책에 관한 사항) 제주특별자치도 경제일자리과 064-710-3795</t>
+        </is>
+      </c>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>xodnd255@jba.or.kr</t>
+        </is>
+      </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>064-710-3795</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF309" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125495</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 제30차 세계한인경제인대회 경상북도 공동관 참가기업 추가모집 공고(3차)</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>이메일 접수 (uujin0110@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>□ (편도항공료) 편도 항공료 지원(1인/1개사 이코노미 기준 50만원 한도)</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>보완 및 평가 참가기업 최종 선정, 전시 참가 온라인 바이어 매칭 전시 온라인 사전설명회, 상기 일정은 추진 상황에 따라 변경될 수 있음, 전시회 개요, 일간 ※ 10/8 부스 설치, (전시장소) 중국(선전컨벤션전시센터), (전시품목) 종합, (주요내용) OKTA 바이어 대상 상품 전시</t>
+        </is>
+      </c>
+      <c r="AB310" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 마케팅팀 054-470-8551, uujin0110@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AC310" t="inlineStr">
+        <is>
+          <t>uujin0110@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD310" t="inlineStr">
+        <is>
+          <t>054-470-8551</t>
+        </is>
+      </c>
+      <c r="AE310" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF310" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125494</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>[경기] 화성시 2026년 하반기 마케팅 활성화 지원  참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>화성산업진흥원</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-10-30</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>온라인 접수 (화성시 기업지원플랫폼)</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>□ 사업내용: 마케팅 비용 기업당 최대 2개 분야, 3백만원 이내 (부가세 제외)지원</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>3백만원</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>❍ (신청 시, 필수 제출 ● 선택 제출, 구분 서류명 필수 해당 시 비고, 사업신청서 ● 진흥원 서식, 서명 필수, 자가점검표 ● 진흥원 서식, 사업참여 및 중복지원 금지 서약서 ● 진흥원 서식, 청렴 서약서 ● 진흥원 서식</t>
+        </is>
+      </c>
+      <c r="AB311" t="inlineStr">
+        <is>
+          <t>화성산업진흥원 031-374-6468, joy@hsbiz.or.kr</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr">
+        <is>
+          <t>joy@hsbiz.or.kr</t>
+        </is>
+      </c>
+      <c r="AD311" t="inlineStr">
+        <is>
+          <t>031-374-6468</t>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF311" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125493</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>[경북] 영덕군 2026년 농공단지 입주기업 물류비 지원사업 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jungheon.ha@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>□ (지원규모) 6개사 정도</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>6개</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>검토 9월 지원 요건 충족 및 서류 누락 여부 검토, 지원기업 선정 9월 지원기업 선정 및 지원금 확정, 지원금 지급 9~10월 선정기업 물류비 지원금 지급, 상기 일정은 추진 상황에 따라 변경될 수 있음, 사업목적, 기업 경영부담 절감 및 기업 경쟁력 강화, 국제 경기 장기 침체에 따른 기업의 운반비 부담 감소, 주요 공지사항</t>
+        </is>
+      </c>
+      <c r="AB312" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 ESGㆍ기업지원팀 054-470-8503, jungheon.ha@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AC312" t="inlineStr">
+        <is>
+          <t>jungheon.ha@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD312" t="inlineStr">
+        <is>
+          <t>054-470-8503</t>
+        </is>
+      </c>
+      <c r="AE312" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF312" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125492</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 멜버른 한류박람회 연계 무역사절단 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>KOTRA대구경북지원본부</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>온라인 접수 (KOTRA 무역투자24)</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>항공임 ⋅대구시 기업 대상, 왕복항공임의 50% (지원한도 80만원, 1개사 1인)</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>80만원</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>가 허위로 판명될 경우 선정이, [참고] 윤리 청렴 기준, 국내외 인권 및 윤리 규범을 준수하며, 최근 5년간 중대한 인권침해 및 부패 행위(공정, 회계 청렴성, 노동(인권), 환경 등)가, 있을 경우</t>
+        </is>
+      </c>
+      <c r="AB313" t="inlineStr">
+        <is>
+          <t>KOTRA대구경북지원본부 053-659-2556</t>
+        </is>
+      </c>
+      <c r="AC313" t="inlineStr">
+        <is>
+          <t>delegation@kotra.com.au</t>
+        </is>
+      </c>
+      <c r="AD313" t="inlineStr">
+        <is>
+          <t>053-659-2556</t>
+        </is>
+      </c>
+      <c r="AE313" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF313" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125491</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026년 창업 식품기업 지원사업 사업대상자 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>직접수행</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>해당 시군 접수
+- 접수처 : 전북특별자치도 및 시군 창업식품기업 지원사업 담당 부서
+※ 자세한 신청방법 공고문 내 문의처 참조</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>첨부) → 각 시군 →, 신청장소 및 방법 :, 사업신청서 및 사업계획서 작성 후 해당 시, 군에 제출, 추진 일정 및 접수, 사 업 명, 공고기간, 접수기간</t>
+        </is>
+      </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>전북특별자치도 농식품산업과 푸드테크팀 063-280-3667 및 시군별 문의처 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr"/>
+      <c r="AD314" t="inlineStr">
+        <is>
+          <t>063-280-3667</t>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF314" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125490</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 웹툰기업 지원사업(패키지 지원) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>대구디지털혁신진흥원</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>이메일 접수 (yes1@dip.or.kr)
+※ 접수 후 확인 전화 필수 053-655-5604</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>초과하는 경우(단, 지원금이 1억원 원 이하인 과제는 제외)</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>1억원</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>사업 신청서 및 계획서 등 일체 ※ 후속 페이지 ‘, 목록’ 참조, 평가일정: 2026년 9월 1~2주차 중 예정, Ⅲ 지원대상 자격요건, 지원대상(공고일 기준), ※ 예: 창작 및 예술관련 서비스업, 만화 출판업, 콘텐츠 제작업 등</t>
+        </is>
+      </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>대구디지털혁신진흥원 053-655-5604, yes1@dip.or.kr</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>yes1@dip.or.kr</t>
+        </is>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>053-655-5604</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125489</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026년 대구콘텐츠코리아랩 추경 사업 미드폼 콘텐츠 제작지원사업 참가기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>대구디지털혁신진흥원</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>이메일 접수 (hmj@dip.or.kr)
+※ 접수확인 이메일을 순차적으로 발송 예정으로, 8/20(목) 16:00까지 회신 받지 못할 경우 연락 요청</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>❍ 지원규모: 1개사 / 35백만원</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>35백만원</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>제출 여부 확인 등, 적합성 검토 등, ∘ 발표자료 기반 발표평가, ∘ 예산편성 기준에 따른 사업비 조정 심의, ∘ 평균 70점 이상 고득점순으로 지원기업 선정, 차 발표평가, ※ 발표평가는 각 20분 예정(발표 10분 내외, 질의응답 10분 내외)</t>
+        </is>
+      </c>
+      <c r="AB316" t="inlineStr">
+        <is>
+          <t>대구디지털혁신진흥원 대구디지털혁신진흥원 053-215-4914, hmj@dip.or.kr</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>hmj@dip.or.kr</t>
+        </is>
+      </c>
+      <c r="AD316" t="inlineStr">
+        <is>
+          <t>053-215-4914</t>
+        </is>
+      </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF316" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125488</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 바이오플러스 인터펙스코리아 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>전남바이오진흥원</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>이메일 접수 (hyeonuk@jbf.kr)
+※ 이메일 신청 후 내선 확인 필수</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>m 기업당 9㎡ 내외 전시 공간 및 프로모션 제공(기업당 약 500만원 상당)</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>m 참가기업 신청서(붙임1), m 사업계획서, 전시회 참가 서약서, 개인정보 동의서 (붙임2), m 세부항목별 증빙자료(PDF 파일 별첨), 중소기업확인서 사본 필수 제출, ※ 결과보고서, 제한사항</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>전남바이오진흥원 경영기획본부 061-339-1318</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>hyeonuk@jbf.kr</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>061-339-1318</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125487</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026년 중소기업 제조물책임(PL)보험료 지원사업 신청 공고(7월 가입자)</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>중소기업중앙회</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>온라인 접수 (중소기업중앙회)
+※ 지역별 신청사이트 확인</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>지원금액 : 지원신청서 참조 (※다른사업과의 중복지원 불가)</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>① PL보험료 지원 신청서, ④ 회사명의 통장사본, ⑤ (인천 소재 기업) 매출액증빙 또는 수출실적증명, 문의 및 제출처, 중소기업중앙회 장, 전결 08/11, 과장조영근 실장, 이기중</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>중소기업중앙회 PL손해공제실 02-2124-4351, 4352, 4353, 4354</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>cyk81@kbiz.or.kr</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>02-2124-4351</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF318" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125486</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>[울산] 울주군 2026년 3차 중소기업 ESG 관리 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>울산지역산업진흥원</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>온라인 접수(지역산업진흥원 수혜기업 관리 시스템)</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>□ (지원규모) 예산소진 시 마감</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>(단계Ⅰ(ESG 교육)만 신청할 경우, [붙임 2-1] 서식만 제출), 구분, 비고, 필수 참가신청서 서식, 필수 개인정보 제공 수집 이용 동의서 서식, 필수 참가 서약서 서식, 필수 사업등록증사본 국세청 홈텍스</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>울산지역산업진흥원 ESG 관리 052-248-5767, twkim@riia.or.kr</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>twkim@riia.or.kr</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>052-248-5767</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125485</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 두바이 건축자재박람회(Big5) 공동관 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>청주상공회의소</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>온라인 접수 (충북 글로벌 마케팅 시스템)</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>O 참여기업 자부담금: 3696200원</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>3696200원</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>'1.통상촉진단 진행상태 접수중, OMIA: 두바이 월드 트레이드 센터, O 개최규모: 113</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>충청북도 국제통상과 043-220-3473 / 청주상공회의소 043-229-2720</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr"/>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>043-220-3473</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125484</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>[경기] 김포시 2026년 에너지효율시장 조성사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>김포산업지원센터</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>이메일 또는 우편 접수
+- 이메일 : dhkim@gopa.or.kr
+- 접수처 : 김포시 양촌읍 황금1로 122 5층 (재)김포산업지원센터</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>○ 지원규모 : 6개사 내외, 기업당 최대 1000만원 지원</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>1000만원</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>6개</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>및 기업현황 등 평가, 고득점순으로 선정, 동일 점수일 경우 정성평가 점수, 정량평가 점수순으로 선정, 지원 제외대상, 금융기관 등으로부터 금융불량 거래처로 규제 중인 기업, 휴·폐업 중인 기업, 신청서 및</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>김포산업지원센터 기업육성팀 070-4269-4085</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>dhkim@gopa.or.kr</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>070-4269-4085</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125482</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 흥해라 신라난전 참여 소상공인 모집 공고</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>대구경북디자인진흥원</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>온라인 접수 (흥해라 신라난전 홈페이지)
+※ 사업 신청기간이 시작되는 일시에 맞춰 홈페이지가 활성화 될 예정이니 확인부탁드립니다.</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>※수료증 및 보건증 제출 시기 : 최종 선정 후 2주 이내 제출</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>참가 신청서, 참가 서약서, 추천 확인서(해당시), 정보제공 동의서, 소상공인(중소기업)확인서, 각종 증빙 서류, 문의처 재 대구경북디자인진흥원 공공서비스디자인연구팀, 흥해라 신라난전 참가 서약서 필수 부</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>대구경북디자인진흥원 공공서비스디자인연구팀 053-740-0033</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>aaa@naver.com</t>
+        </is>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>053-740-0033</t>
+        </is>
+      </c>
+      <c r="AE322" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF322" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125481</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026년 블록체인 진흥주간 전시부스 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>한국인터넷진흥원</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-09-14</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>이메일 접수 (achain@kisa.or.kr)</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>(모집규모)</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>작성 후 이메일 접수(achain@kisa.or.kr), 참가신청서(붙임 참조), (문의처), (선정방법), 평가위원회를 통해 선정 예정, ※ 지원필요성, 기술경쟁력, 전시적합성 등을 고려하여 최종 선정 예정</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>한국인터넷진흥원 061-820-3921</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>achain@kisa.or.kr</t>
+        </is>
+      </c>
+      <c r="AD323" t="inlineStr">
+        <is>
+          <t>061-820-3921</t>
+        </is>
+      </c>
+      <c r="AE323" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF323" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125480</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026년 KOMICS Thailand 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>한국콘텐츠진흥원</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>온라인 접수 (콘텐츠수출마케팅플랫폼(WelCon))</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>&lt;지원내용&gt;&lt;&gt;</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr"/>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>(사업문의) 한국콘텐츠진흥원 만화웹툰산업팀 061-900-6432, hanakang@kocca.kr / (웰콘문의) WelCon Help Desk 1566-9984, welcon@kocca.kr</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>hanakang@kocca.kr</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>061-900-6432</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF324" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125479</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>대구 제품 런칭 패키지 수혜기업 모집 공고(제조전문형 메이커 스페이스 사업)</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>경북대학교 스타트업지원센터</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>이메일 접수 (cf4000@iact.or.kr) 
+※ 메일 제목 : 제품 런칭 패키지(포장)_기업명 / 제품 런칭 패키지(전시회)_기업명</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>(기업당 300만 원) (기업당 500만 원)</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>▢ 평가절차, ◦ (선정평가), 를 평가 기준에 따라 내·외부 전문가 서류, 으로 수혜기업 및 예비 순위 선정, 발생을 고려한 예비 순위 선정, (포장(패키지)제작) 최종 수혜기업 5개社, 예비 2개社 선정, (국내·외 전시회 참가) 최종 수혜기업 3개社</t>
+        </is>
+      </c>
+      <c r="AB325" t="inlineStr">
+        <is>
+          <t>경북대학교 스타트업지원센터 053-219-4105, cf4000@iact.or.kr</t>
+        </is>
+      </c>
+      <c r="AC325" t="inlineStr">
+        <is>
+          <t>cf4000@iact.or.kr</t>
+        </is>
+      </c>
+      <c r="AD325" t="inlineStr">
+        <is>
+          <t>053-219-4105</t>
+        </is>
+      </c>
+      <c r="AE325" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF325" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125478</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>[전남광주] AI어장 현장실증(시설ㆍ제품 고도화) 지원 모집 2차 연장 공고(AI기반 어장공간정보 빅데이터 플랫폼 구축 및 활용사업)</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>전남정보문화산업진흥원</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>이메일, 우편 또는 방문 접수
+- 이메일 : seo@jcia.or.kr
+- 접수처 : 전남광주통합특별시 목포시 대양산단로 200번길 107 (재)전남정보문화산업진흥원 AX지원팀</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>• 1인당 1일 최대 4시간(시간당 10만원으로 산정, 3시간 이상부터 과제사업비 사용결과 부당사용, 기타 협약의 해약사유가 발생될 경우,</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr"/>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>재무건전성 등, 선정평가(서류+발표) • 발표평가 : 추진계획 타당성, 기술성, 변환하여 자본으로 인정할 때 자본전액잠식이 아닌 경우, • 평가의견에 따른 수정 사업계획서 접수, • 과제 승인 및 협약, • 착수보고 : 과제별 착수보고, 사업비 집행 및 회계정산 교육 등</t>
+        </is>
+      </c>
+      <c r="AB326" t="inlineStr">
+        <is>
+          <t>전남정보문화산업진흥원 AX지원팀 061-280-7409</t>
+        </is>
+      </c>
+      <c r="AC326" t="inlineStr">
+        <is>
+          <t>seo@jcia.or.kr</t>
+        </is>
+      </c>
+      <c r="AD326" t="inlineStr">
+        <is>
+          <t>061-280-7409</t>
+        </is>
+      </c>
+      <c r="AE326" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF326" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125477</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>[경기] 군포시 2026년 4차 지식재산 긴급지원 사업(국내출원지원) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>경기지식재산센터</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>온라인 접수 (지원사업 신청시스템)</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>o 기업 당 2000만원 이내(지원금 합산 기준, 자부담 제외)</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>2000만원</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>신청서‧사업추진(활용)계획서 및 필수(선택), 지원절차, 지원규모, o 기업 당 2, 만원 이내(지원금 합산 기준, 자부담 제외), 기업분담금, o 기업분담금 : 40%</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>경기지식재산센터 군포시 지식재산 긴급지원 담당자 031-500-3061, 031-500-3048</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr"/>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>031-500-3048</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125476</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>대구 초도물량 양산 패키지 수혜기업 모집 공고(제조전문형 메이커 스페이스 사업)</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>경북대학교 스타트업지원센터</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>이메일 접수 (cf4000@iact.or.kr)
+※ 메일 제목 : 초도물량 양산 패키지_기업명</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>▢ 지원규모 : 3개社(기업당 최대 2천만 원 간접지원)</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>2천만원</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>를 평가 기준에 따라 내·외부 전문가 서면, ◦ (발표평가) 기업당 발표 10분, 질의응답 10분 실시, ▢ 평가기준, 평가항목 세부내용 배점, l 서류평가 진행 결격사유 유무, 적격 평가* 적/부, 누락</t>
+        </is>
+      </c>
+      <c r="AB328" t="inlineStr">
+        <is>
+          <t>경북대학교 스타트업지원센터 053-219-4105, cf4000@iact.or.kr</t>
+        </is>
+      </c>
+      <c r="AC328" t="inlineStr">
+        <is>
+          <t>cf4000@iact.or.kr</t>
+        </is>
+      </c>
+      <c r="AD328" t="inlineStr">
+        <is>
+          <t>053-219-4105</t>
+        </is>
+      </c>
+      <c r="AE328" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF328" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125475</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026년 4차 소상공인 물류 서비스 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>한국중소벤처기업유통원</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>온라인 접수 (판판대로)</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>**** 본 사업은 메뉴판 지원한도(600만원) 내에서 지원하는 사업으로, 예비 지원 대상이</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>600만원</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>소상공인확인서, 구 분 내 용 비 고, 소상공인 · 신청일 기준, 유효기간이 남아있어야만 인정 중소기업현황, 확인서 (소상공인으로 명시된 업체만 인정) 정보시스템, 국세 · 신청일 기준, 유효기간이 남아있어야만 인정 국세청, 지방세 · 신청일 기준</t>
+        </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>온판상담소 1899-0309</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr"/>
+      <c r="AD329" t="inlineStr"/>
+      <c r="AE329" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF329" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125473</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>[경기] 용인시 2026년 3차 소공인특화지원센터 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>용인시산업진흥원</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>온라인 접수 (소상공인24)</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>지원금액 총계 3천만원 이상 -3점 -</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>3천만원</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>서류 미비에 따른 불이익이 있을 수 있습니다., 사업개요, 지원규모: 총 2개 지원사업, 개사 내외, 지원자격: 아래 사항에 모두 해당하는 제조업 소공인, 용인 기흥구 영덕동, 하갈동, 구갈동</t>
+        </is>
+      </c>
+      <c r="AB330" t="inlineStr">
+        <is>
+          <t>(사업 관련 문의) 용인시산업진흥원 소공인특화지원센터 031-8067-5013 / (소상공인24 홈페이지 및 시스템 문의) 소상공인24 콜센터 1644-5302</t>
+        </is>
+      </c>
+      <c r="AC330" t="inlineStr"/>
+      <c r="AD330" t="inlineStr">
+        <is>
+          <t>031-8067-5013</t>
+        </is>
+      </c>
+      <c r="AE330" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF330" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125472</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>[부산] 맞춤형 AllSET 컨설팅 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>동서대학교</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>이메일 접수 (mihee009@gdsu.dongseo.ac.kr)</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>© 지원내용(규모, 혜택, 조건 등) : 전문가 매칭 후 1:1 컨설팅 지원 (무료)</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>기업진단 컨설팅 신청서, 가족회원 무/유료 신청서, ㅇ 문의처 순 :, 기관/부서 : 동서대학교 앵커사업단</t>
+        </is>
+      </c>
+      <c r="AB331" t="inlineStr">
+        <is>
+          <t>동서대학교 앵커사업단 mihee009@gdsu.dongseo.ac.kr 및 문의처 출처 바로가기 내 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC331" t="inlineStr">
+        <is>
+          <t>mihee009@gdsu.dongseo.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD331" t="inlineStr">
+        <is>
+          <t>011166009</t>
+        </is>
+      </c>
+      <c r="AE331" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF331" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125471</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>[전북] 남원시 2026년 국내외 개별 박람회 참가 지원사업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 남원시청 기업정책과</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>❍ 사 업 비 : 20백만원(시비) / * 자부담 20% 이상</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>20백만원</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr"/>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>(사본일 경우는 원본 대조필 날인), ④ [서식 4], ⑤ [서식 5] 지방보조사업자 관리카드, ⑥ [서식 6] 청렴이행서약서, [서식 1], 국내외 개별 박람회 참가 지원 사업 신청서, 참가기업, 현황</t>
+        </is>
+      </c>
+      <c r="AB332" t="inlineStr">
+        <is>
+          <t>남원시 기업정책과 기업지원팀 063-620-6645</t>
+        </is>
+      </c>
+      <c r="AC332" t="inlineStr"/>
+      <c r="AD332" t="inlineStr">
+        <is>
+          <t>063-620-6645</t>
+        </is>
+      </c>
+      <c r="AE332" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF332" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125470</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>[전북] 군산시 전담예술가와 우리가게 핫플레이스 만들기 소상공인 점포 모집 재공고</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>이메일 접수 (ysh3381@korea.kr)</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>금 325만원 지원</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>325만원</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>신청서 및, 임대차계약서 등), ※ 이메일 접수 시 파일명 :, 핫플레이스 만들기 참가 신청_점포명, ② 개인정보 수집·이용·제공에 관한 동의서 1부., ④ (필수) 임대차계약서 사본 1부., ⑤ (필수), 년) 각 1부.</t>
+        </is>
+      </c>
+      <c r="AB333" t="inlineStr">
+        <is>
+          <t>군산시 문화예술과 예술진흥계 063-454-3283</t>
+        </is>
+      </c>
+      <c r="AC333" t="inlineStr">
+        <is>
+          <t>ysh3381@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD333" t="inlineStr">
+        <is>
+          <t>063-454-3283</t>
+        </is>
+      </c>
+      <c r="AE333" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF333" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125469</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>[충남] 예산군 착한가격업소 소규모 시설개선 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>방문, 우편 접수
+- 접수처 : 예산군 예산읍 군청로 22 예산군청 경제과 경제팀 / 우편번호 32435 (예산군청 경제과 경제팀(6층))</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>- 지원금액 : 업체별 최대 1000만원 한도</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>1000만원</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr"/>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>사각형입니다., ❍ 접수방법 : 방문·등기우편, ※ 근무시간 중 접수(공휴일 제외), 등기우편은 접수마감일 18:00까지 도착 시 유효, 접수장소 : 예산군청 경제과 경제팀(6층), 사업신청서, 사업계획서, 개인정보 제공 동의서 각 1부 &amp;lt;서식 1</t>
+        </is>
+      </c>
+      <c r="AB334" t="inlineStr">
+        <is>
+          <t>예산군 경제과 041-339-7253</t>
+        </is>
+      </c>
+      <c r="AC334" t="inlineStr"/>
+      <c r="AD334" t="inlineStr">
+        <is>
+          <t>041-339-7253</t>
+        </is>
+      </c>
+      <c r="AE334" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF334" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125468</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>[충남] 청양군 2026년 5차 음식점 시설개선 지원사업 계획 공고</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 청양군청 행복민원과(위생팀)</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>m 총 개·보수비용의 60% 지원(1개소 당 500만원 한도)</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>점검 및 현장 확인, m 지원 제외 대상, 각종 세금 및 과태료 등을 체납 중인 자, 영업 신고 기간(지위승계 후)이 2년 미만인 업소(단, 가족간 지위승계는 제외), 소재지 이전으로 인한 주방 시설을 구비하고자 하는 경우, 사업 내용에 부합하지 않은 업소, 신청방법 및</t>
+        </is>
+      </c>
+      <c r="AB335" t="inlineStr">
+        <is>
+          <t>청양군청 행복민원과 위생팀 041-940-2183</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr"/>
+      <c r="AD335" t="inlineStr">
+        <is>
+          <t>041-940-2183</t>
+        </is>
+      </c>
+      <c r="AE335" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF335" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125467</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026년 3차 기술유출방지시스템 구축사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>대중소기업농어업협력재단</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>온라인 접수 (기술보호울타리 홈페이지)</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>자체관리형 5천만원 ❹온프레미스 구독형 보안 80% 온프레미스 구독형</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>5천만원</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>항만운송사업 관련 등록증), ② 항만시설 전용사용승낙서, 신항 배후단지 입주 관련 실시 협약서, ③ 전년도 부산항 이용실적증명서(한국무역통계진흥원) 등, ✓ 인천국제공항공사 우대사항, ※ 민간분야의 경우, 신청기업이 상생협력기금 출연기관과 사업 참여 및 기금, 연계를 사전에 협의한 후 신청하여야 함</t>
+        </is>
+      </c>
+      <c r="AB336" t="inlineStr">
+        <is>
+          <t>대ㆍ중소기업ㆍ농어업협력재단 기술보호지원부 02-368-8916, 8724 / prevention@win-win.or.kr</t>
+        </is>
+      </c>
+      <c r="AC336" t="inlineStr">
+        <is>
+          <t>prevention@win-win.or.kr</t>
+        </is>
+      </c>
+      <c r="AD336" t="inlineStr">
+        <is>
+          <t>02-368-8916</t>
+        </is>
+      </c>
+      <c r="AE336" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF336" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125466</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>[전북] 임실군 2026년 사회적기업 자치단체 지역특화사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>방문 또는 이메일 접수
+- 접수처 : 임실군청 경제교통과(2층) 민생경제팀
+- 이메일 : wlsdl9416@korea.kr</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>❍ 총사업비 : 15백만원(도 4.</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>15백만원</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>※ 주민등록번호 13자리 모두 기재, 공고일 이후 발급분 제출(공고일 포함), 연번 서류명 비고, 사업 신청서 1부 서식 1, 사업 계획서 1부 서식 2, 예산운용계획서 1부 서식 3, 유사사업 수행실적(최근 3년간) 서식 4, 지방보조사업자 관리카드 서식 5</t>
+        </is>
+      </c>
+      <c r="AB337" t="inlineStr">
+        <is>
+          <t>임실군청 경제교통과 063-640-2406</t>
+        </is>
+      </c>
+      <c r="AC337" t="inlineStr">
+        <is>
+          <t>wlsdl9416@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD337" t="inlineStr">
+        <is>
+          <t>063-640-2406</t>
+        </is>
+      </c>
+      <c r="AE337" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF337" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125465</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>[전북] 김제시 2026년 사회적경제 판로지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-18</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>방문 또는 이메일 접수
+- 접수처 : 김제시 사회연대경제지원센터(김제시 보건소 지하 1층)
+- 이메일 : gimjese@naver.com</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>❍ (사 업 비) 20백만원</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>20백만원</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>[서식1~5]신청서 등 각 1부, 기타 증빙자료(별첨 참고), Ⅲ 선 정 기 준, ❍ (선정방법) 서면심사, 평가항목 평가지표 배점 점수, ￭ 사업비 및 세부 사업계획, 내용이 적정한가? 15, 사업내용의</t>
+        </is>
+      </c>
+      <c r="AB338" t="inlineStr">
+        <is>
+          <t>김제시 사회연대경제지원센터 063-540-6932, 6933</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>gimjese@naver.com</t>
+        </is>
+      </c>
+      <c r="AD338" t="inlineStr">
+        <is>
+          <t>063-540-6932</t>
+        </is>
+      </c>
+      <c r="AE338" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF338" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125464</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026년 3차 전력산업정책개발 신규지원 대상과제 2차 재공고 </t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>한국전력공사</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>온라인 전산등록 및 우편ㆍ방문 접수
+- 온라인 : 전력기금사업단
+- 접수처 : 서울시 영등포구 국회대로 62길 25, (우) 07236 교육시설공제회관 3층 전력기금사업단 기반사업부
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>ㅇ 34000000원</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>34000000원</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>사업계획서 원본 1부, 주관, 기타 증빙서류, (기관 및 참여 연구원의 연구실적 등), 기 타, 계약으로 함, ㅇ 총괄책임자는 주관기관에 소속된 자를 원칙으로 함, 는 반환하지 않으며</t>
+        </is>
+      </c>
+      <c r="AB339" t="inlineStr">
+        <is>
+          <t>한국전력공사 전력기금사업단 기반사업부 02-6007-0363, 0364 / 전산등록 문의처 02-6007-0359</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr"/>
+      <c r="AD339" t="inlineStr">
+        <is>
+          <t>02-6007-0359</t>
+        </is>
+      </c>
+      <c r="AE339" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF339" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125463</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026년 소프트웨어 산업발전 유공자 포상계획 재연장 공고</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>정보통신산업진흥원</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>이메일 접수 (swsubmit@nipa.kr)</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr"/>
+      <c r="AB340" t="inlineStr">
+        <is>
+          <t>정보통신산업진흥원 043-931-5317, swsubmit@nipa.kr</t>
+        </is>
+      </c>
+      <c r="AC340" t="inlineStr">
+        <is>
+          <t>swsubmit@nipa.kr</t>
+        </is>
+      </c>
+      <c r="AD340" t="inlineStr">
+        <is>
+          <t>043-931-5317</t>
+        </is>
+      </c>
+      <c r="AE340" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF340" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125462</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026년 2차 로봇산업기술개발사업 신규지원 대상과제 공고</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>한국산업기술기획평가원</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>온라인 접수 (범부처통합연구지원시스템)</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>공고예산 100억원</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>100억원</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>사항, 기타 유의 사항, 문의처, 사업개요, 사업목적, 지원하여 산업경쟁력을 제고하고 미래 신산업을 육성, (로봇산업핵심기술개발) 제조로봇, 서비스로봇 등 다양한 로봇 응용분야에서 성장이</t>
+        </is>
+      </c>
+      <c r="AB341" t="inlineStr">
+        <is>
+          <t>한국산업기술기획평가원 AI기계 로봇실 053-718-8392 외 문의처 공고문 참조 / 로봇PD 053-718-8432, ektmfla97@keit.re.kr / 범부처통합연구지원시스템 고객센터 1877-2041 / R&amp;D상담콜센터 1544 - 6633</t>
+        </is>
+      </c>
+      <c r="AC341" t="inlineStr">
+        <is>
+          <t>ektmfla97@keit.re.kr</t>
+        </is>
+      </c>
+      <c r="AD341" t="inlineStr">
+        <is>
+          <t>053-718-8392</t>
+        </is>
+      </c>
+      <c r="AE341" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF341" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125461</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>[서울] 2026년 서울창업허브M+ 글로벌 오픈 이노베이션 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>서울경제진흥원</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>온라인 접수 (서울창업허브M+)</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>③ 현지 PoC 수행비용 지원 (기업당 최대 1000만원)</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>1000만원</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>기반 평가, 발표평가 9. 22.(화) 발표 기반 평가, 선정 결과 안내 9. 23.(수) 선정 결과 안내, 보고서 제공 11월 중 시장분석 보고서, PoC 결과보고서 제공, 모집개요, ❍ 모집기간: ~ 9. 11.(금) 23시 59분까지, • 신산업분야의 경우 10년 이내</t>
+        </is>
+      </c>
+      <c r="AB342" t="inlineStr">
+        <is>
+          <t>서울경제진흥원 클러스터혁신팀 02-6958-9107, jamie@sba.seoul.kr</t>
+        </is>
+      </c>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>jamie@sba.seoul.kr</t>
+        </is>
+      </c>
+      <c r="AD342" t="inlineStr">
+        <is>
+          <t>02-6958-9107</t>
+        </is>
+      </c>
+      <c r="AE342" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF342" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125460</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>AI 기반 지역관광 문제해결 프로젝트(역사문화형) 참여 모집 공고</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>한국관광공사</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>온라인 접수 (온오프믹스)</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>90백만원 십리벚꽃길,</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>90백만원</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr"/>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>양식 [붙임3] 참고, 구분 필수제출 선택제출, ① 참가신청서 및 기술기획서 전체본, 및 요약본 각 1부(PPT), 예산산출내역, 수행인력리스트 등 포함, ⑩기술 관련 인증확인서 및 포트, ② 개인정보 수집·활용 동의서</t>
+        </is>
+      </c>
+      <c r="AB343" t="inlineStr">
+        <is>
+          <t>(신청 문의) 오픈 이노베이션 사무국 070-5089-0454, 2026xlab@gmail.com / (사업 및 과제내용 문의) 한국관광공사 트래블X-Lab 033-738-3693, 3687</t>
+        </is>
+      </c>
+      <c r="AC343" t="inlineStr">
+        <is>
+          <t>2026xlab@gmail.com</t>
+        </is>
+      </c>
+      <c r="AD343" t="inlineStr">
+        <is>
+          <t>033-738-3693</t>
+        </is>
+      </c>
+      <c r="AE343" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF343" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125459</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026년 충북청주강소연구개발특구 연구소기업 전주기 통합지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>충북대학교 산학협력단</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>세부사업별 상이</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>이메일 접수 (gangso@cbnu.ac.kr)</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>지원규모 8개 사 이내 기업당 최대 30백만원 이내 4개 사 이내 기업당 최대 10백만원 이내</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>30백만원</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>8개</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>공고문 및 신청서 양식 다운로드, ※ 모든 서류는 공고일 기준, 직전 3개월 이내 발급된 서류 제출 필수, 구분, 비고, 참여 신청서 필수(붙임 1), 사업계획서 필수(붙임 2), 신청자격 적정성 확인서 필수(붙임 3)</t>
+        </is>
+      </c>
+      <c r="AB344" t="inlineStr">
+        <is>
+          <t>충북대학교 산학협력단 강소특구지원센터 043-249-1474, seqnws@cbnu.ac.kr</t>
+        </is>
+      </c>
+      <c r="AC344" t="inlineStr">
+        <is>
+          <t>seqnws@cbnu.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD344" t="inlineStr">
+        <is>
+          <t>043-249-1474</t>
+        </is>
+      </c>
+      <c r="AE344" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF344" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125458</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>[서울] 2026년 서울창업허브 공덕 웹서밋(Web Summit 2026) 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>서울경제진흥원</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>온라인 접수 (스타트업플러스)</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>q 글로벌 시장 진출을 위한 사업화 지원금 350만 원</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>350만원</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr"/>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>연번 구분 서류명 내용, 사업계획서 국·영문 사업 계획서(통합파일) 1부, 영문 기업 소개 내용이 포함된 IR deck 1부, (팀 구성, 제품/서비스, 비즈니스 모델, 및 주요 성장 지표 포함), 필수</t>
+        </is>
+      </c>
+      <c r="AB345" t="inlineStr">
+        <is>
+          <t>서울경제진흥원 스케일업1팀 02-2115-2012, hylee1014@sba.seoul.kr</t>
+        </is>
+      </c>
+      <c r="AC345" t="inlineStr">
+        <is>
+          <t>hylee1014@sba.seoul.kr</t>
+        </is>
+      </c>
+      <c r="AD345" t="inlineStr">
+        <is>
+          <t>02-2115-2012</t>
+        </is>
+      </c>
+      <c r="AE345" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF345" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125457</t>
         </is>
       </c>
     </row>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -47507,8 +47507,6 @@
           <t>m 지원내용 : 기업 전용 5G 기반 통신망 지원</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr">
         <is>
           <t>Y</t>
@@ -47668,7 +47666,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr">
         <is>
           <t>Y</t>
@@ -47829,7 +47826,6 @@
           <t>1억원</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr">
         <is>
           <t>Y</t>
@@ -48306,7 +48302,6 @@
           <t>□ (지원규모) 6개사 정도</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
           <t>6개</t>
@@ -48628,8 +48623,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr"/>
-      <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
         <is>
           <t>N</t>
@@ -48735,7 +48728,6 @@
           <t>전북특별자치도 농식품산업과 푸드테크팀 063-280-3667 및 시군별 문의처 공고문 참조</t>
         </is>
       </c>
-      <c r="AC314" t="inlineStr"/>
       <c r="AD314" t="inlineStr">
         <is>
           <t>063-280-3667</t>
@@ -48784,7 +48776,6 @@
           <t>1억원</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr">
         <is>
           <t>Y</t>
@@ -49106,7 +49097,6 @@
           <t>500만원</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr">
         <is>
           <t>Y</t>
@@ -49260,8 +49250,6 @@
           <t>지원금액 : 지원신청서 참조 (※다른사업과의 중복지원 불가)</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr"/>
-      <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr">
         <is>
           <t>Y</t>
@@ -49414,8 +49402,6 @@
           <t>□ (지원규모) 예산소진 시 마감</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr"/>
-      <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr">
         <is>
           <t>N</t>
@@ -49573,7 +49559,6 @@
           <t>3696200원</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr">
         <is>
           <t>N</t>
@@ -49679,7 +49664,6 @@
           <t>충청북도 국제통상과 043-220-3473 / 청주상공회의소 043-229-2720</t>
         </is>
       </c>
-      <c r="AC320" t="inlineStr"/>
       <c r="AD320" t="inlineStr">
         <is>
           <t>043-220-3473</t>
@@ -49887,8 +49871,6 @@
           <t>※수료증 및 보건증 제출 시기 : 최종 선정 후 2주 이내 제출</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr"/>
-      <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr">
         <is>
           <t>Y</t>
@@ -50041,8 +50023,6 @@
           <t>(모집규모)</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr"/>
-      <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr">
         <is>
           <t>N</t>
@@ -50195,8 +50175,6 @@
           <t>&lt;지원내용&gt;&lt;&gt;</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr">
         <is>
           <t>N</t>
@@ -50292,7 +50270,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA324" t="inlineStr"/>
       <c r="AB324" t="inlineStr">
         <is>
           <t>(사업문의) 한국콘텐츠진흥원 만화웹툰산업팀 061-900-6432, hanakang@kocca.kr / (웰콘문의) WelCon Help Desk 1566-9984, welcon@kocca.kr</t>
@@ -50351,7 +50328,6 @@
           <t>500만원</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr">
         <is>
           <t>Y</t>
@@ -50511,7 +50487,6 @@
           <t>10만원</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr">
         <is>
           <t>Y</t>
@@ -50669,7 +50644,6 @@
           <t>2000만원</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr">
         <is>
           <t>N</t>
@@ -50775,7 +50749,6 @@
           <t>경기지식재산센터 군포시 지식재산 긴급지원 담당자 031-500-3061, 031-500-3048</t>
         </is>
       </c>
-      <c r="AC327" t="inlineStr"/>
       <c r="AD327" t="inlineStr">
         <is>
           <t>031-500-3048</t>
@@ -50986,7 +50959,6 @@
           <t>600만원</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr">
         <is>
           <t>Y</t>
@@ -51092,8 +51064,6 @@
           <t>온판상담소 1899-0309</t>
         </is>
       </c>
-      <c r="AC329" t="inlineStr"/>
-      <c r="AD329" t="inlineStr"/>
       <c r="AE329" t="inlineStr">
         <is>
           <t>소상공인</t>
@@ -51136,7 +51106,6 @@
           <t>3천만원</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr">
         <is>
           <t>Y</t>
@@ -51242,7 +51211,6 @@
           <t>(사업 관련 문의) 용인시산업진흥원 소공인특화지원센터 031-8067-5013 / (소상공인24 홈페이지 및 시스템 문의) 소상공인24 콜센터 1644-5302</t>
         </is>
       </c>
-      <c r="AC330" t="inlineStr"/>
       <c r="AD330" t="inlineStr">
         <is>
           <t>031-8067-5013</t>
@@ -51285,8 +51253,6 @@
           <t>© 지원내용(규모, 혜택, 조건 등) : 전문가 매칭 후 1:1 컨설팅 지원 (무료)</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr"/>
-      <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr">
         <is>
           <t>N</t>
@@ -51445,7 +51411,6 @@
           <t>20백만원</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr">
         <is>
           <t>Y</t>
@@ -51551,7 +51516,6 @@
           <t>남원시 기업정책과 기업지원팀 063-620-6645</t>
         </is>
       </c>
-      <c r="AC332" t="inlineStr"/>
       <c r="AD332" t="inlineStr">
         <is>
           <t>063-620-6645</t>
@@ -51599,7 +51563,6 @@
           <t>325만원</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr">
         <is>
           <t>Y</t>
@@ -51758,7 +51721,6 @@
           <t>1000만원</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr">
         <is>
           <t>Y</t>
@@ -51864,7 +51826,6 @@
           <t>예산군 경제과 041-339-7253</t>
         </is>
       </c>
-      <c r="AC334" t="inlineStr"/>
       <c r="AD334" t="inlineStr">
         <is>
           <t>041-339-7253</t>
@@ -52023,7 +51984,6 @@
           <t>청양군청 행복민원과 위생팀 041-940-2183</t>
         </is>
       </c>
-      <c r="AC335" t="inlineStr"/>
       <c r="AD335" t="inlineStr">
         <is>
           <t>041-940-2183</t>
@@ -52071,7 +52031,6 @@
           <t>5천만원</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr">
         <is>
           <t>Y</t>
@@ -52231,7 +52190,6 @@
           <t>15백만원</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr"/>
       <c r="H337" t="inlineStr">
         <is>
           <t>Y</t>
@@ -52391,7 +52349,6 @@
           <t>20백만원</t>
         </is>
       </c>
-      <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr">
         <is>
           <t>Y</t>
@@ -52552,7 +52509,6 @@
           <t>34000000원</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr">
         <is>
           <t>Y</t>
@@ -52658,7 +52614,6 @@
           <t>한국전력공사 전력기금사업단 기반사업부 02-6007-0363, 0364 / 전산등록 문의처 02-6007-0359</t>
         </is>
       </c>
-      <c r="AC339" t="inlineStr"/>
       <c r="AD339" t="inlineStr">
         <is>
           <t>02-6007-0359</t>
@@ -52701,8 +52656,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
       <c r="H340" t="inlineStr">
         <is>
           <t>N</t>
@@ -52798,7 +52751,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA340" t="inlineStr"/>
       <c r="AB340" t="inlineStr">
         <is>
           <t>정보통신산업진흥원 043-931-5317, swsubmit@nipa.kr</t>
@@ -52856,7 +52808,6 @@
           <t>100억원</t>
         </is>
       </c>
-      <c r="G341" t="inlineStr"/>
       <c r="H341" t="inlineStr">
         <is>
           <t>N</t>
@@ -53014,7 +52965,6 @@
           <t>1000만원</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr"/>
       <c r="H342" t="inlineStr">
         <is>
           <t>Y</t>
@@ -53172,7 +53122,6 @@
           <t>90백만원</t>
         </is>
       </c>
-      <c r="G343" t="inlineStr"/>
       <c r="H343" t="inlineStr">
         <is>
           <t>Y</t>
@@ -53492,7 +53441,6 @@
           <t>350만원</t>
         </is>
       </c>
-      <c r="G345" t="inlineStr"/>
       <c r="H345" t="inlineStr">
         <is>
           <t>Y</t>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF345"/>
+  <dimension ref="A1:AF392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53567,6 +53567,7323 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026년 제조전문형 메이커스페이스 제조창업지원 양산연계 지원프로그램 모집 공고</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>전남대학교</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>이메일 접수 (info@mandulmaru.net)</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>□ 지원내용 : 양산화 과정에 필요한 단계별 재료 및 제조 지원 및 컨설팅(최대 4000천원)</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr"/>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr"/>
+      <c r="AB346" t="inlineStr">
+        <is>
+          <t>전남대학교 만들마루 062-530-5059, info@mandulmaru.net</t>
+        </is>
+      </c>
+      <c r="AC346" t="inlineStr">
+        <is>
+          <t>info@mandulmaru.net</t>
+        </is>
+      </c>
+      <c r="AD346" t="inlineStr">
+        <is>
+          <t>062-530-5059</t>
+        </is>
+      </c>
+      <c r="AE346" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF346" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125549</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026년 일본 오사카(간사이) 지역 진출 지원사업 Plug in Osaka #12 참가 스타트업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>부산창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>이메일 접수(daeun@ccei.kr)</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>◦ (항공료) 기업당 1인 왕복 항공료 실비 지원(최대 40만원)</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>40만원</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr"/>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>부산창조경제혁신센터 홈페이지에서 양식 다운로드, 구 분, · [붙임3] 개인정보 수집 및 이용 동의서, 필수, · 법인등기사항전부증명서 1부, · 영어 기업 소개자료, 해당 시 · 일본어 또는 국문 기업/제품 소개자료, 지원 내용</t>
+        </is>
+      </c>
+      <c r="AB347" t="inlineStr">
+        <is>
+          <t>부산창조경제혁신센터 글로벌OI팀 (사업 관련 및 전국소재 신청 문의) 051-749-8930, daeun@ccei.kr / (부산소재 신청 문의) 051-749-8947, bkkim@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AC347" t="inlineStr">
+        <is>
+          <t>bkkim@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AD347" t="inlineStr">
+        <is>
+          <t>051-749-8930</t>
+        </is>
+      </c>
+      <c r="AE347" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF347" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125548</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 경북도청 추석 특별판매전 참가업체 모집 공고</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>경상북도청년CEO협회</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>이메일 접수 (kyceo@kyceo.or.kr)</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>지원내용</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr"/>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>신청서(양식), 제품사진, 지원내용, 참가업체 판매를 위한 행사 부스(판매부스, 테이블, 의자 등) 제공, (현수막, 전단지</t>
+        </is>
+      </c>
+      <c r="AB348" t="inlineStr">
+        <is>
+          <t>경상북도청년CEO협회 문의처 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC348" t="inlineStr">
+        <is>
+          <t>kyceo@kyceo.or.kr</t>
+        </is>
+      </c>
+      <c r="AD348" t="inlineStr">
+        <is>
+          <t>010-9864-9880</t>
+        </is>
+      </c>
+      <c r="AE348" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF348" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125547</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 캐릭터 글로벌 진입 프로젝트 참가자 추가 모집 공고(대구콘텐츠코리아랩)</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>대구디지털혁신진흥원</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>이메일 접수 (dgckl@dip.or.kr)
+※ 접수확인 이메일을 회신 받아야 최종 접수 완료됨
+※ 접수확인 이메일은 순차적으로 발송 예정으로, 8/28(금) 16:00까지 회신 받지 못할 경우 연락 요청</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>❍ 지원규모: 2개사 내외</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>※ 접수확인 이메일을 회신 받아야 최종 접수 완료됨, ※ 접수확인 이메일은 순차적으로 발송 예정으로, ❍ 신청 참고사항, ∘ 신청기한 준수, 기한 초과 시 절대 접수 불가, 는 추가 제출 또는 보완 불가, 는 1개월 이내 발급일에 한해 인정되며, 제출한 서류는 일제 반환하지 않음</t>
+        </is>
+      </c>
+      <c r="AB349" t="inlineStr">
+        <is>
+          <t>대구디지털혁신진흥원 사업담당자 053-215-4914 / hmj@dip.or.kr, dgckl@dip.or.kr</t>
+        </is>
+      </c>
+      <c r="AC349" t="inlineStr">
+        <is>
+          <t>dgckl@dip.or.kr</t>
+        </is>
+      </c>
+      <c r="AD349" t="inlineStr">
+        <is>
+          <t>053-215-4914</t>
+        </is>
+      </c>
+      <c r="AE349" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF349" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125546</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 5차 정보보호기업 성장지원(창업ㆍ벤처육성, 사업화) 모집 공고(충청권 지역거점 정보보호 클러스터 구축사업)</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>대전정보문화산업진흥원</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>온라인 접수 (DICIA 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr"/>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr"/>
+      <c r="AB350" t="inlineStr">
+        <is>
+          <t>대전정보문화산업진흥원 AI혁신추진단 042-479-4142, jsy@dicia.or.kr</t>
+        </is>
+      </c>
+      <c r="AC350" t="inlineStr">
+        <is>
+          <t>jsy@dicia.or.kr</t>
+        </is>
+      </c>
+      <c r="AD350" t="inlineStr">
+        <is>
+          <t>042-479-4142</t>
+        </is>
+      </c>
+      <c r="AE350" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF350" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125545</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 6차 전시회 단체 참가지원 코리아 비즈니스 엑스포 선전 전시회 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>전북특별자치도경제통상진흥원</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>온라인 접수(전북특별자치도 수출통합지원시스템)</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>❍ 모집규모 : 8개사 정도</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>8개</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>p이내 작성), ❍ (필수) 상품자료([붙임2] 참조), ❍ (필수) 전시회 참가서약서 1부 ([붙임3] 참조), ❍ (필수) 수출실적증명서(2025년)*, 수출신고필증(관세청), 수출실적증명서(한국무역통계진흥원), 수출실적의 확인 및 증명, 발급신청서(한국무역협회) 중 택 1</t>
+        </is>
+      </c>
+      <c r="AB351" t="inlineStr">
+        <is>
+          <t>전북특별자치도경제통상진흥원 수출지원팀 063-711-2051, hse@jbba.kr</t>
+        </is>
+      </c>
+      <c r="AC351" t="inlineStr">
+        <is>
+          <t>hse@jbba.kr</t>
+        </is>
+      </c>
+      <c r="AD351" t="inlineStr">
+        <is>
+          <t>063-711-2051</t>
+        </is>
+      </c>
+      <c r="AE351" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF351" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125544</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>[강원] 양양군 2026년 2차 중소기업 수출경쟁력 강화 지원사업 참가기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>강원특별자치도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>이메일 접수 (dnwls0801@gwep.or.kr)</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>○ 지원규모 : 2개 기업 내외</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>&lt;구분&gt;&lt;주요내용&gt;&lt;비고&gt;, &lt;필수제출&gt;&lt;① 지원사업 신청서(양식 1) ② &gt;</t>
+        </is>
+      </c>
+      <c r="AB352" t="inlineStr">
+        <is>
+          <t>강원특별자치도경제진흥원 전략사업부 033-749-3359</t>
+        </is>
+      </c>
+      <c r="AC352" t="inlineStr">
+        <is>
+          <t>dnwls0801@gwep.or.kr</t>
+        </is>
+      </c>
+      <c r="AD352" t="inlineStr">
+        <is>
+          <t>033-749-3359</t>
+        </is>
+      </c>
+      <c r="AE352" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF352" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125543</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026년 2차 강원 영동권 관광 가치이음 지원사업 모집 변경 공고</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>강원특별자치도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>이메일 접수 (wm6515643@gwep.or.kr)
+※ 파일명 : (기업명) 영동권 관광가치 이음 지원사업(관광)</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>총 2000만원 지원금 운영 결과보고서 및</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>2000만원</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>(6종) 작성 후 이메일 제출·신청, 이메일 : wm6515643@gwep.or.kr, 대상자 선정결과 공고, 강원특별자치도경제진흥원 홈페이지 공고( 및, 선정자 개별 문자 안내, 신청자격, 신청자격 및 제외대상, 구분 세부 내용</t>
+        </is>
+      </c>
+      <c r="AB353" t="inlineStr">
+        <is>
+          <t>강원특별자치도경제진흥원 성장지원부 033-749-3396, 033-749-2606, wm6515643@gwep.or.kr</t>
+        </is>
+      </c>
+      <c r="AC353" t="inlineStr">
+        <is>
+          <t>wm6515643@gwep.or.kr</t>
+        </is>
+      </c>
+      <c r="AD353" t="inlineStr">
+        <is>
+          <t>033-749-2606</t>
+        </is>
+      </c>
+      <c r="AE353" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF353" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125542</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026년 4차 벤처기업 공동채용 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>벤처기업협회</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>온라인 접수 (신청폼)</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr"/>
+      <c r="AB354" t="inlineStr">
+        <is>
+          <t>벤처기업협회 혁신인재본부 02-6331-7051, job@v-job.or.kr</t>
+        </is>
+      </c>
+      <c r="AC354" t="inlineStr">
+        <is>
+          <t>job@v-job.or.kr</t>
+        </is>
+      </c>
+      <c r="AD354" t="inlineStr">
+        <is>
+          <t>02-6331-7051</t>
+        </is>
+      </c>
+      <c r="AE354" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF354" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125541</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>[강원] 횡성군 2026년 2차 중소기업 수출경쟁력 강화 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>강원특별자치도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>이메일 접수 (gwep3362@naver.com)</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>&lt;해외 인증마크 획득 및 현지화&gt;&lt; - 해외 인증마크 획득에 소요되는 비용 지원   ‧ 컨설팅비, 시험비, 심사비   ‧ 재인증 지원 가능   ‧ 단, 인증마크 최종 획득 시에만 지원 가능(결과 보고 시, 인증서 제출 必)  - 해외 현지 규정에 맞는 라벨 제작 비용 및 라벨링에 필요한 검사비(영양성분검사 등) 지원  - 기업당 최대 200만원 한도 내 지원&gt;&lt;세금계산서 공급가액의 80% 지원, VAT등 기타금액 기업 자부담&gt;</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>200만원</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA355" t="inlineStr"/>
+      <c r="AB355" t="inlineStr">
+        <is>
+          <t>강원특별자치도경제진흥원 전략사업부 033-749-3387</t>
+        </is>
+      </c>
+      <c r="AC355" t="inlineStr"/>
+      <c r="AD355" t="inlineStr">
+        <is>
+          <t>033-749-3387</t>
+        </is>
+      </c>
+      <c r="AE355" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF355" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125540</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>[경북] 포항시 2026년 온라인 셀러 성장 지원기업 추가 모집 공고(온라인 판로 지원사업)</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jhrin5199@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 10개사 정도</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>연번, 제출 비고, 참가신청서 외(양식) 각 1부 붙임, 국세, 년 부가가치세표준증명원 1부, 공장등록증 또는 건물건축물대장 1부, 보유 인증서 및 특허 등 각 1부, ❍ 지원 제외대상</t>
+        </is>
+      </c>
+      <c r="AB356" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 마케팅팀 054-470-8574, jhrin5199@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AC356" t="inlineStr">
+        <is>
+          <t>jhrin5199@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD356" t="inlineStr">
+        <is>
+          <t>054-470-8574</t>
+        </is>
+      </c>
+      <c r="AE356" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF356" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125539</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026년 6차 관계부처 해외홍보관(UAE) 콘텐츠존 입점기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>한국콘텐츠진흥원</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>이메일 접수(korea360uae.op@gmail.com)</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>□ 주요 지원내용</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>(양식) 다운로드 및 이메일, 신청 → korea360uae.op@gmail.com, 첨부 → ④ 제출, 구분, 필수 선택 비고, 서류 (hwp) 문서작성, ② (양식2) 입점희망상품 목록 ● 양식#2 / 엑셀, (최대 10개 품목 소개) (xlsx) 문서작성</t>
+        </is>
+      </c>
+      <c r="AB357" t="inlineStr">
+        <is>
+          <t>KOREA360 Help Desk +971-4-261-3206(한국시간 기준 14:00 – 20:00 까지), korea360uae.op@gmail.com</t>
+        </is>
+      </c>
+      <c r="AC357" t="inlineStr">
+        <is>
+          <t>korea360uae.op@gmail.com</t>
+        </is>
+      </c>
+      <c r="AD357" t="inlineStr"/>
+      <c r="AE357" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF357" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125538</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>[경북] 포항시 2026년 AI라이브커머스 지원기업 추가 모집 공고(온라인 판로 지원사업)</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jhrin5199@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 10개사 정도</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>연번, 제출 비고, 참가신청서 외(양식) 각 1부 붙임, 통신판매업신고증 1부, 국세, 년 부가가치세표준증명원 1부, 공장등록증 또는 건물건축물대장 1부, 보유 인증서 및 특허 등 각 1부</t>
+        </is>
+      </c>
+      <c r="AB358" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 마케팅팀 054-470-8574, jhrin5199@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AC358" t="inlineStr">
+        <is>
+          <t>jhrin5199@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD358" t="inlineStr">
+        <is>
+          <t>054-470-8574</t>
+        </is>
+      </c>
+      <c r="AE358" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF358" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125537</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>[충남] 2026년 사회적경제기업 희망드림 판매전 참가기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>충남경제진흥원</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>온라인 접수 (충남경제진흥원 통합지원시스템)</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>- 오프라인 판매전 이벤트 경품 제공(소비자가 10만 원 이내)</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>국세‧지방세 납입증명서, 제품 카탈로그 및 기업 포트폴리오, 희망드림판매전 상품 리스트(붙임 5), 통신판매업신고증, 선택서류, (해당 시), 위탁생산 공장등록증, 제작 의뢰 계약서 등</t>
+        </is>
+      </c>
+      <c r="AB359" t="inlineStr">
+        <is>
+          <t>충남경제진흥원 041-404-1374, 1372 / cepa_mkt@naver.com</t>
+        </is>
+      </c>
+      <c r="AC359" t="inlineStr">
+        <is>
+          <t>cepa_mkt@naver.com</t>
+        </is>
+      </c>
+      <c r="AD359" t="inlineStr">
+        <is>
+          <t>041-404-1374</t>
+        </is>
+      </c>
+      <c r="AE359" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF359" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125536</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026년 GP Switzerland AI 부품 산업자동화 파트너십 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2026-08-17 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>온라인 접수 (무역투자24, 구글폼)
+※ 무역투자24, 구글폼(bit.ly/2026GPSwiss) 모두를 완료 요망
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>11) 최종 선정기업 발표 (참가신청 이메일)</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr"/>
+      <c r="AB360" t="inlineStr">
+        <is>
+          <t>취리히무역관 +41-44-503-5304, 5305 / m.im@kotra.ch, celine.choi@kotra.ch / 소재부품장비팀 02-3460-7654, hama3060@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AC360" t="inlineStr">
+        <is>
+          <t>celine.choi@kotra.ch</t>
+        </is>
+      </c>
+      <c r="AD360" t="inlineStr">
+        <is>
+          <t>02-3460-7654</t>
+        </is>
+      </c>
+      <c r="AE360" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF360" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125535</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>[인천] 2026년 3차 자동차 산업ㆍ기업 도약 패키지(공정 안전고도화 및 환경개선) 기업지원 참여기업 모집 공고(인천 자동차 업종 상생협약 확산 지원사업)</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>인천상공회의소</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>온라인 접수 (비즈오케이)</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr"/>
+      <c r="AB361" t="inlineStr">
+        <is>
+          <t>인천상공회의소 소통강화공공사업실 032-810-2915, aikim@incham.net</t>
+        </is>
+      </c>
+      <c r="AC361" t="inlineStr">
+        <is>
+          <t>aikim@incham.net</t>
+        </is>
+      </c>
+      <c r="AD361" t="inlineStr">
+        <is>
+          <t>032-810-2915</t>
+        </is>
+      </c>
+      <c r="AE361" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF361" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125533</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026년 국내 정책노선(제주-인천) 활성화를 위한 운항장려금 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>직접수행</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>방문 또는 우편 접수
+- 접수처 : 제주특별자치도 제주시 문연로 30, 제주도청 제2청사 공항확충지원과</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>금 200백만원</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>200백만원</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>서식1, 지원사업 신청서, 서식2, 확약서, 서식3, 개인정보 수집·이용 및 제3자 제공 동의서, 확약서 제출 관련 유의사항, ‧ 기한 내 미제출 시 선정이 취소될 수 있음</t>
+        </is>
+      </c>
+      <c r="AB362" t="inlineStr">
+        <is>
+          <t>제주특별자치도청 공항확충지원과 064-710-4843</t>
+        </is>
+      </c>
+      <c r="AC362" t="inlineStr"/>
+      <c r="AD362" t="inlineStr">
+        <is>
+          <t>064-710-4843</t>
+        </is>
+      </c>
+      <c r="AE362" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF362" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125532</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>[세종] 2026년 식품안심업소(위생등급제) 컨설팅 지원사업 참여업소 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>직접수행</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>모집 완료시까지</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>방문, 이메일 접수
+- 접수처 : 세종특별자치시 한누리대로 2130, 세종시청 3층 보건정책과 위생관리팀
+- 이메일 : misoli93@korea.kr
+※ 이메일 발송 후 유선 확인 요망</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>검토, (지원비용) 전액 무료, (식품안심업소 전문 컨설팅 업체 위탁 수행), 모집대상, (모집업소), 관내 일반·휴게·제과점 및 집단급식소 총 4개소, (신청자격) 아래의 요건을 모두 충족하는 업소, 관내</t>
+        </is>
+      </c>
+      <c r="AB363" t="inlineStr">
+        <is>
+          <t>세종시청 보건정책과 위생관리팀 044-300-5743</t>
+        </is>
+      </c>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>misoli93@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD363" t="inlineStr">
+        <is>
+          <t>044-300-5743</t>
+        </is>
+      </c>
+      <c r="AE363" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF363" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125531</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026년 중국 푸저우 해양장비전 연계 GP 수출상담회 참가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>온라인 접수 (무역투자24)</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>ㅇ 모집규모: 국내 조선·해양 기자재 유망기업 10~15개사</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>15개</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>파일 첨부는 1개만 가능하므로 참가신청서, 시스템 용량 제한(50MB)으로 업로드가 불가능한 경우, 아래 문의처 이메일로 압축파일을 별도 송부</t>
+        </is>
+      </c>
+      <c r="AB364" t="inlineStr">
+        <is>
+          <t>KOTRA 소재부품장비팀 02-3460-7643, skmk0038@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AC364" t="inlineStr">
+        <is>
+          <t>skmk0038@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AD364" t="inlineStr">
+        <is>
+          <t>02-3460-7643</t>
+        </is>
+      </c>
+      <c r="AE364" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF364" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125530</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 유기농 명인 지정계획 공고</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>직접수행</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-09-02</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>우편 또는 이메일 접수
+- 접수처 : (우) 58564 전남광주통합특별시 무안군 삼향읍 오룡길 1 전남광주통합특별시 친환경농업과 유기농육성팀
+- 이메일 : h2co3ju@korea.kr</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>나. 추 천 자, : 시장·군수, 다. 제출, 서류 : 원본 제출, ｢붙임 3｣유기농명인 지정 신청서, 작성요령 참고, ｢붙임 4｣유기농명인 재배 매뉴얼, ｢붙임 5｣추천기관(시․군) 자체 평가표</t>
+        </is>
+      </c>
+      <c r="AB365" t="inlineStr">
+        <is>
+          <t>전남광주통합특별시 친환경농업과 유기농육성팀 061-286-6342 및 시군 접수처 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC365" t="inlineStr">
+        <is>
+          <t>h2co3ju@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD365" t="inlineStr">
+        <is>
+          <t>061-286-6342</t>
+        </is>
+      </c>
+      <c r="AE365" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF365" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125529</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 하반기 관광진흥개발기금 융자지원 계획 공고</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>직접수행</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>방문 및 우편 접수
+- (시설자금) 방문, (운영자금) 방문 및 등기우편 제출
+- 접수처 : 전남광주통합특별시 시ㆍ군 관광부서
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>: 총 50억 원 내외</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>50억원</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z366" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>※ 제출된 서류는 일체 반환하지 않음., 가. 시설자금, (공통), 융자신청서(붙임1), 대출상담확인서(붙임2), 사업계획서(붙임3), 견적서사업계획승인 사본, 건축허가(신고)서 사본 또는 개발행위허가서</t>
+        </is>
+      </c>
+      <c r="AB366" t="inlineStr">
+        <is>
+          <t>전남광주통합특별시 관광과 061-286-5226 및 시군별 관광진흥개발기금 융자사업 접수처 문의처 공고문 8p 참조</t>
+        </is>
+      </c>
+      <c r="AC366" t="inlineStr"/>
+      <c r="AD366" t="inlineStr">
+        <is>
+          <t>061-286-5226</t>
+        </is>
+      </c>
+      <c r="AE366" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF366" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125528</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>[충남] 2026년 AI 기반 태양광 설비 유지보수 솔루션 보급 시범사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>충남테크노파크</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>이메일 접수 (hollywater@ctp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>□ 총사업비 : 20백만원(기업당 최대 10백만원) ※ 부가가치세 지원 제외</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>20백만원</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>를 허위로 작성한 경우, 유의사항, 미체출 시 선정제외, 접수서류는 일체 반환하지 않음, ◦ 선정평가에 의하여 지원 선정 또는 탈락되며, 선정기업은 평가 결과, 에 따라 사업내용 및 지원금액 등이 조정될 수 있음, 지원성</t>
+        </is>
+      </c>
+      <c r="AB367" t="inlineStr">
+        <is>
+          <t>충남테크노파크 탄소중립산업센터 041-338-7957</t>
+        </is>
+      </c>
+      <c r="AC367" t="inlineStr">
+        <is>
+          <t>hollywater@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD367" t="inlineStr">
+        <is>
+          <t>041-338-7957</t>
+        </is>
+      </c>
+      <c r="AE367" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF367" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125525</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>[경남] 2026년 독일 뒤셀도르프 국제의료기기 전시회 참가 지원사업 참가업체 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>김해의생명산업진흥원</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>온라인 접수(경상남도 해외마케팅 사업지원시스템)</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>◦ 모집규모 : 도내 의료산업 분야 수출 중소기업 1개사</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA368" t="inlineStr"/>
+      <c r="AB368" t="inlineStr">
+        <is>
+          <t>김해의생명산업진흥원 055-310-1473 / 경상남도 국제통상과 055-211-3183</t>
+        </is>
+      </c>
+      <c r="AC368" t="inlineStr"/>
+      <c r="AD368" t="inlineStr">
+        <is>
+          <t>055-211-3183</t>
+        </is>
+      </c>
+      <c r="AE368" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF368" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125524</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>[경기] 시흥시 2026년 하반기 시흥창업센터 메이커스페이스 참여 모집 공고</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>시흥산업진흥원</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>이메일 접수(als10wns@sida.kr, bhlee0815@naver.com)
+※ 시흥창업센터 담당자 또는 수행 용역사 中 이메일 제출 택 1</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>설명 비고, ① 신청서 공고문 붙임 신청서 양식, [필수], ② 개인정보 동의서 공고문 붙임 개인정보 동의서 양식, ③ 제품설계 파일 STL, OBJ 등, [선택] 공유 가능한 서류, (민감 정보 등 제외)</t>
+        </is>
+      </c>
+      <c r="AB369" t="inlineStr">
+        <is>
+          <t>시흥산업진흥원 시흥창업센터 031-497-1497, als10wns@sida.kr</t>
+        </is>
+      </c>
+      <c r="AC369" t="inlineStr">
+        <is>
+          <t>als10wns@sida.kr</t>
+        </is>
+      </c>
+      <c r="AD369" t="inlineStr">
+        <is>
+          <t>031-497-1497</t>
+        </is>
+      </c>
+      <c r="AE369" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF369" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125523</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 보스턴 오픈이노베이션 활성화 지원사업 미국 바이오 전시회 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>전북테크노파크</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>2026-08-17 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>온라인 접수 (전북 R&amp;D종합정보시스템)</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>□ 지원한도 : 기업당 2명, 최대 1천만원 한도 내 지원(평가시 조정가능)</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>1천만원</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z370" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>업로드, 지원사업] 구분 메뉴에서 신청서 작성 후 등록, 신청 시 전산 업로드 (오프라인 제출 X), 파일형식 : PDF, PNG 등 스캔파일 및 HWP, EXCEL 등 문서파일, 필수, ② (서식1) 참가신청서 및 사업계획서</t>
+        </is>
+      </c>
+      <c r="AB370" t="inlineStr">
+        <is>
+          <t>전북테크노파크 정책기획단 바이오산산업기획팀 063-219-2205, gjkim@jbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC370" t="inlineStr">
+        <is>
+          <t>gjkim@jbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD370" t="inlineStr">
+        <is>
+          <t>063-219-2205</t>
+        </is>
+      </c>
+      <c r="AE370" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF370" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125522</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>[전북] 전주시 2026년 4차 소공인특화지원센터 지원사업 통합 공고(8월)</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>전북벤처산업발전협의회</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2026-08-17 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>방문, 우편, 온라인 접수
+- 접수처 : 전북특별자치도 전주시 덕진구 신복로 80 전주대장간 2층 사무실
+- 온라인 : 소상공인24</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>○ 지원규모 : 1개 사업 총 2개 사</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z371" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA371" t="inlineStr"/>
+      <c r="AB371" t="inlineStr">
+        <is>
+          <t>전주팔복 금속가공 소공인특화지원센터 063-902-1105, 1106 / jkmoon@jvada.or.kr, ssyang@jvada.or.kr 시스템 문의(오류 등) 1644-5302</t>
+        </is>
+      </c>
+      <c r="AC371" t="inlineStr">
+        <is>
+          <t>jkmoon@jvada.or.kr</t>
+        </is>
+      </c>
+      <c r="AD371" t="inlineStr">
+        <is>
+          <t>063-902-1105</t>
+        </is>
+      </c>
+      <c r="AE371" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF371" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125520</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 전북지역기술혁신허브 해외 진출(호라이즌 유럽) 컨설팅 지원 모집 공고(전북지역기술혁신허브 비R&amp;D 지원사업)</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>전북테크노파크</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>온라인 접수 (전북R&amp;D종합정보시스템)</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 기업당 최대 3백만원 이내, 3건 내</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>3백만원</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>3건</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>의 미비 또는, 가 사실과 다른 경우, 기타 본 사업에 적정하지 않다고 판단되는 경우, 추진 절차 및 일정, 사업공고 서면평가 선정안내 협약체결, (화) ⇨ ⇨ ⇨, ~28.(금), 결과보고서 해외시장개척단 컨설팅수행</t>
+        </is>
+      </c>
+      <c r="AB372" t="inlineStr">
+        <is>
+          <t>전북테크노파크 이차전지사업단 이차전지반도체진흥팀 063-260-9366, baeeunji04@jbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC372" t="inlineStr">
+        <is>
+          <t>baeeunji04@jbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD372" t="inlineStr">
+        <is>
+          <t>063-260-9366</t>
+        </is>
+      </c>
+      <c r="AE372" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF372" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125519</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 3차 빛고을투자챌린지 IR 예선 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>광주창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>이메일 접수(ak6352@ccei.kr)</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>&lt;연번&gt;&lt;지원항목&gt;&lt;지원내용&gt;</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA373" t="inlineStr"/>
+      <c r="AB373" t="inlineStr">
+        <is>
+          <t>광주창조경제혁신센터 전략기획팀 062-364-9137</t>
+        </is>
+      </c>
+      <c r="AC373" t="inlineStr"/>
+      <c r="AD373" t="inlineStr">
+        <is>
+          <t>062-364-9137</t>
+        </is>
+      </c>
+      <c r="AE373" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF373" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125518</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>[울산] 2026년 2차 울산테크노파크 기술투자촉진사업 수요기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>울산테크노파크</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>온라인 접수 (U Biz Platform 기업지원사업 관리시스템)</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 기업당 최대 400만원 지원(자부담 10% 및 부가세 별도)</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>400만원</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z374" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>붙임 1., 동의서 각 1부, 붙임 2. 신청자격 자가진단 확인서, 중소기업확인서, ❍ 접수 및 문의처, 기업지원단 최명현 연구원, 평가방법 및 기준, ❍ 평가방법 : 사업신청서 내용을 바탕으로 지원 필요성</t>
+        </is>
+      </c>
+      <c r="AB374" t="inlineStr">
+        <is>
+          <t>울산테크노파크 기업지원단 052-219-8678, hyeoun970920@utp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC374" t="inlineStr">
+        <is>
+          <t>hyeoun970920@utp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD374" t="inlineStr">
+        <is>
+          <t>052-219-8678</t>
+        </is>
+      </c>
+      <c r="AE374" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF374" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125517</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>[전남광주] 2027년 미국 라스베가스 소비자전자제품전시회(CES) 전남대학교 공동관 참가기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>전남대학교 산학협력단</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>이메일 접수 (kyungsic07@jnu.ac.kr)
+※ 메일제목: [CES참가신청] 기업명_신청서)</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>2 지원내용 및 규모</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z375" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>신청 기간: ’26.8.12.(수)~8.28.(금), 신청 방법: 담당자 이메일 제출, ◦ 제출 방법:, 전남대학교 AI융합연구원 담당자 메일로 발송, 목록, 서류 제출 목록 구분 비고, 참가신청서 필수 [서식 1], 기타 홍보자료(국문/영문) 선택 브로슈어</t>
+        </is>
+      </c>
+      <c r="AB375" t="inlineStr">
+        <is>
+          <t>신청 문의 062-530-5071,5074 예산 문의 062-530-5073</t>
+        </is>
+      </c>
+      <c r="AC375" t="inlineStr">
+        <is>
+          <t>hongildong@naver.com</t>
+        </is>
+      </c>
+      <c r="AD375" t="inlineStr">
+        <is>
+          <t>062-530-5071</t>
+        </is>
+      </c>
+      <c r="AE375" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF375" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125516</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>[경기] 안산시 2026년 지역특화분야 유망 창업기업 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>한양대ERICA 혁신스타트업지원센터</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>온라인 접수(한양대ERICA 산학연협력단지사업단)</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>가형 7개사내외 1500만원</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>1500만원</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>7개</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>가 사실과 다르거나, 기타 본 사업의 취지에 적정하지 않다고 판단되는 경우, ⦁휴폐업중인 기업, ⦁기타 중대한 사유가 발생한 경우, 지원절차 및 선정기준, 사업 지원절차, 추진절차 일정 내용 주관, 선정평가 및 선정 9월 2주차</t>
+        </is>
+      </c>
+      <c r="AB376" t="inlineStr">
+        <is>
+          <t>한양대ERICA 혁신스타트업지원센터 031-400-4934, jiho79@hanyang.ac.kr</t>
+        </is>
+      </c>
+      <c r="AC376" t="inlineStr">
+        <is>
+          <t>jiho79@hanyang.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD376" t="inlineStr">
+        <is>
+          <t>031-400-4934</t>
+        </is>
+      </c>
+      <c r="AE376" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF376" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125515</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>[강원] 2026년 지역산업맞춤형 일자리창출 지원사업 일자리 선순환 프로젝트 강원 바이오기업 성장 촉진 및 고용 활성화 지원사업 기업지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>춘천바이오산업진흥원</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-10-30</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>방문, 우편, 이메일 접수 
+- 접수처 : 강원도 춘천시 소양강로 32, BIO-1동 101호 기업지원팀
+- 이메일 : marketing@cbf.or.kr</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>지원기관 지원사업 지원내용 지원규모</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>작성을 위한 시험 및 분석, 획득 지원, 검증, 컨설팅 비용 지원, • 국외 바이오분야 전문 전시회 참가 비용 지원, 국외전시회 - 전시회 부스(공간) 임차비용, 참가 지원 - 전시회 부스 장치 설치, 임차비용</t>
+        </is>
+      </c>
+      <c r="AB377" t="inlineStr">
+        <is>
+          <t>(재)춘천바이오 산업진흥원 033-258-6957, marketing@cbf.or.kr</t>
+        </is>
+      </c>
+      <c r="AC377" t="inlineStr">
+        <is>
+          <t>marketing@cbf.or.kr</t>
+        </is>
+      </c>
+      <c r="AD377" t="inlineStr">
+        <is>
+          <t>033-258-6957</t>
+        </is>
+      </c>
+      <c r="AE377" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF377" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125514</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 발달장애인 가족창업 특화사업 기업(사업화) 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>장애인기업종합지원센터</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>우편, 방문, 이메일 접수
+- 접수처 : (42709) 경북 안동시 동흥2길 20, 가치만드소
+- 이메일 : wmh@debc.or.kr
+※ 메일 발송 후 확인전화 必
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>□ 지원분야 기업별 2개 과제 수행 가능, 최대 1천만원 지원</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>1천만원</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z378" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>그 내용이, 수 있음. (증빙가능 사항만 기재), ◦ 센터는, 의 보완을 요청할 수 있으며, 센터가 고지한 기간 내에 보완, :00 도착 분 까지, ※ 8월 27일(목) 16시 이후 접수된 신청서 불인정, 접수방법 : 내방</t>
+        </is>
+      </c>
+      <c r="AB378" t="inlineStr">
+        <is>
+          <t>장애인기업종합지원센터 지역육성부 054-900-1173, 1258~60</t>
+        </is>
+      </c>
+      <c r="AC378" t="inlineStr">
+        <is>
+          <t>wmh@debc.or.kr</t>
+        </is>
+      </c>
+      <c r="AD378" t="inlineStr">
+        <is>
+          <t>054-900-1173</t>
+        </is>
+      </c>
+      <c r="AE378" t="inlineStr">
+        <is>
+          <t>장애인기업</t>
+        </is>
+      </c>
+      <c r="AF378" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125513</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026년 4차 상세페이지 제작지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>한국중소벤처기업유통원</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>온라인 접수 (판판대로)</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>**** 본 사업은 메뉴판 지원한도(600만원) 내에서 지원하는 사업으로, 예비 선정 대상이</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>600만원</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z379" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>소상공인확인서, 종류&gt;, 구 분 내 용 비 고, 소상공인 · 신청일 기준, 유효기간이 남아있어야만 인정 중소기업현황, 확인서 (소상공인으로 명시된 업체만 인정) 정보시스템, 국세 · 신청일 기준, 유효기간이 남아있어야만 인정 국세청</t>
+        </is>
+      </c>
+      <c r="AB379" t="inlineStr">
+        <is>
+          <t>통합 문의처 온판상담소 1899-0309</t>
+        </is>
+      </c>
+      <c r="AC379" t="inlineStr"/>
+      <c r="AD379" t="inlineStr"/>
+      <c r="AE379" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF379" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125512</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>[서울] 종로구 2026년 소상공인 라이브커머스 지원사업 참여자 모집 재공고</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-12-31</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>방문, 이메일 접수
+- 접수처 : 서울시 종로구 종로1길 50 케이트윈타워B동 6층 지역경제과 소상공인지원팀
+- 이메일 : lje0215@mail.jongno.go.kr</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>: 숙박‧음식점업 15억, 예술‧스포츠‧서비스업 30억원 등</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>30억원</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>(필수) ① ~ ⑤번, (추가) ⑥번(해당 시 제출), ① 참여신청서 및 정보 제공 동의서, 서약서(붙임1), ③ 소상공인확인서*, 중소기업현황정보시스템, 온라인 발급 가능, 소상공인확인서 대체서류]</t>
+        </is>
+      </c>
+      <c r="AB380" t="inlineStr">
+        <is>
+          <t>종로구청 지역경제과 소상공인지원팀 02-2148-2252</t>
+        </is>
+      </c>
+      <c r="AC380" t="inlineStr">
+        <is>
+          <t>lje0215@mail.jongno.go.kr</t>
+        </is>
+      </c>
+      <c r="AD380" t="inlineStr">
+        <is>
+          <t>02-2148-2252</t>
+        </is>
+      </c>
+      <c r="AE380" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF380" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125511</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>[부산] 2026년 3차 지식재산 긴급지원 사업 모집 공고(국내외권리화)</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>부산지식재산센터</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>온라인 접수(지원사업 신청시스템)</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>o 기업 당 2000만원 이내(지원금 합산 기준, 자부담 제외)</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>2000만원</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr"/>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z381" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>신청서‧사업추진(활용)계획서 및 필수(선택), 지원절차, o 신청·접수 → 서류검토 및 기업상담(현장방문, 유선 등) → 선정심의(지원, 지원규모, o 기업 당 2, 만원 이내(지원금 합산 기준, 자부담 제외)</t>
+        </is>
+      </c>
+      <c r="AB381" t="inlineStr">
+        <is>
+          <t>부산지식재산센터 051-714-0685, 6762</t>
+        </is>
+      </c>
+      <c r="AC381" t="inlineStr"/>
+      <c r="AD381" t="inlineStr">
+        <is>
+          <t>051-714-0685</t>
+        </is>
+      </c>
+      <c r="AE381" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF381" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125510</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 2차 탄소소재 활용 방산 관련기업 기술사업화 지원사업 지원계획 공고</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>전북테크노파크</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>온라인 접수(전북 과학기술 종합정보시스템)</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>지원규모 • 총 110000천원(금일억일천만원)</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>업로드), (전산접수 가능용량 100MB), 평가절차 및 일정(안), 사업계획서 등 서면, 현장 대면(발표) 결과통보 및 지원과제 확정, 모집공고 ⇨ ⇨ ⇨ ⇨ ⇨, 온라인접수 실사 평가 이의신청 처리 협약체결, (사업계획서</t>
+        </is>
+      </c>
+      <c r="AB382" t="inlineStr">
+        <is>
+          <t>전북테크노파크 방산안전진흥팀 063-260-9341, kjw@jbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC382" t="inlineStr">
+        <is>
+          <t>kjw@jbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD382" t="inlineStr">
+        <is>
+          <t>063-260-9341</t>
+        </is>
+      </c>
+      <c r="AE382" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF382" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125508</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026년 4차 소상공인 상품개선 지원사업(패키지ㆍ브랜드 디자인 개선ㆍ제작) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>한국중소벤처기업유통원</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>온라인 접수 (판판대로)</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>**** 본 사업은 메뉴판 지원한도(600만원) 내에서 지원하는 사업으로, 예비 선정 대상이</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>600만원</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z383" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>소상공인확인서, 종류&gt;, 구 분 내 용 비 고, 소상공인 · 신청일 기준, 유효기간이 남아있어야만 인정 중소기업현황, 확인서 (소상공인으로 명시된 업체만 인정) 정보시스템, 국세 · 신청일 기준, 유효기간이 남아있어야만 인정 국세청</t>
+        </is>
+      </c>
+      <c r="AB383" t="inlineStr">
+        <is>
+          <t>통합문의처 온판상담소 1899-0309</t>
+        </is>
+      </c>
+      <c r="AC383" t="inlineStr"/>
+      <c r="AD383" t="inlineStr"/>
+      <c r="AE383" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF383" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125507</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>[경남] 2026년 가스터빈 소재ㆍ부품 품질평가 및 성능검증 플랫폼 개발사업 경상남도 에너지산업대전 박람회 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>경남테크노파크</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-09-30</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>온라인 접수(경남테크노파크)</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>ㅇ 기업당 최대 5백만원 이내 지원(VAT 제외)</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>5백만원</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z384" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>구분, 목록 비고, ① [서식1] 기업지원 지원신청서 1부, ② [서식2] 기업지원 사업계획서 1부, ④ [서식4] 신청자격 적정성 확인서, 필수, ⑤ [서식5] 공공재정환수법 준수 서약서, ⑧ 4대보험 가입자명부(현재 기준) 1부</t>
+        </is>
+      </c>
+      <c r="AB384" t="inlineStr">
+        <is>
+          <t>경남테크노파크 055-545-3904 ju89@gntp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC384" t="inlineStr">
+        <is>
+          <t>ju89@gntp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD384" t="inlineStr">
+        <is>
+          <t>055-545-3904</t>
+        </is>
+      </c>
+      <c r="AE384" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF384" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125506</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026년 1차 베트남 ODA 스마트공장 공정개선 컨설팅 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>서울테크노파크</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>이메일 접수 (hjlee@seoultp.or.kr)
+※ 한국시간 기준 필수서류 모두 제출시에 접수된 것으로 간주</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>◦ (지원한도) 920만원(정부지원금 100%)</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>920만원</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z385" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>모두 제출시에 접수된 것으로 간주, 신청서 및, 목록&gt;</t>
+        </is>
+      </c>
+      <c r="AB385" t="inlineStr">
+        <is>
+          <t>서울테크노파크 02-944-6053, hjlee@seoultp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC385" t="inlineStr">
+        <is>
+          <t>hjlee@seoultp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD385" t="inlineStr">
+        <is>
+          <t>02-944-6053</t>
+        </is>
+      </c>
+      <c r="AE385" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF385" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125505</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>[경남] 동남형 사이버 복원 패키지 사업 수요기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>경남테크노파크</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-10-30</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jmy@gntp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>지원금액 최대 7500만원 (자부담금 없음))</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>7500만원</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>신청서 1부, 제출방법: 이메일 제출 (jmy@gntp.or.kr), ※ 신청서를 통해 기업 기본정보만 확인하며, Ⅳ 문의처, 기업연구관 204호, 스마트엠투엠 hyeongonkim@sma, (운영기업) rtm2m.co.kr</t>
+        </is>
+      </c>
+      <c r="AB386" t="inlineStr">
+        <is>
+          <t>경남테크노파크 055-294-2404, jmy@gntp.or.kr 스마트엠투엠(운영기업) hyeongonkim@smartm2m.co.kr</t>
+        </is>
+      </c>
+      <c r="AC386" t="inlineStr">
+        <is>
+          <t>hyeongonkim@smartm2m.co.kr</t>
+        </is>
+      </c>
+      <c r="AD386" t="inlineStr">
+        <is>
+          <t>055-294-2404</t>
+        </is>
+      </c>
+      <c r="AE386" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF386" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125504</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026년 중소ㆍ중견기업 해외 공급망 ESG 요구대응 맞춤형 컨설팅 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-20</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>온라인 접수 (무역투자24)</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>[중소기업] 최근 3년간 50억원 이상 10억원 미만</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>50억원</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z387" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>신청 시 제출 필수자료 첨부, 제출된 자료를 바탕으로, 참가기업 선정 예정, &lt;제출 필수자료&gt;, ① 참가기업 신청서 *제공된 양식(첨부2) 활용, ③ 중소·중견기업 확인서, ④ 회사소개서, 제품소개서</t>
+        </is>
+      </c>
+      <c r="AB387" t="inlineStr">
+        <is>
+          <t>KOTRA 소재부품장비팀 02-3460-7641, mwjie@kotra.or.kr (ESG경영혁신실) 02-3460-3492, choiye@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AC387" t="inlineStr">
+        <is>
+          <t>choiye@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AD387" t="inlineStr">
+        <is>
+          <t>02-3460-3492</t>
+        </is>
+      </c>
+      <c r="AE387" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF387" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125503</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026년 2차 해외 온라인플랫폼 활용지원 사업 참여 소상공인 모집 공고</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>소상공인시장진흥공단</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>온라인 접수(소상공인24)</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>ㅇ 최종 선정된 소상공인은 자부담금과 부가세를 수행기관으로 납부해야 하며, 기한(계약 후 2주) 내 미납부 시 선정 취소될 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z388" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA388" t="inlineStr"/>
+      <c r="AB388" t="inlineStr">
+        <is>
+          <t>(사업문의) 소상공인시장진흥공단 스마트지원실 온라인판로팀 042-363-7825, 7826 (소상공인 24 시스템 문의) 1644-5302 (중소기업확인서(소상공인) 발급 문의) 1357</t>
+        </is>
+      </c>
+      <c r="AC388" t="inlineStr"/>
+      <c r="AD388" t="inlineStr">
+        <is>
+          <t>042-363-7825</t>
+        </is>
+      </c>
+      <c r="AE388" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF388" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125502</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026년 의료기기 사업화 촉진 사업 지원 기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>한국산업기술시험원</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>이메일 접수 (gkdp1224@ktl.re.kr)</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>③수행사업비:금일천팔백칠십오만원(18750000원,부가세포함)</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>18750000원</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>신청 방법, ◦ 신청 방법 : 신청서 양식 작성하여 날인 후, 와 함께 이메일로 제출, 지원신청서 (붙임1. 참조), 개인(신용)정보 활용 동의서 (붙임2. 참조), 중복지원금지 확약서 (붙임3. 참조), 체크리스트 1부 (붙임4. 참조), 중소/중견기업 확인서 1부</t>
+        </is>
+      </c>
+      <c r="AB389" t="inlineStr">
+        <is>
+          <t>한국산업기술시험원 바이오융합평가센터 (사업내용 문의) 02-860-1611, jbpark@ktl.re.kr (신청서 접수) 02-860-1072, gkdp1224@ktl.re.kr</t>
+        </is>
+      </c>
+      <c r="AC389" t="inlineStr">
+        <is>
+          <t>gkdp1224@ktl.re.kr</t>
+        </is>
+      </c>
+      <c r="AD389" t="inlineStr">
+        <is>
+          <t>02-860-1072</t>
+        </is>
+      </c>
+      <c r="AE389" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF389" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125501</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026년 중국(선양-칭다오) 프랜차이즈 로드쇼 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>온라인 접수(무역투자24)</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>◦ 모집 규모 : 국내 중소 중견 외식 프랜차이즈 기업 10개사</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z390" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>업로드, 브랜드홍보 카탈로그, ◦ 참가비 무료, ◦ KOTRA 지원사항, 현지 세미나 및 수출상담회 참가 지원, 수출상담회 통역 지원, 현지 내 단체이동 및 간담회 지원, 항공임 및 숙박비 등 체재비는 기업 자부담</t>
+        </is>
+      </c>
+      <c r="AB390" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사 서비스산업팀 02-3460-7611, 7613 / franchise@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AC390" t="inlineStr">
+        <is>
+          <t>franchise@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AD390" t="inlineStr">
+        <is>
+          <t>02-3460-7611</t>
+        </is>
+      </c>
+      <c r="AE390" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF390" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125500</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>[서울] 용산구 이태원 1ㆍ2동 대상 특별 중소기업육성기금 융자지원계획 공고</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 용산구청 우리은행 중소기업육성기금 원스톱서비스 창구
+※ 단, 신용보증서로 담보제공 시 신용보증재단 용산종합지원센터(남영역 1번출구 하차)에서 사전상담 필수
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>총 10억원</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>10억원</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W391" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X391" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z391" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>가. 신청기간 :, (수) ～ 자금 소진 시까지, ☞ 6호선 녹사평역(3번 출구) 하차, 횡단보도 건너 용산종합행정타운 1층, 신용보증서, 다., 미비 시 접수 불가, 융자신청서 및 사업계획서(첨부파일)</t>
+        </is>
+      </c>
+      <c r="AB391" t="inlineStr">
+        <is>
+          <t>우리은행 중소기업육성기금 원스톱창구 02-795-8014, 내선 311 / 서울신용보증재단 용산종합지원센터 02-2174-4721, 4727 / 용산구청 지역경제과 지역경제팀 02- 2199-6784</t>
+        </is>
+      </c>
+      <c r="AC391" t="inlineStr"/>
+      <c r="AD391" t="inlineStr">
+        <is>
+          <t>02-2174-4721</t>
+        </is>
+      </c>
+      <c r="AE391" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF391" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125499</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>[인천] 2026년 우수 식품위생업소 홍보영상 제작 지원 사업 지원기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>인천광역시 식품산업육성지원센터</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jin@ifdsc.or.kr)
+※ 접수 후 유선 확인 必</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>m 지원내용 : 지원기업 맞춤형 숏폼 홍보 영상 3편 제작</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z392" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>에 대한 적격심사, 차 : 모집규모 초과 시, 선정평가표에 따른 평가, 붙임 3-1, 선정평가표 참고, m 1차 적격심사 기준, 필수, 제출 여부</t>
+        </is>
+      </c>
+      <c r="AB392" t="inlineStr">
+        <is>
+          <t>인천식품산업육성지원센터 담당자 032-822-8793</t>
+        </is>
+      </c>
+      <c r="AC392" t="inlineStr">
+        <is>
+          <t>jin@ifdsc.or.kr</t>
+        </is>
+      </c>
+      <c r="AD392" t="inlineStr">
+        <is>
+          <t>032-822-8793</t>
+        </is>
+      </c>
+      <c r="AE392" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF392" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125498</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF392"/>
+  <dimension ref="A1:AF443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53593,8 +53593,6 @@
           <t>□ 지원내용 : 양산화 과정에 필요한 단계별 재료 및 제조 지원 및 컨설팅(최대 4000천원)</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr"/>
-      <c r="G346" t="inlineStr"/>
       <c r="H346" t="inlineStr">
         <is>
           <t>Y</t>
@@ -53690,7 +53688,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA346" t="inlineStr"/>
       <c r="AB346" t="inlineStr">
         <is>
           <t>전남대학교 만들마루 062-530-5059, info@mandulmaru.net</t>
@@ -53748,7 +53745,6 @@
           <t>40만원</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr"/>
       <c r="H347" t="inlineStr">
         <is>
           <t>Y</t>
@@ -53901,8 +53897,6 @@
           <t>지원내용</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr"/>
-      <c r="G348" t="inlineStr"/>
       <c r="H348" t="inlineStr">
         <is>
           <t>N</t>
@@ -54057,7 +54051,6 @@
           <t>❍ 지원규모: 2개사 내외</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr"/>
       <c r="G349" t="inlineStr">
         <is>
           <t>2개</t>
@@ -54215,8 +54208,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr"/>
-      <c r="G350" t="inlineStr"/>
       <c r="H350" t="inlineStr">
         <is>
           <t>N</t>
@@ -54312,7 +54303,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA350" t="inlineStr"/>
       <c r="AB350" t="inlineStr">
         <is>
           <t>대전정보문화산업진흥원 AI혁신추진단 042-479-4142, jsy@dicia.or.kr</t>
@@ -54365,7 +54355,6 @@
           <t>❍ 모집규모 : 8개사 정도</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr">
         <is>
           <t>8개</t>
@@ -54523,7 +54512,6 @@
           <t>○ 지원규모 : 2개 기업 내외</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr">
         <is>
           <t>2개</t>
@@ -54687,7 +54675,6 @@
           <t>2000만원</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr"/>
       <c r="H353" t="inlineStr">
         <is>
           <t>Y</t>
@@ -54840,8 +54827,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr"/>
-      <c r="G354" t="inlineStr"/>
       <c r="H354" t="inlineStr">
         <is>
           <t>N</t>
@@ -54937,7 +54922,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA354" t="inlineStr"/>
       <c r="AB354" t="inlineStr">
         <is>
           <t>벤처기업협회 혁신인재본부 02-6331-7051, job@v-job.or.kr</t>
@@ -54995,7 +54979,6 @@
           <t>200만원</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr"/>
       <c r="H355" t="inlineStr">
         <is>
           <t>Y</t>
@@ -55091,13 +55074,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA355" t="inlineStr"/>
       <c r="AB355" t="inlineStr">
         <is>
           <t>강원특별자치도경제진흥원 전략사업부 033-749-3387</t>
         </is>
       </c>
-      <c r="AC355" t="inlineStr"/>
       <c r="AD355" t="inlineStr">
         <is>
           <t>033-749-3387</t>
@@ -55140,7 +55121,6 @@
           <t>❍ 지원규모 : 10개사 정도</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr">
         <is>
           <t>10개</t>
@@ -55298,8 +55278,6 @@
           <t>□ 주요 지원내용</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr"/>
-      <c r="G357" t="inlineStr"/>
       <c r="H357" t="inlineStr">
         <is>
           <t>Y</t>
@@ -55410,7 +55388,6 @@
           <t>korea360uae.op@gmail.com</t>
         </is>
       </c>
-      <c r="AD357" t="inlineStr"/>
       <c r="AE357" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -55448,7 +55425,6 @@
           <t>❍ 지원규모 : 10개사 정도</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr"/>
       <c r="G358" t="inlineStr">
         <is>
           <t>10개</t>
@@ -55611,7 +55587,6 @@
           <t>10만원</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr"/>
       <c r="H359" t="inlineStr">
         <is>
           <t>N</t>
@@ -55766,8 +55741,6 @@
           <t>11) 최종 선정기업 발표 (참가신청 이메일)</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr"/>
-      <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr">
         <is>
           <t>N</t>
@@ -55863,7 +55836,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA360" t="inlineStr"/>
       <c r="AB360" t="inlineStr">
         <is>
           <t>취리히무역관 +41-44-503-5304, 5305 / m.im@kotra.ch, celine.choi@kotra.ch / 소재부품장비팀 02-3460-7654, hama3060@kotra.or.kr</t>
@@ -55916,8 +55888,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr"/>
-      <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr">
         <is>
           <t>Y</t>
@@ -56013,7 +55983,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA361" t="inlineStr"/>
       <c r="AB361" t="inlineStr">
         <is>
           <t>인천상공회의소 소통강화공공사업실 032-810-2915, aikim@incham.net</t>
@@ -56072,7 +56041,6 @@
           <t>200백만원</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr">
         <is>
           <t>Y</t>
@@ -56178,7 +56146,6 @@
           <t>제주특별자치도청 공항확충지원과 064-710-4843</t>
         </is>
       </c>
-      <c r="AC362" t="inlineStr"/>
       <c r="AD362" t="inlineStr">
         <is>
           <t>064-710-4843</t>
@@ -56224,8 +56191,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F363" t="inlineStr"/>
-      <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr">
         <is>
           <t>N</t>
@@ -56378,7 +56343,6 @@
           <t>ㅇ 모집규모: 국내 조선·해양 기자재 유망기업 10~15개사</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr">
         <is>
           <t>15개</t>
@@ -56538,8 +56502,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr"/>
-      <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr">
         <is>
           <t>N</t>
@@ -56700,7 +56662,6 @@
           <t>50억원</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr">
         <is>
           <t>Y</t>
@@ -56806,7 +56767,6 @@
           <t>전남광주통합특별시 관광과 061-286-5226 및 시군별 관광진흥개발기금 융자사업 접수처 문의처 공고문 8p 참조</t>
         </is>
       </c>
-      <c r="AC366" t="inlineStr"/>
       <c r="AD366" t="inlineStr">
         <is>
           <t>061-286-5226</t>
@@ -56854,7 +56814,6 @@
           <t>20백만원</t>
         </is>
       </c>
-      <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr">
         <is>
           <t>Y</t>
@@ -57007,7 +56966,6 @@
           <t>◦ 모집규모 : 도내 의료산업 분야 수출 중소기업 1개사</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr">
         <is>
           <t>1개</t>
@@ -57108,13 +57066,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA368" t="inlineStr"/>
       <c r="AB368" t="inlineStr">
         <is>
           <t>김해의생명산업진흥원 055-310-1473 / 경상남도 국제통상과 055-211-3183</t>
         </is>
       </c>
-      <c r="AC368" t="inlineStr"/>
       <c r="AD368" t="inlineStr">
         <is>
           <t>055-211-3183</t>
@@ -57158,8 +57114,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr"/>
-      <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr">
         <is>
           <t>N</t>
@@ -57476,7 +57430,6 @@
           <t>○ 지원규모 : 1개 사업 총 2개 사</t>
         </is>
       </c>
-      <c r="F371" t="inlineStr"/>
       <c r="G371" t="inlineStr">
         <is>
           <t>1개</t>
@@ -57577,7 +57530,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA371" t="inlineStr"/>
       <c r="AB371" t="inlineStr">
         <is>
           <t>전주팔복 금속가공 소공인특화지원센터 063-902-1105, 1106 / jkmoon@jvada.or.kr, ssyang@jvada.or.kr 시스템 문의(오류 등) 1644-5302</t>
@@ -57792,8 +57744,6 @@
           <t>&lt;연번&gt;&lt;지원항목&gt;&lt;지원내용&gt;</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr"/>
-      <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr">
         <is>
           <t>N</t>
@@ -57889,13 +57839,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA373" t="inlineStr"/>
       <c r="AB373" t="inlineStr">
         <is>
           <t>광주창조경제혁신센터 전략기획팀 062-364-9137</t>
         </is>
       </c>
-      <c r="AC373" t="inlineStr"/>
       <c r="AD373" t="inlineStr">
         <is>
           <t>062-364-9137</t>
@@ -57943,7 +57891,6 @@
           <t>400만원</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr">
         <is>
           <t>Y</t>
@@ -58097,8 +58044,6 @@
           <t>2 지원내용 및 규모</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr"/>
-      <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr">
         <is>
           <t>Y</t>
@@ -58415,8 +58360,6 @@
           <t>지원기관 지원사업 지원내용 지원규모</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
       <c r="H377" t="inlineStr">
         <is>
           <t>Y</t>
@@ -58740,7 +58683,6 @@
           <t>600만원</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr">
         <is>
           <t>Y</t>
@@ -58846,8 +58788,6 @@
           <t>통합 문의처 온판상담소 1899-0309</t>
         </is>
       </c>
-      <c r="AC379" t="inlineStr"/>
-      <c r="AD379" t="inlineStr"/>
       <c r="AE379" t="inlineStr">
         <is>
           <t>소상공인</t>
@@ -58892,7 +58832,6 @@
           <t>30억원</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr">
         <is>
           <t>Y</t>
@@ -59050,7 +58989,6 @@
           <t>2000만원</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr">
         <is>
           <t>N</t>
@@ -59156,7 +59094,6 @@
           <t>부산지식재산센터 051-714-0685, 6762</t>
         </is>
       </c>
-      <c r="AC381" t="inlineStr"/>
       <c r="AD381" t="inlineStr">
         <is>
           <t>051-714-0685</t>
@@ -59199,8 +59136,6 @@
           <t>지원규모 • 총 110000천원(금일억일천만원)</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr"/>
-      <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
           <t>Y</t>
@@ -59358,7 +59293,6 @@
           <t>600만원</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr">
         <is>
           <t>Y</t>
@@ -59464,8 +59398,6 @@
           <t>통합문의처 온판상담소 1899-0309</t>
         </is>
       </c>
-      <c r="AC383" t="inlineStr"/>
-      <c r="AD383" t="inlineStr"/>
       <c r="AE383" t="inlineStr">
         <is>
           <t>소상공인</t>
@@ -59508,7 +59440,6 @@
           <t>5백만원</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr">
         <is>
           <t>Y</t>
@@ -59667,7 +59598,6 @@
           <t>920만원</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr">
         <is>
           <t>Y</t>
@@ -59825,7 +59755,6 @@
           <t>7500만원</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr">
         <is>
           <t>Y</t>
@@ -59983,7 +59912,6 @@
           <t>50억원</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr">
         <is>
           <t>Y</t>
@@ -60136,8 +60064,6 @@
           <t>ㅇ 최종 선정된 소상공인은 자부담금과 부가세를 수행기관으로 납부해야 하며, 기한(계약 후 2주) 내 미납부 시 선정 취소될 수 있습니다.</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr">
         <is>
           <t>N</t>
@@ -60233,13 +60159,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA388" t="inlineStr"/>
       <c r="AB388" t="inlineStr">
         <is>
           <t>(사업문의) 소상공인시장진흥공단 스마트지원실 온라인판로팀 042-363-7825, 7826 (소상공인 24 시스템 문의) 1644-5302 (중소기업확인서(소상공인) 발급 문의) 1357</t>
         </is>
       </c>
-      <c r="AC388" t="inlineStr"/>
       <c r="AD388" t="inlineStr">
         <is>
           <t>042-363-7825</t>
@@ -60287,7 +60211,6 @@
           <t>18750000원</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
           <t>Y</t>
@@ -60440,7 +60363,6 @@
           <t>◦ 모집 규모 : 국내 중소 중견 외식 프랜차이즈 기업 10개사</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr">
         <is>
           <t>10개</t>
@@ -60606,7 +60528,6 @@
           <t>10억원</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr">
         <is>
           <t>Y</t>
@@ -60712,7 +60633,6 @@
           <t>우리은행 중소기업육성기금 원스톱창구 02-795-8014, 내선 311 / 서울신용보증재단 용산종합지원센터 02-2174-4721, 4727 / 용산구청 지역경제과 지역경제팀 02- 2199-6784</t>
         </is>
       </c>
-      <c r="AC391" t="inlineStr"/>
       <c r="AD391" t="inlineStr">
         <is>
           <t>02-2174-4721</t>
@@ -60756,8 +60676,6 @@
           <t>m 지원내용 : 지원기업 맞춤형 숏폼 홍보 영상 3편 제작</t>
         </is>
       </c>
-      <c r="F392" t="inlineStr"/>
-      <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr">
         <is>
           <t>N</t>
@@ -60881,6 +60799,7913 @@
       <c r="AF392" t="inlineStr">
         <is>
           <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125498</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026년 중소기업 ESG 경영 컨설팅 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>한국임업진흥원</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>온라인 및 이메일 접수
+- 온라인 : 온라인 상생누리
+- 이메일 : yeony@kofpi.or.kr
+※ 온라인 접수 후 이메일로 제출 서류 송부</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>□ (지원내용) 외부 전문가를 활용한 ESG 지표별 컨설팅 진행</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z393" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA393" t="inlineStr"/>
+      <c r="AB393" t="inlineStr">
+        <is>
+          <t>한국임업진흥원 기획조정실 02-6393-2518</t>
+        </is>
+      </c>
+      <c r="AC393" t="inlineStr"/>
+      <c r="AD393" t="inlineStr">
+        <is>
+          <t>02-6393-2518</t>
+        </is>
+      </c>
+      <c r="AE393" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF393" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125600</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>[경기] 하남시 2027년 기업환경 개선사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>우편, 방문 접수
+- 접수처 : (12951) 경기도 하남시 대청로 10, 하남시청 투자유치과 기업설립지원팀(본관, 3층)
+※ 사업계획서(한글), 내역서(엑셀)파일은 이메일로도 제출(ijy5510@korea.kr)</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>(총사업비 7억원 이내)</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>7억원</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr"/>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z394" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>공통, 서류, 사업계획서1부(견적서 및 산출내역서 등 증빙서류 포함), ※ 도면, 내역서, 일위대가 등 포함(단순 견적서 불가), 자부담 확약서1부, 시설물유지 동의서1부</t>
+        </is>
+      </c>
+      <c r="AB394" t="inlineStr">
+        <is>
+          <t>하남시 투자유치과 기업설립지원팀 031-5182-1483</t>
+        </is>
+      </c>
+      <c r="AC394" t="inlineStr">
+        <is>
+          <t>ijy5510@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD394" t="inlineStr">
+        <is>
+          <t>031-5182-1483</t>
+        </is>
+      </c>
+      <c r="AE394" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF394" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125599</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026년 지역서점 스마트 기기 지원 참여서점 모집 공고</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>한국서점연합회</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>온라인 접수(e나라도움)</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>□ 지원 비용 : 최대 150~300만원, 공급가액의 90% 국비 지원</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>300만원</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr"/>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z395" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>파일 첨부 후 ‘신청서 제출’ 클릭, ※ 파일 총 용량은 50MB로 제한, ‘제출’이면 신청 완료, ※ 수정이 필요한 경우 ‘회수’ 클릭해서 수정 가능, 수정 불가, 안내, 파일 3개, ① 신청서 (확약서</t>
+        </is>
+      </c>
+      <c r="AB395" t="inlineStr">
+        <is>
+          <t>한국서점연합회 유통정보화사업팀 02-927-1439, 4700 / ict@kfoba.or.kr e나라도움 고객센터 1670-9595</t>
+        </is>
+      </c>
+      <c r="AC395" t="inlineStr">
+        <is>
+          <t>ict@kfoba.or.kr</t>
+        </is>
+      </c>
+      <c r="AD395" t="inlineStr">
+        <is>
+          <t>02-927-1439</t>
+        </is>
+      </c>
+      <c r="AE395" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF395" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125598</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>[강원] 2026년 3차 수출기업 해외 물류비 지원사업 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>강원특별자치도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>온라인 접수(수출기업 서포트)</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>m 지원내용 : 수출 목적의 해외 물류비(2026) 지원</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr"/>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>가 제출된 시점을 기준으로 선착순 지원, 를 일부만 제출한 경우 순위가 부여되지 않음을 유의), (PDF 합본 업로드), 공 통 구 분, 수출신고필증(보유시), EMS프리미엄 2. 운송장, 결제 영수증 *운송장 번호가 표기된 영수증, ~15%의 요금 할인 혜택 제공</t>
+        </is>
+      </c>
+      <c r="AB396" t="inlineStr">
+        <is>
+          <t>강원특별자치도경제진흥원 전략사업부 033-749-3393, take1105@gwep.or.kr</t>
+        </is>
+      </c>
+      <c r="AC396" t="inlineStr">
+        <is>
+          <t>take1105@gwep.or.kr</t>
+        </is>
+      </c>
+      <c r="AD396" t="inlineStr">
+        <is>
+          <t>033-749-3393</t>
+        </is>
+      </c>
+      <c r="AE396" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF396" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125597</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>[부산] 남구 제2회 청년 창업 아이디어 경진대회 참가자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2026-09-07 ~ 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jejecks@korea.kr)
+※ 하나의 파일로 압축하여 제출
+※ 이메일 신청 시, 제목은 ‘부산 남구 청년 창업 아이디어 경진대회_참가자(팀)명’으로 기재, 접수번호가 회신되면 접수완료된 것임(3일 이내 회신)</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>&lt;예선  통과자&gt;&lt;10명(팀)  이내&gt;&lt; 아이디어 고도화 지원금(최대 50만원, 사후지급)  1:1 맞춤형 컨설팅(희망분야)&gt;</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z397" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA397" t="inlineStr"/>
+      <c r="AB397" t="inlineStr">
+        <is>
+          <t>남구청 일자리경제과 청년정책팀 051-607-3681</t>
+        </is>
+      </c>
+      <c r="AC397" t="inlineStr"/>
+      <c r="AD397" t="inlineStr">
+        <is>
+          <t>051-607-3681</t>
+        </is>
+      </c>
+      <c r="AE397" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF397" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125596</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>[경기] 화성시 2026년 사회적경제기업 맞춤형 컨설팅 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>이메일, 우편, 방문 접수
+- 접수처 : (18274) 경기도 화성시 만세구 남양읍 시청로 159 4층 기본사회담당관 사회적경제기획팀
+- 이메일 : ydyking@korea.kr</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>▢ 지원 내용</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z398" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>구분, 공통, ·사회적경제기업 컨설팅 신청서, ·개인정보 수집·이용 / 제공 동의서, 사회적기업인증서, 협동조합설립신고필증 등 기타 증빙서류사본)</t>
+        </is>
+      </c>
+      <c r="AB398" t="inlineStr">
+        <is>
+          <t>화성시 기본사회담당관 031-5189-6053</t>
+        </is>
+      </c>
+      <c r="AC398" t="inlineStr">
+        <is>
+          <t>ydyking@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD398" t="inlineStr">
+        <is>
+          <t>031-5189-6053</t>
+        </is>
+      </c>
+      <c r="AE398" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF398" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125595</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>[부산] 서구 2026년 청년 창업자 임차료 지원사업 참여 신청 공고</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>이메일 접수 (sgyouth@korea.kr)</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>사업장 임차료 월 30만 원 한도, 최대 6개월간 지원 ※ 자부담 30%</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>30만원</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>6개</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z399" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>공고일(2026. 8. 18.) 이후, 발급한 서류만 인정, 연번, 서 류 명, 유의사항, 청년 창업자 임차료 지원사업 참여 신청서, [서식 1], 참여자 서약서</t>
+        </is>
+      </c>
+      <c r="AB399" t="inlineStr">
+        <is>
+          <t>서구청 일자리경제과 청년정책계 051-240-4791</t>
+        </is>
+      </c>
+      <c r="AC399" t="inlineStr">
+        <is>
+          <t>sgyouth@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD399" t="inlineStr">
+        <is>
+          <t>051-240-4791</t>
+        </is>
+      </c>
+      <c r="AE399" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF399" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125594</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>[전북] 전주시ㆍ익산시ㆍ정읍시 2026년 3차 BIONE고용혁신 프로젝트 숨은시간 활용 일ㆍ생활 균형 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>전북바이오융합산업진흥원</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>이메일 접수(jife6581@gmail.com)
+※ 담당자 유선 확인 필수</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>□ 지원규모 : 바이오기업* 2개사 내외, 기업당 최대 40백만원* 바이오기업 : 바이오의약품, 바이오헬스, 바이오화학·연료, 기능성식품·화장품 등공고문 하단 지원대상 산업분류 코드 참고</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>40백만원</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z400" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA400" t="inlineStr"/>
+      <c r="AB400" t="inlineStr">
+        <is>
+          <t>전북바이오융합산업진흥원 창업일자리팀 063-210-6581, 6583 / jife6581@gmail.com</t>
+        </is>
+      </c>
+      <c r="AC400" t="inlineStr">
+        <is>
+          <t>jife6581@gmail.com</t>
+        </is>
+      </c>
+      <c r="AD400" t="inlineStr">
+        <is>
+          <t>063-210-6581</t>
+        </is>
+      </c>
+      <c r="AE400" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF400" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125593</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026년 하반기 완도군 단체관광객 유치 여행사 인센티브 지원계획 공고</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>방문, 우편, 이메일 접수
+- 접수처 : (59124) 전남 완도군 완도읍 청해진남로 51, 완도군청 관광과
+- 이메일 : didgusal@korea.kr ※ l(영어 L 소문자)
+※ 사전계획서 제출, 인센티브 지급 신청 방법이 상이하므로 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>12000원</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>12000원</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr"/>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z401" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>사전계획서 1부.(붙임 1), 여행일정표 1부.(붙임 2), 인센티브 지급, 신청 (여행사 → 군), ❍ 신청기한 :, 여행 종료 후 15일 이내, ❍ 신청방법 : 직접방문, 등기우편</t>
+        </is>
+      </c>
+      <c r="AB401" t="inlineStr">
+        <is>
+          <t>완도군 관광과 관광마케팅팀 061-550-5432</t>
+        </is>
+      </c>
+      <c r="AC401" t="inlineStr">
+        <is>
+          <t>didgusal@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD401" t="inlineStr">
+        <is>
+          <t>061-550-5432</t>
+        </is>
+      </c>
+      <c r="AE401" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF401" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125592</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>[전남광주] 영광군 2026년 5차 소규모사업장 방지시설 설치 지원사업 공고(사물인터넷(IoT) 측정기기 부착 지원)</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 방문접수(영광군청 환경과 기후환경팀)</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>사 업 비 : 26백만 원(국비 40%, 군비 20%, 자부담 40%)</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>26백만원</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr"/>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z402" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA402" t="inlineStr">
+        <is>
+          <t>포함) 총2부 노란색 정부화일철 제출, 스캔본(PDF파일) USB 저장 제출 또는 이메일 송부, 모든 서류 도장 날인 시, 인감도장 사용, 사용인감 날인 시 사용인감계 제출, 사본의 경우 원본대조필 날인 후 제출, 보조금 지급 절차 및 방식, 공고 및 접수 현장조사 및 심사 사업승인 통보</t>
+        </is>
+      </c>
+      <c r="AB402" t="inlineStr">
+        <is>
+          <t>영광군청 환경과 기후환경팀 061-350-4858</t>
+        </is>
+      </c>
+      <c r="AC402" t="inlineStr"/>
+      <c r="AD402" t="inlineStr">
+        <is>
+          <t>061-350-4858</t>
+        </is>
+      </c>
+      <c r="AE402" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF402" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125591</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 지능형첨단부품산업의 디지털전환 거점 구축 사업 AI 융합 제품ㆍ솔루션 고도화 지원 수혜기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>충북테크노파크</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>온라인 접수 (충북테크노파크 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>q (지원내용) 기존 제품·부품에 AI 기능 적용 또는 기존 AI 솔루션의</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z403" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA403" t="inlineStr">
+        <is>
+          <t>누락 등 최종 제출되지 않은 경우, 접수 불가, 사업 신청 시 아래 서류를 온라인으로 등록, m 모든 서류는 공고일(`26.8.18.) 기준, 직전 3개월(`26.5.18이후) 이내, 발급된 서류 제출 필수, `26. 5. 18. 이전 서류는 불인정, 비고</t>
+        </is>
+      </c>
+      <c r="AB403" t="inlineStr">
+        <is>
+          <t>충북테크노파크 스마트제조혁신센터 제조AI팀 043-270-2851, shkim@cbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC403" t="inlineStr">
+        <is>
+          <t>shkim@cbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD403" t="inlineStr">
+        <is>
+          <t>043-270-2851</t>
+        </is>
+      </c>
+      <c r="AE403" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF403" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125590</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>[강원] 2026년 강원 청년 창업 경진대회 참가자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>강원창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>온라인 접수 (구글폼)</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>◦ (사업화지원금) 수상팀별 최대 1000만원</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>1000만원</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z404" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>하기의 서류 제출, 구분 요건별서류 공통서류, 주민등록초본1부 - [붙임1] 참가신청서1부., 예비창업자, [붙임3] 참가자서약서, Ⅲ 선정 절차, 선정평가, 공개 심사(대표자 발표 원칙)</t>
+        </is>
+      </c>
+      <c r="AB404" t="inlineStr">
+        <is>
+          <t>강원창조경제혁신센터 033-248-7949, rud5907@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AC404" t="inlineStr">
+        <is>
+          <t>rud5907@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AD404" t="inlineStr">
+        <is>
+          <t>033-248-7949</t>
+        </is>
+      </c>
+      <c r="AE404" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF404" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125589</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>[경남] 진주시 2026년 슬로바키아-루마니아 종합무역사절단 참가기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>KOTRA경남지원본부</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>온라인 접수(경상남도 해외마케팅 사업지원시스템)</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z405" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA405" t="inlineStr">
+        <is>
+          <t>필수, 해당사항, 참가신청서〔붙임1〕, 참가기업 각서〔붙임2〕, 기업정보 수집·이용·제공 동의서〔붙임3〕, 개인정보 활용 동의서〔붙임4〕, 기업프로필(엑셀)〔붙임5〕, 카탈로그(영문) PDF파일</t>
+        </is>
+      </c>
+      <c r="AB405" t="inlineStr">
+        <is>
+          <t>진주시 기업통상과 055-749-8147 KOTRA 경남지원본부 055-290-0602</t>
+        </is>
+      </c>
+      <c r="AC405" t="inlineStr"/>
+      <c r="AD405" t="inlineStr">
+        <is>
+          <t>055-290-0602</t>
+        </is>
+      </c>
+      <c r="AE405" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF405" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125588</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>[전남광주] 강진군 2026년 5차 음식점 지원사업 신청업소 모집 수정 공고</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>방문, 우편, 이메일, 팩스 접수
+- 방문 접수처 : 강진군청 관광체육국 축제마케팅추진단 식품위생팀(4층)
+- 우편 접수처 : 강진읍 탐진로 111, 관광체육국 축제마케팅추진단 식품위생팀(4층)
+- 이메일 : mahj0215@korea.kr
+- 팩스 : 061-430-3359</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>- 입식식탁 단가 : 1세트(식탁 1개 + 의자 4개 기준) 당 40만 원 이내</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>40만원</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z406" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA406" t="inlineStr">
+        <is>
+          <t>신청서, 개인정보동의서, 청렴이행서약서, 사업계획서, 견적서(부가세 포함), 영업주 주민등록등본, 자. 신청방법 : 방문, 우편</t>
+        </is>
+      </c>
+      <c r="AB406" t="inlineStr">
+        <is>
+          <t>강진군 축제마케팅추진단 061-430-3194</t>
+        </is>
+      </c>
+      <c r="AC406" t="inlineStr">
+        <is>
+          <t>mahj0215@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD406" t="inlineStr">
+        <is>
+          <t>061-430-3194</t>
+        </is>
+      </c>
+      <c r="AE406" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF406" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125587</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>[경북] 김천시ㆍ칠곡군 2026년 7차 시군특화 맞춤형 일자리 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>구미전자정보기술원</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>온라인 접수 (구미시 창업지원 통합안내사이트)</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>최종 선정 및        도제식</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr"/>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z407" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>대 보험 가입자 명부, 미래가지, PDF 파일로 변환 후, = 12] 파일로 제출 (파일명, /21(월), 예정, 신청방법, ㅇ 신청 사이트 수소 startup.gerire.kr</t>
+        </is>
+      </c>
+      <c r="AB407" t="inlineStr">
+        <is>
+          <t>구미전자정보기술원 창업성장지원센터 054-479-2054</t>
+        </is>
+      </c>
+      <c r="AC407" t="inlineStr"/>
+      <c r="AD407" t="inlineStr">
+        <is>
+          <t>054-479-2054</t>
+        </is>
+      </c>
+      <c r="AE407" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF407" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125586</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>[경기] 성남시 2026년 폴란드 시장개척단 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>성남산업진흥원</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>온라인 접수 (성남산업진흥원)</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>□ 항공료(1사 1인, 최대 100만원), 상담장 임차료, 시장조사비 등</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr"/>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z408" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA408" t="inlineStr"/>
+      <c r="AB408" t="inlineStr">
+        <is>
+          <t>성남산업진흥원 글로벌마케팅부 031-782-3062, hen039@snip.or.kr</t>
+        </is>
+      </c>
+      <c r="AC408" t="inlineStr">
+        <is>
+          <t>hen039@snip.or.kr</t>
+        </is>
+      </c>
+      <c r="AD408" t="inlineStr">
+        <is>
+          <t>031-782-3062</t>
+        </is>
+      </c>
+      <c r="AE408" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF408" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125585</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026년 콘크리트 2차 제품 제조기업 및 레미콘기업 패키지 지원사업 추가 공고(시멘트산업 이산화탄소 저감 및 종합실증센터 구축사업)</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>충북테크노파크</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>온라인 접수 
+- 온라인 : 컨택센터(과제관리시스템)
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>5천만 원 이상의 기업으로 이 중 1개 이상 해당하는 컨설팅 전문회사</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>5천만원</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z409" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>작성 후 컨택센터( )을 통한 접수, (원본 제출) 접수는 온라인으로만 진행하며, 선정기업에 한해 원본, 요청 예정, 구분, 비고, 사업신청서 1부 [서식1], 사업계획서 1부 [서식2]</t>
+        </is>
+      </c>
+      <c r="AB409" t="inlineStr">
+        <is>
+          <t>충북테크노파크 043-270-2234, dhkim@cbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC409" t="inlineStr">
+        <is>
+          <t>dhkim@cbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD409" t="inlineStr">
+        <is>
+          <t>043-270-2234</t>
+        </is>
+      </c>
+      <c r="AE409" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF409" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125584</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>[경기] 2026년 지역 혁신 Start-up Demo Day 프로그램 신청 공고</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>창업진흥원</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-09-03</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>온라인 접수(메이커스페이스전문랩)</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>대상                        중기부장관상                         1개                            500만원</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z410" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA410" t="inlineStr"/>
+      <c r="AB410" t="inlineStr">
+        <is>
+          <t>경기스케일업팩토리 메이커스페이스 전문랩 031-888-9552</t>
+        </is>
+      </c>
+      <c r="AC410" t="inlineStr"/>
+      <c r="AD410" t="inlineStr">
+        <is>
+          <t>031-888-9552</t>
+        </is>
+      </c>
+      <c r="AE410" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF410" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125583</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[전남광주] 2026년 해외지사화 지원사업 참여기업 모집 공고 </t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>KOTRA광주전남지원본부</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>온라인 접수
+- 발전 : (수출바우처 홈페이지) www.exportvoucher.com 
+- 긴급 : (KOTRA 홈페이지) https://www.kotra.or.kr/index.do</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>150~360만원</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>360만원</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z411" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>확인 후 기업 요청 계좌로 해외지사화 지원금 입금, [ 신청 시, 필수, 제출, 서류, ① 참가신청서 및 정보제공동의서 (별첨1, ④ 해외지사화 협약서 사본, ⑤ 기업참가비 납부 증빙</t>
+        </is>
+      </c>
+      <c r="AB411" t="inlineStr">
+        <is>
+          <t>KOTRA 광주전남지원본부 062-369-9055, kotragj@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AC411" t="inlineStr">
+        <is>
+          <t>kotragj@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AD411" t="inlineStr">
+        <is>
+          <t>062-369-9055</t>
+        </is>
+      </c>
+      <c r="AE411" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF411" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125582</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 지역중소기업 밀집지역 생태계 공동회복 지원과제 수요기업 모집 추가 공고(중소기업 밀집지역 위기대응 체계 구축사업)</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>충북테크노파크</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>온라인 접수 (충북테크노파크 컨택센터)</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>지원내용</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z412" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA412" t="inlineStr">
+        <is>
+          <t>업로드 (zip파일), 구분 제 출 서 류 비고, ① 사업신청서 1부 [서식1], ② 수행계획서 [서식2], 필수, ⑥ 과세표준증명원, 대보험가입자명부 각 1부 -, 해당시 ⑦ 보유 인증 및 특허</t>
+        </is>
+      </c>
+      <c r="AB412" t="inlineStr">
+        <is>
+          <t>충북 지역중소기업 위기지원센터(충북테크노파크) 043-270-2234, 2236 / dhkim@cbtp.or.kr, yhlee@cbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC412" t="inlineStr">
+        <is>
+          <t>dhkim@cbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD412" t="inlineStr">
+        <is>
+          <t>043-270-2234</t>
+        </is>
+      </c>
+      <c r="AE412" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF412" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125581</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>[전남광주] 나주시ㆍ목포시ㆍ장성군ㆍ함평군 2026년 에너지산업 융복합단지 활성화 기업지원사업 통합 공고</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>전남테크노파크</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>온라인, 방문(우편), 이메일 접수
+※ 프로그램별 신청방법 상이하므로 공고문 6p 참조</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>프로그램 지원규모(기업당) 선정규모 핵심 키워드</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z413" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>검토(관련기관) 및 현장방문(필요시), ㅇ 2차 선정평가 : 분야별 외부 전문가를 평가, ㅇ 평가절차 : 사업계획서 10분 발표, 질의응답 10분, 인력양성, ㅇ 신청서 등, 검토 및 별도 협의(수요 맞춤형 교육과정 운영), 신청방법 및</t>
+        </is>
+      </c>
+      <c r="AB413" t="inlineStr">
+        <is>
+          <t>전남테크노파크 에너지산업센터 061-337-5061 / 한국기계전기전자시험연구원 전력기반센터 061-935-5001, cjf9400@ktc.re.kr / 한국전기산업진흥회 에너지밸리기업개발원 070-4825-1172, ysk@evedi.or.kr / 에너지밸리산학융합원 기업지원실 061-338-8674, ibkim@eiuca.or.kr</t>
+        </is>
+      </c>
+      <c r="AC413" t="inlineStr">
+        <is>
+          <t>cjf9400@ktc.re.kr</t>
+        </is>
+      </c>
+      <c r="AD413" t="inlineStr">
+        <is>
+          <t>061-337-5061</t>
+        </is>
+      </c>
+      <c r="AE413" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF413" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125580</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 전남광주통합특별시 소재 소상공인ㆍ사회적경제기업 판로 확대 지원기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>한국인터넷진흥원</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>이메일 접수 (esg@kisa.or.kr)</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>지원금(100만원) 및홈페이지 보안 취약점 무료 점검</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z414" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA414" t="inlineStr">
+        <is>
+          <t>제출, ※ 제목: 2026년 KISA 판로 확대 지원기업 공모, 신청서, 소상공인·사회적경제기업확인서, 구 분, 내 용, 비 고, · 업체 정보</t>
+        </is>
+      </c>
+      <c r="AB414" t="inlineStr">
+        <is>
+          <t>한국인터넷진흥원 ESG추진팀 지역상생 담당자 061-820-1337</t>
+        </is>
+      </c>
+      <c r="AC414" t="inlineStr">
+        <is>
+          <t>esg@kisa.or.kr</t>
+        </is>
+      </c>
+      <c r="AD414" t="inlineStr">
+        <is>
+          <t>061-820-1337</t>
+        </is>
+      </c>
+      <c r="AE414" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF414" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125579</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026년 부산 극한극지 산업용 화합물 반도체 제조 인프라 구축 기업지원 모집 공고</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>부산테크노파크</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-10-30</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>이메일 접수 (smju71@btp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>※ 부산테크노파크 전력반도체센터 보유 장비를 활용한 직접지원이 원칙이며, 세부 지원 내용은</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z415" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA415" t="inlineStr"/>
+      <c r="AB415" t="inlineStr">
+        <is>
+          <t>부산테크노파크 전력반도체센터 051-583-3992, smju71@btp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC415" t="inlineStr">
+        <is>
+          <t>smju71@btp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD415" t="inlineStr">
+        <is>
+          <t>051-583-3992</t>
+        </is>
+      </c>
+      <c r="AE415" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF415" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125578</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>[경남] 2026년 4차 타깃마케팅(프랑스) 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>경남테크노파크</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경남테크노파크)</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>&lt;지역&gt;&lt;행사명&gt;&lt;추진일정&gt;&lt;모집기업&gt;&lt;지원내용&gt;</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z416" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA416" t="inlineStr">
+        <is>
+          <t>수혜기업 지원신청서 1부, ㅇ(수혜기업 선정절차), &lt;절 차&gt;&lt;&gt;&lt;일 정&gt;&lt;&gt;&lt;비 고&gt;&lt;&gt;&lt;주 체&gt;, 주말 및 공휴일 제외)&gt;&lt;&gt;&lt;우주항공본부&gt;, ※ 상기 추진 일정은 사정에 따라 변경될 수 있음</t>
+        </is>
+      </c>
+      <c r="AB416" t="inlineStr">
+        <is>
+          <t>경남테크노파크 우주항공본부 055-853-6822, true1113@gntp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC416" t="inlineStr">
+        <is>
+          <t>true1113@gntp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD416" t="inlineStr">
+        <is>
+          <t>055-853-6822</t>
+        </is>
+      </c>
+      <c r="AE416" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF416" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125577</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>[충남] 2026년 충남창업마루나비 전시ㆍ박람회 참가기업 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>충남창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>온라인 접수 (충남창조경제혁신센터 통합시스템)</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>❍ 지원내용: 부스비, 장치비, 홍보비 등 전시·박람회 참가비 지원(300만원</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>300만원</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z417" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA417" t="inlineStr">
+        <is>
+          <t>를 바탕으로 내부 심사를 통한 자격 심사, (서류평가) 신청서 및 사업계획서 서면평가, (발표평가) PT 발표평가(5분 발표, 분 질의응답), · 평가위원 점수 총점을 산술평균 점수 산출 후, 종합표에서 고득점자 순으로, 발표평가 대상자 선정, · 동점자 발생 시</t>
+        </is>
+      </c>
+      <c r="AB417" t="inlineStr">
+        <is>
+          <t>충남창조경제혁신센터 투자육성실 041-536-7834</t>
+        </is>
+      </c>
+      <c r="AC417" t="inlineStr"/>
+      <c r="AD417" t="inlineStr">
+        <is>
+          <t>041-536-7834</t>
+        </is>
+      </c>
+      <c r="AE417" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF417" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125576</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 7차 ILP 서비스 기술연결 수요기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>전북테크노파크</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>온라인 접수(전북특별자치도 ILP 서비스 시스템)
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>지원내용 수요-공급 기술 연결 및 기술확보 방안</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z418" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA418" t="inlineStr"/>
+      <c r="AB418" t="inlineStr">
+        <is>
+          <t>전북테크노파크 기업지원단 기술사업화팀 063-219-2168, annalee@jbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC418" t="inlineStr">
+        <is>
+          <t>annalee@jbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD418" t="inlineStr">
+        <is>
+          <t>063-219-2168</t>
+        </is>
+      </c>
+      <c r="AE418" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF418" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125575</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 3차 차세대 이차전지 공동연구센터 산학공동기술개발과제 공고(지역혁신중심 대학지원체계(RISE))</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>충북대학교</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>온라인 접수 (지역산업진흥원 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z419" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA419" t="inlineStr"/>
+      <c r="AB419" t="inlineStr">
+        <is>
+          <t>국립한국교통대학교 RISE사업단 R&amp;BD팀 043-849-1733, wmg85@ut.ac.kr</t>
+        </is>
+      </c>
+      <c r="AC419" t="inlineStr">
+        <is>
+          <t>wmg85@ut.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD419" t="inlineStr">
+        <is>
+          <t>043-849-1733</t>
+        </is>
+      </c>
+      <c r="AE419" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF419" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125574</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 3차 첨단바이오 공동연구센터 산학공동기술개발과제 공고(지역혁신중심 대학지원체계(RISE))</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>충북대학교</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>온라인 접수 (지역산업진흥원 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>□ 지원내용</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z420" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA420" t="inlineStr"/>
+      <c r="AB420" t="inlineStr">
+        <is>
+          <t>건국대학교 RISE사업단 043-840-4914, sim1023@kku.ac.kr</t>
+        </is>
+      </c>
+      <c r="AC420" t="inlineStr">
+        <is>
+          <t>sim1023@kku.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD420" t="inlineStr">
+        <is>
+          <t>043-840-4914</t>
+        </is>
+      </c>
+      <c r="AE420" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF420" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125573</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 경량소재산업 경쟁력강화 기술지원사업 연구기관 장비활용 기업지원 공고</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>경북테크노파크</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경북테크노파크)</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>지원규모 : 기업 당 5000천원 이내로 총 4개 기업 내외 지원</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>4개</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z421" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA421" t="inlineStr"/>
+      <c r="AB421" t="inlineStr">
+        <is>
+          <t>경북테크노파크 미래차부품경량화추진실 054-634-6591</t>
+        </is>
+      </c>
+      <c r="AC421" t="inlineStr"/>
+      <c r="AD421" t="inlineStr">
+        <is>
+          <t>054-634-6591</t>
+        </is>
+      </c>
+      <c r="AE421" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF421" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125572</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>[경북] 구미시 2026년 2차 소상공인 로컬팩(Local Pack) 지원사업 구미시 로컬 커넥트 그룹지원 참여자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>구미전자정보기술원</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>온라인 접수 (구미시 창업지원안내사이트)</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>000만원 지원"</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>0만원</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr"/>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z422" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>O 참가신청서 및 계획서”, 붙임서류(주민등록등본", 발표자료”, 참가신청서는 공고 내 AAS SAS 사용하여야 하며, 임의 양식으로 제출 시 평가, 료는, 유의 사항, O 사업 신청 및 선정 유의 사항</t>
+        </is>
+      </c>
+      <c r="AB422" t="inlineStr">
+        <is>
+          <t>구미전자정보기술원 창업성장지원센터 로컬팩 사업 담당자 054-479-2071</t>
+        </is>
+      </c>
+      <c r="AC422" t="inlineStr"/>
+      <c r="AD422" t="inlineStr">
+        <is>
+          <t>054-479-2071</t>
+        </is>
+      </c>
+      <c r="AE422" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF422" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125571</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026년 공개SW 및 SW안전 유공자 표창 계획 공고</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>정보통신산업진흥원</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-14</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>이메일 접수 (cgy@nipa.kr)
+※ 원본 한글파일(HWP)과 서명 스캔본(PDF) 모두 제출
+※ 파일명은 양식별로 ‘서식번호. 제출서류명_소속_성명’으로 작성하여 제출</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z423" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA423" t="inlineStr"/>
+      <c r="AB423" t="inlineStr">
+        <is>
+          <t>정보통신산업진흥원 043-931-5379</t>
+        </is>
+      </c>
+      <c r="AC423" t="inlineStr"/>
+      <c r="AD423" t="inlineStr">
+        <is>
+          <t>043-931-5379</t>
+        </is>
+      </c>
+      <c r="AE423" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF423" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125570</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026년 산업재해예방시설자금 융자금 지원사업 수정 공고</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>한국산업안전보건공단</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-12-31</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>온라인 접수 (산업안전포털)</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>③ 정부지원 정책자금을 융자 신청일의 직전 년도 말일부터 최근 3년 동안 100억원을 초과</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>100억원</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X424" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Y424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z424" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>ㅇ 실거래금액 증빙자료 ㅇ 실거래금액 증빙자료 간소화, 간소화 - 전자세금계산서 XML, PDF파일, 거래 - 전자세금계산서 XML파일만 제출, (7p) 사실 확인서 4.24, 년 산업재해예방시설자금, 융자금 지원사업 수정(2차) 공고, 같이 수정 공고합니다.</t>
+        </is>
+      </c>
+      <c r="AB424" t="inlineStr">
+        <is>
+          <t>융자금 지원사업 대표번호 1544-3088 및 일선기관별 관할지역 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC424" t="inlineStr"/>
+      <c r="AD424" t="inlineStr">
+        <is>
+          <t>02-2086-8014</t>
+        </is>
+      </c>
+      <c r="AE424" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF424" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125569</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 글로벌 플랫폼 연계 사업화 기술지원 수혜기업 추가 모집 공고(지능형첨단부품산업의 디지털전환 거점 구축 사업)</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>충북테크노파크</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>온라인 접수 (충북테크노파크 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>q (지원내용)</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z425" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>누락 등 최종 제출되지 않은 경우, 접수 불가, 사업 신청 시 아래 서류를 온라인으로 등록, m 모든 서류는 공고일(`26.8.18.) 기준, 직전 3개월(`26.5.18이후) 이내, 발급된 서류 제출 필수, `26. 5. 18. 이전 서류는 불인정, 비고</t>
+        </is>
+      </c>
+      <c r="AB425" t="inlineStr">
+        <is>
+          <t>충북테크노파크 스마트제조혁신센터 제조AI팀 043-270-2851, shkim@cbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC425" t="inlineStr">
+        <is>
+          <t>shkim@cbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD425" t="inlineStr">
+        <is>
+          <t>043-270-2851</t>
+        </is>
+      </c>
+      <c r="AE425" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF425" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125568</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026년 2차 안전동행 지원사업 수정 공고</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>한국산업안전보건공단</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>온라인 접수 (산업안전포털)</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>운영기관) 지원금액 1천만원 이상인 경우 인정</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>1천만원</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z426" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA426" t="inlineStr">
+        <is>
+          <t>신청 가능한 공정의 범위는 주조, 소성가공, 표면처리에 한함, ※ 뿌리기업 확인서에 주조, 표면처리 여부가 명시되지 않은 경우, 공장등록증, 경우만 인정, 주조산업 소성가공산업 표면처리산업</t>
+        </is>
+      </c>
+      <c r="AB426" t="inlineStr">
+        <is>
+          <t>안전동행 지원사업 대표번호 1644-4555 및 공단 일선 기관별 문의처 참고</t>
+        </is>
+      </c>
+      <c r="AC426" t="inlineStr"/>
+      <c r="AD426" t="inlineStr">
+        <is>
+          <t>02-2086-8014</t>
+        </is>
+      </c>
+      <c r="AE426" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF426" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125567</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>[경남] 2026년 ICT 이노베이션스퀘어확산사업 기업협력 프로젝트 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>한국기술사업화진흥협회</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-10-09</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>온라인 접수(구글폼)</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>인턴 종료 후 정규직 전환 Al 1인당 500만 원 지원</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z427" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA427" t="inlineStr"/>
+      <c r="AB427" t="inlineStr">
+        <is>
+          <t>한국기술사업화진흥협회 교육운영팀 070-8897-3810 사업기획팀 070-8897-3822, coedu2021@naver.com</t>
+        </is>
+      </c>
+      <c r="AC427" t="inlineStr">
+        <is>
+          <t>coedu2021@naver.com</t>
+        </is>
+      </c>
+      <c r="AD427" t="inlineStr">
+        <is>
+          <t>070-8897-3810</t>
+        </is>
+      </c>
+      <c r="AE427" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF427" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125566</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>[경북] 문경시 2026년 소상공인 카드수수료 지원사업 참여점포 모집 변경 공고</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>온라인 접수 및 방문 접수
+- 온라인 : 행복카드.kr
+- 접수처
+ㆍ읍, 면, 동 행정복지센터
+ㆍ 경상북도경제진흥원 북부지소(안동시 북순환로 387, 2층)
+ㆍ 문경시 소상공인연합회(경북 문경시 신흥로 165, 2층)
+※ 접수 우선순위는 온라인(행복카드.kr) 등록 기준으로 결정되며, 팩스ㆍ우편 등의 방법으로 제출할 경우 접수 순번이 늦어질 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>○ 사 업 대 상 : 전년도(‘25년) 연매출액 4억원 이하인 소상공인</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>4억원</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z428" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>온라인 접수 시 방문 접수 시, 심사 및 선정, ㅇ 사업 신청 접수순으로 심사, 미비 시 접수순서는 유지하되, 보완 완료 후 심사 가능, ※ 서류 보완 안내 개인 연락처로 안내되오니, 연락처 정확히 기재 바랍니다, ㅇ 국세청 세무신고 여부</t>
+        </is>
+      </c>
+      <c r="AB428" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 북부지소 054-900-3838 / 문경시 소상공인연합회 054-554-0099</t>
+        </is>
+      </c>
+      <c r="AC428" t="inlineStr"/>
+      <c r="AD428" t="inlineStr">
+        <is>
+          <t>054-554-0099</t>
+        </is>
+      </c>
+      <c r="AE428" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF428" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125565</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>[경기] 성남시 2027년 기업환경 개선사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>방문 또는 우편접수
+- 접수처 : 성남시 중원구 성남대로 997, 성남시청 서관 8층 기업혁신과
+※ 우편 신청 시 담당자 수신 여부 유선 확인 필수 (031-729-2583)</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>∙ 사업비 15백만원(VAT 제외) 이상 공사는 반드시 건축공사업 또는 해당</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>15백만원</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z429" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA429" t="inlineStr">
+        <is>
+          <t>∙ 주 소: 성남시 중원구 성남대로 997, 성남시청 서관 8층 기업혁신과, 사업계획서(서식) 1부, 자부담확약서(서식) 1부, 시설물 유지 동의서(서식) 1부, 중소기업 확인서 1부, (서식은 붙임의, 사업추진 동의서(토지·건물주 동의서</t>
+        </is>
+      </c>
+      <c r="AB429" t="inlineStr">
+        <is>
+          <t>성남시 기업혁신과 기업고도화팀 031-729-2583</t>
+        </is>
+      </c>
+      <c r="AC429" t="inlineStr"/>
+      <c r="AD429" t="inlineStr">
+        <is>
+          <t>031-729-2583</t>
+        </is>
+      </c>
+      <c r="AE429" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF429" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125564</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026년 3차 안전일터 조성지원 사업 수정 공고</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>한국산업안전보건공단</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>세부사업별 상이</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>온라인 접수 (산업안전포털)
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>ㅇ (지원한도) 동일 사업주 또는 법인 당 최대 3000만원까지</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>3000만원</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z430" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>를 확인, 신속지원으로 신청 시 심사위원회 생략, ㅇ 신청시, 및 원가계산서 제출시기, (5p) - 견적서 등 보조 신청금 산출내역서 명확화, (신청시, 견적서, (원가계산서 제출시기) 우선선정 후</t>
+        </is>
+      </c>
+      <c r="AB430" t="inlineStr">
+        <is>
+          <t>안전일터 조성지원 대표번호 1544-3088 및 공단 일선기관별 문의처 공고문 참고</t>
+        </is>
+      </c>
+      <c r="AC430" t="inlineStr">
+        <is>
+          <t>OOOOOOO@naver.com</t>
+        </is>
+      </c>
+      <c r="AD430" t="inlineStr">
+        <is>
+          <t>000-000-0000</t>
+        </is>
+      </c>
+      <c r="AE430" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF430" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125563</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>미래자동차 소음저감 기술 평가 기반구축 지원사업 기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>한국자동차연구원</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>우편 또는 방문 접수
+- 접수처 : 광주 광산구 진곡산단중앙로55, 한국자동차연구원 전장기술연구센터</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z431" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA431" t="inlineStr"/>
+      <c r="AB431" t="inlineStr">
+        <is>
+          <t>한국자동차연구원 062-960-9208, 9219 / 광주 미래차모빌리티진흥원 062-960-9547</t>
+        </is>
+      </c>
+      <c r="AC431" t="inlineStr"/>
+      <c r="AD431" t="inlineStr">
+        <is>
+          <t>062-960-9208</t>
+        </is>
+      </c>
+      <c r="AE431" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF431" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125562</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>[전남광주] 보성군 2026년 소규모 사업장 사물인터넷 측정기기 (IoT) 부착 지원사업 추가 공고</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2026-08-12 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>방문 또는 우편 접수
+- 접수처 : (59455) 보성군 보성읍 송재로 165 보성군청 3층 기후환경과</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>27만원(부착</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>27만원</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z432" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>를 직접 방문하여 보성군청 기후환경과 접수, 나. 우편접수 : 신청서 및, 를 우편 발송(운송료 신청, 자 부담), 보내실 곳 :, (우)59455 보성군 보성읍 송재로 165 보성군청, 층 기후환경과, 지원내용 및 금액</t>
+        </is>
+      </c>
+      <c r="AB432" t="inlineStr">
+        <is>
+          <t>보성군 기후환경과 061-850-5346</t>
+        </is>
+      </c>
+      <c r="AC432" t="inlineStr"/>
+      <c r="AD432" t="inlineStr">
+        <is>
+          <t>061-850-5346</t>
+        </is>
+      </c>
+      <c r="AE432" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF432" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125561</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>[서울] 서초구 2026년 소상공인 대상 AI 홍보 컨텐츠 제작지원 신청자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>상시 접수</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>온라인 접수(구글폼)</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>* 월 OF 10만원 상당의 요금제</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z433" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA433" t="inlineStr"/>
+      <c r="AB433" t="inlineStr">
+        <is>
+          <t>서초구 스마트 도시과 02-2155-6431 드랩 hi@draph.ai</t>
+        </is>
+      </c>
+      <c r="AC433" t="inlineStr">
+        <is>
+          <t>hi@draph.ai</t>
+        </is>
+      </c>
+      <c r="AD433" t="inlineStr">
+        <is>
+          <t>02-2155-6431</t>
+        </is>
+      </c>
+      <c r="AE433" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF433" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125560</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 상인ㆍ소상공인 AI코칭 지원사업 참여자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>이메일 접수 (hjlee@gepa.kr)
+※ 신청 후 접수 확인전화 필수</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>사업수행 최종선정 보완서류 요청</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z434" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>번호 서류 발급처, 공고문 내, 사업신청서(서식1), 붙임서류 참조, 국세청, 중소기업현황, 소상공인확인서, 정보시스템</t>
+        </is>
+      </c>
+      <c r="AB434" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 민생경제지원팀 054-995-9926</t>
+        </is>
+      </c>
+      <c r="AC434" t="inlineStr">
+        <is>
+          <t>hjlee@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD434" t="inlineStr">
+        <is>
+          <t>054-995-9926</t>
+        </is>
+      </c>
+      <c r="AE434" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF434" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125559</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>[서울] 마포구 2026년 하반기 중소기업육성기금 융자 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 마포구 월드컵로 212, 마포구청 8층 경제진흥과
+※ 재원 소진 시까지 선착순 모집하여 접수 조기 마감될 수 있으므로, 반드시 신청 가능 여부 문의 후 신청 (02-3153-8576)</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>융자규모: 총 20억 원</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>20억원</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z435" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA435" t="inlineStr"/>
+      <c r="AB435" t="inlineStr">
+        <is>
+          <t>마포구청 경제진흥과 02-3153-8576</t>
+        </is>
+      </c>
+      <c r="AC435" t="inlineStr"/>
+      <c r="AD435" t="inlineStr">
+        <is>
+          <t>02-3153-8576</t>
+        </is>
+      </c>
+      <c r="AE435" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF435" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125558</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>[전남광주] 광산구 청년 노동자 주거 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-03</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>방문, 우편 또는 이메일 접수
+- 접수처 : 전남광주통합특별시 서구 대남대로 465 광주상공회의소 604호(내일엔)
+- 이메일 : mojankim@naver.com</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>o 지원내용: 청년 1인당 월 최대 50만원씩 최소 2년(최대 8년)간 주거비 지원</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z436" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>연번 작성 및, 비고, 참여 신청서 서식1, 참여기업 재직 청년 현황(신청용) 서식2, 참여자격 확인서(사업주용) 서식3, 중소기업확인서 〃, 홈택스 주업종코드확인서 캡처 화면 〃, 고용보험 사업장 자격취득자 명부(사업자용) 〃</t>
+        </is>
+      </c>
+      <c r="AB436" t="inlineStr">
+        <is>
+          <t>광산구청년노동자주거지원센터 062-716-2841, 내선3 / 광산구청 지속가능일자리특구추진단 062-960-4121, 4122</t>
+        </is>
+      </c>
+      <c r="AC436" t="inlineStr"/>
+      <c r="AD436" t="inlineStr">
+        <is>
+          <t>062-716-2841</t>
+        </is>
+      </c>
+      <c r="AE436" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF436" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125557</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>[서울] 노원구 2026년 하반기 중소기업ㆍ소상공인 육성기금 융자지원 계획 공고</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 노원구청 3층 지역경제과</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>융자규모 : 총 15억원</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>15억원</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W437" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X437" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y437" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z437" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA437" t="inlineStr">
+        <is>
+          <t>제출이 불가한 업체, 신청일정 및 방법, 가. 공고방법 : 노원구청 홈페이지, 오전 9시 ~ 오후 3시, 심의위원회, 개최 및 결정통보, 국민은행 &lt;신용보증서 및 부동산 담보 상담&gt;, 노원구청 1층 국민은행</t>
+        </is>
+      </c>
+      <c r="AB437" t="inlineStr">
+        <is>
+          <t>노원구청 지역경제과 02-2116-3497 (신용보증서 및 부동산 담보 상담) 국민은행 노원구청점 02-3392-5961</t>
+        </is>
+      </c>
+      <c r="AC437" t="inlineStr"/>
+      <c r="AD437" t="inlineStr">
+        <is>
+          <t>02-2116-3497</t>
+        </is>
+      </c>
+      <c r="AE437" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF437" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125556</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>[서울] 성북구 2026년 하반기 중소기업육성기금 융자지원 계획 공고</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>서울신용보증재단</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 성북구청 8층 지역경제과</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>2026년도 하반기 융자 규모: 15억 3천만원</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>3천만원</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z438" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA438" t="inlineStr">
+        <is>
+          <t>중소기업육성기금 융자추천 신청서 1부, 다., 접 수 처, 라. 접수 방법 : 방문 접수, 상담 및 문의처, 담보 대출은 우리은행 성북구청지점, 내선번호 222, ※ 성북구청 홈페이지:</t>
+        </is>
+      </c>
+      <c r="AB438" t="inlineStr">
+        <is>
+          <t>성북구청 지역경제과 02-2241-3965 (담보 대출) 우리은행 성북구청지점 02-924-4161, 내선번호 222 (신용 대출) 서울신용보증재단 성북지점 02-2174-4579, 4580</t>
+        </is>
+      </c>
+      <c r="AC438" t="inlineStr"/>
+      <c r="AD438" t="inlineStr">
+        <is>
+          <t>02-2174-4579</t>
+        </is>
+      </c>
+      <c r="AE438" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF438" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125555</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>[경기] 시흥시 2026년 소공인 수출ㆍ마케팅지원사업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>시흥산업진흥원</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>온라인 접수 (소상공인24)</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>가액만 지급(최대 3백만원, 지원금액 한도 이상 비용은 신청인이 수행업체로 지급)</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>3백만원</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W439" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X439" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y439" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z439" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA439" t="inlineStr">
+        <is>
+          <t>비고, 사업신청서/사업계획서 서식1/서식5, 자가진단 체크리스트 서식2, 개인정보 동의서 서식3, 견적서 및 비교견적서, 구체적인 내용(수량, 단가 등)이 기재되어 있어야 하며, 스캔본 제출</t>
+        </is>
+      </c>
+      <c r="AB439" t="inlineStr">
+        <is>
+          <t>시흥산업진흥원 소상공인지원본부 소공인지원실 시흥정왕전기장비센터 031-434-8737, sogong@sida.kr</t>
+        </is>
+      </c>
+      <c r="AC439" t="inlineStr">
+        <is>
+          <t>sogong@sida.kr</t>
+        </is>
+      </c>
+      <c r="AD439" t="inlineStr">
+        <is>
+          <t>031-434-8737</t>
+        </is>
+      </c>
+      <c r="AE439" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF439" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125554</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>[서울] 성동구 2026년 지역특화 일자리사업 성동 워크업(Work-Up) 프로젝트 참여 기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>서울청년센터</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>온라인 접수(구글폼)</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>최대 50만원 최대 50만원</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z440" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA440" t="inlineStr">
+        <is>
+          <t>는 최종 선정기업에 별도 안내</t>
+        </is>
+      </c>
+      <c r="AB440" t="inlineStr">
+        <is>
+          <t>서울청년센터 성동 070-4282-1758</t>
+        </is>
+      </c>
+      <c r="AC440" t="inlineStr"/>
+      <c r="AD440" t="inlineStr">
+        <is>
+          <t>070-4282-1758</t>
+        </is>
+      </c>
+      <c r="AE440" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF440" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125553</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>[경기] 화성시 2026년 4차 중소기업 운전자금 지원사업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>온라인 접수(화성시기업지원플랫폼)
+① 지원 접수 전, 취급은행과 대출 상담 권고(대출 가능 여부 및 한도 확인)
+② 화성시기업지원플랫폼을 통한 온라인 접수로 모든 구비서류는 플랫폼을 통한 제출
+※ 오프라인ㆍ이메일 접수 불가
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>❍ 지원내용: 기업당 최대 5억원 융자에 대한 금리 2% 지원</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>5억원</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z441" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA441" t="inlineStr"/>
+      <c r="AB441" t="inlineStr">
+        <is>
+          <t>기업지원과 기업SOS팀 031-5189-7422 및 협약은행 각 모점 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC441" t="inlineStr"/>
+      <c r="AD441" t="inlineStr">
+        <is>
+          <t>031-5189-7422</t>
+        </is>
+      </c>
+      <c r="AE441" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF441" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125552</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026년 사회연대경제기업 공공구매 상담회 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>한국사회적기업진흥원</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>이메일 접수 (value@value-plus.kr)
+※ 운영기관에게 서류 접수 확인 연락(044-864-8676)</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>25개소 선정</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>25개</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z442" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>메일 제출), 운영기관에게, 서류 접수 확인 연락, (월), 신청기업 개별 연락 예정, 참여희망기업→운영기관, 운영기관, 신청방법 :</t>
+        </is>
+      </c>
+      <c r="AB442" t="inlineStr">
+        <is>
+          <t>가치플러스 사회적협동조합 044-864-8676</t>
+        </is>
+      </c>
+      <c r="AC442" t="inlineStr">
+        <is>
+          <t>value@value-plus.kr</t>
+        </is>
+      </c>
+      <c r="AD442" t="inlineStr">
+        <is>
+          <t>044-864-8676</t>
+        </is>
+      </c>
+      <c r="AE442" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF442" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125551</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>AI EXPO MARS 2026 부스 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>화성산업진흥원</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>온라인 접수 (기업지원플랫폼)</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>□ (선정규모) 00개사</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>00개</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z443" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA443" t="inlineStr"/>
+      <c r="AB443" t="inlineStr">
+        <is>
+          <t>화성산업진흥원 031-374-6896, ji0024@hsbiz.or.kr / 사무국(운영) 02-6000-6726,7717, etw0401@exporum.com, shannon@exporum.com</t>
+        </is>
+      </c>
+      <c r="AC443" t="inlineStr">
+        <is>
+          <t>etw0401@exporum.com</t>
+        </is>
+      </c>
+      <c r="AD443" t="inlineStr">
+        <is>
+          <t>02-6000-6726</t>
+        </is>
+      </c>
+      <c r="AE443" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF443" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125550</t>
         </is>
       </c>
     </row>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF443"/>
+  <dimension ref="A1:AF487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60831,8 +60831,6 @@
           <t>□ (지원내용) 외부 전문가를 활용한 ESG 지표별 컨설팅 진행</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr"/>
-      <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr">
         <is>
           <t>N</t>
@@ -60928,13 +60926,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA393" t="inlineStr"/>
       <c r="AB393" t="inlineStr">
         <is>
           <t>한국임업진흥원 기획조정실 02-6393-2518</t>
         </is>
       </c>
-      <c r="AC393" t="inlineStr"/>
       <c r="AD393" t="inlineStr">
         <is>
           <t>02-6393-2518</t>
@@ -60984,7 +60980,6 @@
           <t>7억원</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr">
         <is>
           <t>Y</t>
@@ -61142,7 +61137,6 @@
           <t>300만원</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr">
         <is>
           <t>Y</t>
@@ -61295,8 +61289,6 @@
           <t>m 지원내용 : 수출 목적의 해외 물류비(2026) 지원</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr"/>
-      <c r="G396" t="inlineStr"/>
       <c r="H396" t="inlineStr">
         <is>
           <t>Y</t>
@@ -61556,13 +61548,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA397" t="inlineStr"/>
       <c r="AB397" t="inlineStr">
         <is>
           <t>남구청 일자리경제과 청년정책팀 051-607-3681</t>
         </is>
       </c>
-      <c r="AC397" t="inlineStr"/>
       <c r="AD397" t="inlineStr">
         <is>
           <t>051-607-3681</t>
@@ -61607,8 +61597,6 @@
           <t>▢ 지원 내용</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr">
         <is>
           <t>Y</t>
@@ -62029,7 +62017,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA400" t="inlineStr"/>
       <c r="AB400" t="inlineStr">
         <is>
           <t>전북바이오융합산업진흥원 창업일자리팀 063-210-6581, 6583 / jife6581@gmail.com</t>
@@ -62090,7 +62077,6 @@
           <t>12000원</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr">
         <is>
           <t>Y</t>
@@ -62249,7 +62235,6 @@
           <t>26백만원</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr">
         <is>
           <t>Y</t>
@@ -62355,7 +62340,6 @@
           <t>영광군청 환경과 기후환경팀 061-350-4858</t>
         </is>
       </c>
-      <c r="AC402" t="inlineStr"/>
       <c r="AD402" t="inlineStr">
         <is>
           <t>061-350-4858</t>
@@ -62398,8 +62382,6 @@
           <t>q (지원내용) 기존 제품·부품에 AI 기능 적용 또는 기존 AI 솔루션의</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr"/>
-      <c r="G403" t="inlineStr"/>
       <c r="H403" t="inlineStr">
         <is>
           <t>Y</t>
@@ -62557,7 +62539,6 @@
           <t>1000만원</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr">
         <is>
           <t>Y</t>
@@ -62710,8 +62691,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr">
         <is>
           <t>Y</t>
@@ -62817,7 +62796,6 @@
           <t>진주시 기업통상과 055-749-8147 KOTRA 경남지원본부 055-290-0602</t>
         </is>
       </c>
-      <c r="AC405" t="inlineStr"/>
       <c r="AD405" t="inlineStr">
         <is>
           <t>055-290-0602</t>
@@ -63026,8 +63004,6 @@
           <t>최종 선정 및        도제식</t>
         </is>
       </c>
-      <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr"/>
       <c r="H407" t="inlineStr">
         <is>
           <t>N</t>
@@ -63133,7 +63109,6 @@
           <t>구미전자정보기술원 창업성장지원센터 054-479-2054</t>
         </is>
       </c>
-      <c r="AC407" t="inlineStr"/>
       <c r="AD407" t="inlineStr">
         <is>
           <t>054-479-2054</t>
@@ -63181,7 +63156,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr"/>
       <c r="H408" t="inlineStr">
         <is>
           <t>N</t>
@@ -63277,7 +63251,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA408" t="inlineStr"/>
       <c r="AB408" t="inlineStr">
         <is>
           <t>성남산업진흥원 글로벌마케팅부 031-782-3062, hen039@snip.or.kr</t>
@@ -63599,13 +63572,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA410" t="inlineStr"/>
       <c r="AB410" t="inlineStr">
         <is>
           <t>경기스케일업팩토리 메이커스페이스 전문랩 031-888-9552</t>
         </is>
       </c>
-      <c r="AC410" t="inlineStr"/>
       <c r="AD410" t="inlineStr">
         <is>
           <t>031-888-9552</t>
@@ -63655,7 +63626,6 @@
           <t>360만원</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr">
         <is>
           <t>Y</t>
@@ -63808,8 +63778,6 @@
           <t>지원내용</t>
         </is>
       </c>
-      <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr"/>
       <c r="H412" t="inlineStr">
         <is>
           <t>Y</t>
@@ -63963,8 +63931,6 @@
           <t>프로그램 지원규모(기업당) 선정규모 핵심 키워드</t>
         </is>
       </c>
-      <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr">
         <is>
           <t>N</t>
@@ -64122,7 +64088,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G414" t="inlineStr"/>
       <c r="H414" t="inlineStr">
         <is>
           <t>Y</t>
@@ -64275,8 +64240,6 @@
           <t>※ 부산테크노파크 전력반도체센터 보유 장비를 활용한 직접지원이 원칙이며, 세부 지원 내용은</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr">
         <is>
           <t>N</t>
@@ -64372,7 +64335,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA415" t="inlineStr"/>
       <c r="AB415" t="inlineStr">
         <is>
           <t>부산테크노파크 전력반도체센터 051-583-3992, smju71@btp.or.kr</t>
@@ -64425,8 +64387,6 @@
           <t>&lt;지역&gt;&lt;행사명&gt;&lt;추진일정&gt;&lt;모집기업&gt;&lt;지원내용&gt;</t>
         </is>
       </c>
-      <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr"/>
       <c r="H416" t="inlineStr">
         <is>
           <t>N</t>
@@ -64584,7 +64544,6 @@
           <t>300만원</t>
         </is>
       </c>
-      <c r="G417" t="inlineStr"/>
       <c r="H417" t="inlineStr">
         <is>
           <t>Y</t>
@@ -64690,7 +64649,6 @@
           <t>충남창조경제혁신센터 투자육성실 041-536-7834</t>
         </is>
       </c>
-      <c r="AC417" t="inlineStr"/>
       <c r="AD417" t="inlineStr">
         <is>
           <t>041-536-7834</t>
@@ -64734,8 +64692,6 @@
           <t>지원내용 수요-공급 기술 연결 및 기술확보 방안</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr">
         <is>
           <t>N</t>
@@ -64831,7 +64787,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA418" t="inlineStr"/>
       <c r="AB418" t="inlineStr">
         <is>
           <t>전북테크노파크 기업지원단 기술사업화팀 063-219-2168, annalee@jbtp.or.kr</t>
@@ -64884,8 +64839,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr"/>
       <c r="H419" t="inlineStr">
         <is>
           <t>N</t>
@@ -64981,7 +64934,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA419" t="inlineStr"/>
       <c r="AB419" t="inlineStr">
         <is>
           <t>국립한국교통대학교 RISE사업단 R&amp;BD팀 043-849-1733, wmg85@ut.ac.kr</t>
@@ -65034,8 +64986,6 @@
           <t>□ 지원내용</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr"/>
       <c r="H420" t="inlineStr">
         <is>
           <t>N</t>
@@ -65131,7 +65081,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA420" t="inlineStr"/>
       <c r="AB420" t="inlineStr">
         <is>
           <t>건국대학교 RISE사업단 043-840-4914, sim1023@kku.ac.kr</t>
@@ -65184,7 +65133,6 @@
           <t>지원규모 : 기업 당 5000천원 이내로 총 4개 기업 내외 지원</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr">
         <is>
           <t>4개</t>
@@ -65285,13 +65233,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA421" t="inlineStr"/>
       <c r="AB421" t="inlineStr">
         <is>
           <t>경북테크노파크 미래차부품경량화추진실 054-634-6591</t>
         </is>
       </c>
-      <c r="AC421" t="inlineStr"/>
       <c r="AD421" t="inlineStr">
         <is>
           <t>054-634-6591</t>
@@ -65339,7 +65285,6 @@
           <t>0만원</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr"/>
       <c r="H422" t="inlineStr">
         <is>
           <t>Y</t>
@@ -65445,7 +65390,6 @@
           <t>구미전자정보기술원 창업성장지원센터 로컬팩 사업 담당자 054-479-2071</t>
         </is>
       </c>
-      <c r="AC422" t="inlineStr"/>
       <c r="AD422" t="inlineStr">
         <is>
           <t>054-479-2071</t>
@@ -65490,8 +65434,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F423" t="inlineStr"/>
-      <c r="G423" t="inlineStr"/>
       <c r="H423" t="inlineStr">
         <is>
           <t>N</t>
@@ -65587,13 +65529,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA423" t="inlineStr"/>
       <c r="AB423" t="inlineStr">
         <is>
           <t>정보통신산업진흥원 043-931-5379</t>
         </is>
       </c>
-      <c r="AC423" t="inlineStr"/>
       <c r="AD423" t="inlineStr">
         <is>
           <t>043-931-5379</t>
@@ -65641,7 +65581,6 @@
           <t>100억원</t>
         </is>
       </c>
-      <c r="G424" t="inlineStr"/>
       <c r="H424" t="inlineStr">
         <is>
           <t>N</t>
@@ -65747,7 +65686,6 @@
           <t>융자금 지원사업 대표번호 1544-3088 및 일선기관별 관할지역 공고문 참조</t>
         </is>
       </c>
-      <c r="AC424" t="inlineStr"/>
       <c r="AD424" t="inlineStr">
         <is>
           <t>02-2086-8014</t>
@@ -65790,8 +65728,6 @@
           <t>q (지원내용)</t>
         </is>
       </c>
-      <c r="F425" t="inlineStr"/>
-      <c r="G425" t="inlineStr"/>
       <c r="H425" t="inlineStr">
         <is>
           <t>Y</t>
@@ -65949,7 +65885,6 @@
           <t>1천만원</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr"/>
       <c r="H426" t="inlineStr">
         <is>
           <t>N</t>
@@ -66055,7 +65990,6 @@
           <t>안전동행 지원사업 대표번호 1644-4555 및 공단 일선 기관별 문의처 참고</t>
         </is>
       </c>
-      <c r="AC426" t="inlineStr"/>
       <c r="AD426" t="inlineStr">
         <is>
           <t>02-2086-8014</t>
@@ -66103,7 +66037,6 @@
           <t>500만원</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr"/>
       <c r="H427" t="inlineStr">
         <is>
           <t>N</t>
@@ -66199,7 +66132,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA427" t="inlineStr"/>
       <c r="AB427" t="inlineStr">
         <is>
           <t>한국기술사업화진흥협회 교육운영팀 070-8897-3810 사업기획팀 070-8897-3822, coedu2021@naver.com</t>
@@ -66263,7 +66195,6 @@
           <t>4억원</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr"/>
       <c r="H428" t="inlineStr">
         <is>
           <t>Y</t>
@@ -66369,7 +66300,6 @@
           <t>경상북도경제진흥원 북부지소 054-900-3838 / 문경시 소상공인연합회 054-554-0099</t>
         </is>
       </c>
-      <c r="AC428" t="inlineStr"/>
       <c r="AD428" t="inlineStr">
         <is>
           <t>054-554-0099</t>
@@ -66419,7 +66349,6 @@
           <t>15백만원</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr"/>
       <c r="H429" t="inlineStr">
         <is>
           <t>Y</t>
@@ -66525,7 +66454,6 @@
           <t>성남시 기업혁신과 기업고도화팀 031-729-2583</t>
         </is>
       </c>
-      <c r="AC429" t="inlineStr"/>
       <c r="AD429" t="inlineStr">
         <is>
           <t>031-729-2583</t>
@@ -66574,7 +66502,6 @@
           <t>3000만원</t>
         </is>
       </c>
-      <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr">
         <is>
           <t>Y</t>
@@ -66728,8 +66655,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr"/>
       <c r="H431" t="inlineStr">
         <is>
           <t>N</t>
@@ -66825,13 +66750,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA431" t="inlineStr"/>
       <c r="AB431" t="inlineStr">
         <is>
           <t>한국자동차연구원 062-960-9208, 9219 / 광주 미래차모빌리티진흥원 062-960-9547</t>
         </is>
       </c>
-      <c r="AC431" t="inlineStr"/>
       <c r="AD431" t="inlineStr">
         <is>
           <t>062-960-9208</t>
@@ -66880,7 +66803,6 @@
           <t>27만원</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr"/>
       <c r="H432" t="inlineStr">
         <is>
           <t>Y</t>
@@ -66986,7 +66908,6 @@
           <t>보성군 기후환경과 061-850-5346</t>
         </is>
       </c>
-      <c r="AC432" t="inlineStr"/>
       <c r="AD432" t="inlineStr">
         <is>
           <t>061-850-5346</t>
@@ -67034,7 +66955,6 @@
           <t>10만원</t>
         </is>
       </c>
-      <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr">
         <is>
           <t>N</t>
@@ -67130,7 +67050,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA433" t="inlineStr"/>
       <c r="AB433" t="inlineStr">
         <is>
           <t>서초구 스마트 도시과 02-2155-6431 드랩 hi@draph.ai</t>
@@ -67184,8 +67103,6 @@
           <t>사업수행 최종선정 보완서류 요청</t>
         </is>
       </c>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr">
         <is>
           <t>Y</t>
@@ -67345,7 +67262,6 @@
           <t>20억원</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr"/>
       <c r="H435" t="inlineStr">
         <is>
           <t>N</t>
@@ -67441,13 +67357,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA435" t="inlineStr"/>
       <c r="AB435" t="inlineStr">
         <is>
           <t>마포구청 경제진흥과 02-3153-8576</t>
         </is>
       </c>
-      <c r="AC435" t="inlineStr"/>
       <c r="AD435" t="inlineStr">
         <is>
           <t>02-3153-8576</t>
@@ -67497,7 +67411,6 @@
           <t>50만원</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr">
         <is>
           <t>Y</t>
@@ -67603,7 +67516,6 @@
           <t>광산구청년노동자주거지원센터 062-716-2841, 내선3 / 광산구청 지속가능일자리특구추진단 062-960-4121, 4122</t>
         </is>
       </c>
-      <c r="AC436" t="inlineStr"/>
       <c r="AD436" t="inlineStr">
         <is>
           <t>062-716-2841</t>
@@ -67652,7 +67564,6 @@
           <t>15억원</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr">
         <is>
           <t>Y</t>
@@ -67758,7 +67669,6 @@
           <t>노원구청 지역경제과 02-2116-3497 (신용보증서 및 부동산 담보 상담) 국민은행 노원구청점 02-3392-5961</t>
         </is>
       </c>
-      <c r="AC437" t="inlineStr"/>
       <c r="AD437" t="inlineStr">
         <is>
           <t>02-2116-3497</t>
@@ -67807,7 +67717,6 @@
           <t>3천만원</t>
         </is>
       </c>
-      <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr">
         <is>
           <t>Y</t>
@@ -67913,7 +67822,6 @@
           <t>성북구청 지역경제과 02-2241-3965 (담보 대출) 우리은행 성북구청지점 02-924-4161, 내선번호 222 (신용 대출) 서울신용보증재단 성북지점 02-2174-4579, 4580</t>
         </is>
       </c>
-      <c r="AC438" t="inlineStr"/>
       <c r="AD438" t="inlineStr">
         <is>
           <t>02-2174-4579</t>
@@ -67961,7 +67869,6 @@
           <t>3백만원</t>
         </is>
       </c>
-      <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr">
         <is>
           <t>Y</t>
@@ -68119,7 +68026,6 @@
           <t>50만원</t>
         </is>
       </c>
-      <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr">
         <is>
           <t>N</t>
@@ -68225,7 +68131,6 @@
           <t>서울청년센터 성동 070-4282-1758</t>
         </is>
       </c>
-      <c r="AC440" t="inlineStr"/>
       <c r="AD440" t="inlineStr">
         <is>
           <t>070-4282-1758</t>
@@ -68277,7 +68182,6 @@
           <t>5억원</t>
         </is>
       </c>
-      <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr">
         <is>
           <t>N</t>
@@ -68373,13 +68277,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA441" t="inlineStr"/>
       <c r="AB441" t="inlineStr">
         <is>
           <t>기업지원과 기업SOS팀 031-5189-7422 및 협약은행 각 모점 공고문 참조</t>
         </is>
       </c>
-      <c r="AC441" t="inlineStr"/>
       <c r="AD441" t="inlineStr">
         <is>
           <t>031-5189-7422</t>
@@ -68423,7 +68325,6 @@
           <t>25개소 선정</t>
         </is>
       </c>
-      <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr">
         <is>
           <t>25개</t>
@@ -68581,7 +68482,6 @@
           <t>□ (선정규모) 00개사</t>
         </is>
       </c>
-      <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr">
         <is>
           <t>00개</t>
@@ -68682,7 +68582,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA443" t="inlineStr"/>
       <c r="AB443" t="inlineStr">
         <is>
           <t>화성산업진흥원 031-374-6896, ji0024@hsbiz.or.kr / 사무국(운영) 02-6000-6726,7717, etw0401@exporum.com, shannon@exporum.com</t>
@@ -68706,6 +68605,6908 @@
       <c r="AF443" t="inlineStr">
         <is>
           <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125550</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>[울산] K-함정 융합협력 플랫폼 구축 사업 R&amp;D 과제기획 수요기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>울산테크노파크</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-02</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>이메일 접수 (kimyj5139@utp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>○ (지원규모) 1개사 내외(기업당 최대 200만원)</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>200만원</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z444" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA444" t="inlineStr"/>
+      <c r="AB444" t="inlineStr">
+        <is>
+          <t>울산테크노파크 기업지원단 조선방산지원실 052-219-8674, kimyj5139@utp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC444" t="inlineStr">
+        <is>
+          <t>kimyj5139@utp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD444" t="inlineStr">
+        <is>
+          <t>052-219-8674</t>
+        </is>
+      </c>
+      <c r="AE444" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF444" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125645</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 4차 대학ㆍ기업 융합형 선도연구소 육성사업 협업ㆍ지원대상 기업 모집 공고(대구광역시 지역성장 인재양성체계(앵커)사업)</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>경북대학교 첨단정보통신융합산업기술원</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>2026-09-01 ~ 2026-09-28</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>이메일 접수
+- 협업형 기술개발 : 제출서류 이메일(lsg6479@iact.or.kr) 제출​
+- 학ㆍ학ㆍ산／산ㆍ학ㆍ연 : 제출서류 이메일(nyh7@iact.or.kr) 제출
+※ 지원분야별 접수 이메일 상이하므로 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>정부 지원금 + 기업 대응투자금 4400만원 총사업비의 25% 이상 현금(현물불가)</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>4400만원</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>이메일(lsg6479@iact.or.kr) 제출, 학·연·산 / 학·학·산 협업 :, 이메일(nyh7@iact.or.kr) 제출, 마감일 17시 이전 도착분에 한하며, 제출 시 기업명으로 접수, 순번 구분, 수량 유형 비고, 청렴 · 성실의무이행 · 중복지원방지 서약서</t>
+        </is>
+      </c>
+      <c r="AB445" t="inlineStr">
+        <is>
+          <t>경북대학교 첨단정보통신융합산업기술원 053-219-0543, 053-219-0400 및 과제별 문의처 상이하므로 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC445" t="inlineStr">
+        <is>
+          <t>hw83@iact.or.kr</t>
+        </is>
+      </c>
+      <c r="AD445" t="inlineStr">
+        <is>
+          <t>053-219-0400</t>
+        </is>
+      </c>
+      <c r="AE445" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF445" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125644</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>[강원] 2026년 강원가상융합산업 혁신센터 해외 전시회 참가지원 사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>강원정보문화산업진흥원</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>이메일 접수(kai@gica.or.kr)
+※유선을 통한 접수확인 요망(미확인에 의한 미접수 책임은 접수기업에 있음)</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>지원규모: 2개사 지원(기업 당 1100만원 내외 지원)</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>1100만원</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z446" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>원본 제출(kai@gica.or.kr), 라., 구분 No, 비고, 참가신청서 1부 붙임1 서식 참조, 참가계획서 1부 붙임2 서식 참조, 참가확약서 1부 붙임3 서식 참조, 한국무역통계진흥원</t>
+        </is>
+      </c>
+      <c r="AB446" t="inlineStr">
+        <is>
+          <t>강원정보문화산업진흥원 디지털콘텐츠팀 담당자 033-245-6311</t>
+        </is>
+      </c>
+      <c r="AC446" t="inlineStr">
+        <is>
+          <t>kai@gica.or.kr</t>
+        </is>
+      </c>
+      <c r="AD446" t="inlineStr">
+        <is>
+          <t>033-245-6311</t>
+        </is>
+      </c>
+      <c r="AE446" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF446" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125643</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>[대전] 서구 2026년 사회적경제 장터 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>이메일 접수 (pss0501@korea.kr)</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>모집규모</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z447" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>연번, 비 고, 해당서류 1부, 사회적경제기업 관련 인증서(지정서) 사본 1부, 참여기업 신청서, 서식 1, 개인정보 수집･이용 및 제공동의서 및 서약서 각 1부, 서식 2</t>
+        </is>
+      </c>
+      <c r="AB447" t="inlineStr">
+        <is>
+          <t>서구 사회적경제지원센터 042-288-2172 / 서구청 전략사업과 042-288-2443</t>
+        </is>
+      </c>
+      <c r="AC447" t="inlineStr">
+        <is>
+          <t>pss0501@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD447" t="inlineStr">
+        <is>
+          <t>042-288-2172</t>
+        </is>
+      </c>
+      <c r="AE447" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF447" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125642</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>[대전] 사회연대경제 청년 일경험사업 시범사업 3차 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>이메일 접수 (bik@djbea.or.kr)</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>□ 지원내용 : 참여청년 인건비*, 참여청년 1인당 운영비월 20만원,</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>20만원</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z448" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>제출 ‣(진흥원) 참여기업 심사·평가, 및 최종 선정 통보, ❻ 청년-기업 확정 ❺ 참여청년 면접 ❹ 참여청년 모집, ‣(진흥원) 청년-기업 매칭 확정 부 검토, 면접 주관 및 지원 참여청년 모집 공고, 용24를 통해, 제출, ※ 추진상황에 따라 일정 변동 가능</t>
+        </is>
+      </c>
+      <c r="AB448" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원 사회적경제지원팀 042-632-3732, 3734 / bik@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AC448" t="inlineStr">
+        <is>
+          <t>bik@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AD448" t="inlineStr">
+        <is>
+          <t>042-632-3732</t>
+        </is>
+      </c>
+      <c r="AE448" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF448" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125641</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>[경북] 김천시 2026년 중소기업 기숙사 임차비 지원사업 참여기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jungheon.ha@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>○ 대상자별지원금액 : 1실당 월 최대 300000원 지원</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>300000원</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z449" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>일체를 제출하는 기업 중 신청 접수순 선정, 지 원 기 간 : 최대 12개월, 대상자별지원금액 : 1실당 월 최대 300, 원 지원, 지 원 규 모 : 50개실 정도(기업당 10개실 한도), 추진절차, 모집공고 신청·접수 서류 검토, (목)</t>
+        </is>
+      </c>
+      <c r="AB449" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 ESGㆍ기업지원팀 054-470-8503, jungheon.ha@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AC449" t="inlineStr">
+        <is>
+          <t>jungheon.ha@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD449" t="inlineStr">
+        <is>
+          <t>054-470-8503</t>
+        </is>
+      </c>
+      <c r="AE449" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF449" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125640</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>[서울] 강남구 2026년 중국 무역사절단 참가기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>한국무역협회</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-21</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>온라인 접수(구글폼)</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z450" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA450" t="inlineStr">
+        <is>
+          <t>일괄 업로드:, 참가 신청서 (서식 1), 제품설명서 (서식 2), 참가 서약서 (서식 3), '25년), 수출실적증명서 ('24년, '25년) ※ 무역협회/무역통계진흥원 발급, CE 등)</t>
+        </is>
+      </c>
+      <c r="AB450" t="inlineStr">
+        <is>
+          <t>한국무역협회 마케팅전략실 02-6000-5371 강남구청 지역경제과 02-3423-5502</t>
+        </is>
+      </c>
+      <c r="AC450" t="inlineStr"/>
+      <c r="AD450" t="inlineStr">
+        <is>
+          <t>02-3423-5502</t>
+        </is>
+      </c>
+      <c r="AE450" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF450" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125639</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 베트남 호치민 K-라이프 커넥트데이 수출컨소시엄 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>이메일 접수 (pjh6446@djbea.or.kr)</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>- 물류비(1cbm 당 최대 600000원 지원 / 해상, 항공 동일)</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>600000원</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z451" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA451" t="inlineStr">
+        <is>
+          <t>목록 ※ 번호 매긴 후 압축하여 제출, [붙임 1] 사업 참가 신청서(필수), [붙임 2] 제품소개서(필수), [붙임 3] 참가기업 서약서 및 개인정보 동의서(필수), [붙임 4] 개인정보 수집 및 활용 동의서(필수), 공장등록증명원(해당 시), 통장사본(필수), • 기타서류</t>
+        </is>
+      </c>
+      <c r="AB451" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원 기업통상지원팀 042-380-3043, pjh6446@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AC451" t="inlineStr">
+        <is>
+          <t>pjh6446@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AD451" t="inlineStr">
+        <is>
+          <t>042-380-3043</t>
+        </is>
+      </c>
+      <c r="AE451" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF451" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125638</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>[경북] 고령군 2026년 중소기업 기숙사 임차비 지원사업 참여기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jungheon.ha@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>○ 대상자별지원금액 : 1실당 월 최대 300000원 지원</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>300000원</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z452" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA452" t="inlineStr">
+        <is>
+          <t>일체를 제출하는 기업 중 신청 접수순 선정, 대상자별지원금액 : 1실당 월 최대 300, 원 지원, 지 원 규 모 : 4개실 정도(기업당 3개실 한도), 추진절차, 모집공고 신청·접수 서류 검토, (목), 검토</t>
+        </is>
+      </c>
+      <c r="AB452" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 ESGㆍ기업지원팀 054-470-8503, jungheon.ha@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AC452" t="inlineStr">
+        <is>
+          <t>jungheon.ha@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD452" t="inlineStr">
+        <is>
+          <t>054-470-8503</t>
+        </is>
+      </c>
+      <c r="AE452" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF452" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125637</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026년 빅웨이브(BiiG WAVE) IR사업 2회차 바이오 특화 IR 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>인천창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-02</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>온라인 접수(구글폼)</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t> (지원내용)</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z453" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA453" t="inlineStr"/>
+      <c r="AB453" t="inlineStr">
+        <is>
+          <t>인천창조경제혁신센터 032-458-5066, biigwave@ccei.kr 티비지파트너스 032-858-1727</t>
+        </is>
+      </c>
+      <c r="AC453" t="inlineStr">
+        <is>
+          <t>biigwave@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AD453" t="inlineStr">
+        <is>
+          <t>032-458-5066</t>
+        </is>
+      </c>
+      <c r="AE453" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF453" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125636</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 제3회 중소기업 밀집지역 위기기업을 위한 원스톱 중소기업 현장지원단 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>전라남도중소기업일자리경제진흥원</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-02</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>이메일 또는 팩스 접수
+- 이메일 : jihye05@jepa.kr
+- 팩스 : 0303-3261-1137</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>&lt;&gt;&lt;О 전남중소기업일자리경제진흥원 교육 또는 컨설팅 이수기업(신청일 기준 1년 이내 2회 이상)에 대하여 중소기업육성자금 한도 및 이자지원 우대  ◈ 추천한도금액 우대 (경영안정자금 3억원 → 6억원 등)  ◈ 경영안정자금 이자지원 우대(2.</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>6억원</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z454" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA454" t="inlineStr">
+        <is>
+          <t>상담회 참가신청서 1부(소정양식), &lt;&gt;&lt; 상담회 참여기업 우대 지원&gt;&lt;&gt;, &lt;서식</t>
+        </is>
+      </c>
+      <c r="AB454" t="inlineStr">
+        <is>
+          <t>전라남도중소기업일자리경제진흥원 061-288-3834</t>
+        </is>
+      </c>
+      <c r="AC454" t="inlineStr">
+        <is>
+          <t>jihye05@jepa.kr</t>
+        </is>
+      </c>
+      <c r="AD454" t="inlineStr">
+        <is>
+          <t>061-288-3834</t>
+        </is>
+      </c>
+      <c r="AE454" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF454" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125635</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>[강원] 2026년 지역 여성 창업기업 초기물품 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>강원특별자치도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>이메일 접수 (tpdud7230@gwep.or.kr)</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>❍ 지원규모: 금20000000원(금이천만원)</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>20000000원</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z455" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA455" t="inlineStr"/>
+      <c r="AB455" t="inlineStr">
+        <is>
+          <t>강원광역새일센터 033-256-9226</t>
+        </is>
+      </c>
+      <c r="AC455" t="inlineStr"/>
+      <c r="AD455" t="inlineStr">
+        <is>
+          <t>033-256-9226</t>
+        </is>
+      </c>
+      <c r="AE455" t="inlineStr">
+        <is>
+          <t>여성기업</t>
+        </is>
+      </c>
+      <c r="AF455" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125634</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 1차 대기업 유통사 연계 판로확대 지원사업 참여기업 모집 공고(뷰티대전(롯데백화점 연계))</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>온라인 접수 (대전일자리경제진흥원)</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>&lt; ※ 유의사항 : 하단의 조건에 해당할 경우 참가신청 제외 및 최종선정 취소  · 지원사업 진행 기간 중 본사 또는 공장 소재지 이관  · 지원사업 진행 기간 중 과제 수행 불성실 및 기타 사업 참여가 어려운 사유가     발생하는 기업 &gt;</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr"/>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z456" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA456" t="inlineStr">
+        <is>
+          <t>서면평가(외부위원회), 추진일정</t>
+        </is>
+      </c>
+      <c r="AB456" t="inlineStr">
+        <is>
+          <t>대전일자리경제진흥원 기업통상지원팀 042-380-3046, 1004@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AC456" t="inlineStr">
+        <is>
+          <t>1004@djbea.or.kr</t>
+        </is>
+      </c>
+      <c r="AD456" t="inlineStr">
+        <is>
+          <t>042-380-3046</t>
+        </is>
+      </c>
+      <c r="AE456" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF456" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125633</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2027년 영국 런던 교육장비 전시회(British Educational Training and Technology) 한국관 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>아래 3가지 절차를 모두 완료해야 최종 신청 완료로 간주
+① 온라인 신청( KOTRA 무역투자24 또는 글로벌전시플랫폼(www.gep.or.kr) 접속)
+② 신청서류 이메일 제출 (ksiic@ksiic.or.kr)
+③ 참가 신청금 납부</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>(총 참가비가 아닌 참가 신청금 500만원을 한국과학기기공업협동조합 으로 선납부 必)</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z457" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA457" t="inlineStr">
+        <is>
+          <t>이메일 제출, (3) 참가 신청금 납부, 신청방법 세부 안내, ① 온라인 신청, (3) 공고문 하단 [신청하기] 버튼 클릭, (4) 온라인 신청서 작성 및 파일 업로드, ※(유의사항), 제출처 : 한국과학기기공업협동조합 최준환 부장</t>
+        </is>
+      </c>
+      <c r="AB457" t="inlineStr">
+        <is>
+          <t>(전시회 관련 문의) 한국과학기기공업협동조합 담당자 02-725-4495, ksiic@ksiic.or.kr / (GEP 신청 오류 문의) KOTRA 해외전시팀 02-3460-7288 / (KOTRA 무역투자 24사이트 회원가입ㆍ로그인 오류 문의) KOTRA 고객전략팀 1600-7119</t>
+        </is>
+      </c>
+      <c r="AC457" t="inlineStr">
+        <is>
+          <t>ksiic@ksiic.or.kr</t>
+        </is>
+      </c>
+      <c r="AD457" t="inlineStr">
+        <is>
+          <t>02-3460-7288</t>
+        </is>
+      </c>
+      <c r="AE457" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF457" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125632</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>한-UAE 에너지인프라 온라인 사절단 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>온라인 접수 (무역투자 24)
+※ 홈페이지 업로드 용량 제한에 따라, 용량이 커서 첨부가 어려운 경우 green@kotra.or.kr로 이메일 송부</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>2 신청방법 및 지원내용</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z458" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA458" t="inlineStr">
+        <is>
+          <t>첨부, 참가신청서(첨부 1), 중소기업확인서, 수출, 실적증명서, 외국어 카달로그(영어), ※ 홈페이지 업로드 용량 제한에 따라, 용량이 커서 첨부가 어려운 경우</t>
+        </is>
+      </c>
+      <c r="AB458" t="inlineStr">
+        <is>
+          <t>KOTRA 기후에너지산업팀 02-3460-7486, green@kotra.or.kr / KOTRA 두바이무역관 971-4-450-4360-126, sj.park@kotra.or.kr / 한국서부발전 동반상생실 041-400-1432, springbt@iwest.co.kr</t>
+        </is>
+      </c>
+      <c r="AC458" t="inlineStr">
+        <is>
+          <t>green@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AD458" t="inlineStr">
+        <is>
+          <t>02-3460-7486</t>
+        </is>
+      </c>
+      <c r="AE458" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF458" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125631</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>[경남] 김해시 2026년 3차 중소기업 해외지사화 지원사업 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>김해의생명산업진흥원</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경상남도 해외마케팅 지원시스템)</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>(업체별 300만원 한도, 1개사 1개 무역관 제한)</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>300만원</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z459" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA459" t="inlineStr">
+        <is>
+          <t>해외마케팅 지원시스템에서 양식 다운로드, &lt;구분&gt;&lt;, &lt;필수&gt;&lt;- 해외지사화 지원사업 신청서, 계획서 및 서약서, 정보활용동의서&gt;&lt;-&gt;</t>
+        </is>
+      </c>
+      <c r="AB459" t="inlineStr">
+        <is>
+          <t>김해의생명산업진흥원 기업지원팀 055-310-9222</t>
+        </is>
+      </c>
+      <c r="AC459" t="inlineStr"/>
+      <c r="AD459" t="inlineStr">
+        <is>
+          <t>055-310-9222</t>
+        </is>
+      </c>
+      <c r="AE459" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF459" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125630</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>[충남] 2026년 첨단제조기술(AI-DFAM) 기반 모빌리티 제조 혁신거점 조성사업 기업지원 모집 공고</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>충남테크노파크</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-01</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>이메일(원본 PDF 스캔) 발송 후 우편, 방문 접수
+- 이메일 : lwk0611@ctp.or.kr
+- 접수처 : (32422) 충남 예산군 예산읍 수철길 10, 충남테크노파크 미래자동차센터(202호)
+※ 우편 접수일 경우, 반드시 담당자와 수령여부 확인 必</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>□ 지원내용 : 모빌리티 부품 시제품 제작 지원</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="inlineStr"/>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z460" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA460" t="inlineStr"/>
+      <c r="AB460" t="inlineStr">
+        <is>
+          <t>충남테크노파크 미래자동차센터 041-331-8023, 8022, 8012 / lwk0611@ctp.or.kr, yubin.yoon@ctp.or.kr, tjdgus25@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC460" t="inlineStr">
+        <is>
+          <t>lwk0611@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD460" t="inlineStr">
+        <is>
+          <t>041-331-8023</t>
+        </is>
+      </c>
+      <c r="AE460" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF460" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125629</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>[경기] 안양시 2027년 기업환경 개선사업 수요조사 실시 공고</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>방문 및 이메일 접수
+- 접수처 : 안양시 동안구 시민대로235, 7층(안양시청 기업경제과)
+- 이메일 : july23th@korea.kr</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>○ 사업비 20백만원(VAT제외) 초과인 공사, 물품의 구매인 경우는 전자조달</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>20백만원</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z461" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA461" t="inlineStr">
+        <is>
+          <t>(양식 첨부파일 확인), 사업계획서[서식] (사업비 산출내역서 및 견적서 포함), 자부담 확약서[서식], 시설물 유지 동의서[서식], 국세 및 지방세 완납증명원 각 1부, 대 사회보험 사업장 가입자 명부(고용인원 확인), 건물주 및 임대인 동의서 (자가가 아닌 경우), 공장등록 증명서(공장건축면적 500㎡이상)</t>
+        </is>
+      </c>
+      <c r="AB461" t="inlineStr">
+        <is>
+          <t>안양시청 기업경제과 기업지원팀 031-8045-5566</t>
+        </is>
+      </c>
+      <c r="AC461" t="inlineStr">
+        <is>
+          <t>july23th@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD461" t="inlineStr">
+        <is>
+          <t>031-8045-5566</t>
+        </is>
+      </c>
+      <c r="AE461" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF461" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125628</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>[경기] 안양시 2026년 2차 소규모 사업장 사물인터넷(IoT) 설치 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>경기환경에너지진흥원</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>온라인 접수 (네이버 폼)</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>부착하여야 함[단, 부착 시 18만원(부착비용의 60%) 추가 지원]</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>18만원</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z462" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA462" t="inlineStr">
+        <is>
+          <t>와 함께 사업을, 신청하고, 검토, 현장평가 및 평가위원회를 통하여 승인, 지원조건, 으로 자료를 전송하여야 함, 통보서를 접수기관에 제출하여야 함, 신청접수 및 추진절차</t>
+        </is>
+      </c>
+      <c r="AB462" t="inlineStr">
+        <is>
+          <t>경기환경에너지진흥원 환경사업팀 031-985-0485</t>
+        </is>
+      </c>
+      <c r="AC462" t="inlineStr"/>
+      <c r="AD462" t="inlineStr">
+        <is>
+          <t>031-985-0485</t>
+        </is>
+      </c>
+      <c r="AE462" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF462" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125627</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 모빌리티 부품 제조AI 확산센터 구축 사업 기업지원 수혜기업 모집 통합 연장 공고</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>지능형자동차부품진흥원</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2026-08-17 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>이메일 접수
+※ 지원프로그램에 따라 해당 기관 접수처로 이메일 접수
+- 제조 AI 기술도입을 위한 기술지원 : 지능형자동차부품진흥원 gamja38@kiapi.or.kr
+- 차량 SW 설계ㆍ특화ㆍ검증 및 기술지원 : 한국전자기술연구원 youngbo.shim@keti.re.kr
+- 제조공정 혁신 및 공정지원 특화 기술지원 : 대구경북과학기술원 kjp@dgist.ac.kr</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>프로그램별 상세 지원내용은 상세안내문 첨부 파일 참고</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z463" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA463" t="inlineStr">
+        <is>
+          <t>지원신청서 및 프로그램별 상세사업계획서 등 아래표 참조, 필요 시, 외 기업 확인을 위한 기타 서류 요청 가능, 󰊳 신청방법 및 지원절차, 기관 접수처로 이메일 접수, 선정 및 지원절차, 󰊴 평가방법 및 기준, 평가방법 선정평가 서류평가</t>
+        </is>
+      </c>
+      <c r="AB463" t="inlineStr">
+        <is>
+          <t>지능형자동차부품진흥원 053-670-4784 / 한국전자기술연구원 031-739-7454 / 대구경북과학기술원 053-785-6314</t>
+        </is>
+      </c>
+      <c r="AC463" t="inlineStr"/>
+      <c r="AD463" t="inlineStr">
+        <is>
+          <t>031-739-7454</t>
+        </is>
+      </c>
+      <c r="AE463" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF463" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125626</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>[경기] 광명시 2027년 기업환경 개선사업 수요 조사 공고</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-17</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 경기도 광명시 시청로 20, 광명시청 제1별관 2층 투자유치과</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>지원요건 ￭ 총 사업비가 최소 10백만원 이상 사업</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>10백만원</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z464" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA464" t="inlineStr">
+        <is>
+          <t>구분, ① 사업계획서 1부 【서식1】, ㉠ 중소기업: 자부담 확약서, 시설물 유지 동의서, 건물주 및 임대인 동의서 포함 【서식2】, ㉡ 지식산업센터: 자부담 확약서, 입주기업 동의서 포함, ⑥ 4대 사회보험 가입자 명부 1부(고용인원 확인용)</t>
+        </is>
+      </c>
+      <c r="AB464" t="inlineStr">
+        <is>
+          <t>광명시청 투자유치과 기업지원팀 02-2680-2266</t>
+        </is>
+      </c>
+      <c r="AC464" t="inlineStr"/>
+      <c r="AD464" t="inlineStr">
+        <is>
+          <t>02-2680-2266</t>
+        </is>
+      </c>
+      <c r="AE464" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF464" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125625</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026년 2차 신재생에너지R&amp;D(수소) 신규지원대상 연구개발과제 공고</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>한국에너지기술평가원</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>2026-08-25 ~ 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>온라인 접수(범부처통합연구지원시스템)
+※ 재무제표 원클릭서비스로 제출 (m.one-click.co.kr/#/ketep)
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>o 총 7억원 내외 지원</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>7억원</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z465" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA465" t="inlineStr">
+        <is>
+          <t>사업개요, 사업목적, 온실가스 감축 및 자원 안보에 기여, 지원대상분야, o 신재생에너지핵심기술개발사업(수소), 연구개발비 지원 규모 및 기간, o 총 7억원 내외 지원, (단위 : 억원</t>
+        </is>
+      </c>
+      <c r="AB465" t="inlineStr">
+        <is>
+          <t>한국에너지기술평가원 수소산업실 02-3469-8345, 8349 및 기타 문의처 공고문 17p 참조</t>
+        </is>
+      </c>
+      <c r="AC465" t="inlineStr"/>
+      <c r="AD465" t="inlineStr">
+        <is>
+          <t>02-3469-8345</t>
+        </is>
+      </c>
+      <c r="AE465" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF465" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125624</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>[강원] 2026년 2차 해외 온라인 마케팅 지원 참가기업 모집 공고(중동아프리카권)</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>강원특별자치도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>온라인 접수(강원특별자치도 수출기업서포트)</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 도내 기업 5개사 내외</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z466" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA466" t="inlineStr">
+        <is>
+          <t>에 허위사실 기재로 확인된 경우, 지원내용, ❍ 권역별 지원내용, 연번 국가권역 지원내용, 중동, ▫ 인플루언서 활용 SNS 홍보 지원, 아프리카권, ▫ 제품 선적 및 수출지원</t>
+        </is>
+      </c>
+      <c r="AB466" t="inlineStr">
+        <is>
+          <t>강원특별자치도경제진흥원 전략사업부 033-749-3362, jaesub2019@naver.com</t>
+        </is>
+      </c>
+      <c r="AC466" t="inlineStr">
+        <is>
+          <t>jaesub2019@naver.com</t>
+        </is>
+      </c>
+      <c r="AD466" t="inlineStr">
+        <is>
+          <t>033-749-3362</t>
+        </is>
+      </c>
+      <c r="AE466" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF466" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125623</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>[울산] 울주군 2026년 3차 청년 스마트팜 보급 육성 지원사업 지원기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>울산테크노파크</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-10</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>이메일 접수 (indus12@utp.or.kr)
+※ 이메일 접수 후 접수 여부 담당자 유선 확인 필수</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>· 신규 설비지원 지원금 : 100백만원/1개사 내외, 자부담금 1억 이상</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>100백만원</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z467" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA467" t="inlineStr">
+        <is>
+          <t>목록에 제시된, 가 보완 요청에도 불구하고 정해진 기간, 까지 제출되지 않은 경우, 기업의 부도, 세무당국에 의하여 국세, 지방세 등의 체납처분을 받은 경우, 정보 집중기관에 채무불이행자로 등록된 경우, 파산·회생절차·개인회생절차의 개시 신청이 이루어진 경우</t>
+        </is>
+      </c>
+      <c r="AB467" t="inlineStr">
+        <is>
+          <t>울산테크노파크 AI미래본부 052-219-8652, 8606 / dylee@utp.or.kr, indus12@utp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC467" t="inlineStr">
+        <is>
+          <t>dylee@utp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD467" t="inlineStr">
+        <is>
+          <t>052-219-8652</t>
+        </is>
+      </c>
+      <c r="AE467" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF467" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125622</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 기업 성장단계별 맞춤형 기술 지원사업 (Track-1) 과제 기업 모집 공고(대구형 R&amp;D 전주기 지원체계 구축)</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>경북대학교 지산학연협력기술연구소</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경북대학교 과제관리시스템)</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>※ 기업 대응투자금은 협업대학 과제책임자의 1회(1회 당 20만원)이상 기술자문료에 사용 必</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>20만원</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z468" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA468" t="inlineStr">
+        <is>
+          <t>선정결과 통보, 지원여부 심의 결과 통보, ※ 필요시 사전 또는 사후 기업 방문, 󰊳 평가항목 및 배점, 평가항목, 평 가 내 용, 배점, 과제 수행계획 충실성</t>
+        </is>
+      </c>
+      <c r="AB468" t="inlineStr">
+        <is>
+          <t>경북대학교 지산학연협력기술연구소 053-219-3754, kjo1387@knu.ac.kr</t>
+        </is>
+      </c>
+      <c r="AC468" t="inlineStr">
+        <is>
+          <t>kjo1387@knu.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD468" t="inlineStr">
+        <is>
+          <t>053-219-3754</t>
+        </is>
+      </c>
+      <c r="AE468" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF468" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125621</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>[전남광주] 목포시 2026년 착한가격업소 신규모집 공고</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>방문, 우편, 이메일 접수 
+- 접수처 : 목포시 양을로 203, 목포시청 3층 지역경제과
+- 이메일 : tjrqls03@korea.kr
+※ 이메일 신청 후 정상 접수 여부 확인을 위해 전화 연락 필수(061-270-8459)</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>√ 지방세를 3회 이상 또는 100만원 이상 체납하고 있는 경우(신청일 기준)</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z469" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA469" t="inlineStr">
+        <is>
+          <t>지정신청서(붙임1), 개인정보 동의서(붙임2), 표창장사본, 위생등급 결과서(해당시), 신청방법 :, 작성 후 이메일, 방문, 우편 제출(택1)</t>
+        </is>
+      </c>
+      <c r="AB469" t="inlineStr">
+        <is>
+          <t>목포시청 지역경제과 061-270-8459</t>
+        </is>
+      </c>
+      <c r="AC469" t="inlineStr">
+        <is>
+          <t>tjrqls03@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD469" t="inlineStr">
+        <is>
+          <t>061-270-8459</t>
+        </is>
+      </c>
+      <c r="AE469" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF469" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125620</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>[전남광주] 여수시 중동사태 어업용 면세유 유가연동보조금 지원사업 신청 공고</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-09-10</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 수산경영과 어업지도팀, 주소지 관할 읍ㆍ면ㆍ동 주민센터</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>3원/ℓ</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>3원</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr"/>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z470" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA470" t="inlineStr">
+        <is>
+          <t>신청서 1부(붙임), 신분증 및 통장 사본 각 1부, 면세유류카드 사본 1부, 유의사항, 접수된 서류는 일체 반환되지 않습니다., 허위 기재, 이중 신청, 면세유의 어업 외 사용 등 부정한 방법</t>
+        </is>
+      </c>
+      <c r="AB470" t="inlineStr">
+        <is>
+          <t>여수시 수산경영과 어업지도팀 061-659-3921</t>
+        </is>
+      </c>
+      <c r="AC470" t="inlineStr"/>
+      <c r="AD470" t="inlineStr">
+        <is>
+          <t>061-659-3921</t>
+        </is>
+      </c>
+      <c r="AE470" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF470" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125619</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>[경북] 경주시 2026년 두바이 자동차부품전(Automechanika Dubai) 공동관 참가기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>모집 완료시</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>이메일 접수 (summerseol@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>참가기업 모집 제출서류 보완 및 평가 참가기업 최종 선정</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="inlineStr"/>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z471" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA471" t="inlineStr">
+        <is>
+          <t>보완 및 평가 참가기업 최종 선정, 상기 일정은 추진 상황에 따라 변경될 수 있음, 전시회 개요, (전시장소) 아랍에미리트(두바이), (전시품목) 자동차부품(애프터마켓 부품, 자동차 액세서리, 유지보수 제품, 비 서비스 등)</t>
+        </is>
+      </c>
+      <c r="AB471" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 동부지소 054-612-2971, summerseol@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AC471" t="inlineStr">
+        <is>
+          <t>summerseol@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD471" t="inlineStr">
+        <is>
+          <t>054-612-2971</t>
+        </is>
+      </c>
+      <c r="AE471" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF471" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125618</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>[경북] 경주시 제24차 세계 한상대회 경주시 공동관 참가기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>이메일 접수 (summerseol@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>※부스 운영비의 10% 기업 자부담금 발생(20만원)</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>20만원</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr"/>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z472" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA472" t="inlineStr">
+        <is>
+          <t>보완 및 평가 참가기업 최종 선정, 상기 일정은 추진 상황에 따라 변경될 수 있음, 전시회 개요, (전시회명) 제24차 세계 한상대회 기업전시회, (전시장소) 인천 송도(송도컨벤시아 1~3홀), (전시품목) 종합 소비재, (주요내용) 전시 참가 및 부스 운영 지원 일부, 상담 지원 등</t>
+        </is>
+      </c>
+      <c r="AB472" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 동부지소 054-612-2971, summerseol@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AC472" t="inlineStr">
+        <is>
+          <t>summerseol@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD472" t="inlineStr">
+        <is>
+          <t>054-612-2971</t>
+        </is>
+      </c>
+      <c r="AE472" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF472" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125617</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>[전남광주] 여수시 2026년 안전복지형 연근해어선 기반구축사업 추가 신청 공고</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 여수시 수산경영과 어업지도팀(국동임시별관)</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>농림수산업자신용보증기금(이하 농신보) 보증 한도 : 어업인 30억원, 법인 70억원</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>70억원</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr"/>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z473" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA473" t="inlineStr">
+        <is>
+          <t>① [별지 제3호서식] 신용조사서(대출취급기관 발급), ③ 지방세, 국세(완납증명서 각 1부), 어업인을 증명하는 서류, (전자허가증 또는 허가내역서, 선적증서, 어선검사증서), 기타사항</t>
+        </is>
+      </c>
+      <c r="AB473" t="inlineStr">
+        <is>
+          <t>(안내기관) 여수시 수산경영과 어업지도팀 061-659-3921, FAX 061-659-5828 (융자상담) 농림수산업자신용보증기금 061-720-3100</t>
+        </is>
+      </c>
+      <c r="AC473" t="inlineStr"/>
+      <c r="AD473" t="inlineStr">
+        <is>
+          <t>061-659-3921</t>
+        </is>
+      </c>
+      <c r="AE473" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF473" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125616</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026년 농식품 벤처육성 지원사업(창업기업 대상) 추가 사업화자금 지원기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>한국농업기술진흥원</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>온라인 접수 (농식품창업정보망)</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>󰊲 선정규모</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="inlineStr"/>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W474" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z474" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA474" t="inlineStr">
+        <is>
+          <t>※ 서명란에는 반드시 서명하여야 함, &lt;구 분&gt;&lt;세부내용&gt;&lt;비고&gt;, &lt;해당 시&gt;&lt;2. 2026년 매출, 고용</t>
+        </is>
+      </c>
+      <c r="AB474" t="inlineStr">
+        <is>
+          <t>한국농업기술진흥원 창업육성팀 063-919-1433 및 관할 농식품벤처창업센터</t>
+        </is>
+      </c>
+      <c r="AC474" t="inlineStr"/>
+      <c r="AD474" t="inlineStr">
+        <is>
+          <t>063-919-1433</t>
+        </is>
+      </c>
+      <c r="AE474" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF474" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125615</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026년 프랜차이즈 수준평가 참여 브랜드 모집 공고</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>소상공인시장진흥공단</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>온라인 접수(소상공인24)</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>□ 지원내용 : 우수프랜차이즈 지정 등</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="inlineStr"/>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z475" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA475" t="inlineStr"/>
+      <c r="AB475" t="inlineStr">
+        <is>
+          <t>소상공인시장진흥공단 유통지원팀 042-363-7745</t>
+        </is>
+      </c>
+      <c r="AC475" t="inlineStr"/>
+      <c r="AD475" t="inlineStr">
+        <is>
+          <t>042-363-7745</t>
+        </is>
+      </c>
+      <c r="AE475" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF475" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125614</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026년 마이데이터 컨설팅 및 교육 지원 사업 공고</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>한국데이터산업진흥원</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>온라인 접수 (마이데이터 원스톱 통합지원 서비스)</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>ㅇ (지원내용) 마이데이터 사업화 특화 컨설팅 및 참여기업 대상 데이터 활용 역량 강화를 위한 분야별 전문교육 제공(21개社)</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>21개</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z476" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA476" t="inlineStr"/>
+      <c r="AB476" t="inlineStr">
+        <is>
+          <t>한국데이터산업진흥원 마이데이터 컨설팅 운영사무국 02-3786-0409, mydata@kmac.co.kr</t>
+        </is>
+      </c>
+      <c r="AC476" t="inlineStr">
+        <is>
+          <t>mydata@kmac.co.kr</t>
+        </is>
+      </c>
+      <c r="AD476" t="inlineStr">
+        <is>
+          <t>02-3786-0409</t>
+        </is>
+      </c>
+      <c r="AE476" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF476" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125613</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026년 대구 동구 청년센터 예비 창업 지원 제5기 Pre D-Link 프로그램 참여자 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>동구청년센터the꿈</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2026-07-24 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>이메일로 접수 (theggum3355@gmail.com)</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>m 최종 선정 시 창업지원금 각 300만원 및 멘토링 지원 ※ 지원항목 [붙임5] 참고</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>300만원</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr"/>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z477" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA477" t="inlineStr">
+        <is>
+          <t>를 순서대로 묶어 1개의 PDF 파일로 제출, 신청서와, 는 반드시 기한 내 제출되어야 함, 【신청제외대상】, 국세 및 지방세 체납 중인 자, 기타 정상적으로 금융거래가 어려운 경우, 신청자가, 를 허위로 작성한 경우</t>
+        </is>
+      </c>
+      <c r="AB477" t="inlineStr">
+        <is>
+          <t>동구청년센터 the꿈 053-261-3355</t>
+        </is>
+      </c>
+      <c r="AC477" t="inlineStr">
+        <is>
+          <t>theggum3355@gmail.com</t>
+        </is>
+      </c>
+      <c r="AD477" t="inlineStr">
+        <is>
+          <t>053-261-3355</t>
+        </is>
+      </c>
+      <c r="AE477" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF477" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125612</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026년 2차 모두의 창업 프로젝트 모집 공고</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>창업진흥원</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-17</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>온라인 접수 (모두의 창업 프로젝트 홈페이지)</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>1:1멘토링 5억원 1:1멘토링 1억원</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>5억원</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr"/>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z478" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA478" t="inlineStr">
+        <is>
+          <t>없음, 향후, 및 숏폼(30~60초 내외) 제출 가능(선택사항), 이미지(jpg, gif) 형식으로 제출, 숏폼은 URL 첨부, ◦ 멘토기관별 보육 및 선발 계획, 멘토 Pool 등을 확인 후 멘토기관 선택</t>
+        </is>
+      </c>
+      <c r="AB478" t="inlineStr">
+        <is>
+          <t>(사업 문의) 국번 없이 1357+5 및 분야별, 지역별 추가 문의처 공고문 19~20p 참조</t>
+        </is>
+      </c>
+      <c r="AC478" t="inlineStr">
+        <is>
+          <t>bm@semas.or.kr</t>
+        </is>
+      </c>
+      <c r="AD478" t="inlineStr">
+        <is>
+          <t>02-739-8170</t>
+        </is>
+      </c>
+      <c r="AE478" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF478" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125611</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026년 2차 기계장비산업기술개발사업 신규지원 대상과제 공고</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>한국산업기술기획평가원</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>온라인 접수(범부처통합연구지원시스템)</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>공고예산 198억원 25억원</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>198억원</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr"/>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z479" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA479" t="inlineStr">
+        <is>
+          <t>사항, 기타 유의 사항, 문의처, 사업개요, 사업목적, 국내 기계장비기업의 글로벌 경쟁력 강화, 연구개발비 지원 규모 및 기간, 세부사업 기계장비산업기술개발 기계장비산업기술개발</t>
+        </is>
+      </c>
+      <c r="AB479" t="inlineStr">
+        <is>
+          <t>(선정평가 일정 및 절차) 한국산업기술기획평가원 AI기계 로봇실 053-718-8276, 8477, 8727, 8747,8748 (과제 제안요구서(기획의도)) 피지컬AI PD 053-718-8381, dongwank@keit.re.kr (온라인 시스템 접수 및 규정 등 문의) 범부처통합연구지원시스템 고객센터 1877-2041 R&amp;D상담콜센터 1544-6633</t>
+        </is>
+      </c>
+      <c r="AC479" t="inlineStr">
+        <is>
+          <t>dongwank@keit.re.kr</t>
+        </is>
+      </c>
+      <c r="AD479" t="inlineStr">
+        <is>
+          <t>053-718-8276</t>
+        </is>
+      </c>
+      <c r="AE479" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF479" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125610</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>[부산] 강서구 2026년 하반기 소상공인 광고물 정비 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>방문, 우편, 이메일 접수
+- 접수처 : (46702) 부산광역시 강서구 낙동북로 477(대저1동) 부산 강서구 도시관리과 디자인광고계
+- 이메일 : 2879tist@korea.kr</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>m 지원규모: 1개 업소당 최대 1000천원(부가세 별도)</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z480" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA480" t="inlineStr">
+        <is>
+          <t>사업신청서[서식1], 지원 신청내용 견적서(옥외광고사업자* 정보, 광고물 사양, 수량, 가격 등 명시), 부산 강서구 내 옥외광고등록업체, 중소기업(소상공인) 확인서, 국세완납증명서</t>
+        </is>
+      </c>
+      <c r="AB480" t="inlineStr">
+        <is>
+          <t>강서구 도시관리과 051-970-4282</t>
+        </is>
+      </c>
+      <c r="AC480" t="inlineStr">
+        <is>
+          <t>2879tist@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD480" t="inlineStr">
+        <is>
+          <t>051-970-4282</t>
+        </is>
+      </c>
+      <c r="AE480" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF480" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125609</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>[부산] 강서구 2026년 3차 사물인터넷 측정기기 부착지원사업 참여 신청 공고</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>방문 또는 우편, 이메일 접수
+- 이메일 : yebin0714@korea.kr
+- 접수처 : 부산광역시 강서구 낙동북로477(대저1동, 강서구청) 6층 환경위생과 환경관리계 ‘사물인터넷 측정기기 부착지원사업’ 담당자 앞
+※ 방문 또는 우편 접수 - 사본(스캔본) 이메일 필수 송부
+※ 발송 후 유선으로 접수 여부 확인 요망</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>- 사업비 산출내역에 기술자문료(사업비의 5%, 100만원 한도)포함(필수)</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr"/>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z481" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA481" t="inlineStr">
+        <is>
+          <t>지참하여 직접 방문, 강서구청 6층 환경위생과 환경관리계, ② 우편접수 : 신청서 및, 를 우편 발송(운송료 신청자 부담), 보내실 곳 : 부산광역시 강서구 낙동북로477(대저1동, 강서구청) 6층, 환경위생과 환경관리계 ‘사물인터넷 측정기기 부착, 지원사업’ 담당자 앞</t>
+        </is>
+      </c>
+      <c r="AB481" t="inlineStr">
+        <is>
+          <t>부산광역시 강서구 환경위생과 담당자 051-970-4384</t>
+        </is>
+      </c>
+      <c r="AC481" t="inlineStr">
+        <is>
+          <t>yebin0714@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD481" t="inlineStr">
+        <is>
+          <t>051-970-4384</t>
+        </is>
+      </c>
+      <c r="AE481" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF481" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125608</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 2차 AI 라이선스 구독 지원 참가기업 모집 공고(대구글로벌게임센터)</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>대구디지털혁신진흥원</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>이메일 접수 (dggc@dip.or.kr)</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>지원금액: 바우처 총 120만원 이내(월 약 30만원 정도)</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>120만원</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr"/>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z482" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA482" t="inlineStr">
+        <is>
+          <t>구비여부 및 조건, 부합 여부 등 서면 검토, ※ 사업담당자, [2단계], 서면평가, 평가일정: 2026. 08. 28.(금) 예정, 평가방법: 서류평가, 평가내용: 도입 필요성 및 시급성</t>
+        </is>
+      </c>
+      <c r="AB482" t="inlineStr">
+        <is>
+          <t>대구디지털혁신진흥원 게임웹툰육성팀 053-215-4916</t>
+        </is>
+      </c>
+      <c r="AC482" t="inlineStr">
+        <is>
+          <t>dggc@dip.or.kr</t>
+        </is>
+      </c>
+      <c r="AD482" t="inlineStr">
+        <is>
+          <t>053-215-4916</t>
+        </is>
+      </c>
+      <c r="AE482" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF482" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125607</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026년 바이오ㆍ헬스케어 오픈이노베이션 프로그램 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>인천테크노파크</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>이메일 접수( jspark93@itp.or.kr, partners@jnpmedi.com)
+※ 동시 제출 必</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>2 지원내용</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr"/>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z483" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA483" t="inlineStr">
+        <is>
+          <t>ㅇ 신청방법 : 전담, 수행기관 E-mail 제출 ※ 동시 제출 必, (전담기관)jspark93@itp.or.kr, (수행기관)partners@jnpmedi.com, 서식1, : 한글파일과 PDF 파일 각 1부, 서식3, 별첨 등 : PDF 각 1부</t>
+        </is>
+      </c>
+      <c r="AB483" t="inlineStr">
+        <is>
+          <t>인천테크노파크 바이오센터 032-260-0833 제이앤피메디파트너스 jw.jung@jnpmedi.com 및 기타 문의처 원출처 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC483" t="inlineStr">
+        <is>
+          <t>jw.jung@jnpmedi.com</t>
+        </is>
+      </c>
+      <c r="AD483" t="inlineStr">
+        <is>
+          <t>032-260-0833</t>
+        </is>
+      </c>
+      <c r="AE483" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF483" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125606</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026년 K-브랜드 해외 상표권 보호ㆍ라이선싱 전략 지원(시범)사업 연장 공고</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>한국지식재산보호원</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>온라인 접수(국제 지재권분쟁 대응전략 지원사업 지원기업 서비스)</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>* 위탁정산비용은 과제별 150000원(VAT 미포함)으로 경비에 포함 필수, 추후 별도 안내</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>150000원</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z484" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA484" t="inlineStr">
+        <is>
+          <t>제출온라인 신청만 가능하며 방문 우편 접수 불가, 온라인 사업신청 사용자 매뉴얼 붙임 참조, 모든 붙임서류는 또는 형태로만 첨부 가능하며 다수, 파일을 등록 할 경우 개의 로 변환 및 병합하여 업로드, 제출 및 작성서류 목록, ㅇ 신청기업, 【신청기업 제출 및 작성서류 목록】, 일반 신청 간소화 신청</t>
+        </is>
+      </c>
+      <c r="AB484" t="inlineStr">
+        <is>
+          <t>한국지식재산보호원 상표디자인분쟁대응실 (사업내용 문의) 02-2183-5894, 02-6196-2016 (이메일 문의) kbrand@koipa.re.kr 및 기타 문의처 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC484" t="inlineStr">
+        <is>
+          <t>kbrand@koipa.re.kr</t>
+        </is>
+      </c>
+      <c r="AD484" t="inlineStr">
+        <is>
+          <t>02-2183-5894</t>
+        </is>
+      </c>
+      <c r="AE484" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF484" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125605</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>[경기] 하남시 2026년 소상공인 마케팅 판로 지원사업(경영환경개선 지원사업) 소상공인 모집공고</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>경기테크노파크</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>온라인, 방문, 우편, 이메일 접수
+- 접수처 :(15588) 경기도 안산시 상록구 해안로705 (재)경기테크노파크 4동(지원편의동) 3층 318호 기술사업화팀
+- 이메일 : ygh6463@gtp.or.kr</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>O 지원규모 : 30개사 (사업대상자당 최대 180만원 지원)</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>180만원</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>30개</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z485" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA485" t="inlineStr">
+        <is>
+          <t>제출, '24~25년 부가세 증명원, 점포사진, 시공계획서 등, ㆍ 제줄서류 검토(, 적격 검토, ㆍ 신청서 및 시공계획서 근거 선정자 자율 견적서 제줄, ㆍ 완료보고서에 시공 전후 사진</t>
+        </is>
+      </c>
+      <c r="AB485" t="inlineStr">
+        <is>
+          <t>경기테크노파크 031-500-3037, ygh6463@gtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC485" t="inlineStr">
+        <is>
+          <t>ygh6463@gtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD485" t="inlineStr">
+        <is>
+          <t>031-500-3037</t>
+        </is>
+      </c>
+      <c r="AE485" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF485" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125604</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026년 디지털커머스 전문기관(소담스퀘어 in 부산) 제품사진 촬영지원 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>부산경제진흥원</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2026-07-01 ~ 2026-09-30</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>온라인 접수 (판판대로, 소담스퀘어 in 부산)
+※ 2곳에서 ‘모두’ 신청 완료하여야 함
+※ 자세한 신청방법 공고문 참조</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 60개사, 600개 제품 내외 ※ 업체당 제품 10개 내외</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>60개</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z486" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA486" t="inlineStr">
+        <is>
+          <t>구분 준비서류, ➀ &lt;서식1∼3&gt; 참가신청서, 확약서, 개인정보제공동의서, 필수, ➂ 중소기업확인서(소상공인확인서), 지방세납입증명서 ※ 정부24 발급, ※ 기한 내 서류 미제출 시 지원대상 제외</t>
+        </is>
+      </c>
+      <c r="AB486" t="inlineStr">
+        <is>
+          <t>부산경제진흥원 소상공인지원단 051-600-1367, zmk81@bepa.kr</t>
+        </is>
+      </c>
+      <c r="AC486" t="inlineStr">
+        <is>
+          <t>zmk81@bepa.kr</t>
+        </is>
+      </c>
+      <c r="AD486" t="inlineStr">
+        <is>
+          <t>051-600-1367</t>
+        </is>
+      </c>
+      <c r="AE486" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF486" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125603</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2027년 미국 마이애미 코스모프로프 뷰티 전시회 한국관 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>아래 3가지 절차를 모두 완료해야 최종 신청 완료로 간주
+① 온라인 신청 : 무역투자24(www.kotra.or.kr) 또는 글로벌전시플랫폼(www.gep.or.kr)
+② 신청서류 이메일 제출 (대한화장품협회 글로벌협력실 sbeen11@kcia.or.kr)
+③ 참가 신청금 납부</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>(총 참가비가 아닌 참가 신청금 700만원을 (사)대한화장품협회로 선납부 必)</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>700만원</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr"/>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z487" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA487" t="inlineStr">
+        <is>
+          <t>이메일 제출, (3) 참가 신청금 납부, 신청방법 세부 안내, ① 온라인 신청, (3) 공고문 하단 [신청하기] 버튼 클릭, (4) 온라인 신청서 작성 및 파일 업로드, ※(유의사항), (2) 한국관 참가 신청서</t>
+        </is>
+      </c>
+      <c r="AB487" t="inlineStr">
+        <is>
+          <t>(전시회 관련 문의) 대한화장품협회 글로벌협력실 02-2135-5771, sbeen11@kcia.or.kr / KOTRA 해외전시팀 02-3460-7282, mirine@kotra.or.kr (시스템 문의) KOTRA 고객전략팀 1600-7119</t>
+        </is>
+      </c>
+      <c r="AC487" t="inlineStr">
+        <is>
+          <t>mirine@kotra.or.kr</t>
+        </is>
+      </c>
+      <c r="AD487" t="inlineStr">
+        <is>
+          <t>02-2135-5771</t>
+        </is>
+      </c>
+      <c r="AE487" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF487" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125602</t>
         </is>
       </c>
     </row>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF487"/>
+  <dimension ref="A1:AF536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68739,7 +68739,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA444" t="inlineStr"/>
       <c r="AB444" t="inlineStr">
         <is>
           <t>울산테크노파크 기업지원단 조선방산지원실 052-219-8674, kimyj5139@utp.or.kr</t>
@@ -68800,7 +68799,6 @@
           <t>4400만원</t>
         </is>
       </c>
-      <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr">
         <is>
           <t>Y</t>
@@ -69116,8 +69114,6 @@
           <t>모집규모</t>
         </is>
       </c>
-      <c r="F447" t="inlineStr"/>
-      <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr">
         <is>
           <t>Y</t>
@@ -69275,7 +69271,6 @@
           <t>20만원</t>
         </is>
       </c>
-      <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr">
         <is>
           <t>Y</t>
@@ -69433,7 +69428,6 @@
           <t>300000원</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr">
         <is>
           <t>Y</t>
@@ -69586,8 +69580,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr">
         <is>
           <t>Y</t>
@@ -69693,7 +69685,6 @@
           <t>한국무역협회 마케팅전략실 02-6000-5371 강남구청 지역경제과 02-3423-5502</t>
         </is>
       </c>
-      <c r="AC450" t="inlineStr"/>
       <c r="AD450" t="inlineStr">
         <is>
           <t>02-3423-5502</t>
@@ -69741,7 +69732,6 @@
           <t>600000원</t>
         </is>
       </c>
-      <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr">
         <is>
           <t>Y</t>
@@ -69899,7 +69889,6 @@
           <t>300000원</t>
         </is>
       </c>
-      <c r="G452" t="inlineStr"/>
       <c r="H452" t="inlineStr">
         <is>
           <t>Y</t>
@@ -70052,8 +70041,6 @@
           <t> (지원내용)</t>
         </is>
       </c>
-      <c r="F453" t="inlineStr"/>
-      <c r="G453" t="inlineStr"/>
       <c r="H453" t="inlineStr">
         <is>
           <t>N</t>
@@ -70149,7 +70136,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA453" t="inlineStr"/>
       <c r="AB453" t="inlineStr">
         <is>
           <t>인천창조경제혁신센터 032-458-5066, biigwave@ccei.kr 티비지파트너스 032-858-1727</t>
@@ -70209,7 +70195,6 @@
           <t>6억원</t>
         </is>
       </c>
-      <c r="G454" t="inlineStr"/>
       <c r="H454" t="inlineStr">
         <is>
           <t>Y</t>
@@ -70367,7 +70352,6 @@
           <t>20000000원</t>
         </is>
       </c>
-      <c r="G455" t="inlineStr"/>
       <c r="H455" t="inlineStr">
         <is>
           <t>N</t>
@@ -70463,13 +70447,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA455" t="inlineStr"/>
       <c r="AB455" t="inlineStr">
         <is>
           <t>강원광역새일센터 033-256-9226</t>
         </is>
       </c>
-      <c r="AC455" t="inlineStr"/>
       <c r="AD455" t="inlineStr">
         <is>
           <t>033-256-9226</t>
@@ -70512,8 +70494,6 @@
           <t>&lt; ※ 유의사항 : 하단의 조건에 해당할 경우 참가신청 제외 및 최종선정 취소  · 지원사업 진행 기간 중 본사 또는 공장 소재지 이관  · 지원사업 진행 기간 중 과제 수행 불성실 및 기타 사업 참여가 어려운 사유가     발생하는 기업 &gt;</t>
         </is>
       </c>
-      <c r="F456" t="inlineStr"/>
-      <c r="G456" t="inlineStr"/>
       <c r="H456" t="inlineStr">
         <is>
           <t>N</t>
@@ -70674,7 +70654,6 @@
           <t>500만원</t>
         </is>
       </c>
-      <c r="G457" t="inlineStr"/>
       <c r="H457" t="inlineStr">
         <is>
           <t>Y</t>
@@ -70828,8 +70807,6 @@
           <t>2 신청방법 및 지원내용</t>
         </is>
       </c>
-      <c r="F458" t="inlineStr"/>
-      <c r="G458" t="inlineStr"/>
       <c r="H458" t="inlineStr">
         <is>
           <t>Y</t>
@@ -71097,7 +71074,6 @@
           <t>김해의생명산업진흥원 기업지원팀 055-310-9222</t>
         </is>
       </c>
-      <c r="AC459" t="inlineStr"/>
       <c r="AD459" t="inlineStr">
         <is>
           <t>055-310-9222</t>
@@ -71143,8 +71119,6 @@
           <t>□ 지원내용 : 모빌리티 부품 시제품 제작 지원</t>
         </is>
       </c>
-      <c r="F460" t="inlineStr"/>
-      <c r="G460" t="inlineStr"/>
       <c r="H460" t="inlineStr">
         <is>
           <t>N</t>
@@ -71240,7 +71214,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA460" t="inlineStr"/>
       <c r="AB460" t="inlineStr">
         <is>
           <t>충남테크노파크 미래자동차센터 041-331-8023, 8022, 8012 / lwk0611@ctp.or.kr, yubin.yoon@ctp.or.kr, tjdgus25@ctp.or.kr</t>
@@ -71300,7 +71273,6 @@
           <t>20백만원</t>
         </is>
       </c>
-      <c r="G461" t="inlineStr"/>
       <c r="H461" t="inlineStr">
         <is>
           <t>Y</t>
@@ -71458,7 +71430,6 @@
           <t>18만원</t>
         </is>
       </c>
-      <c r="G462" t="inlineStr"/>
       <c r="H462" t="inlineStr">
         <is>
           <t>Y</t>
@@ -71564,7 +71535,6 @@
           <t>경기환경에너지진흥원 환경사업팀 031-985-0485</t>
         </is>
       </c>
-      <c r="AC462" t="inlineStr"/>
       <c r="AD462" t="inlineStr">
         <is>
           <t>031-985-0485</t>
@@ -71611,8 +71581,6 @@
           <t>프로그램별 상세 지원내용은 상세안내문 첨부 파일 참고</t>
         </is>
       </c>
-      <c r="F463" t="inlineStr"/>
-      <c r="G463" t="inlineStr"/>
       <c r="H463" t="inlineStr">
         <is>
           <t>N</t>
@@ -71718,7 +71686,6 @@
           <t>지능형자동차부품진흥원 053-670-4784 / 한국전자기술연구원 031-739-7454 / 대구경북과학기술원 053-785-6314</t>
         </is>
       </c>
-      <c r="AC463" t="inlineStr"/>
       <c r="AD463" t="inlineStr">
         <is>
           <t>031-739-7454</t>
@@ -71767,7 +71734,6 @@
           <t>10백만원</t>
         </is>
       </c>
-      <c r="G464" t="inlineStr"/>
       <c r="H464" t="inlineStr">
         <is>
           <t>Y</t>
@@ -71873,7 +71839,6 @@
           <t>광명시청 투자유치과 기업지원팀 02-2680-2266</t>
         </is>
       </c>
-      <c r="AC464" t="inlineStr"/>
       <c r="AD464" t="inlineStr">
         <is>
           <t>02-2680-2266</t>
@@ -71923,7 +71888,6 @@
           <t>7억원</t>
         </is>
       </c>
-      <c r="G465" t="inlineStr"/>
       <c r="H465" t="inlineStr">
         <is>
           <t>N</t>
@@ -72029,7 +71993,6 @@
           <t>한국에너지기술평가원 수소산업실 02-3469-8345, 8349 및 기타 문의처 공고문 17p 참조</t>
         </is>
       </c>
-      <c r="AC465" t="inlineStr"/>
       <c r="AD465" t="inlineStr">
         <is>
           <t>02-3469-8345</t>
@@ -72072,7 +72035,6 @@
           <t>❍ 지원규모 : 도내 기업 5개사 내외</t>
         </is>
       </c>
-      <c r="F466" t="inlineStr"/>
       <c r="G466" t="inlineStr">
         <is>
           <t>5개</t>
@@ -72398,7 +72360,6 @@
           <t>20만원</t>
         </is>
       </c>
-      <c r="G468" t="inlineStr"/>
       <c r="H468" t="inlineStr">
         <is>
           <t>Y</t>
@@ -72559,7 +72520,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G469" t="inlineStr"/>
       <c r="H469" t="inlineStr">
         <is>
           <t>Y</t>
@@ -72718,7 +72678,6 @@
           <t>3원</t>
         </is>
       </c>
-      <c r="G470" t="inlineStr"/>
       <c r="H470" t="inlineStr">
         <is>
           <t>Y</t>
@@ -72824,7 +72783,6 @@
           <t>여수시 수산경영과 어업지도팀 061-659-3921</t>
         </is>
       </c>
-      <c r="AC470" t="inlineStr"/>
       <c r="AD470" t="inlineStr">
         <is>
           <t>061-659-3921</t>
@@ -72867,8 +72825,6 @@
           <t>참가기업 모집 제출서류 보완 및 평가 참가기업 최종 선정</t>
         </is>
       </c>
-      <c r="F471" t="inlineStr"/>
-      <c r="G471" t="inlineStr"/>
       <c r="H471" t="inlineStr">
         <is>
           <t>Y</t>
@@ -73026,7 +72982,6 @@
           <t>20만원</t>
         </is>
       </c>
-      <c r="G472" t="inlineStr"/>
       <c r="H472" t="inlineStr">
         <is>
           <t>Y</t>
@@ -73185,7 +73140,6 @@
           <t>70억원</t>
         </is>
       </c>
-      <c r="G473" t="inlineStr"/>
       <c r="H473" t="inlineStr">
         <is>
           <t>Y</t>
@@ -73291,7 +73245,6 @@
           <t>(안내기관) 여수시 수산경영과 어업지도팀 061-659-3921, FAX 061-659-5828 (융자상담) 농림수산업자신용보증기금 061-720-3100</t>
         </is>
       </c>
-      <c r="AC473" t="inlineStr"/>
       <c r="AD473" t="inlineStr">
         <is>
           <t>061-659-3921</t>
@@ -73334,8 +73287,6 @@
           <t>󰊲 선정규모</t>
         </is>
       </c>
-      <c r="F474" t="inlineStr"/>
-      <c r="G474" t="inlineStr"/>
       <c r="H474" t="inlineStr">
         <is>
           <t>N</t>
@@ -73441,7 +73392,6 @@
           <t>한국농업기술진흥원 창업육성팀 063-919-1433 및 관할 농식품벤처창업센터</t>
         </is>
       </c>
-      <c r="AC474" t="inlineStr"/>
       <c r="AD474" t="inlineStr">
         <is>
           <t>063-919-1433</t>
@@ -73484,8 +73434,6 @@
           <t>□ 지원내용 : 우수프랜차이즈 지정 등</t>
         </is>
       </c>
-      <c r="F475" t="inlineStr"/>
-      <c r="G475" t="inlineStr"/>
       <c r="H475" t="inlineStr">
         <is>
           <t>Y</t>
@@ -73581,13 +73529,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA475" t="inlineStr"/>
       <c r="AB475" t="inlineStr">
         <is>
           <t>소상공인시장진흥공단 유통지원팀 042-363-7745</t>
         </is>
       </c>
-      <c r="AC475" t="inlineStr"/>
       <c r="AD475" t="inlineStr">
         <is>
           <t>042-363-7745</t>
@@ -73630,7 +73576,6 @@
           <t>ㅇ (지원내용) 마이데이터 사업화 특화 컨설팅 및 참여기업 대상 데이터 활용 역량 강화를 위한 분야별 전문교육 제공(21개社)</t>
         </is>
       </c>
-      <c r="F476" t="inlineStr"/>
       <c r="G476" t="inlineStr">
         <is>
           <t>21개</t>
@@ -73731,7 +73676,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA476" t="inlineStr"/>
       <c r="AB476" t="inlineStr">
         <is>
           <t>한국데이터산업진흥원 마이데이터 컨설팅 운영사무국 02-3786-0409, mydata@kmac.co.kr</t>
@@ -73789,7 +73733,6 @@
           <t>300만원</t>
         </is>
       </c>
-      <c r="G477" t="inlineStr"/>
       <c r="H477" t="inlineStr">
         <is>
           <t>Y</t>
@@ -73947,7 +73890,6 @@
           <t>5억원</t>
         </is>
       </c>
-      <c r="G478" t="inlineStr"/>
       <c r="H478" t="inlineStr">
         <is>
           <t>N</t>
@@ -74105,7 +74047,6 @@
           <t>198억원</t>
         </is>
       </c>
-      <c r="G479" t="inlineStr"/>
       <c r="H479" t="inlineStr">
         <is>
           <t>N</t>
@@ -74260,7 +74201,6 @@
           <t>m 지원규모: 1개 업소당 최대 1000천원(부가세 별도)</t>
         </is>
       </c>
-      <c r="F480" t="inlineStr"/>
       <c r="G480" t="inlineStr">
         <is>
           <t>1개</t>
@@ -74427,7 +74367,6 @@
           <t>100만원</t>
         </is>
       </c>
-      <c r="G481" t="inlineStr"/>
       <c r="H481" t="inlineStr">
         <is>
           <t>Y</t>
@@ -74585,7 +74524,6 @@
           <t>120만원</t>
         </is>
       </c>
-      <c r="G482" t="inlineStr"/>
       <c r="H482" t="inlineStr">
         <is>
           <t>Y</t>
@@ -74739,8 +74677,6 @@
           <t>2 지원내용</t>
         </is>
       </c>
-      <c r="F483" t="inlineStr"/>
-      <c r="G483" t="inlineStr"/>
       <c r="H483" t="inlineStr">
         <is>
           <t>Y</t>
@@ -74898,7 +74834,6 @@
           <t>150000원</t>
         </is>
       </c>
-      <c r="G484" t="inlineStr"/>
       <c r="H484" t="inlineStr">
         <is>
           <t>Y</t>
@@ -75217,7 +75152,6 @@
           <t>❍ 지원규모 : 60개사, 600개 제품 내외 ※ 업체당 제품 10개 내외</t>
         </is>
       </c>
-      <c r="F486" t="inlineStr"/>
       <c r="G486" t="inlineStr">
         <is>
           <t>60개</t>
@@ -75383,7 +75317,6 @@
           <t>700만원</t>
         </is>
       </c>
-      <c r="G487" t="inlineStr"/>
       <c r="H487" t="inlineStr">
         <is>
           <t>Y</t>
@@ -75507,6 +75440,7651 @@
       <c r="AF487" t="inlineStr">
         <is>
           <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125602</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026년 예비오션스타 기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>해양수산과학기술진흥원</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>온라인 접수(바다봄지식정보시스템)</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>* 연 매출액 1000억 원 이상 달성이 기대되는 해양수산 벤처‧스타트업</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>1000억원</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr"/>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z488" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA488" t="inlineStr"/>
+      <c r="AB488" t="inlineStr">
+        <is>
+          <t>해양수산과학기술진흥원 산업정책실 창업투자팀 02-3460-0376, dbtmf123@kimst.re.kr</t>
+        </is>
+      </c>
+      <c r="AC488" t="inlineStr">
+        <is>
+          <t>dbtmf123@kimst.re.kr</t>
+        </is>
+      </c>
+      <c r="AD488" t="inlineStr">
+        <is>
+          <t>02-3460-0376</t>
+        </is>
+      </c>
+      <c r="AE488" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF488" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125696</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>[경기] 안양시 2026년 유망기업 온ㆍ오프라인 유통망 입점 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>안양산업진흥원</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2026-09-03 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>이메일 접수 (ssy@aba.or.kr)</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>❍ 지원규모</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr"/>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z489" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA489" t="inlineStr">
+        <is>
+          <t>및 유의사항, 구 분, 비 고 (유의사항), · 공고일 기준 국세청 홈텍스 발급분만 인정, · 국세 완납 증명서, 필 수 · 국세청 홈텍스 발급 가능, (공고일 기준), 필 수 · 정부24 발급 가능</t>
+        </is>
+      </c>
+      <c r="AB489" t="inlineStr">
+        <is>
+          <t>안양산업진흥원 031-8045-6712</t>
+        </is>
+      </c>
+      <c r="AC489" t="inlineStr">
+        <is>
+          <t>ssy@aba.or.kr</t>
+        </is>
+      </c>
+      <c r="AD489" t="inlineStr">
+        <is>
+          <t>031-8045-6712</t>
+        </is>
+      </c>
+      <c r="AE489" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF489" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125695</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>[경기] 2026년 인도네시아 자카르타 할랄 식품 전시회(SIAL InterFood Indonesia) 참가 기업모집 공고</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>성남산업진흥원</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-10</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>온라인 접수 (중소기업 해외전시포탈)</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>※ 기업당 국고 지원액 : 약1000만원 ~ 1300만원</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>1300만원</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr"/>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z490" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA490" t="inlineStr">
+        <is>
+          <t>등록,  문 의, 박원지 주 임 (TEL. 031-782-3065), 성남산업진흥원장, 참 고, 리스트,  공통, 구분 주요 서류</t>
+        </is>
+      </c>
+      <c r="AB490" t="inlineStr">
+        <is>
+          <t>성남산업진흥원 글로벌마케팅 031-782-3061, 031-782-3065</t>
+        </is>
+      </c>
+      <c r="AC490" t="inlineStr"/>
+      <c r="AD490" t="inlineStr">
+        <is>
+          <t>031-782-3061</t>
+        </is>
+      </c>
+      <c r="AE490" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF490" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125694</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026년 3차 홍콩 소비재 메가쇼 전시회 수출 컨소시엄 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>강원특별자치도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-26</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>온라인 접수 (중소기업 해외전시포탈)</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>❍ 모집규모 : 2개사</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z491" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA491" t="inlineStr"/>
+      <c r="AB491" t="inlineStr">
+        <is>
+          <t>강원특별자치도 경제진흥원 033-749-3362, jaesub2019@naver.com</t>
+        </is>
+      </c>
+      <c r="AC491" t="inlineStr">
+        <is>
+          <t>jaesub2019@naver.com</t>
+        </is>
+      </c>
+      <c r="AD491" t="inlineStr">
+        <is>
+          <t>033-749-3362</t>
+        </is>
+      </c>
+      <c r="AE491" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF491" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125693</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>[경기] 화성시 2026년 하반기 그린안전리모델링 지원사업 참여기업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>화성산업진흥원</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-03</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>온라인 접수(화성시 기업지원플랫폼)</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>&lt;A&gt;&lt;내·외벽 도색 00개 사&gt;&lt;기업당 최대 500만 원까지&gt;</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>00개</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z492" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA492" t="inlineStr"/>
+      <c r="AB492" t="inlineStr">
+        <is>
+          <t>화성산업진흥원 안전기획팀 031-278-6465, jhpark@hsbiz.or.kr</t>
+        </is>
+      </c>
+      <c r="AC492" t="inlineStr">
+        <is>
+          <t>jhpark@hsbiz.or.kr</t>
+        </is>
+      </c>
+      <c r="AD492" t="inlineStr">
+        <is>
+          <t>031-278-6465</t>
+        </is>
+      </c>
+      <c r="AE492" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF492" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125692</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026년 한식 페스타 부스 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>한식진흥원</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>이메일 접수(hansikfesta@hansik.or.kr)</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>지원 내용</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr"/>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z493" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA493" t="inlineStr"/>
+      <c r="AB493" t="inlineStr">
+        <is>
+          <t>한식페스타 사무국 02-550-2557, hansikfesta@hansik.or.kr</t>
+        </is>
+      </c>
+      <c r="AC493" t="inlineStr">
+        <is>
+          <t>hansikfesta@hansik.or.kr</t>
+        </is>
+      </c>
+      <c r="AD493" t="inlineStr">
+        <is>
+          <t>02-550-2557</t>
+        </is>
+      </c>
+      <c r="AE493" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF493" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125691</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>[경남] 거제시 2026년 3차 하청노동자 기후재난 예방 지원사업 재공고</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>온라인 접수(보탬e) 후 원본서류 직접 또는 등기우편 제출
+- 접수처 : 거제시청 조선지원과</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>※선정 이후라도 동일·유사 사업 중복 지원이 확인될 경우 선정 취소, 보조금 결정 취소 및 환수 등 필요한 조치를 할 수 있음</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr"/>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z494" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA494" t="inlineStr">
+        <is>
+          <t>구분, 부수, 비고(서식), 지원신청서, 서식1, 사업계획서, 서식2, 기업소개서</t>
+        </is>
+      </c>
+      <c r="AB494" t="inlineStr">
+        <is>
+          <t>거제시청 조선지원과 노동자지원팀 055-639-4453</t>
+        </is>
+      </c>
+      <c r="AC494" t="inlineStr"/>
+      <c r="AD494" t="inlineStr">
+        <is>
+          <t>055-639-4453</t>
+        </is>
+      </c>
+      <c r="AE494" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF494" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125690</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>[대구] 2026년 AI 로봇 글로벌 혁신특구 수혜기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>대구기계부품연구원</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-03</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>이메일 접수 (zem727@dmi.re.kr, kss0603@dmi.re.kr)</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>1 신산업 보험 22개 기업 이내 6300000원 이내</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>6300000원</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>22개</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z495" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA495" t="inlineStr">
+        <is>
+          <t>작성 후 아래 이메일로 제출, 접수 기관 담당자 및 연락처, Ÿ 담당자 : 기계로봇연구본부 기계로봇연구본부, 장은실 책임연구원, Ÿ 연락처 : TEL. 053-608-2045, (재)대구기계부품연구원, 김성신 선임연구원, Ÿ 연락처 : TEL. 053-608-2072</t>
+        </is>
+      </c>
+      <c r="AB495" t="inlineStr">
+        <is>
+          <t>대구기계부품연구원 기계로봇연구본부 기계로봇연구본부 053-608-2045, 2072</t>
+        </is>
+      </c>
+      <c r="AC495" t="inlineStr">
+        <is>
+          <t>kss0603@dmi.re.kr</t>
+        </is>
+      </c>
+      <c r="AD495" t="inlineStr">
+        <is>
+          <t>053-608-2045</t>
+        </is>
+      </c>
+      <c r="AE495" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF495" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125689</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 메가쇼 시즌2 오프라인 판촉전 운영 및 참가지원 사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>전남사회적경제통합지원센터</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>이메일 접수 (sdcenter@jnsec.kr)
+※ 신청서 제출 후 전화로 접수 확인 요망(접수확인 필수)</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr"/>
+      <c r="G496" t="inlineStr"/>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z496" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA496" t="inlineStr"/>
+      <c r="AB496" t="inlineStr">
+        <is>
+          <t>전남사회적통합지원센터 061-741-9943</t>
+        </is>
+      </c>
+      <c r="AC496" t="inlineStr"/>
+      <c r="AD496" t="inlineStr">
+        <is>
+          <t>061-741-9943</t>
+        </is>
+      </c>
+      <c r="AE496" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF496" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125688</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>[경북] 안동시 2026년 수출기업 역량강화 지원사업 참여기업 모집 연장 공고(수출매뉴얼 지원)</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>2026-07-21 ~ 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>이메일, 우편(등기) 접수 
+- 이메일 : gepa_north@naver.com
+- 접수처 : 경상북도 안동시 북순환로 387, 2층 경상북도경제진흥원
+※ 신청서류를 하나의 문서로 스캔(pdf파일)하여 제출</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>○ 대상자별지원금액 : 기업별 최대 3백만원 한도</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>3백만원</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr"/>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z497" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA497" t="inlineStr">
+        <is>
+          <t>를 하나의 문서로 스캔(pdf파일)하여 제출, No 제 출 서 류 제출부수 비 고 사 항, 사업참여 신청서 1부 1부, 사업 수행계획서 1부, [서식집] 양식 사용, 개인정보의 수집‧이용에 관한 동의서 1부, 지원요건 준수 확인서 1부, 중소기업 확인서 1부</t>
+        </is>
+      </c>
+      <c r="AB497" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 북부지소 054-900-3801, gepa_north@naver.com</t>
+        </is>
+      </c>
+      <c r="AC497" t="inlineStr">
+        <is>
+          <t>gepa_north@naver.com</t>
+        </is>
+      </c>
+      <c r="AD497" t="inlineStr">
+        <is>
+          <t>054-900-3801</t>
+        </is>
+      </c>
+      <c r="AE497" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF497" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125687</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 KEPCO-사회연대경제 상생 팝업스토어 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>전남사회적경제통합지원센터</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-01</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>이메일 접수 (yeosumommom@naver.com)
+※ 신청서 제출 후 운영사 전화 확인 요망(접수확인 필수)</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>○ 지원규모 : 전남광주통합특별시 사회연대경제기업 50개소</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>50개</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z498" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA498" t="inlineStr">
+        <is>
+          <t>는 압축파일로 이메일 제출, &lt;구 분&gt;&lt;세 부 내 용&gt;, &lt;필 수&gt;&lt;, (예비)마을기업 지정서&gt;, &lt;선 택&gt;&lt;, &gt;&lt;① 제품 소개서 ② 기업 홍보 자료&gt;, 문 의 처, &lt; 4. 추진 일정&gt;</t>
+        </is>
+      </c>
+      <c r="AB498" t="inlineStr">
+        <is>
+          <t>전남사회적경제통합지원센터 061-741-9943 / 운영사 ㈜다락방 061-662-3377</t>
+        </is>
+      </c>
+      <c r="AC498" t="inlineStr">
+        <is>
+          <t>yeosumommom@naver.com</t>
+        </is>
+      </c>
+      <c r="AD498" t="inlineStr">
+        <is>
+          <t>061-662-3377</t>
+        </is>
+      </c>
+      <c r="AE498" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF498" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125686</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026년 4차 국가유산 활용 상품 디자인 보호 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>한국지식재산보호원</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>온라인 접수 (한국지식재산보호원)</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>분쟁예방 디자인권 보호전략(권리화) 수립 28백만원 최대 2.</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>28백만원</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr"/>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z499" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA499" t="inlineStr">
+        <is>
+          <t>종 • 기업, 전자정부 서비스* 신청시, 종 - 전자정부 서비스* 신청시, 필수 해당시, 기업 기업규모 증명서 O 기업규모 증명서 O, 대상제품 설명&amp;판매자료 O, 추가 대상제품 설명&amp;판매자료 O, 수출 증빙자료 O</t>
+        </is>
+      </c>
+      <c r="AB499" t="inlineStr">
+        <is>
+          <t>한국지식재산보호원 상표디자인분쟁대응실 02-2183-5896, kwave@koipa.re.kr</t>
+        </is>
+      </c>
+      <c r="AC499" t="inlineStr">
+        <is>
+          <t>kwave@koipa.re.kr</t>
+        </is>
+      </c>
+      <c r="AD499" t="inlineStr">
+        <is>
+          <t>02-2183-5896</t>
+        </is>
+      </c>
+      <c r="AE499" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF499" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125685</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026년도 딥테크 특화 창업중심대학 추천형 창업기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>창업진흥원</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>온라인 접수 (K-Startup 누리집)</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>2억원 내외(최대 1.</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>2억원</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr"/>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z500" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA500" t="inlineStr">
+        <is>
+          <t>중 일부를 별도로 발급받지 않아도, 자동 연동하여 제출 가능합니다. * 4. 접수방법 -, 참고, 사업 개요, 사업 목적 :, 지원 대상 :, [붙임1] 신산업 창업 분야 참고, 대 과학기술원: 광주과학기술원(GIST)</t>
+        </is>
+      </c>
+      <c r="AB500" t="inlineStr">
+        <is>
+          <t>(시스템 문의) 국번없이 1357 / (사업문의) 주관기관 담당자 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC500" t="inlineStr"/>
+      <c r="AD500" t="inlineStr">
+        <is>
+          <t>042-350-4732</t>
+        </is>
+      </c>
+      <c r="AE500" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF500" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125684</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026년 탄소중립펀드 투자유치 피칭데이 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>경기창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-09-08</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>온라인 접수 (구글폼)</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>◦ 본선 수상팀(6팀)에 대한 총 상금 1천만원(최대 3백만원) 및 상장(6점) 수여</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>1천만원</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr"/>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z501" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA501" t="inlineStr">
+        <is>
+          <t>구분, ② [붙임2] 개인정보의 수집·이용에 관한 동의서 1부, Ⅳ 평가 방식, 평가방법, 심의기준 및 배점사항, &lt;평가기준표(안)&gt;, 평가항목 세부내용 배점, 문제인식 개발배경 및 필요성 / 사회</t>
+        </is>
+      </c>
+      <c r="AB501" t="inlineStr">
+        <is>
+          <t>경기창조경제혁신센터 창업육성팀 031-780-9048</t>
+        </is>
+      </c>
+      <c r="AC501" t="inlineStr"/>
+      <c r="AD501" t="inlineStr">
+        <is>
+          <t>031-780-9048</t>
+        </is>
+      </c>
+      <c r="AE501" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF501" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125683</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>[서울] 2026년 중동상황 대응 수출위기 극복 물류지원금 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>서울경제진흥원</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>온라인 접수 (서울경제진흥원)</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>○ 지원 한도: 예산 소진 시까지 지원 (기업당 최대 3000만 원 한도 내)</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>3000만원</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z502" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA502" t="inlineStr">
+        <is>
+          <t>기반 서류 통과 기업 대상, 홈페이지 접수 ➡ ➡ ➡, 검토 서류평가 지원금 지급, 사업대상, 서울 소재 수출기업으로서, 아래의 ①, ③ 요건을 모두 충족하는 기업, 본사 또는 독립된 사업장(지사 등)이</t>
+        </is>
+      </c>
+      <c r="AB502" t="inlineStr">
+        <is>
+          <t>(사업 관련 문의(신청, 자격, 지원내용 등)) SBA 글로벌마케팅팀 02-2657-5725, jypark01@sba.seoul.kr(메일 문의 권장) / (물류비 및 증빙서류 문의(운임, 서류 인정 여부 등)) 관세사 ubis@ubiscs.com</t>
+        </is>
+      </c>
+      <c r="AC502" t="inlineStr">
+        <is>
+          <t>jypark01@sba.seoul.kr</t>
+        </is>
+      </c>
+      <c r="AD502" t="inlineStr">
+        <is>
+          <t>02-2657-5725</t>
+        </is>
+      </c>
+      <c r="AE502" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF502" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125682</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026년 GovTech 창업 경진대회 모집 공고</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>정보통신산업진흥원</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-21</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>온라인 접수 (GovTech 창업 경진대회)</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>제품·서비스개발 1 1500만원</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>1500만원</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z503" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA503" t="inlineStr">
+        <is>
+          <t>추후, 구분 자격, (2차 평가시), ①참가신청서, ②개인정보 수집 이용 동의서, 아이디어, 예비창업자 ③참가자 서약서 발표자료(PPT), 기획 분야</t>
+        </is>
+      </c>
+      <c r="AB503" t="inlineStr">
+        <is>
+          <t>2025년 GovTech 창업 경진대회 운영사무국 02-726-1096 / k-govtech@wips.co.kr (카카오톡) @2026govtech</t>
+        </is>
+      </c>
+      <c r="AC503" t="inlineStr">
+        <is>
+          <t>k-govtech@wips.co.kr</t>
+        </is>
+      </c>
+      <c r="AD503" t="inlineStr">
+        <is>
+          <t>02-726-1096</t>
+        </is>
+      </c>
+      <c r="AE503" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF503" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125681</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>[경기] 2026년 2차 중소기업육성자금 융자지원계획 변경 공고</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>경기신용보증재단</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2026-09-01 ~ 2026-12-31</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>온라인 및 방문 접수
+- 온라인 : 경기도중소기업육성자금(G-money)
+- 방문 : 사업장 소재지 경기신용보증재단 지점</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>신기술기업 벤처창업기업 (기금융자 5억원 3년 (1년)</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>5억원</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr"/>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z504" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA504" t="inlineStr"/>
+      <c r="AB504" t="inlineStr">
+        <is>
+          <t>경기신용보증재단 고객센터 대표번호 1577-5900 및 지점별 문의처 공고문 3p참조</t>
+        </is>
+      </c>
+      <c r="AC504" t="inlineStr"/>
+      <c r="AD504" t="inlineStr">
+        <is>
+          <t>01 070-7614</t>
+        </is>
+      </c>
+      <c r="AE504" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF504" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125680</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>[서울] 2026년 중동상황 대응 중소기업 수출위기극복 및 대체시장 개척 심화컨설팅 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>서울경제진흥원</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>온라인 접수 (서울경제진흥원 홈페이지)</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>지원규모 45개사 내외(총 예산 : 약 8억원)</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>8억원</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>45개</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z505" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA505" t="inlineStr">
+        <is>
+          <t>정비 자문, 금융·환리스크 금융·환리스크, 대응서, ③ 물류비 절감 및, 공급망 다변화, 나. 지원 규모 및 조건, ❍ 지원 규모: 기업당 최대 2, 만 원 한도 (부가세 제외)</t>
+        </is>
+      </c>
+      <c r="AB505" t="inlineStr">
+        <is>
+          <t>서울경제진흥원 글로벌마케팅팀 02-2657-5729, namutegi@sba.seoul.kr</t>
+        </is>
+      </c>
+      <c r="AC505" t="inlineStr">
+        <is>
+          <t>namutegi@sba.seoul.kr</t>
+        </is>
+      </c>
+      <c r="AD505" t="inlineStr">
+        <is>
+          <t>02-2657-5729</t>
+        </is>
+      </c>
+      <c r="AE505" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF505" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125679</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026년 H-스타트업 창업경진대회 참가자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-07</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>온라인 접수(화성산업진흥원 기업지원플랫폼)</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>800만원</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>800만원</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr"/>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z506" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA506" t="inlineStr">
+        <is>
+          <t>접수방법, 접수기간:, (목) ~ 9. 7.(월) 18:00까지, 제출 이후에 수정 필요시, 신청 취소 후 수정 및 재신청하여야 함., 접수방법:, 화성산업진흥원 기업지원플랫폼, 온라인 신청</t>
+        </is>
+      </c>
+      <c r="AB506" t="inlineStr">
+        <is>
+          <t>화성시청 기업지원과 031-5189-6938</t>
+        </is>
+      </c>
+      <c r="AC506" t="inlineStr"/>
+      <c r="AD506" t="inlineStr">
+        <is>
+          <t>031-5189-6938</t>
+        </is>
+      </c>
+      <c r="AE506" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF506" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125678</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026년 3차 원전기업 인증 신청기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>한국원자력산업협회</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>2026-08-13 ~ 2026-09-14</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>이메일 및 방문 또는 우편 접수
+- 이메일 : edu@kaif.or.kr
+- 접수처 : (04505) 서울특별시 중구 서소문로 38, 9층 한국원자력산업협회, 원전기업 인증사무국
+※ PDF 파일 이메일 제출과 인쇄본 제출(우편ㆍ방문 등) 두 가지 방법으로 전부 완료되어야 함</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>[별지-01 원전기업 인증 신청서] 하단 기재 첨부서류 일체</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>1원</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr"/>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z507" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA507" t="inlineStr">
+        <is>
+          <t>갱신신청서(서식 제3호) - 갱신 신청 기업 필수 제출, 인증신청서, 자체심사표상 제출이 필요한 증빙서류 일체, 제출방법 및 유의사항, 직접 등) 두 가지 방법으로 전부 완료되어야 함, 제출 파일명 : ‘2026년 3차 원전기업 인증제도, _기업명.pdf’, 참고사항 : 반드시 1개의 PDF 파일로 통합하여 제출</t>
+        </is>
+      </c>
+      <c r="AB507" t="inlineStr">
+        <is>
+          <t>한국원자력산업협회 원전기업 인증 사무국 02-6953-2523, edu@kaif.or.kr</t>
+        </is>
+      </c>
+      <c r="AC507" t="inlineStr">
+        <is>
+          <t>edu@kaif.or.kr</t>
+        </is>
+      </c>
+      <c r="AD507" t="inlineStr">
+        <is>
+          <t>02-6953-2523</t>
+        </is>
+      </c>
+      <c r="AE507" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF507" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125677</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>[경북] 상주시 2026년 해외 수출마케팅 협력사업(무역사절단) 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-07</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>이메일 접수 (bc100@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>ㅇ 편도 항공료(1인/1개사, 100만원 한도)</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z508" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA508" t="inlineStr">
+        <is>
+          <t>구분, 비고, 사업 신청서 및 기업정보 확인서 등 양식1~3, 공장등록증 또는 건축물관리대장 또는 수출신고필증 필수, 중소기업확인서 필수, 년 수출실적증명원 선택, 국세청 국세, 지방세 납입증명서 필수</t>
+        </is>
+      </c>
+      <c r="AB508" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 마케팅팀 054-470-8539, bc100@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AC508" t="inlineStr">
+        <is>
+          <t>bc100@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD508" t="inlineStr">
+        <is>
+          <t>054-470-8539</t>
+        </is>
+      </c>
+      <c r="AE508" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF508" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125676</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026년 카자흐스탄 현지 진출지원 사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>중소벤처기업진흥공단</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>이메일 접수 (sukyk@kosmes.or.kr)</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>□ (지원내용) 바이어매칭, 항공료 50만원, 현지 교통(단체), 식사 등 지원</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr"/>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z509" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA509" t="inlineStr"/>
+      <c r="AB509" t="inlineStr">
+        <is>
+          <t>중소벤처기업진흥공단 카자흐스탄 알마티GBC +7-727-274-2500, sukyk@kosmes.or.kr</t>
+        </is>
+      </c>
+      <c r="AC509" t="inlineStr">
+        <is>
+          <t>sukyk@kosmes.or.kr</t>
+        </is>
+      </c>
+      <c r="AD509" t="inlineStr"/>
+      <c r="AE509" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF509" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125675</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>[울산] 2026년 글로벌 OTA 연계 관광상품 개발 및 런칭 지원 사업 참여기업 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>직접수행</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>이메일 또는 방문 접수
+- 접수처 : 울산광역시 관광과
+- 이메일 : lyh3257@korea.kr</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>· 1년 이내 사업정지 또는 과징금 80만 원 이상의</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>80만원</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr"/>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z510" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA510" t="inlineStr">
+        <is>
+          <t>구분, 제 출 서 류, 비고, 붙임1, 참가 신청서, 붙임2, 사업 계획서, 붙임3</t>
+        </is>
+      </c>
+      <c r="AB510" t="inlineStr">
+        <is>
+          <t>울산광역시 관광산업팀 052-229-3885</t>
+        </is>
+      </c>
+      <c r="AC510" t="inlineStr">
+        <is>
+          <t>lyh3257@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD510" t="inlineStr">
+        <is>
+          <t>052-229-3885</t>
+        </is>
+      </c>
+      <c r="AE510" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF510" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125674</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>[울산] 2026년 2차 지역기업 판로개척 패키지 지원사업 기술개발인증 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>울산경제일자리진흥원</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-21</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>온라인 접수 (울산통상지원시스템)</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>- (기술개발제품 인증지원) 2개사 내외, 기업당 최대 10백만원 이내</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>10백만원</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W511" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y511" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z511" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA511" t="inlineStr">
+        <is>
+          <t>미제출 시 1차 보완요청 후 미이행 시 요건 결격, 지원불가, 구분 신청 유의사항 신청기관, ∘ 울산통상지원시스템 회원가입, 수출실적 등) 갱신(필수), ※ 창업기업 또는 간편장부 대상자 대체자료, 신청방법 www.ultrade.kr, 사업 신청내용(분야별 중복신청 가능</t>
+        </is>
+      </c>
+      <c r="AB511" t="inlineStr">
+        <is>
+          <t>울산경제일자리진흥원 기업지원부 판로개척팀 052-283-7141, hjkwon@ubpi.or.kr</t>
+        </is>
+      </c>
+      <c r="AC511" t="inlineStr">
+        <is>
+          <t>hjkwon@ubpi.or.kr</t>
+        </is>
+      </c>
+      <c r="AD511" t="inlineStr">
+        <is>
+          <t>052-283-7141</t>
+        </is>
+      </c>
+      <c r="AE511" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF511" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125673</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026년 BOUNCE 2026 글로벌 오피스아워 참여 스타트업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>부산창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>온라인 접수(구글폼)</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>※ 최종 선정기업 대상 일시 개별 안내 예정</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr"/>
+      <c r="G512" t="inlineStr"/>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z512" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA512" t="inlineStr"/>
+      <c r="AB512" t="inlineStr">
+        <is>
+          <t>부산창조경제혁신센터 창업육성팀 051-749-8963, wlszh19@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AC512" t="inlineStr">
+        <is>
+          <t>wlszh19@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AD512" t="inlineStr">
+        <is>
+          <t>051-749-8963</t>
+        </is>
+      </c>
+      <c r="AE512" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF512" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125672</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>[충남] 2027년 전통시장 및 상점가 시설현대화사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>직접수행</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>기한내 전자문서로 신청(첨부파일 용량 초과시 담당자 이메일 송부)
+- 전통시장ㆍ상점가ㆍ상권활성화구역(시군 신청) → 시ㆍ군(추천) → 도(선정)
+※ 신청기간 내 첨부양식 포함 신청서류를 제출한 신청건에 한해 접수 및 평가실시</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>❍ 총사업비 1억원 이상인 경우</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>1억원</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr"/>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z513" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA513" t="inlineStr">
+        <is>
+          <t>를 제출한 신청건에 한해 접수 및 평가실시, 선정절차, 신청접수, 심 사(도), 선 정(도), 최종결과, 사업추진,  전통시장 등</t>
+        </is>
+      </c>
+      <c r="AB513" t="inlineStr">
+        <is>
+          <t>충청남도 경제통상국 소상공경제정책과 041-635-3318 및 시ㆍ군 전통시장 지원업무 담당 부서 문의(공고문 5p 참조)</t>
+        </is>
+      </c>
+      <c r="AC513" t="inlineStr"/>
+      <c r="AD513" t="inlineStr">
+        <is>
+          <t>041-635-3318</t>
+        </is>
+      </c>
+      <c r="AE513" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF513" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125671</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>[서울] 2026년 서울커리업 바로채용 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>서울시여성가족재단</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-10-08</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>온라인 접수 (서울커리업 홈페이지)</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t> 지원내용 : 고용장려금 (최대 300만원)</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>300만원</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr"/>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z514" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA514" t="inlineStr">
+        <is>
+          <t>구분 제출 목록 비고, 기업참여신청서 온라인 작성, 필수 참여기업 직무기술서 온라인 작성, 개인정보 수집·이용·제공 동의서 온라인 작성, 기업관련 인증서, 파일첨부, (가족친화인증, 서울형 강소기업</t>
+        </is>
+      </c>
+      <c r="AB514" t="inlineStr">
+        <is>
+          <t>서울특별시여성가족재단(대행기관) 대표전화1660-3040, 3번 기업</t>
+        </is>
+      </c>
+      <c r="AC514" t="inlineStr"/>
+      <c r="AD514" t="inlineStr"/>
+      <c r="AE514" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF514" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125670</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 충북바이오산학융합원 K-바이오헬스 지역센터 지원기업 모집 추가 공고</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>충북바이오산학융합원</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>우편, 방문, 이메일 접수
+※ 원본(우편 또는 방문)과 사본(이메일) 둘 다 제출
+- 접수처 : (28160) 충북 청주시 흥덕구 오송읍 오송생명1로 194-25, 408호(K-바이오헬스지역센터)
+- 이메일 : biotion@cbio.or.kr</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>시제품 ▸바이오헬스 기술 실증을 위한 1000만원</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>1000만원</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr"/>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z515" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA515" t="inlineStr">
+        <is>
+          <t>확인, ※ 발표평가자 대상 자료 제출 개별 안내 예정, ◦ 평가결과, ◦ 평가지표, 평가항목 세부 평가지표 배점, 사업 목표의 명확성 및 적정성, 사업 추진, 사업 추진 필요성 및 사업 계획 타당성 25점</t>
+        </is>
+      </c>
+      <c r="AB515" t="inlineStr">
+        <is>
+          <t>충북바이오산학융합원 대외협력실 043-220-1053, 1054, 1055 / jiho@cbio.or.kr, hwmun@cbio.or.kr, jes12@cbio.or.kr 및 충북대학교병원 문의처 공고문 6p참조</t>
+        </is>
+      </c>
+      <c r="AC515" t="inlineStr">
+        <is>
+          <t>hwmun@cbio.or.kr</t>
+        </is>
+      </c>
+      <c r="AD515" t="inlineStr">
+        <is>
+          <t>043-220-1053</t>
+        </is>
+      </c>
+      <c r="AE515" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF515" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125669</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 2차 대덕특구 기업 애로해결 바우처 지원사업(이노폴리스캠퍼스 사업(원스톱 지원 센터 운영사업))</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>대전창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>이메일 접수 (hej71@iva.or.kr)</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>※ 지원한도 500만원 분야('시제품 제작 및 PoC 지원', '해외 테스트베드 및 PoC 지원')는</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr"/>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z516" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA516" t="inlineStr">
+        <is>
+          <t>접수 지원 필요성 검토 선정 및 결과 통보, (8월) (9월) (9월), ⑥ 사업비 지급 ⑤ 결과보고 ④ 바우처 지원, 결과보고 검토 후 결과보고서 제출 분야별 전문가 자문, Ⅲ 지원기업 선정심의, 선정절차, ◦ 1단계 : 신청자격 및, 등 적정성 검토</t>
+        </is>
+      </c>
+      <c r="AB516" t="inlineStr">
+        <is>
+          <t>이노폴리스벤처협회 042-867-9693, hej71@iva.or.kr</t>
+        </is>
+      </c>
+      <c r="AC516" t="inlineStr">
+        <is>
+          <t>hej71@iva.or.kr</t>
+        </is>
+      </c>
+      <c r="AD516" t="inlineStr">
+        <is>
+          <t>042-867-9693</t>
+        </is>
+      </c>
+      <c r="AE516" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF516" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125668</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>[경기] 2026년 일터동행 기업 파트너십 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>경기도일자리재단</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>이메일, 온라인 접수 
+- 이메일 : ggsaeil@gjf.or.kr
+- 온라인 : 구글폼
+※ 메일 접수 후 수신 확인 필수 (031-270-9793, 9802, 9810)</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr"/>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z517" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA517" t="inlineStr">
+        <is>
+          <t>(하단 첨부 1~3 참조) - 참가신청서 1부</t>
+        </is>
+      </c>
+      <c r="AB517" t="inlineStr">
+        <is>
+          <t>경기도일자리재단 남부일자리팀(경기광역새일센터) 031-270-9800</t>
+        </is>
+      </c>
+      <c r="AC517" t="inlineStr">
+        <is>
+          <t>ggsaeil@gjf.or.kr</t>
+        </is>
+      </c>
+      <c r="AD517" t="inlineStr">
+        <is>
+          <t>031-270-9800</t>
+        </is>
+      </c>
+      <c r="AE517" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF517" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125667</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026년 대한민국 물산업 혁신 창업대전 (Startup Water 2026) 참가자(팀) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>한국수자원공사</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-10-19</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>온라인 접수 (스타트업워터 홈페이지)</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>◦ 아이디어 부문 : 총 9팀 (총 상금 17백만원)</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>17백만원</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr"/>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z518" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA518" t="inlineStr">
+        <is>
+          <t>구분, 공 통, 참가서약서 1부 (공고문 붙임 양식2), 아이디어 부문 신청서 1부 (공고문 붙임 양식3), 아이디어 부문, 아이디어 부문 제안서 1부 (공고문 붙임 양식4), 사업화 부문 신청서 1부 (공고문 붙임 양식5), 사업화 부문 사업계획서 1부 (공고문 붙임 양식6)</t>
+        </is>
+      </c>
+      <c r="AB518" t="inlineStr">
+        <is>
+          <t>K-water 물산업혁신처 042-629-2515, 2513</t>
+        </is>
+      </c>
+      <c r="AC518" t="inlineStr"/>
+      <c r="AD518" t="inlineStr">
+        <is>
+          <t>042-629-2515</t>
+        </is>
+      </c>
+      <c r="AE518" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF518" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125666</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026년 일터혁신 우수기업 선정계획 공고</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>노사발전재단</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>이메일 접수(hpws@nosa.or.kr)</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>지원내용</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr"/>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z519" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA519" t="inlineStr">
+        <is>
+          <t>노사동반으로 신청, 된 서류만 접수하며, ①참여신청서, ②일터혁신 추진실적, ③추진실적 증빙자료, 제출, (제출서식 참조), 연번</t>
+        </is>
+      </c>
+      <c r="AB519" t="inlineStr">
+        <is>
+          <t>노사발전재단 일터개선팀 02-6021-1210, 1214, 1225 / hpws@nosa.or.kr</t>
+        </is>
+      </c>
+      <c r="AC519" t="inlineStr">
+        <is>
+          <t>hpws@nosa.or.kr</t>
+        </is>
+      </c>
+      <c r="AD519" t="inlineStr">
+        <is>
+          <t>02-6021-1210</t>
+        </is>
+      </c>
+      <c r="AE519" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF519" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125665</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026년 스마트 플래그십 스토어 (소담상회 with LOTTE ON) 모집 공고</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>한국중소벤처기업유통원</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>온라인 신청 (판판대로)</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>© 모집규모</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr"/>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z520" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA520" t="inlineStr"/>
+      <c r="AB520" t="inlineStr">
+        <is>
+          <t>오엠인터랙티브 070-8633-5400, semd@omin.co.kr 한국중소벤처기업유통원 02-6678-9368, 9364</t>
+        </is>
+      </c>
+      <c r="AC520" t="inlineStr">
+        <is>
+          <t>semd@omin.co.kr</t>
+        </is>
+      </c>
+      <c r="AD520" t="inlineStr">
+        <is>
+          <t>02-6678-9368</t>
+        </is>
+      </c>
+      <c r="AE520" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF520" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125664</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026년 민관협력 오픈이노베이션 지원 규제자유특구 지원 창업기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>창업진흥원</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>온라인 접수(K-Startup)</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>(최대 1억원)</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>1억원</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr"/>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T521" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U521" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V521" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W521" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X521" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y521" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z521" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA521" t="inlineStr">
+        <is>
+          <t>접수 방법-, 참고, 모집 개요, 사업목적 :, 신산업·신기술 분야 규제실증을 촉진, 하고, 지역경제 성장, 을 위해</t>
+        </is>
+      </c>
+      <c r="AB521" t="inlineStr">
+        <is>
+          <t>(사업 문의) 충북창조경제혁신센터 043-710-5932 (시스템 문의) 중소기업통합콜센터 국번없이 1357</t>
+        </is>
+      </c>
+      <c r="AC521" t="inlineStr"/>
+      <c r="AD521" t="inlineStr">
+        <is>
+          <t>043-710-5932</t>
+        </is>
+      </c>
+      <c r="AE521" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF521" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125663</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>[강원] 태백시 2026년 청년농업인 정책자금 이차보전 신청자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 태백시 농업기술센터</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>지원 내용 및 지원시기</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="inlineStr"/>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z522" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA522" t="inlineStr">
+        <is>
+          <t>(신청서 서식 참고), ❍ 신청방법: 태백시 농업기술센터 사무실 방문접수, ❍ 기타 신청문의 및 접수처: 농업기술센터 농업과, 농업과 농업정책팀 ☎ 033-550-2721, 농업과 업무담당자 ☎ 033-550-2674</t>
+        </is>
+      </c>
+      <c r="AB522" t="inlineStr">
+        <is>
+          <t>태백시 농업기술센터 농업과 농업정책팀 033-550-2721 / 업무담당자 033-550-2674</t>
+        </is>
+      </c>
+      <c r="AC522" t="inlineStr"/>
+      <c r="AD522" t="inlineStr">
+        <is>
+          <t>033-550-2674</t>
+        </is>
+      </c>
+      <c r="AE522" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF522" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125662</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>[세종] 2026년 세종시 중소기업 정보보호 지원 사업 수요기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>세종테크노파크</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-18</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>온라인 접수(지역정보보호센터)</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>※ 보안 패키지는 최대 정부지원금 한도 내 지원(IT보안패키지 480만원, SECaaS 패키지 360만원)</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>480만원</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr"/>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z523" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA523" t="inlineStr">
+        <is>
+          <t>에 허위 사실을 기재하거나 기타 부정한 방법으로, 신청한 기업, 참여가 제한된 기업 또는 과학기술정보통신부 장관, 한국인터넷진흥원, &lt; 신청 시 유의사항 &gt;, 협약 해지, 지원금 환수 등 필요한 조치를 할 수 있음, 지원 내용</t>
+        </is>
+      </c>
+      <c r="AB523" t="inlineStr">
+        <is>
+          <t>세종테크노파크 세종정보보호지원센터 044-850-3828, 3837, jylim@sjtp.or.kr, audrnr1114@sjtp.or.kr / 한국인터넷진흥원 02-405-5031, risc@kisa.or.kr</t>
+        </is>
+      </c>
+      <c r="AC523" t="inlineStr">
+        <is>
+          <t>audrnr1114@sjtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD523" t="inlineStr">
+        <is>
+          <t>02-405-5031</t>
+        </is>
+      </c>
+      <c r="AE523" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF523" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125661</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>[경북] 구미시 2026년 예비수소전문기업 육성 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>포항테크노파크</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>온라인 접수 (포항테크노파크)
+※ 사업신청 등록 시 한글파일 양식(hwp)으로 업로드 필수</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>◦ 지원규모: 금228000000원(금이억이천팔백만원)</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>228000000원</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr"/>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z524" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA524" t="inlineStr">
+        <is>
+          <t>지원신청서1) 및 기타 증빙자료, No 서식명 해당여부, ① 사업계획서 1부, [서식 제1호] 필수, ② 기업부담금 현금출자 확약서 1부, [서식 제2호] 필수, ③ 평가결과 수락 확약서 1부, [서식 제3호] 필수</t>
+        </is>
+      </c>
+      <c r="AB524" t="inlineStr">
+        <is>
+          <t>포항테크노파크 에너지사업본부 수소특화단지추진단 054-223-2268, minss@ptp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC524" t="inlineStr">
+        <is>
+          <t>minss@ptp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD524" t="inlineStr">
+        <is>
+          <t>054-223-2268</t>
+        </is>
+      </c>
+      <c r="AE524" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF524" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125660</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>[충남] 지역에너지 문제해결 프로젝트 지원사업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>충남테크노파크</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>이메일 접수 (yoke624@ctp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>◦ 지원규모 : 1개 과제, 기업당 최대 20백만원 이내 지원</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>20백만원</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z525" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA525" t="inlineStr">
+        <is>
+          <t>연번, 부수 비고, 신청서 및 계획서 각 1부 양식1, 협력기업 참여의사 확인서 1부 양식3(해당 시), 국가연구개발사업 참여제한 여부 확인서 1부 양식4, 개인정보활용 동의서 1부 양식5, 중소·중견기업 확인서 1부, 사업관련 유의사항</t>
+        </is>
+      </c>
+      <c r="AB525" t="inlineStr">
+        <is>
+          <t>충남테크노파크 그린산업본부 탄소중립산업센터 041-337-7951, yoke624@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC525" t="inlineStr">
+        <is>
+          <t>yoke624@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD525" t="inlineStr">
+        <is>
+          <t>041-337-7951</t>
+        </is>
+      </c>
+      <c r="AE525" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF525" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125659</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026년 춘천시 일자리박람회 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>2026-08-05 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>방문 또는 이메일 접수
+- 접수처 : 춘천시 기업지원과 일자리창출팀
+- 이메일 : ccjob3782@korea.kr
+- 온라인 : 구글폼</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="inlineStr"/>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z526" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA526" t="inlineStr"/>
+      <c r="AB526" t="inlineStr">
+        <is>
+          <t>춘천시 일자리지원센터 033-250-3782, 3357, 3778</t>
+        </is>
+      </c>
+      <c r="AC526" t="inlineStr">
+        <is>
+          <t>ccjob3782@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD526" t="inlineStr">
+        <is>
+          <t>033-250-3782</t>
+        </is>
+      </c>
+      <c r="AE526" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF526" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125658</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>[충남] 2026년 에너지기술공유대학 산학공동 에너지프로젝트 지원사업 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>충남테크노파크</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>이메일 접수 (yoke624@ctp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>◦ 지원규모 : 2개 과제 내외, 기업당 최대 15백만원 이내 지원</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>15백만원</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z527" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA527" t="inlineStr">
+        <is>
+          <t>연번, 부수 비고, 신청서 및 계획서 각 1부 양식1, 협력기업 참여의사 확인서 1부 양식3(해당 시), 국가연구개발사업 참여제한 여부 확인서 1부 양식4, 개인정보활용 동의서 1부 양식5, 중소·중견기업 확인서 1부, 구실별 주요 연구분야 참고)</t>
+        </is>
+      </c>
+      <c r="AB527" t="inlineStr">
+        <is>
+          <t>충남테크노파크 그린산업본부 탄소중립산업센터 041-337-7951, yoke624@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC527" t="inlineStr">
+        <is>
+          <t>yoke624@ctp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD527" t="inlineStr">
+        <is>
+          <t>041-337-7951</t>
+        </is>
+      </c>
+      <c r="AE527" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF527" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125657</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>[경기] 연천군 2026년 HACCP 시설개선 및 컨설팅 지원사업 추가 공고</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>2026-08-17 ~ 2026-08-24</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>방문 또는 우편 접수
+- 접수처 : (11017) 경기도 연천군 연천읍 연천로 220 연천군청 경제교통과</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>­ 거짓 신청이나 그 밖의 부정한 방법으로 지방보조금을 교부받은 자와 그 사실을 알면서 지방보조금을 교부한 자는 5년 이하의 징역 또는 3천만원 이하 벌금 부과</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>3천만원</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr"/>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z528" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA528" t="inlineStr">
+        <is>
+          <t>를 허위로 제출하였거나 부정한 방법으로 신청한 경우, ▢ 지원금액, 총 지원한도: 기업당 최대 10, 천원, 위생안전 시설 및 장비 구입비, • 총 사업비의 75% 이내 지원, • 현물 부담은 기업부담금 미인정, 컨설팅 비용</t>
+        </is>
+      </c>
+      <c r="AB528" t="inlineStr">
+        <is>
+          <t>경제교통과 기업지원팀 031-839-2281</t>
+        </is>
+      </c>
+      <c r="AC528" t="inlineStr"/>
+      <c r="AD528" t="inlineStr">
+        <is>
+          <t>031-839-2281</t>
+        </is>
+      </c>
+      <c r="AE528" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF528" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125656</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>[대구] 2027년 지역 의료기기 토탈 마케팅 지원사업 WHX Dubai 2027 대구공동관 참가기업 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>대구테크노파크</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-10</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>온라인 접수 (대구수출입지원시스템)</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>❍ 최종 선정된 기업은 (재)대구테크노파크에서 요청하는 자료 제출, 점검 및</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr"/>
+      <c r="G529" t="inlineStr"/>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z529" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA529" t="inlineStr">
+        <is>
+          <t>­ 아래, 를 대구수출입지원시스템에 업로드, 구분, [서식 1] 지원신청서 1부, [서식 2] 사업계획서 1부, [서식 3] 기업 현황 1부, [서식 4] 공동관 참가 규정 및 동의서 1부, [서식 5] 사업 참여 및 중복지원금지 확약서 1부</t>
+        </is>
+      </c>
+      <c r="AB529" t="inlineStr">
+        <is>
+          <t>대구테크노파크 의료바이오본부 (사업수행 문의ㆍ평가 문의) 053-602-1811, 38317ajj@dgtp.or.kr (사업수행 문의) 053-602-1822, roobie87@dgtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC529" t="inlineStr">
+        <is>
+          <t>38317ajj@dgtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD529" t="inlineStr">
+        <is>
+          <t>053-602-1811</t>
+        </is>
+      </c>
+      <c r="AE529" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF529" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125655</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>[경기] 양주시 2026년 해외전시회 참가기업 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>이메일 접수(gbesc@kintex.com)</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>○ 지원규모 : 1개사 내외 (모집현황 및 예산상황에 따라 변동될 수 있음)</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z530" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA530" t="inlineStr"/>
+      <c r="AB530" t="inlineStr">
+        <is>
+          <t>킨텍스 경기도기업전시센터 031-995-8518, 8516 / gbesc@kintex.com 양주시 기업지원과 031-8082-6013</t>
+        </is>
+      </c>
+      <c r="AC530" t="inlineStr">
+        <is>
+          <t>gbesc@kintex.com</t>
+        </is>
+      </c>
+      <c r="AD530" t="inlineStr">
+        <is>
+          <t>031-8082-6013</t>
+        </is>
+      </c>
+      <c r="AE530" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF530" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125654</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>[경기] 광주시 2026년 소상공인 경영환경개선사업 신청자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>이메일, 방문, 우편 접수
+- 접수처 : 경기도 광주시 행정타운로 50, 광주시청 지역경제과 지역경제팀(의회동 3층)
+- 이메일 : sjp5335@korea.kr
+※ 우편접수의 경우 신청기간 내 우체국 소인분 인정
+※ 이메일 접수 시에도 신청서 등에 서명 필수(서식 출력 작성 후 스캔본 권장)</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>최대 200~300만원</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>300만원</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr"/>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q531" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z531" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA531" t="inlineStr">
+        <is>
+          <t>의 누락, 미비 등으로 인한 불이익은 신청자 본인에게 있으며, 년~2026년, 소상공인시장진흥공단 및 경기도, 타 시·군에서 동일, 유사, 지원제외 및 선정취소), 시공(제작)은 선정 후 진행 필수</t>
+        </is>
+      </c>
+      <c r="AB531" t="inlineStr">
+        <is>
+          <t>광주시청 지역경제과 지역경제팀 031-760-4734</t>
+        </is>
+      </c>
+      <c r="AC531" t="inlineStr">
+        <is>
+          <t>sjp5335@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD531" t="inlineStr">
+        <is>
+          <t>031-760-4734</t>
+        </is>
+      </c>
+      <c r="AE531" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF531" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125652</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>[경기] 양주시 2027년 기업환경 개선사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-03</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>방문, 우편, 이메일 접수 
+- 접수처 : (11498) 양주시 부흥로 1533, 기업지원과 기업섬유지원팀
+- 이메일 : dwyj@korea.kr</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>총사업비 7억원 이내(도비 2억원 이내)</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>7억원</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr"/>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q532" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z532" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA532" t="inlineStr">
+        <is>
+          <t>(필수), 작성 방법 및 제출 용도, 발급처, 공통, 제출, 사업계획서, • 사업내용을 구체적으로 작성하여 한글파일로 제출, 서식</t>
+        </is>
+      </c>
+      <c r="AB532" t="inlineStr">
+        <is>
+          <t>양주시청 기업지원과 기업섬유지원팀 031-8082-6012</t>
+        </is>
+      </c>
+      <c r="AC532" t="inlineStr">
+        <is>
+          <t>dwyj@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD532" t="inlineStr">
+        <is>
+          <t>031-8082-6012</t>
+        </is>
+      </c>
+      <c r="AE532" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF532" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125651</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>[인천] 인천형 특별 경영안전자금 지원사업 NH농협은행 협업 자금 추가 지원 변경 공고</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>인천테크노파크</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>온라인 접수 (비즈오케이)</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>지원 규모: 1070억원</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>1070억원</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr"/>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z533" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA533" t="inlineStr">
+        <is>
+          <t>구 분 서류 및 요건, 신청일 기준 1년 이내 발급분, 제조면적 500㎡ 이상 : 공장등록증, 제조업소) 및 임대차계약서(임차시必), 제조관련업 등록증 및 인․허가증, 우대 관련 증빙서류 우대 조건 해당 시 관련 증빙서류, 지원절차, 사전상담 : 기존 지원이력</t>
+        </is>
+      </c>
+      <c r="AB533" t="inlineStr">
+        <is>
+          <t>인천테크노파크 경영지원센터 032-260-0661~0664</t>
+        </is>
+      </c>
+      <c r="AC533" t="inlineStr"/>
+      <c r="AD533" t="inlineStr">
+        <is>
+          <t>032-260-0661</t>
+        </is>
+      </c>
+      <c r="AE533" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF533" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125650</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>[경기] 이천시 2026년 국내박람회 참가지원 사업 홈테이블데코페어 서울 참가업체 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>이메일 접수(naraah@korea.kr)</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>165만원(부가세포함)</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>165만원</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr"/>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z534" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA534" t="inlineStr">
+        <is>
+          <t>(공고일 이후 발급), 지원 취소됨, 중도철수, ❍ 기타문의 : 이천시청, 관광과 공예팀, 붙임1, 년 이천시 국내박람회 참가지원 사업 신청서, 이천시 국내박람회 참가지원 사업 -</t>
+        </is>
+      </c>
+      <c r="AB534" t="inlineStr">
+        <is>
+          <t>이천시청 관광과 공예팀 031-645-3668</t>
+        </is>
+      </c>
+      <c r="AC534" t="inlineStr">
+        <is>
+          <t>naraah@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD534" t="inlineStr">
+        <is>
+          <t>031-645-3668</t>
+        </is>
+      </c>
+      <c r="AE534" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF534" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125648</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>[충남] 2026년 천안 그린스타트업타운 스케일업 프로그램 충남 대학생 창업경진대회 참여자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>충남콘텐츠진흥원</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>이메일 접수 (greenstartuptown@gmail.com)</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>역량을 함양하고, 우수팀 5팀 선발을 통해 최대 2백만 원 상금 시상하는 창업</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>2백만원</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr"/>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z535" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA535" t="inlineStr">
+        <is>
+          <t>한 폴더로 압축 후 전달, ※ 폴더명: 충남대학생창업경진대회_팀명, 연번 구분, 제출 내용, ⦁참가신청서, 개인정보 수집 및 이용·제공 동의서, 서약서, 필수 참가신청서</t>
+        </is>
+      </c>
+      <c r="AB535" t="inlineStr">
+        <is>
+          <t>GST 스케일업 프로그램 운영사무국 041-589-7113, greenstartuptown@gmail.com</t>
+        </is>
+      </c>
+      <c r="AC535" t="inlineStr">
+        <is>
+          <t>greenstartuptown@gmail.com</t>
+        </is>
+      </c>
+      <c r="AD535" t="inlineStr">
+        <is>
+          <t>041-589-7113</t>
+        </is>
+      </c>
+      <c r="AE535" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF535" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125647</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>[경기] 시흥시 2027년 기업환경 개선사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>2026-08-31 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>우편 또는 방문 접수
+- 접수처 : 시흥시 시청로 20 (장현동) 시흥시청 4층 기업지원과
+※ 2026. 9. 11.(금) 18시 도착분에 한함</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>&lt;노동 복지&gt;&lt;노동 환경&gt;&lt;매출액 200억원 이하중소기업(제조업)&gt;&lt;12&gt;&lt;기숙사, 식당, 화장실, 샤워실, 휴게공간 등 ※ 매칭비율 : 기업 순이익별 차등 보조 (자부담 20%~30% 이상)&gt;&lt;지식산업센터&gt;&lt;준공 후 7년 이상경과 된 지식산업센터&gt;&lt;18&gt;&lt;노후 주차장 및 화장실, 공공시설물 등 ※ 매칭 비율 : 도비24% 시비56% 자부담 20% 이상&gt;</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>200억원</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr"/>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z536" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA536" t="inlineStr"/>
+      <c r="AB536" t="inlineStr">
+        <is>
+          <t>시흥시청 기업지원과 기업지원팀 031-310-6096</t>
+        </is>
+      </c>
+      <c r="AC536" t="inlineStr"/>
+      <c r="AD536" t="inlineStr">
+        <is>
+          <t>031-310-6096</t>
+        </is>
+      </c>
+      <c r="AE536" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF536" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125646</t>
         </is>
       </c>
     </row>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -75474,7 +75474,6 @@
           <t>1000억원</t>
         </is>
       </c>
-      <c r="G488" t="inlineStr"/>
       <c r="H488" t="inlineStr">
         <is>
           <t>N</t>
@@ -75570,7 +75569,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA488" t="inlineStr"/>
       <c r="AB488" t="inlineStr">
         <is>
           <t>해양수산과학기술진흥원 산업정책실 창업투자팀 02-3460-0376, dbtmf123@kimst.re.kr</t>
@@ -75623,8 +75621,6 @@
           <t>❍ 지원규모</t>
         </is>
       </c>
-      <c r="F489" t="inlineStr"/>
-      <c r="G489" t="inlineStr"/>
       <c r="H489" t="inlineStr">
         <is>
           <t>Y</t>
@@ -75782,7 +75778,6 @@
           <t>1300만원</t>
         </is>
       </c>
-      <c r="G490" t="inlineStr"/>
       <c r="H490" t="inlineStr">
         <is>
           <t>Y</t>
@@ -75888,7 +75883,6 @@
           <t>성남산업진흥원 글로벌마케팅 031-782-3061, 031-782-3065</t>
         </is>
       </c>
-      <c r="AC490" t="inlineStr"/>
       <c r="AD490" t="inlineStr">
         <is>
           <t>031-782-3061</t>
@@ -75931,7 +75925,6 @@
           <t>❍ 모집규모 : 2개사</t>
         </is>
       </c>
-      <c r="F491" t="inlineStr"/>
       <c r="G491" t="inlineStr">
         <is>
           <t>2개</t>
@@ -76032,7 +76025,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA491" t="inlineStr"/>
       <c r="AB491" t="inlineStr">
         <is>
           <t>강원특별자치도 경제진흥원 033-749-3362, jaesub2019@naver.com</t>
@@ -76190,7 +76182,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA492" t="inlineStr"/>
       <c r="AB492" t="inlineStr">
         <is>
           <t>화성산업진흥원 안전기획팀 031-278-6465, jhpark@hsbiz.or.kr</t>
@@ -76243,8 +76234,6 @@
           <t>지원 내용</t>
         </is>
       </c>
-      <c r="F493" t="inlineStr"/>
-      <c r="G493" t="inlineStr"/>
       <c r="H493" t="inlineStr">
         <is>
           <t>Y</t>
@@ -76340,7 +76329,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA493" t="inlineStr"/>
       <c r="AB493" t="inlineStr">
         <is>
           <t>한식페스타 사무국 02-550-2557, hansikfesta@hansik.or.kr</t>
@@ -76394,8 +76382,6 @@
           <t>※선정 이후라도 동일·유사 사업 중복 지원이 확인될 경우 선정 취소, 보조금 결정 취소 및 환수 등 필요한 조치를 할 수 있음</t>
         </is>
       </c>
-      <c r="F494" t="inlineStr"/>
-      <c r="G494" t="inlineStr"/>
       <c r="H494" t="inlineStr">
         <is>
           <t>Y</t>
@@ -76501,7 +76487,6 @@
           <t>거제시청 조선지원과 노동자지원팀 055-639-4453</t>
         </is>
       </c>
-      <c r="AC494" t="inlineStr"/>
       <c r="AD494" t="inlineStr">
         <is>
           <t>055-639-4453</t>
@@ -76707,8 +76692,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F496" t="inlineStr"/>
-      <c r="G496" t="inlineStr"/>
       <c r="H496" t="inlineStr">
         <is>
           <t>N</t>
@@ -76804,13 +76787,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA496" t="inlineStr"/>
       <c r="AB496" t="inlineStr">
         <is>
           <t>전남사회적통합지원센터 061-741-9943</t>
         </is>
       </c>
-      <c r="AC496" t="inlineStr"/>
       <c r="AD496" t="inlineStr">
         <is>
           <t>061-741-9943</t>
@@ -76861,7 +76842,6 @@
           <t>3백만원</t>
         </is>
       </c>
-      <c r="G497" t="inlineStr"/>
       <c r="H497" t="inlineStr">
         <is>
           <t>Y</t>
@@ -77015,7 +76995,6 @@
           <t>○ 지원규모 : 전남광주통합특별시 사회연대경제기업 50개소</t>
         </is>
       </c>
-      <c r="F498" t="inlineStr"/>
       <c r="G498" t="inlineStr">
         <is>
           <t>50개</t>
@@ -77178,7 +77157,6 @@
           <t>28백만원</t>
         </is>
       </c>
-      <c r="G499" t="inlineStr"/>
       <c r="H499" t="inlineStr">
         <is>
           <t>Y</t>
@@ -77336,7 +77314,6 @@
           <t>2억원</t>
         </is>
       </c>
-      <c r="G500" t="inlineStr"/>
       <c r="H500" t="inlineStr">
         <is>
           <t>Y</t>
@@ -77442,7 +77419,6 @@
           <t>(시스템 문의) 국번없이 1357 / (사업문의) 주관기관 담당자 공고문 참조</t>
         </is>
       </c>
-      <c r="AC500" t="inlineStr"/>
       <c r="AD500" t="inlineStr">
         <is>
           <t>042-350-4732</t>
@@ -77490,7 +77466,6 @@
           <t>1천만원</t>
         </is>
       </c>
-      <c r="G501" t="inlineStr"/>
       <c r="H501" t="inlineStr">
         <is>
           <t>N</t>
@@ -77596,7 +77571,6 @@
           <t>경기창조경제혁신센터 창업육성팀 031-780-9048</t>
         </is>
       </c>
-      <c r="AC501" t="inlineStr"/>
       <c r="AD501" t="inlineStr">
         <is>
           <t>031-780-9048</t>
@@ -77644,7 +77618,6 @@
           <t>3000만원</t>
         </is>
       </c>
-      <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr">
         <is>
           <t>Y</t>
@@ -77802,7 +77775,6 @@
           <t>1500만원</t>
         </is>
       </c>
-      <c r="G503" t="inlineStr"/>
       <c r="H503" t="inlineStr">
         <is>
           <t>Y</t>
@@ -77962,7 +77934,6 @@
           <t>5억원</t>
         </is>
       </c>
-      <c r="G504" t="inlineStr"/>
       <c r="H504" t="inlineStr">
         <is>
           <t>N</t>
@@ -78058,13 +78029,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA504" t="inlineStr"/>
       <c r="AB504" t="inlineStr">
         <is>
           <t>경기신용보증재단 고객센터 대표번호 1577-5900 및 지점별 문의처 공고문 3p참조</t>
         </is>
       </c>
-      <c r="AC504" t="inlineStr"/>
       <c r="AD504" t="inlineStr">
         <is>
           <t>01 070-7614</t>
@@ -78274,7 +78243,6 @@
           <t>800만원</t>
         </is>
       </c>
-      <c r="G506" t="inlineStr"/>
       <c r="H506" t="inlineStr">
         <is>
           <t>Y</t>
@@ -78380,7 +78348,6 @@
           <t>화성시청 기업지원과 031-5189-6938</t>
         </is>
       </c>
-      <c r="AC506" t="inlineStr"/>
       <c r="AD506" t="inlineStr">
         <is>
           <t>031-5189-6938</t>
@@ -78431,7 +78398,6 @@
           <t>1원</t>
         </is>
       </c>
-      <c r="G507" t="inlineStr"/>
       <c r="H507" t="inlineStr">
         <is>
           <t>Y</t>
@@ -78751,7 +78717,6 @@
           <t>50만원</t>
         </is>
       </c>
-      <c r="G509" t="inlineStr"/>
       <c r="H509" t="inlineStr">
         <is>
           <t>N</t>
@@ -78847,7 +78812,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA509" t="inlineStr"/>
       <c r="AB509" t="inlineStr">
         <is>
           <t>중소벤처기업진흥공단 카자흐스탄 알마티GBC +7-727-274-2500, sukyk@kosmes.or.kr</t>
@@ -78858,7 +78822,6 @@
           <t>sukyk@kosmes.or.kr</t>
         </is>
       </c>
-      <c r="AD509" t="inlineStr"/>
       <c r="AE509" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -78903,7 +78866,6 @@
           <t>80만원</t>
         </is>
       </c>
-      <c r="G510" t="inlineStr"/>
       <c r="H510" t="inlineStr">
         <is>
           <t>Y</t>
@@ -79218,8 +79180,6 @@
           <t>※ 최종 선정기업 대상 일시 개별 안내 예정</t>
         </is>
       </c>
-      <c r="F512" t="inlineStr"/>
-      <c r="G512" t="inlineStr"/>
       <c r="H512" t="inlineStr">
         <is>
           <t>N</t>
@@ -79315,7 +79275,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA512" t="inlineStr"/>
       <c r="AB512" t="inlineStr">
         <is>
           <t>부산창조경제혁신센터 창업육성팀 051-749-8963, wlszh19@ccei.kr</t>
@@ -79375,7 +79334,6 @@
           <t>1억원</t>
         </is>
       </c>
-      <c r="G513" t="inlineStr"/>
       <c r="H513" t="inlineStr">
         <is>
           <t>N</t>
@@ -79481,7 +79439,6 @@
           <t>충청남도 경제통상국 소상공경제정책과 041-635-3318 및 시ㆍ군 전통시장 지원업무 담당 부서 문의(공고문 5p 참조)</t>
         </is>
       </c>
-      <c r="AC513" t="inlineStr"/>
       <c r="AD513" t="inlineStr">
         <is>
           <t>041-635-3318</t>
@@ -79529,7 +79486,6 @@
           <t>300만원</t>
         </is>
       </c>
-      <c r="G514" t="inlineStr"/>
       <c r="H514" t="inlineStr">
         <is>
           <t>Y</t>
@@ -79635,8 +79591,6 @@
           <t>서울특별시여성가족재단(대행기관) 대표전화1660-3040, 3번 기업</t>
         </is>
       </c>
-      <c r="AC514" t="inlineStr"/>
-      <c r="AD514" t="inlineStr"/>
       <c r="AE514" t="inlineStr">
         <is>
           <t>중소기업</t>
@@ -79682,7 +79636,6 @@
           <t>1000만원</t>
         </is>
       </c>
-      <c r="G515" t="inlineStr"/>
       <c r="H515" t="inlineStr">
         <is>
           <t>Y</t>
@@ -79840,7 +79793,6 @@
           <t>500만원</t>
         </is>
       </c>
-      <c r="G516" t="inlineStr"/>
       <c r="H516" t="inlineStr">
         <is>
           <t>Y</t>
@@ -79996,8 +79948,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F517" t="inlineStr"/>
-      <c r="G517" t="inlineStr"/>
       <c r="H517" t="inlineStr">
         <is>
           <t>N</t>
@@ -80155,7 +80105,6 @@
           <t>17백만원</t>
         </is>
       </c>
-      <c r="G518" t="inlineStr"/>
       <c r="H518" t="inlineStr">
         <is>
           <t>Y</t>
@@ -80261,7 +80210,6 @@
           <t>K-water 물산업혁신처 042-629-2515, 2513</t>
         </is>
       </c>
-      <c r="AC518" t="inlineStr"/>
       <c r="AD518" t="inlineStr">
         <is>
           <t>042-629-2515</t>
@@ -80304,8 +80252,6 @@
           <t>지원내용</t>
         </is>
       </c>
-      <c r="F519" t="inlineStr"/>
-      <c r="G519" t="inlineStr"/>
       <c r="H519" t="inlineStr">
         <is>
           <t>N</t>
@@ -80458,8 +80404,6 @@
           <t>© 모집규모</t>
         </is>
       </c>
-      <c r="F520" t="inlineStr"/>
-      <c r="G520" t="inlineStr"/>
       <c r="H520" t="inlineStr">
         <is>
           <t>N</t>
@@ -80555,7 +80499,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA520" t="inlineStr"/>
       <c r="AB520" t="inlineStr">
         <is>
           <t>오엠인터랙티브 070-8633-5400, semd@omin.co.kr 한국중소벤처기업유통원 02-6678-9368, 9364</t>
@@ -80613,7 +80556,6 @@
           <t>1억원</t>
         </is>
       </c>
-      <c r="G521" t="inlineStr"/>
       <c r="H521" t="inlineStr">
         <is>
           <t>Y</t>
@@ -80719,7 +80661,6 @@
           <t>(사업 문의) 충북창조경제혁신센터 043-710-5932 (시스템 문의) 중소기업통합콜센터 국번없이 1357</t>
         </is>
       </c>
-      <c r="AC521" t="inlineStr"/>
       <c r="AD521" t="inlineStr">
         <is>
           <t>043-710-5932</t>
@@ -80763,8 +80704,6 @@
           <t>지원 내용 및 지원시기</t>
         </is>
       </c>
-      <c r="F522" t="inlineStr"/>
-      <c r="G522" t="inlineStr"/>
       <c r="H522" t="inlineStr">
         <is>
           <t>N</t>
@@ -80870,7 +80809,6 @@
           <t>태백시 농업기술센터 농업과 농업정책팀 033-550-2721 / 업무담당자 033-550-2674</t>
         </is>
       </c>
-      <c r="AC522" t="inlineStr"/>
       <c r="AD522" t="inlineStr">
         <is>
           <t>033-550-2674</t>
@@ -80918,7 +80856,6 @@
           <t>480만원</t>
         </is>
       </c>
-      <c r="G523" t="inlineStr"/>
       <c r="H523" t="inlineStr">
         <is>
           <t>Y</t>
@@ -81077,7 +81014,6 @@
           <t>228000000원</t>
         </is>
       </c>
-      <c r="G524" t="inlineStr"/>
       <c r="H524" t="inlineStr">
         <is>
           <t>Y</t>
@@ -81395,8 +81331,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F526" t="inlineStr"/>
-      <c r="G526" t="inlineStr"/>
       <c r="H526" t="inlineStr">
         <is>
           <t>N</t>
@@ -81492,7 +81426,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA526" t="inlineStr"/>
       <c r="AB526" t="inlineStr">
         <is>
           <t>춘천시 일자리지원센터 033-250-3782, 3357, 3778</t>
@@ -81713,7 +81646,6 @@
           <t>3천만원</t>
         </is>
       </c>
-      <c r="G528" t="inlineStr"/>
       <c r="H528" t="inlineStr">
         <is>
           <t>Y</t>
@@ -81819,7 +81751,6 @@
           <t>경제교통과 기업지원팀 031-839-2281</t>
         </is>
       </c>
-      <c r="AC528" t="inlineStr"/>
       <c r="AD528" t="inlineStr">
         <is>
           <t>031-839-2281</t>
@@ -81862,8 +81793,6 @@
           <t>❍ 최종 선정된 기업은 (재)대구테크노파크에서 요청하는 자료 제출, 점검 및</t>
         </is>
       </c>
-      <c r="F529" t="inlineStr"/>
-      <c r="G529" t="inlineStr"/>
       <c r="H529" t="inlineStr">
         <is>
           <t>Y</t>
@@ -82016,7 +81945,6 @@
           <t>○ 지원규모 : 1개사 내외 (모집현황 및 예산상황에 따라 변동될 수 있음)</t>
         </is>
       </c>
-      <c r="F530" t="inlineStr"/>
       <c r="G530" t="inlineStr">
         <is>
           <t>1개</t>
@@ -82117,7 +82045,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA530" t="inlineStr"/>
       <c r="AB530" t="inlineStr">
         <is>
           <t>킨텍스 경기도기업전시센터 031-995-8518, 8516 / gbesc@kintex.com 양주시 기업지원과 031-8082-6013</t>
@@ -82179,7 +82106,6 @@
           <t>300만원</t>
         </is>
       </c>
-      <c r="G531" t="inlineStr"/>
       <c r="H531" t="inlineStr">
         <is>
           <t>Y</t>
@@ -82339,7 +82265,6 @@
           <t>7억원</t>
         </is>
       </c>
-      <c r="G532" t="inlineStr"/>
       <c r="H532" t="inlineStr">
         <is>
           <t>Y</t>
@@ -82497,7 +82422,6 @@
           <t>1070억원</t>
         </is>
       </c>
-      <c r="G533" t="inlineStr"/>
       <c r="H533" t="inlineStr">
         <is>
           <t>Y</t>
@@ -82603,7 +82527,6 @@
           <t>인천테크노파크 경영지원센터 032-260-0661~0664</t>
         </is>
       </c>
-      <c r="AC533" t="inlineStr"/>
       <c r="AD533" t="inlineStr">
         <is>
           <t>032-260-0661</t>
@@ -82651,7 +82574,6 @@
           <t>165만원</t>
         </is>
       </c>
-      <c r="G534" t="inlineStr"/>
       <c r="H534" t="inlineStr">
         <is>
           <t>Y</t>
@@ -82809,7 +82731,6 @@
           <t>2백만원</t>
         </is>
       </c>
-      <c r="G535" t="inlineStr"/>
       <c r="H535" t="inlineStr">
         <is>
           <t>N</t>
@@ -82969,7 +82890,6 @@
           <t>200억원</t>
         </is>
       </c>
-      <c r="G536" t="inlineStr"/>
       <c r="H536" t="inlineStr">
         <is>
           <t>N</t>
@@ -83065,13 +82985,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA536" t="inlineStr"/>
       <c r="AB536" t="inlineStr">
         <is>
           <t>시흥시청 기업지원과 기업지원팀 031-310-6096</t>
         </is>
       </c>
-      <c r="AC536" t="inlineStr"/>
       <c r="AD536" t="inlineStr">
         <is>
           <t>031-310-6096</t>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF536"/>
+  <dimension ref="A1:AF586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83006,6 +83006,7778 @@
         </is>
       </c>
     </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>[경남] 진주시 2026년 기업환경개선사업 참여 기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-09-03</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 진주시 동진로 271(상대동) 1층 (진주여성새로일하기센터)</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>개 업체당 최대 5백만원 한도 내에서 총사업비의 70%까지 지원</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>5백만원</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr"/>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z537" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA537" t="inlineStr">
+        <is>
+          <t>신청, 부(원본1부, 사본 4부), ① 기업환경개선사업 신청서, 【붙임 1-1~2】, ④ 여성근로자 및 여성복지 현황표, 【붙임 3】, ⑤ 여성친화 진단 측정 지표</t>
+        </is>
+      </c>
+      <c r="AB537" t="inlineStr">
+        <is>
+          <t>진주여성새로일하기센터 055-749-8528</t>
+        </is>
+      </c>
+      <c r="AC537" t="inlineStr"/>
+      <c r="AD537" t="inlineStr">
+        <is>
+          <t>055-749-8528</t>
+        </is>
+      </c>
+      <c r="AE537" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF537" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125747</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>[부산] 2026년 청년 일경험 지원사업(인턴형) 인턴십 프로그램 참여기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>부산디자인진흥원</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>이메일 접수 (work@dcb.or.kr)</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>❍ 참여기업지원금 : 인턴 1인당 12주 60만원</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>60만원</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr"/>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z538" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA538" t="inlineStr">
+        <is>
+          <t>에 대한 서류평가※ 필요시, 발표 평가할 수 있음, ❍ 평가기준 : 기업역량, 일경험 프로그램 적정성, 참여청년 역량강화 노력, 기대효과, ❍ 선정절차 및 일정, 모집공고 선정심사 최종선정 설명회 및 협약체결</t>
+        </is>
+      </c>
+      <c r="AB538" t="inlineStr">
+        <is>
+          <t>부산디자인진흥원 051-790-1072, 1076, work@dcb.or.kr</t>
+        </is>
+      </c>
+      <c r="AC538" t="inlineStr">
+        <is>
+          <t>work@dcb.or.kr</t>
+        </is>
+      </c>
+      <c r="AD538" t="inlineStr">
+        <is>
+          <t>051-790-1072</t>
+        </is>
+      </c>
+      <c r="AE538" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF538" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125746</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>블록체인 기업 맞춤형 보안 고도화 지원 기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>한국인터넷진흥원</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>온라인 접수 (신청폼)</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr"/>
+      <c r="G539" t="inlineStr"/>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z539" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA539" t="inlineStr"/>
+      <c r="AB539" t="inlineStr">
+        <is>
+          <t>㈜씨드젠, ㈜78리서치랩 02-6951-3739, blockchain26@seedgen.kr</t>
+        </is>
+      </c>
+      <c r="AC539" t="inlineStr">
+        <is>
+          <t>blockchain26@seedgen.kr</t>
+        </is>
+      </c>
+      <c r="AD539" t="inlineStr">
+        <is>
+          <t>02-6951-3739</t>
+        </is>
+      </c>
+      <c r="AE539" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF539" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125745</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>[경남] 산청군 2026년 음식점 대상 주방 위생환경개선 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 한국외식업중앙회 경상남도지회 산청군지부 (경남 산청군 산청읍 꽃봉산로91번길 9 1층)</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>제37조(벌칙) 거짓 신청이나 그 밖의 부정한 방법으로 지방보조금을 교부받은 자 또는 그 사실을 알면서                지방보조금을 교부한 자는 10년 이하의 징역 또는 1억원 이하의 벌금에 처한다.</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>1억원</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr"/>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z540" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA540" t="inlineStr">
+        <is>
+          <t>나., 사업신청서 1부[서식 1-1], 사업계획서 1부[서식 1-2], 견적서 2부(본 견적서, 비교견적서), 주민등록초본 1부, 개인정보동의서 1부[서식 1-3], 건물주 동의서 1부(건물임대자일 경우)[서식 1-4]</t>
+        </is>
+      </c>
+      <c r="AB540" t="inlineStr">
+        <is>
+          <t>산청군청 환경위생과 위생담당 055-970-7152</t>
+        </is>
+      </c>
+      <c r="AC540" t="inlineStr"/>
+      <c r="AD540" t="inlineStr">
+        <is>
+          <t>055-970-7152</t>
+        </is>
+      </c>
+      <c r="AE540" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF540" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125744</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>[경남] 산청군 2026년 4차 산업단지 등 기숙사 임차 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>방문 또는 우편 접수
+- 접수처 : (우 52221) 경상남도 산청군 산청읍 산엔청로 1 산청군청 산청군 경제기업과 일자리창출담당</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>(단, 근로자 1명당 월 최대 30만원 한도)</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>30만원</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z541" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA541" t="inlineStr">
+        <is>
+          <t>① [서식1] 기숙사 임차 지원사업 참여신청서 1부, ② [서식2] 기숙사 임차지원금 대상 근로자 명부 1부, ③ [서식3] 개인정보 수집·이용 동의서 1부, ⑥ 대표자 가족관계증명서 1부, ⑦ 4대보험 사업장 가입자 명부(신청일 기준, 사업장 전체 근로자) 1부, ⑧ 대상 근로자 근로계약서 사본 및 재직증명서 각 1부, ⑩ 기숙사 임대차계약서 사본(관리비 등 명시) 1부</t>
+        </is>
+      </c>
+      <c r="AB541" t="inlineStr">
+        <is>
+          <t>산청군 경제기업과 일자리창출담당 055-970-6812</t>
+        </is>
+      </c>
+      <c r="AC541" t="inlineStr"/>
+      <c r="AD541" t="inlineStr">
+        <is>
+          <t>055-970-6812</t>
+        </is>
+      </c>
+      <c r="AE541" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF541" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125743</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>[제주] 2026년 낙농가 한시적 특별융자 지원사업 대상자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-01</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 주소지 관할 읍ㆍ면사무소 및 동 주민센터</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>❍ 융자규모: 2800백만 원</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>2800백만원</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr"/>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S542" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z542" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA542" t="inlineStr">
+        <is>
+          <t>융자 신청 시 갖춰야 하는 각종, 「전자정부법」제36조, 제1항에 따라 행정정보공동이용을 통하여 확인하되, 행정정보를, 신청인으로부터 그 서류를 제출 받아 처리하여야 한다., (규칙 제5조 제2항), 구 분, 구 비 서 류</t>
+        </is>
+      </c>
+      <c r="AB542" t="inlineStr">
+        <is>
+          <t>제주특별자치도 친환경축산정책과 064-710-2123 제주시 청정축산과 064-728-3891, 3893 서귀포시 청정축산과 064-760-2661, 2662 주소지 읍·면사무소, 동주민센터(산업부서)</t>
+        </is>
+      </c>
+      <c r="AC542" t="inlineStr"/>
+      <c r="AD542" t="inlineStr">
+        <is>
+          <t>064-710-2123</t>
+        </is>
+      </c>
+      <c r="AE542" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF542" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125742</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>[경남] 하동군 2026년 3차 음식점 대상 주방 위생환경개선 지원사업 대상자 모집 공고</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-03</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 하동군보건소 임시청사 보건정책과 안전위생계 (적량면 공설운동장로 207)</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>※ (예시1) 사업비 200만원(지원금액 140만원(70%), 자부담 60만원(30%))</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>200만원</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr"/>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q543" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z543" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA543" t="inlineStr">
+        <is>
+          <t>(붙임 참고 :신청서식), 심사 및 선정, ❍ 심사기준 : 심사평가 기준표에 의거 배점부여, 음식점 주방 위생환경개선 지원 심사 평가표, 업소명, 영업자, (대표자), 연 락 처</t>
+        </is>
+      </c>
+      <c r="AB543" t="inlineStr">
+        <is>
+          <t>하동군 055-880-2354</t>
+        </is>
+      </c>
+      <c r="AC543" t="inlineStr"/>
+      <c r="AD543" t="inlineStr">
+        <is>
+          <t>055-880-2354</t>
+        </is>
+      </c>
+      <c r="AE543" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF543" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125741</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>[경남] 고성군 2026년 소상공인 소규모 경영환경 개선지원 사업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 고성군 경제기업과</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t> 지원금액 : 최대 200만원 지원</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>200만원</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr"/>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q544" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z544" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA544" t="inlineStr">
+        <is>
+          <t>(총 2회) - 1차 : 지원신청서(신청 및 계획), 차 : 지원금 신청서(완료보고시), 사각형입니다. 선정기준,  선정주체 : 고성군,  선정방법 : 평가표, [붙임1], 에 의해 고득점자 순 선정, 경영환경 개선지원</t>
+        </is>
+      </c>
+      <c r="AB544" t="inlineStr">
+        <is>
+          <t>고성군 경제기업과 지역경제담당 055-670-2304</t>
+        </is>
+      </c>
+      <c r="AC544" t="inlineStr"/>
+      <c r="AD544" t="inlineStr">
+        <is>
+          <t>055-670-2304</t>
+        </is>
+      </c>
+      <c r="AE544" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF544" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125740</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026년 미래혁신기술박람회 FIX 데이터 스페이스 기업공동관 참가기업 모집 공고(데이터 산업 성장 및 활성화 지원사업)</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>대구디지털혁신진흥원</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>이메일 접수 (dipjs@dip.or.kr)</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>산업통상자원부, 수출바우처, 지자체 등 타 기관 지원금(보조금)으로</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr"/>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z545" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA545" t="inlineStr"/>
+      <c r="AB545" t="inlineStr">
+        <is>
+          <t>대구디지털혁신진흥원 AX데이터활용센터 053-655-5610, dipjs@dip.or.kr</t>
+        </is>
+      </c>
+      <c r="AC545" t="inlineStr">
+        <is>
+          <t>dipjs@dip.or.kr</t>
+        </is>
+      </c>
+      <c r="AD545" t="inlineStr">
+        <is>
+          <t>053-655-5610</t>
+        </is>
+      </c>
+      <c r="AE545" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF545" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125739</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>[경남] 창녕군 2026년 3차 중소기업 근로자 기숙사 임차료 지원사업 시행 공고</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 창녕군청 일자리경제과 일자리지원팀</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>- 근로자 1인 월 최대 30만원 / 기업당 근로자 5명 이내</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>30만원</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q546" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S546" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z546" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA546" t="inlineStr">
+        <is>
+          <t>반환 불가, 원본 제출 - 사본일 경우 원본대조필 날인, ① [서식1] 기숙사 임차료 지원사업 참여신청서 1부, ③ [서식3] 개인정보 수집·이용 동의서 1부, ④ (참여기업) 대표자 가족관계증명서 1부, ⑦ (참여기업) 4대보험 사업장가입자명부(신청일 기준, 전체 근로자) 1부, ⑧ (참여기업) 중소기업 확인서(중소기업청 발급) 1부</t>
+        </is>
+      </c>
+      <c r="AB546" t="inlineStr">
+        <is>
+          <t>창녕군청 일자리경제과 일자리지원팀 055-530-1173</t>
+        </is>
+      </c>
+      <c r="AC546" t="inlineStr"/>
+      <c r="AD546" t="inlineStr">
+        <is>
+          <t>055-530-1173</t>
+        </is>
+      </c>
+      <c r="AE546" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF546" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125738</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>[제주] 소상공인 저금리 대환대출 특별보증 한시적 이차보전금 지원 공고</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>제주신용보증재단</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>온라인 접수(제주신용보증재단)</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>(업체당 한도 최대 1천만원, 1년 거치 4년 분할상환)</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>1천만원</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr"/>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z547" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA547" t="inlineStr">
+        <is>
+          <t>신분증 등 제주신용보증재단 및 금융기관이 요구하는 서류, 지원방법:, 처리절차, 「소상공인 저금리 대환대출 특별보증」 신청, 신청업체 → 제주신용보증재단, 도내 위기업종 소상공인 특별보증 신청, 보증서 발급 및, 대출 시행</t>
+        </is>
+      </c>
+      <c r="AB547" t="inlineStr">
+        <is>
+          <t>제주특별자치도 소상공인과 064-710-3905, 3906 제주신용보증재단 (본점) 064-750-4800 (서귀포지점) 064-733-8133 (동제주지점) 064-758-8020</t>
+        </is>
+      </c>
+      <c r="AC547" t="inlineStr"/>
+      <c r="AD547" t="inlineStr">
+        <is>
+          <t>064-710-3905</t>
+        </is>
+      </c>
+      <c r="AE547" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF547" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125737</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>[경남] 함안군 2026년 하반기 농업발전기금 융자시행계획 공고</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>2026-08-18 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 신청인의 주소지 읍ㆍ면 사무소</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>지원한도                 :</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr"/>
+      <c r="G548" t="inlineStr"/>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z548" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA548" t="inlineStr">
+        <is>
+          <t>접수(우편접수 불가), ㅇ 농어업경영자금, 농어업시설자금, 신청기간 : 2026. 8. 18. ~ 9. 11., 신청장소 : 신청인의 주소지 읍면사무소, 읍ㆍ면에서 배부(융자신청서, 사업계획서, 기타 필요한 서류)</t>
+        </is>
+      </c>
+      <c r="AB548" t="inlineStr">
+        <is>
+          <t>함안군농업기술센터 농정담당 055-580-4402</t>
+        </is>
+      </c>
+      <c r="AC548" t="inlineStr"/>
+      <c r="AD548" t="inlineStr">
+        <is>
+          <t>055-580-4402</t>
+        </is>
+      </c>
+      <c r="AE548" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF548" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125736</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026년 2차 반도체 첨단패키징 실증센터 구축사업 기업지원 수혜기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>광주테크노파크</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>이메일 접수 (yb7457@gjtp.or.kr)
+※ 제출기한 내 접수해야 하며 제출 후 담당자 연락 必</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>세부 지원내용 참조)</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr"/>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q549" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S549" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z549" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA549" t="inlineStr">
+        <is>
+          <t>기반 지원 적정성 여부 검토, 기타 유의사항 및 지원 제외대상 해당여부 검토, 평가기준, 서면평가, 계획서 등을 토대로 서면평가 진행, 이상인 기업 중 상위 기업 선정, 평가배점, 평가항목 평가지표 배 점</t>
+        </is>
+      </c>
+      <c r="AB549" t="inlineStr">
+        <is>
+          <t>광주테크노파크 산업기술실증센터 062-602-0201, 8609</t>
+        </is>
+      </c>
+      <c r="AC549" t="inlineStr">
+        <is>
+          <t>yb7457@gjtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD549" t="inlineStr">
+        <is>
+          <t>062-602-0201</t>
+        </is>
+      </c>
+      <c r="AE549" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF549" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125735</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026년 기업 제품ㆍ기술의 실증 및 고도화 지원사업 공고(전남대학교 지역성장 인재양성체계 앵커사업)</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>전남대학교</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2026-08-11 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>이메일 접수 (yeon5915@jnu.ac.kr)</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>◦ (사업 규모) 총 43건 내외 / 총 398000천원 내외</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr"/>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>43건</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q550" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S550" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z550" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA550" t="inlineStr">
+        <is>
+          <t>◦ 사업신청 절차, 신청 방법: 사업 지원유형별 접수(이메일), ⑦ 기업정보 수집‧이용‧제공 동의서 1부, ② 사업계획서 1부 ⑨ 확약서 1부, 사업자, 직접생산증명서(해당시) 각 1부, ⑤ 국세, ⑫ 신용등급 확인서 1부</t>
+        </is>
+      </c>
+      <c r="AB550" t="inlineStr">
+        <is>
+          <t>전남대학교 앵커사업단 062-530-1297, 4921 / ejjin30@jnu.ac.kr, yeon5915@jnu.ac.kr</t>
+        </is>
+      </c>
+      <c r="AC550" t="inlineStr">
+        <is>
+          <t>ejjin30@jnu.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD550" t="inlineStr">
+        <is>
+          <t>062-530-1297</t>
+        </is>
+      </c>
+      <c r="AE550" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF550" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125734</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026년 피지컬 AI 기반 휴머노이드 제조혁신센터 구축사업 수혜기업 통합 모집 공고</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>광주테크노파크</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-09-07</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>이메일 접수 (dhjeong@gjtp.or.kr)</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>프로그램명 지원내용 규모 지원범위</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr"/>
+      <c r="G551" t="inlineStr"/>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z551" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA551" t="inlineStr">
+        <is>
+          <t>검토를 통한 적정성 평가(예비진단 병행), 수혜기업 선정평가(발표평가) : 기술성, 사업성, 기술역량, 파급효과 등을 종합적으로 평가, ※ 예비진단 : 신청기업의 참여제한 등에 대한 사전검토,  평가배점, 항목 지표 배점</t>
+        </is>
+      </c>
+      <c r="AB551" t="inlineStr">
+        <is>
+          <t>광주테크노파크 062-602-8608, dhjeong@gjtp.or.kr 및 지원프로그램 관련 문의처 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC551" t="inlineStr">
+        <is>
+          <t>dhjeong@gjtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD551" t="inlineStr">
+        <is>
+          <t>062-602-8608</t>
+        </is>
+      </c>
+      <c r="AE551" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF551" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125732</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>제15회 대구 국제 로봇산업전(ROBEX 2026) 참가지원 모집 공고</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>부천산업진흥원</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-09-03</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>온라인 접수 (부천산업진흥원)</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>❍ 지원금액 : 최대 2750000원(부가가치세 제외)</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>2750000원</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr"/>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q552" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z552" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA552" t="inlineStr">
+        <is>
+          <t>참가신청서 1부, 전시품목 상세서 1부, 확약서 1부, 개인정보 수집ˑ이용 동의서 1부 (대표이사, 담당자), 대사회보험 사업장 가입자 명부 (3개월이내 발급본), 기업 인증 서류 각 1부씩 (해당인증서류에 한함), 판로개척준비도 1부(홈페이지 캡쳐본)</t>
+        </is>
+      </c>
+      <c r="AB552" t="inlineStr">
+        <is>
+          <t>부천산업진흥원 AI콘텐츠융합팀 032-716-6482, aragon225@bizbc.or.kr</t>
+        </is>
+      </c>
+      <c r="AC552" t="inlineStr">
+        <is>
+          <t>aragon225@bizbc.or.kr</t>
+        </is>
+      </c>
+      <c r="AD552" t="inlineStr">
+        <is>
+          <t>032-716-6482</t>
+        </is>
+      </c>
+      <c r="AE552" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF552" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125731</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 사회문제해결형 R&amp;BD 지원사업 시행 공고</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>연구개발특구진흥재단</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2026-09-10 ~ 2026-09-21</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>온라인 접수(연구개발특구 사업관리시스템)</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>□ 지원규모 : 총 3개 과제 이내(과제당 170백만원 내외)</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>170백만원</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z553" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA553" t="inlineStr"/>
+      <c r="AB553" t="inlineStr">
+        <is>
+          <t>연구개발특구진흥재단 대덕연구개발특구본부 혁신기업지원실 042-865-8973, cmh0324innopolis.or.kr</t>
+        </is>
+      </c>
+      <c r="AC553" t="inlineStr"/>
+      <c r="AD553" t="inlineStr">
+        <is>
+          <t>042-865-8973</t>
+        </is>
+      </c>
+      <c r="AE553" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF553" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125730</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 하반기 마을기업 육성사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>직접수행</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 법인 소재지 관할 시군 마을기업 담당부서(공고문 참조)</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>5천만원</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>5천만원</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr"/>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S554" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z554" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA554" t="inlineStr">
+        <is>
+          <t>구 분, 구 비 서 류, 기본, 서류, 공통, 신청서, ① 사업신청서, 서식 1-1</t>
+        </is>
+      </c>
+      <c r="AB554" t="inlineStr">
+        <is>
+          <t>충청북도 마을기업 지원기관 충북사회적경제센터 043-222-9001 및 관할 시군 마을기업 담당부서 문의처 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC554" t="inlineStr"/>
+      <c r="AD554" t="inlineStr">
+        <is>
+          <t>043-222-9001</t>
+        </is>
+      </c>
+      <c r="AE554" t="inlineStr">
+        <is>
+          <t>마을기업</t>
+        </is>
+      </c>
+      <c r="AF554" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125729</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>[경기] 화성시 2026년 동남아(태국ㆍ싱가포르) 하이브리드 시장개척단 참가 기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>이메일 접수 (info@hstrade.or.kr)</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>○ 모집규모 : 화성시 수출기업 15社 내외, 15개사중 10개사 해외파견</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr"/>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>15개</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z555" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA555" t="inlineStr">
+        <is>
+          <t>미제출 업체, 현지 수행기관의 시장성 평가 60점 미만 업체, · 하단의 지원제외 대상 업종, ※ 지원제외 대상 업종, 표준산업분류, 업 종, 도박기계 및 사행성, 불건전 오락기구 제조업</t>
+        </is>
+      </c>
+      <c r="AB555" t="inlineStr">
+        <is>
+          <t>화성시 수출업무지원센터 031-350-7953 / info@hstrade.or.kr</t>
+        </is>
+      </c>
+      <c r="AC555" t="inlineStr">
+        <is>
+          <t>info@hstrade.or.kr</t>
+        </is>
+      </c>
+      <c r="AD555" t="inlineStr">
+        <is>
+          <t>031-350-7953</t>
+        </is>
+      </c>
+      <c r="AE555" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF555" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125728</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 2차 소재부품산업 국가사업화지원사업 기업지원 공고</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>경북테크노파크</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-09-08</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경북테크노파크)</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>&lt;&gt;&lt;지원내용&gt;</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr"/>
+      <c r="G556" t="inlineStr"/>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z556" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA556" t="inlineStr"/>
+      <c r="AB556" t="inlineStr">
+        <is>
+          <t>경북테크노파크 정책기획단 책임연구원 053-819-3021, immj@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC556" t="inlineStr">
+        <is>
+          <t>immj@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD556" t="inlineStr">
+        <is>
+          <t>053-819-3021</t>
+        </is>
+      </c>
+      <c r="AE556" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF556" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125727</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>[울산] 2026년 2차 소상공인 경영환경개선사업 공고</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>울산광역시소상공인행복드림센터</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>온라인 접수 (울산광역시 소상공인 행복드림센터)
+※ 다만, 온라인 접수가 곤란한 경우에 한해 현장접수 기간(9.3.~9.4.)에만 현장방문접수 가능
+- 접수처 : 울산광역시 북구 산업로 915 (울산경제일자리진흥원 4층)</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>최대 250만원 이내</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>250만원</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr"/>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q557" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R557" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T557" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V557" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W557" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X557" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y557" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z557" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA557" t="inlineStr">
+        <is>
+          <t>사업장 내․외부사진, 사전준비, 하여, 센터 홈페이지에 접수, 홈페이지(, 회원가입, 로그인, 온라인접수</t>
+        </is>
+      </c>
+      <c r="AB557" t="inlineStr">
+        <is>
+          <t>울산광역시 소상공인 행복드림센터 052-283-8390</t>
+        </is>
+      </c>
+      <c r="AC557" t="inlineStr"/>
+      <c r="AD557" t="inlineStr">
+        <is>
+          <t>052-283-8390</t>
+        </is>
+      </c>
+      <c r="AE557" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF557" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125726</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 2차 수요특화 모듈형 LSV 글로벌 혁신 규제자유특구사업 참여기업 모집 공고(글로벌혁신 규제자유특구)</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>경북테크노파크</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경북테크노파크)
+※ 지원 프로그램 및 지원분야 확인 必</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>○ 지원규모 : 총2566000000원 (이십오억육천육백만원) *2차 공고 지원규모: 약537971000원</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>2566000000원</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr"/>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z558" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA558" t="inlineStr">
+        <is>
+          <t>(신청서 등) 미비기업, 유의사항, ① 제출된 서류는 반환하지 않음, ② 민간부담금(10%이상) 현금 매칭 필수이며, 지원금 외 추가비용 발생 시 신청기업 부담, 할 수 있음, 가 허위이거나, 기 지원된 과제와 유사·중복이 확인될 경우 지원취소</t>
+        </is>
+      </c>
+      <c r="AB558" t="inlineStr">
+        <is>
+          <t>경북테크노파크 글로벌혁신특구TFT 054-339-0902, ash1019@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC558" t="inlineStr">
+        <is>
+          <t>ash1019@gbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD558" t="inlineStr">
+        <is>
+          <t>054-339-0902</t>
+        </is>
+      </c>
+      <c r="AE558" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF558" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125725</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026년 원전 생태계 고도화 지원사업 원전 핵심기업 육성 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>한국원자력산업협회</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>이메일 접수 (tech@kaif.or.kr)</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>「2026 원전 생태계 고도화 지원사업」</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>2026원</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr"/>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q559" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z559" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA559" t="inlineStr">
+        <is>
+          <t>(사업지침 서식 참조), 사업구분 서식명 필수여부 사업구분, 사업계획서 필수 공통, 주요 생산제품 소개서 필수 공통, 개인정보 수집·이용·제공 동의서 필수 공통, 청렴이행서약서 필수 공통, 연구시설․장비 구입 계획서 선택 공통, 원전 중소기업 또는 중견기업 확인서 필수 공통</t>
+        </is>
+      </c>
+      <c r="AB559" t="inlineStr">
+        <is>
+          <t>한국원자력산업협회 기업지원팀 02-6953-8732, 02-6257-2596 / tech@kaif.or.kr</t>
+        </is>
+      </c>
+      <c r="AC559" t="inlineStr">
+        <is>
+          <t>tech@kaif.or.kr</t>
+        </is>
+      </c>
+      <c r="AD559" t="inlineStr">
+        <is>
+          <t>02-6257-2596</t>
+        </is>
+      </c>
+      <c r="AE559" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF559" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125724</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>[부산] 2027년 전통시장 및 상점가 등 시설현대화사업 공고</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>직접수행</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 상인조직 등 : 구ㆍ군 전통시장 담당 부서 방문 또는 우편 접수 
+- 구·군 : 전자결재 공문 발송</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>* 해당연도 또는 연차사업으로 총사업비 1억원 이상의 시설현대화사업 추진 시 제출</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>1억원</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr"/>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z560" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA560" t="inlineStr">
+        <is>
+          <t>기간 내 제출된 서류만 인정, 서류 미비 시 각종 평가에서 제외, 상인조직 등, 연번, 비고, 목록, 서식, 사업신청서 및 관리‧운영계획</t>
+        </is>
+      </c>
+      <c r="AB560" t="inlineStr">
+        <is>
+          <t>부산광역시 디지털경제실 중소상공인지원과 051-888-4745 및 각 구ㆍ군별 문의처 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC560" t="inlineStr"/>
+      <c r="AD560" t="inlineStr">
+        <is>
+          <t>051-888-4745</t>
+        </is>
+      </c>
+      <c r="AE560" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF560" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125723</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>[경기] 2026년 농식품기업 해외 인증 검사 지원 수요기업 모집 공고(경기도 무역위기대응 K-Food 비관세장벽 해소지원사업)</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>경기테크노파크</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경기테크노파크)</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>증 유지 및 갱신 비용 지원” 등 제공(총 지원금 350만원(VAT별도))</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>350만원</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr"/>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z561" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA561" t="inlineStr">
+        <is>
+          <t>를 제출하지 아니하였거나 신청서가 허위인 경우, 기업이 부도인 경우, 금융기관을 통한 계좌개설이 불가능하거나, 제외), 국세 또는 지방세를 체납 중인 경우, 민사집행법에 의하여 채무불이행자 명부에 등재되거나, 은행연합회 등 신용정보 집중기관에 채무불이행자로, 등록된 경우</t>
+        </is>
+      </c>
+      <c r="AB561" t="inlineStr">
+        <is>
+          <t>경기테크노파크 031-500-3039, ynhan@gtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC561" t="inlineStr">
+        <is>
+          <t>ynhan@gtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD561" t="inlineStr">
+        <is>
+          <t>031-500-3039</t>
+        </is>
+      </c>
+      <c r="AE561" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF561" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125722</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>[경기] 2026년 독일 뮌헨 반도체ㆍ소부장 수출상담회 수출컨소시엄 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>용인시산업진흥원</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>온라인 접수(중소기업해외전시포털)</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>□지원내용:2026독일뮌헨반도체·소부장수출상담회참가지원</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr"/>
+      <c r="G562" t="inlineStr"/>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z562" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA562" t="inlineStr">
+        <is>
+          <t>구분,  필수여부 비고, 경기도소재확인용, (지사로신청시지사분포함), 중소기업현황정보시스템,  중소기업확인서 필수, (sminfo.mss.go.kr)발급분, 영문회사소개서및제품/서비스</t>
+        </is>
+      </c>
+      <c r="AB562" t="inlineStr">
+        <is>
+          <t>용인시산업진흥원 판로지원팀 031-323-5230 Start2Group한국지사 02-3833-2682 (신청관련문의) susie.choi@start2.group (사업관련문의) bomin.kang@start2.group 및 기타 문의처 원출처 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC562" t="inlineStr">
+        <is>
+          <t>bomin.kang@start2.group</t>
+        </is>
+      </c>
+      <c r="AD562" t="inlineStr">
+        <is>
+          <t>02-3833-2682</t>
+        </is>
+      </c>
+      <c r="AE562" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF562" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125721</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>[경기] 2026년 농식품기업 수출 통관ㆍ검역 지원 컨설팅 수요기업 모집 공고(경기도 무역위기대응 K-Food 비관세장벽 해소지원사업)</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>경기테크노파크</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경기테크노파크)</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>○ 선정규모: 10개사 내외</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S563" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z563" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA563" t="inlineStr">
+        <is>
+          <t>를 제출하지 아니하였거나 신청서가 허위인 경우, 기업이 부도인 경우, 금융기관을 통한 계좌개설이 불가능하거나, 자는 제외), 국세 또는 지방세를 체납 중인 경우, 민사집행법에 의하여 채무불이행자 명부에 등재되거나, 은행연합회 등 신용정보 집중기관에 채무불이행자, 로 등록된 경우</t>
+        </is>
+      </c>
+      <c r="AB563" t="inlineStr">
+        <is>
+          <t>경기테크노파크 031-500-3039, ynhan@gtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC563" t="inlineStr">
+        <is>
+          <t>ynhan@gtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD563" t="inlineStr">
+        <is>
+          <t>031-500-3039</t>
+        </is>
+      </c>
+      <c r="AE563" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF563" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125720</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026년 납품대금 연동 우수기업 포상 공고</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>대중소기업농어업협력재단</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-10-08</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>이메일 접수 (pis@win-win.or.kr)</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>아) 포상추천일 전 3년 이내에 1회 벌금액이 200만원 이상의 벌금형 처분을 받은 자</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>200만원</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr"/>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z564" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA564" t="inlineStr">
+        <is>
+          <t>① (서식1) “포상 신청서” 1부, ② (서식2) “공적조서” 1부, ③ (서식3) “포상에 대한 동의 및 확인서” 1부, ⑤ 기타 공적을 인정할 수 있는 증빙서류 각 1부, 희망 포상 순위 작성 후 제출 바랍니다., 대상자 심사⋅선정, 평가(2차)를 통해 포상 후보자를 중기부·공정위에 추천, 유공자 결정</t>
+        </is>
+      </c>
+      <c r="AB564" t="inlineStr">
+        <is>
+          <t>대ㆍ중소기업ㆍ농어업협력재단 02-368-8929, 8920</t>
+        </is>
+      </c>
+      <c r="AC564" t="inlineStr">
+        <is>
+          <t>pis@win-win.or.kr</t>
+        </is>
+      </c>
+      <c r="AD564" t="inlineStr">
+        <is>
+          <t>02-368-8929</t>
+        </is>
+      </c>
+      <c r="AE564" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF564" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125719</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>[경기] 고양시 2026년 투자 레벨업 프로그램 NEXT ROUND 모집 공고</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>고양산업진흥원</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>이메일 접수 (kevinyoo@startrun.co.kr)</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>&lt;우대 사항&gt;&lt;- 공고일 기준 2년 이내 누적 1000만원 이상 민간 투자 유치 이력이 있는 기업 - 2024년, 2025년 고양산업진흥원의 ‘혁신 창업 스타트업 아카데미’ 수료 기업&gt;</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>1000만원</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr"/>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z565" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA565" t="inlineStr"/>
+      <c r="AB565" t="inlineStr">
+        <is>
+          <t>고양산업진흥원 투자운용팀 031-962-0257, wjlee@gipa.or.kr / (운영기관) 주식회사 스타트런 070-5117-0838, kevinyoo@startrun.co.kr</t>
+        </is>
+      </c>
+      <c r="AC565" t="inlineStr">
+        <is>
+          <t>kevinyoo@startrun.co.kr</t>
+        </is>
+      </c>
+      <c r="AD565" t="inlineStr">
+        <is>
+          <t>031-962-0257</t>
+        </is>
+      </c>
+      <c r="AE565" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF565" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125718</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026년 백년소상공인 위생컨설팅 및 환경개선지원 사업 추가 공고</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>소상공인시장진흥공단</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-09-30</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>온라인 접수 (소상공인24)</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>- 사업장(작업장) 청소비 지원(최대 50만원)</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr"/>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q566" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R566" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S566" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T566" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U566" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V566" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W566" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X566" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y566" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z566" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA566" t="inlineStr">
+        <is>
+          <t>업로드 후 [신청서제출] 클릭하여 접수완료, 사항 ※ 시스템(소상공인24) 문의 1644-5302, 마., 구분, 비고, 개인정보 수집·이용 및 제공 동의서, 본인 행정정보 제공 요구 동의 마이데이터 동의서, 서류 □ 자가진단 체크리스트</t>
+        </is>
+      </c>
+      <c r="AB566" t="inlineStr">
+        <is>
+          <t>(환경개선비 지원, 백년소상공인 문의) 소상공인시장진흥공단 042-363-7905, 7906 (위생컨설팅, 식품안심업소 지정 문의) 한국식품안전관리인증 1599-1102 (시스템 문의) 소상공인24 1644-5302</t>
+        </is>
+      </c>
+      <c r="AC566" t="inlineStr"/>
+      <c r="AD566" t="inlineStr">
+        <is>
+          <t>042-363-7905</t>
+        </is>
+      </c>
+      <c r="AE566" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF566" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125717</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026년 WoW! 메이커스 IR클리닉 모집 공고(메이커스페이스 전문랩 운영사업)</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>수원대학교</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-09-09</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>이메일 접수 (makerspace@suwon.ac.kr)</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>○ 지원 규모 : 5개사</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr"/>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>5개</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S567" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z567" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA567" t="inlineStr">
+        <is>
+          <t>를 기반으로 평가위원회를 통한 서면 평가 진행, 평가 방식, 평가 내용 : 신청자격 적정성 검토 및 제출자료 검토, 평가 지표, 평가항목 평가내용 배점, 기업역량 ⦁기업 및 주요사업 소개 20, ⦁대표자 전문성, 경영 의지</t>
+        </is>
+      </c>
+      <c r="AB567" t="inlineStr">
+        <is>
+          <t>수원대학교 WoW!메이커스 담당자 031-229-8821</t>
+        </is>
+      </c>
+      <c r="AC567" t="inlineStr">
+        <is>
+          <t>-makerspace@suwon.ac.kr</t>
+        </is>
+      </c>
+      <c r="AD567" t="inlineStr">
+        <is>
+          <t>031-229-8821</t>
+        </is>
+      </c>
+      <c r="AE567" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF567" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125716</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026년 세종 한글 술술 축제 부스 운영 기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>세종창조경제혁신센터</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-09-14</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>이메일 접수 (ydd23@ccei.kr)</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>□ (모집규모) 총 30개사 내외 ※ 양조 20개사 / 유관 10개사 내외</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr"/>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>30개</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z568" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA568" t="inlineStr">
+        <is>
+          <t>참가 신청 최종 선정 기업 세종 한글 술술 축제, ➜ 기반 요건 검토 및 ➜ ➜, 서류 제출 및 접수 공지 및 안내 부스 운영, 평가 진행, ※ 추진 일정은 대내외 사정에 의해 변동될 수 있음, 신청 및 접수, ※ 신청 마감일에 사용자 문의 및 접수 건이 급증하여, 시스템 사용에 일부 장애가</t>
+        </is>
+      </c>
+      <c r="AB568" t="inlineStr">
+        <is>
+          <t>세종창조경제혁신센터 044-999-0238, ydd23@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AC568" t="inlineStr">
+        <is>
+          <t>ydd23@ccei.kr</t>
+        </is>
+      </c>
+      <c r="AD568" t="inlineStr">
+        <is>
+          <t>044-999-0238</t>
+        </is>
+      </c>
+      <c r="AE568" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF568" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125715</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>[경북] 성주군 2026년 중소기업 수출 스케일업 지원사업 해외무역사절단 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>이메일 접수 (dkkim00700@daum.net)</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>□ 지원내용: 성주군 관내 중소기업 수출 역량 강화 및 판로 확대 지원</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr"/>
+      <c r="G569" t="inlineStr"/>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z569" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA569" t="inlineStr">
+        <is>
+          <t>순번, 비고, · 신청서, 제품(상품) 소개서, 개인(기업)정보 이용 등에 관한 동의서 각 1부 붙임, · 수출실적증명서(2024년, 년), 각 1부</t>
+        </is>
+      </c>
+      <c r="AB569" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 ESGㆍ기업지원팀 054-470-8559</t>
+        </is>
+      </c>
+      <c r="AC569" t="inlineStr">
+        <is>
+          <t>dkkim00700@daum.net</t>
+        </is>
+      </c>
+      <c r="AD569" t="inlineStr">
+        <is>
+          <t>054-470-8559</t>
+        </is>
+      </c>
+      <c r="AE569" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF569" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125714</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 청년창업제품 온라인 기획전 판로지원 참가기업 모집 연장 공고(청년창업제품 판로개척 지원사업)</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>2026-07-28 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>이메일 접수 (gepa02@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>3 지원내용</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr"/>
+      <c r="G570" t="inlineStr"/>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z570" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA570" t="inlineStr">
+        <is>
+          <t>필수여부 비고, 양식(별첨)활용, 참가신청서* 여, 경제진흥원 홈페이지 게시, 통신판매업신고증 여 홈택스, 주민등록번호 뒷자리, 대표자 신분증 사본 여, 마스킹처리</t>
+        </is>
+      </c>
+      <c r="AB570" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 민생경제지원팀 054- 995-9945</t>
+        </is>
+      </c>
+      <c r="AC570" t="inlineStr">
+        <is>
+          <t>gepa02@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD570" t="inlineStr">
+        <is>
+          <t>026080063</t>
+        </is>
+      </c>
+      <c r="AE570" t="inlineStr">
+        <is>
+          <t>창업벤처</t>
+        </is>
+      </c>
+      <c r="AF570" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125713</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>[부산] 2026년 안전경영 강화 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>부산경제진흥원</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>이메일 접수(whruddyd1234@bepa.kr)</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>○ (지원규모) 10개사 내외 지원 ※ BEF 사업 5개사, 부산경제진흥원 자체 사업 5개사</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr"/>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z571" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA571" t="inlineStr"/>
+      <c r="AB571" t="inlineStr">
+        <is>
+          <t>부산경제진흥원 기업지원단 051-600-1737, whruddyd1234@bepa.kr</t>
+        </is>
+      </c>
+      <c r="AC571" t="inlineStr">
+        <is>
+          <t>whruddyd1234@bepa.kr</t>
+        </is>
+      </c>
+      <c r="AD571" t="inlineStr">
+        <is>
+          <t>051-600-1737</t>
+        </is>
+      </c>
+      <c r="AE571" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF571" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125712</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 농생명바이오 잠재기업군 IR지원 프로그램(전북지역기업 성장사다리 지원사업)</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>전북테크노파크</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>2026-08-31 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>온라인 접수 (기업지원사업 관리시스템)</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 기업당 최대 500만원, 3개사 이내 지원</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>3개</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z572" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA572" t="inlineStr"/>
+      <c r="AB572" t="inlineStr">
+        <is>
+          <t>전북테크노파크 기업지원단 지역균형사업팀 063-219-2123, shjung@jbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC572" t="inlineStr">
+        <is>
+          <t>shjung@jbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD572" t="inlineStr">
+        <is>
+          <t>063-219-2123</t>
+        </is>
+      </c>
+      <c r="AE572" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF572" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125711</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>[경북] 영천시 2026년 지방소멸 대응을 위한 모빌리티 가공부품산업 제조전환 및 구조 효율화 지원사업 추가공고(시군구연고산업육성 협업프로젝트)</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>경북자동차임베디드연구원</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>온라인 접수 (기업지원사업 관리시스템)</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>15억원</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>15억원</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr"/>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z573" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA573" t="inlineStr"/>
+      <c r="AB573" t="inlineStr">
+        <is>
+          <t>경북자동차임베디드연구원 054-339-0051, khkim@givet.re.kr</t>
+        </is>
+      </c>
+      <c r="AC573" t="inlineStr">
+        <is>
+          <t>khkim@givet.re.kr</t>
+        </is>
+      </c>
+      <c r="AD573" t="inlineStr">
+        <is>
+          <t>054-339-0051</t>
+        </is>
+      </c>
+      <c r="AE573" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF573" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125710</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>[경남] 2026년 (예비)사회적기업 판로개척 지원사업 소셜임팩트 페스타 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>모두의경제사회적협동조합</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>2026-08-19 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>온라인 접수(구글폼)</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>의자2개, 현수막, 중식, 이벤트용 상품구입 20만원 상당</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>20만원</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z574" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA574" t="inlineStr"/>
+      <c r="AB574" t="inlineStr">
+        <is>
+          <t>모두의경제사회적협동조합 기획조정실 055-286-7971, mdpc@moducoop.com</t>
+        </is>
+      </c>
+      <c r="AC574" t="inlineStr">
+        <is>
+          <t>mdpc@moducoop.com</t>
+        </is>
+      </c>
+      <c r="AD574" t="inlineStr">
+        <is>
+          <t>055-286-7971</t>
+        </is>
+      </c>
+      <c r="AE574" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF574" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125709</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>[인천] 남동구 2026년 카자흐스탄(알마티) 시장개척단 참가업체 모집 공고</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>인천상공회의소</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-01</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>온라인 접수(비즈오케이)</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 남동구 소재 중소(제조)업체 15개사</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>15개</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z575" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA575" t="inlineStr"/>
+      <c r="AB575" t="inlineStr">
+        <is>
+          <t>인천상공회의소 국제통상실 032-810-2832, hjs@incham.net</t>
+        </is>
+      </c>
+      <c r="AC575" t="inlineStr">
+        <is>
+          <t>hjs@incham.net</t>
+        </is>
+      </c>
+      <c r="AD575" t="inlineStr">
+        <is>
+          <t>032-810-2832</t>
+        </is>
+      </c>
+      <c r="AE575" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF575" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125708</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>[충남ㆍ충북ㆍ대전ㆍ세종] 2026년 중소기업 AI훈련확산센터 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>한국생산성본부</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>모집 완료시</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>온라인 접수 (구글폼)</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>현장 문제를 AI로 해결하는 외부 강사료 시간당 10만원 지원</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr"/>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z576" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA576" t="inlineStr"/>
+      <c r="AB576" t="inlineStr">
+        <is>
+          <t>한국생산성본부 대전세종충청지역본부 042-489-6056, ykkim@kpc.or.kr / 한국생산성본부 AI 전환센터 02-398-7667, ykkim@kpc.or.kr</t>
+        </is>
+      </c>
+      <c r="AC576" t="inlineStr">
+        <is>
+          <t>ykkim@kpc.or.kr</t>
+        </is>
+      </c>
+      <c r="AD576" t="inlineStr">
+        <is>
+          <t>02-398-7667</t>
+        </is>
+      </c>
+      <c r="AE576" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF576" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125707</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>[제주] 2026년 상생브랜드 선정을 위한 제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>제주특별자치도경제통상진흥원</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-03</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>이메일 접수(ksh3117@jba.or.kr)</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>&lt;모집공고&gt;&lt;▶&gt;&lt;신청서류  적정성 검토&gt;&lt;▶&gt;&lt;선정위원회  개최&gt;&lt;▶&gt;&lt;최종 선정  및 선정제품 통보&gt;</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr"/>
+      <c r="G577" t="inlineStr"/>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z577" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA577" t="inlineStr">
+        <is>
+          <t>&lt;진흥원&gt;&lt;진흥원&gt;&lt;선정위원&gt;&lt;도-진흥원 &gt;, ※ 상기 추진일정은</t>
+        </is>
+      </c>
+      <c r="AB577" t="inlineStr">
+        <is>
+          <t>제주특별자치도경제통상진흥원 유통혁신센터 064-805-3352</t>
+        </is>
+      </c>
+      <c r="AC577" t="inlineStr"/>
+      <c r="AD577" t="inlineStr">
+        <is>
+          <t>064-805-3352</t>
+        </is>
+      </c>
+      <c r="AE577" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF577" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125706</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 2차 중소기업육성자금 융자(이차보전) 지원계획 변경 공고</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>충청북도기업진흥원</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>방문, 우편 접수
+- 접수처 : (28399) 충북 청주시 흥덕구 풍산로 50 충청북도기업진흥원 2층 기업지원부</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>- 지원규모 : 20억원(10억원 증액 : 기존 10억원 ➝ 20억원)</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>20억원</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr"/>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S578" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W578" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z578" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA578" t="inlineStr">
+        <is>
+          <t>제출), 협약은행, ④ 대출실행 : 기업↔협약은행(융자결정서 승인 내용, 금액 내 대출실행), 협약은행(대출 가능 은행), ❍ 협약은행 : 11개 은행, 공통 8개 은행 : 국민, 기업</t>
+        </is>
+      </c>
+      <c r="AB578" t="inlineStr">
+        <is>
+          <t>충청북도기업진흥원 기업지원부 043-230-9751, 9729</t>
+        </is>
+      </c>
+      <c r="AC578" t="inlineStr"/>
+      <c r="AD578" t="inlineStr">
+        <is>
+          <t>043-230-9751</t>
+        </is>
+      </c>
+      <c r="AE578" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF578" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125705</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>[경기] 동부거점 2026년 3차 중소기업 개발생산판로 맞춤형 지원사업 통합 공고</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>경기도경제과학진흥원</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-09-11</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>온라인 접수 (경기기업비서)</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>○ 지원규모 : 각 과제별 한도내 지원(여러과제 지원시 연간 20백만원 이내)</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>20백만원</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr"/>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W579" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z579" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA579" t="inlineStr">
+        <is>
+          <t>미비 시 보완이 요청될 수 있으며, 기한내 보완이 완료되지 않는 경우 지원 배제, 사업 공고문 및 세부운영기준, 각 유의사항 미숙지에 따른 책임은 신청기업에 있음, 지방세 체납기업은 신청/지원이 불가하므로, 체납여부 사전 확인 필요, 사업비 출연 시군 소재 여부, ※ 공장등록증 불인정</t>
+        </is>
+      </c>
+      <c r="AB579" t="inlineStr">
+        <is>
+          <t>경기도경제과학진흥원 동부거점센터 (광주시, 여주시, 양평군) 031-830-8566 (하남시, 이천시) 031-830-8568</t>
+        </is>
+      </c>
+      <c r="AC579" t="inlineStr"/>
+      <c r="AD579" t="inlineStr">
+        <is>
+          <t>031-830-8566</t>
+        </is>
+      </c>
+      <c r="AE579" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF579" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125704</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 우수상품 전주국제발효식품엑스포 단체관 참가지원 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>전북특별자치도경제통상진흥원</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>온라인 접수 (전북특별자치도 중소기업종합지원시스템)</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>4m) 1개 비용(1980000원) 중</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>1980000원</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z580" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA580" t="inlineStr">
+        <is>
+          <t>구분 서류명 비고, 신청서 [서식 1], 서약서 [서식 2], 개인정보 수집‧이용‧제공 동의서 [서식 3], 필수, 중소기업확인서 유효기간 내, 특허증(최대 2건) 2021년 이후 등록건, 홈페이지</t>
+        </is>
+      </c>
+      <c r="AB580" t="inlineStr">
+        <is>
+          <t>전북특별자치도경제통상진흥원 마케팅팀 063-711-2075</t>
+        </is>
+      </c>
+      <c r="AC580" t="inlineStr"/>
+      <c r="AD580" t="inlineStr">
+        <is>
+          <t>063-711-2075</t>
+        </is>
+      </c>
+      <c r="AE580" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF580" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125703</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 우수 수산물 육성사업 대만 해외시장개척단 참가기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>이메일 접수 (osmasis@gepa.kr)</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>□ 지원내용</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr"/>
+      <c r="G581" t="inlineStr"/>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S581" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z581" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA581" t="inlineStr">
+        <is>
+          <t>신청서식 붙임 1참조, ◦ 기타 증빙자료 등 모든 제출자료는 PDF파일로 제출, ◦ 서류 제출 시, 순서에 맞게 하여 하나의 파일로 제출하거나 제출, 순서에 맞추어 파일명을 번호화 하여 작성·제출, ※예시) 1. 신청서, 체크리스트, 선정방법</t>
+        </is>
+      </c>
+      <c r="AB581" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원 동부지소 054-612-2967, osmasis@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AC581" t="inlineStr">
+        <is>
+          <t>osmasis@gepa.kr</t>
+        </is>
+      </c>
+      <c r="AD581" t="inlineStr">
+        <is>
+          <t>054-612-2967</t>
+        </is>
+      </c>
+      <c r="AE581" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF581" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125702</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>[울산] 2026년 중장년 활력UP 일자리사업 참여기관 추가 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>울산경제일자리진흥원</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-08-25</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>이메일 접수(dsdszzz@ubpi.or.kr)</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>- 참여자 활동비 : 월 60만원 이내(시급 12000원 기준)  ※ 최대 360만원 이내</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>360만원</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr"/>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z582" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA582" t="inlineStr"/>
+      <c r="AB582" t="inlineStr">
+        <is>
+          <t>울산경제일자리진흥원 고용창출팀 052-283-7204, dsdszzz@ubpi.or.kr</t>
+        </is>
+      </c>
+      <c r="AC582" t="inlineStr">
+        <is>
+          <t>dsdszzz@ubpi.or.kr</t>
+        </is>
+      </c>
+      <c r="AD582" t="inlineStr">
+        <is>
+          <t>052-283-7204</t>
+        </is>
+      </c>
+      <c r="AE582" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF582" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125701</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>[전남광주] 보성군 2026년 3차 새싹 키움터 사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>전남테크노파크</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>온라인 접수 (전남테크노파크 기업혁신성장플랫폼)</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>총사업비 사업비 20 백만원 ( 지원금액 20백만원, 민간부담금 2백만원)</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>20백만원</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr"/>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z583" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA583" t="inlineStr">
+        <is>
+          <t>제출여부, 공장등록증. 1부. 필수, ③ 수혜기업 대표의 참여의사 확인, 신용정보제공 및 조회 동의서 필수, ④ 국세·지방세 납입 증명서 필수, ⑤ 사업신청서 및 사업계획서 필수, ⑥ 기타 기술력을 증명할 수 있는 서류 해당 시, 평가방법 및 기준</t>
+        </is>
+      </c>
+      <c r="AB583" t="inlineStr">
+        <is>
+          <t>전남테크노파크 미래산업본부 스마트팜실증센터 061-858-1563, dndrud2@jntp.or.kr</t>
+        </is>
+      </c>
+      <c r="AC583" t="inlineStr">
+        <is>
+          <t>dndrud2@jntp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD583" t="inlineStr">
+        <is>
+          <t>061-858-1563</t>
+        </is>
+      </c>
+      <c r="AE583" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF583" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125700</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 2차 우수 소상공인 기획전 참여 업체 모집 공고</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>모집 완료시</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>이메일 접수(yamun114@gjep.or.kr)</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>❍ 모집 규모 : 관내 소상공인 50개사 내외</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr"/>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>50개</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z584" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA584" t="inlineStr"/>
+      <c r="AB584" t="inlineStr">
+        <is>
+          <t>광주경제진흥상생일자리재단 소상공인디지털전환실 062-960-2675</t>
+        </is>
+      </c>
+      <c r="AC584" t="inlineStr"/>
+      <c r="AD584" t="inlineStr">
+        <is>
+          <t>062-960-2675</t>
+        </is>
+      </c>
+      <c r="AE584" t="inlineStr">
+        <is>
+          <t>소상공인</t>
+        </is>
+      </c>
+      <c r="AF584" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125699</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 전북지역기술혁신허브 맞춤형 기술지원 참여기업 모집 상시 통합 공고(전북지역기술혁신허브 비R&amp;D 지원사업)</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>전북테크노파크</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-10-16</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>온라인 접수 (전북R&amp;D종합정보시스템)</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>❍ 지원규모 : 기업당 최대 45백만원 이내, 15건 내외</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>45백만원</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>15건</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q585" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z585" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA585" t="inlineStr">
+        <is>
+          <t>의 미비 또는, 가 사실과 다른 경우, 기타 본 사업에 적정하지 않다고 판단되는 경우, ❍ 협약 체결 및 공급기업 등록 기준, 지원유형Ⅰ, 공급기업은 아래 요건 중 하나를 충족하여야 함, 미등록 기업의 경우, 협약 체결 전까지 공급기업 등록을 완료하여야 하며</t>
+        </is>
+      </c>
+      <c r="AB585" t="inlineStr">
+        <is>
+          <t>전북테크노파크 이차전지사업단 이차전지반도체진흥팀 063-260-9366, baeeunji04@jbtp.or.kr / 원투자파트너스 063-213-2289, megacbj@gmail.com</t>
+        </is>
+      </c>
+      <c r="AC585" t="inlineStr">
+        <is>
+          <t>baeeunji04@jbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD585" t="inlineStr">
+        <is>
+          <t>063-213-2289</t>
+        </is>
+      </c>
+      <c r="AE585" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF585" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125698</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026년 시설농업 AI로봇 실증기반 구축사업 시험ㆍ평가ㆍ인증 지원 프로그램 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>전북테크노파크</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>2026-08-20 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>온라인 접수 (R&amp;D종합정보시스템)</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>○ 지원금액 : 10백만원 이내</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>10백만원</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr"/>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q586" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z586" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA586" t="inlineStr">
+        <is>
+          <t>검토 ➤ ➤, 지원규모 내에서 지원기업 선정 - 협약체결, ➀ 사전검토, 참여신청서 및, 등을 기반으로 자격요건, 사업비, 지원항목 등에 대한, 적정성 등을 검토</t>
+        </is>
+      </c>
+      <c r="AB586" t="inlineStr">
+        <is>
+          <t>전북테크노파크 스마트제조혁신단 스마트융합사업팀 063-720-3715, handhh@jbtp.or.kr 및 인프라 활용 문의처 공고문 참조</t>
+        </is>
+      </c>
+      <c r="AC586" t="inlineStr">
+        <is>
+          <t>handhh@jbtp.or.kr</t>
+        </is>
+      </c>
+      <c r="AD586" t="inlineStr">
+        <is>
+          <t>063-720-3715</t>
+        </is>
+      </c>
+      <c r="AE586" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF586" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125697</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/daily_accumulated.xlsx
+++ b/data/daily_accumulated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF586"/>
+  <dimension ref="A1:AF645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83038,7 +83038,6 @@
           <t>5백만원</t>
         </is>
       </c>
-      <c r="G537" t="inlineStr"/>
       <c r="H537" t="inlineStr">
         <is>
           <t>Y</t>
@@ -83144,7 +83143,6 @@
           <t>진주여성새로일하기센터 055-749-8528</t>
         </is>
       </c>
-      <c r="AC537" t="inlineStr"/>
       <c r="AD537" t="inlineStr">
         <is>
           <t>055-749-8528</t>
@@ -83192,7 +83190,6 @@
           <t>60만원</t>
         </is>
       </c>
-      <c r="G538" t="inlineStr"/>
       <c r="H538" t="inlineStr">
         <is>
           <t>Y</t>
@@ -83345,8 +83342,6 @@
           <t>확인 필요 (원문 참고)</t>
         </is>
       </c>
-      <c r="F539" t="inlineStr"/>
-      <c r="G539" t="inlineStr"/>
       <c r="H539" t="inlineStr">
         <is>
           <t>N</t>
@@ -83442,7 +83437,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA539" t="inlineStr"/>
       <c r="AB539" t="inlineStr">
         <is>
           <t>㈜씨드젠, ㈜78리서치랩 02-6951-3739, blockchain26@seedgen.kr</t>
@@ -83501,7 +83495,6 @@
           <t>1억원</t>
         </is>
       </c>
-      <c r="G540" t="inlineStr"/>
       <c r="H540" t="inlineStr">
         <is>
           <t>Y</t>
@@ -83607,7 +83600,6 @@
           <t>산청군청 환경위생과 위생담당 055-970-7152</t>
         </is>
       </c>
-      <c r="AC540" t="inlineStr"/>
       <c r="AD540" t="inlineStr">
         <is>
           <t>055-970-7152</t>
@@ -83766,7 +83758,6 @@
           <t>산청군 경제기업과 일자리창출담당 055-970-6812</t>
         </is>
       </c>
-      <c r="AC541" t="inlineStr"/>
       <c r="AD541" t="inlineStr">
         <is>
           <t>055-970-6812</t>
@@ -83815,7 +83806,6 @@
           <t>2800백만원</t>
         </is>
       </c>
-      <c r="G542" t="inlineStr"/>
       <c r="H542" t="inlineStr">
         <is>
           <t>Y</t>
@@ -83921,7 +83911,6 @@
           <t>제주특별자치도 친환경축산정책과 064-710-2123 제주시 청정축산과 064-728-3891, 3893 서귀포시 청정축산과 064-760-2661, 2662 주소지 읍·면사무소, 동주민센터(산업부서)</t>
         </is>
       </c>
-      <c r="AC542" t="inlineStr"/>
       <c r="AD542" t="inlineStr">
         <is>
           <t>064-710-2123</t>
@@ -83970,7 +83959,6 @@
           <t>200만원</t>
         </is>
       </c>
-      <c r="G543" t="inlineStr"/>
       <c r="H543" t="inlineStr">
         <is>
           <t>Y</t>
@@ -84076,7 +84064,6 @@
           <t>하동군 055-880-2354</t>
         </is>
       </c>
-      <c r="AC543" t="inlineStr"/>
       <c r="AD543" t="inlineStr">
         <is>
           <t>055-880-2354</t>
@@ -84125,7 +84112,6 @@
           <t>200만원</t>
         </is>
       </c>
-      <c r="G544" t="inlineStr"/>
       <c r="H544" t="inlineStr">
         <is>
           <t>Y</t>
@@ -84231,7 +84217,6 @@
           <t>고성군 경제기업과 지역경제담당 055-670-2304</t>
         </is>
       </c>
-      <c r="AC544" t="inlineStr"/>
       <c r="AD544" t="inlineStr">
         <is>
           <t>055-670-2304</t>
@@ -84274,8 +84259,6 @@
           <t>산업통상자원부, 수출바우처, 지자체 등 타 기관 지원금(보조금)으로</t>
         </is>
       </c>
-      <c r="F545" t="inlineStr"/>
-      <c r="G545" t="inlineStr"/>
       <c r="H545" t="inlineStr">
         <is>
           <t>N</t>
@@ -84371,7 +84354,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA545" t="inlineStr"/>
       <c r="AB545" t="inlineStr">
         <is>
           <t>대구디지털혁신진흥원 AX데이터활용센터 053-655-5610, dipjs@dip.or.kr</t>
@@ -84540,7 +84522,6 @@
           <t>창녕군청 일자리경제과 일자리지원팀 055-530-1173</t>
         </is>
       </c>
-      <c r="AC546" t="inlineStr"/>
       <c r="AD546" t="inlineStr">
         <is>
           <t>055-530-1173</t>
@@ -84588,7 +84569,6 @@
           <t>1천만원</t>
         </is>
       </c>
-      <c r="G547" t="inlineStr"/>
       <c r="H547" t="inlineStr">
         <is>
           <t>Y</t>
@@ -84694,7 +84674,6 @@
           <t>제주특별자치도 소상공인과 064-710-3905, 3906 제주신용보증재단 (본점) 064-750-4800 (서귀포지점) 064-733-8133 (동제주지점) 064-758-8020</t>
         </is>
       </c>
-      <c r="AC547" t="inlineStr"/>
       <c r="AD547" t="inlineStr">
         <is>
           <t>064-710-3905</t>
@@ -84738,8 +84717,6 @@
           <t>지원한도                 :</t>
         </is>
       </c>
-      <c r="F548" t="inlineStr"/>
-      <c r="G548" t="inlineStr"/>
       <c r="H548" t="inlineStr">
         <is>
           <t>N</t>
@@ -84845,7 +84822,6 @@
           <t>함안군농업기술센터 농정담당 055-580-4402</t>
         </is>
       </c>
-      <c r="AC548" t="inlineStr"/>
       <c r="AD548" t="inlineStr">
         <is>
           <t>055-580-4402</t>
@@ -84889,8 +84865,6 @@
           <t>세부 지원내용 참조)</t>
         </is>
       </c>
-      <c r="F549" t="inlineStr"/>
-      <c r="G549" t="inlineStr"/>
       <c r="H549" t="inlineStr">
         <is>
           <t>Y</t>
@@ -85043,7 +85017,6 @@
           <t>◦ (사업 규모) 총 43건 내외 / 총 398000천원 내외</t>
         </is>
       </c>
-      <c r="F550" t="inlineStr"/>
       <c r="G550" t="inlineStr">
         <is>
           <t>43건</t>
@@ -85201,8 +85174,6 @@
           <t>프로그램명 지원내용 규모 지원범위</t>
         </is>
       </c>
-      <c r="F551" t="inlineStr"/>
-      <c r="G551" t="inlineStr"/>
       <c r="H551" t="inlineStr">
         <is>
           <t>Y</t>
@@ -85360,7 +85331,6 @@
           <t>2750000원</t>
         </is>
       </c>
-      <c r="G552" t="inlineStr"/>
       <c r="H552" t="inlineStr">
         <is>
           <t>Y</t>
@@ -85618,13 +85588,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA553" t="inlineStr"/>
       <c r="AB553" t="inlineStr">
         <is>
           <t>연구개발특구진흥재단 대덕연구개발특구본부 혁신기업지원실 042-865-8973, cmh0324innopolis.or.kr</t>
         </is>
       </c>
-      <c r="AC553" t="inlineStr"/>
       <c r="AD553" t="inlineStr">
         <is>
           <t>042-865-8973</t>
@@ -85673,7 +85641,6 @@
           <t>5천만원</t>
         </is>
       </c>
-      <c r="G554" t="inlineStr"/>
       <c r="H554" t="inlineStr">
         <is>
           <t>Y</t>
@@ -85779,7 +85746,6 @@
           <t>충청북도 마을기업 지원기관 충북사회적경제센터 043-222-9001 및 관할 시군 마을기업 담당부서 문의처 공고문 참조</t>
         </is>
       </c>
-      <c r="AC554" t="inlineStr"/>
       <c r="AD554" t="inlineStr">
         <is>
           <t>043-222-9001</t>
@@ -85822,7 +85788,6 @@
           <t>○ 모집규모 : 화성시 수출기업 15社 내외, 15개사중 10개사 해외파견</t>
         </is>
       </c>
-      <c r="F555" t="inlineStr"/>
       <c r="G555" t="inlineStr">
         <is>
           <t>15개</t>
@@ -85980,8 +85945,6 @@
           <t>&lt;&gt;&lt;지원내용&gt;</t>
         </is>
       </c>
-      <c r="F556" t="inlineStr"/>
-      <c r="G556" t="inlineStr"/>
       <c r="H556" t="inlineStr">
         <is>
           <t>N</t>
@@ -86077,7 +86040,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA556" t="inlineStr"/>
       <c r="AB556" t="inlineStr">
         <is>
           <t>경북테크노파크 정책기획단 책임연구원 053-819-3021, immj@gbtp.or.kr</t>
@@ -86137,7 +86099,6 @@
           <t>250만원</t>
         </is>
       </c>
-      <c r="G557" t="inlineStr"/>
       <c r="H557" t="inlineStr">
         <is>
           <t>Y</t>
@@ -86243,7 +86204,6 @@
           <t>울산광역시 소상공인 행복드림센터 052-283-8390</t>
         </is>
       </c>
-      <c r="AC557" t="inlineStr"/>
       <c r="AD557" t="inlineStr">
         <is>
           <t>052-283-8390</t>
@@ -86292,7 +86252,6 @@
           <t>2566000000원</t>
         </is>
       </c>
-      <c r="G558" t="inlineStr"/>
       <c r="H558" t="inlineStr">
         <is>
           <t>Y</t>
@@ -86450,7 +86409,6 @@
           <t>2026원</t>
         </is>
       </c>
-      <c r="G559" t="inlineStr"/>
       <c r="H559" t="inlineStr">
         <is>
           <t>Y</t>
@@ -86610,7 +86568,6 @@
           <t>1억원</t>
         </is>
       </c>
-      <c r="G560" t="inlineStr"/>
       <c r="H560" t="inlineStr">
         <is>
           <t>N</t>
@@ -86716,7 +86673,6 @@
           <t>부산광역시 디지털경제실 중소상공인지원과 051-888-4745 및 각 구ㆍ군별 문의처 공고문 참조</t>
         </is>
       </c>
-      <c r="AC560" t="inlineStr"/>
       <c r="AD560" t="inlineStr">
         <is>
           <t>051-888-4745</t>
@@ -86764,7 +86720,6 @@
           <t>350만원</t>
         </is>
       </c>
-      <c r="G561" t="inlineStr"/>
       <c r="H561" t="inlineStr">
         <is>
           <t>Y</t>
@@ -86917,8 +86872,6 @@
           <t>□지원내용:2026독일뮌헨반도체·소부장수출상담회참가지원</t>
         </is>
       </c>
-      <c r="F562" t="inlineStr"/>
-      <c r="G562" t="inlineStr"/>
       <c r="H562" t="inlineStr">
         <is>
           <t>Y</t>
@@ -87071,7 +87024,6 @@
           <t>○ 선정규모: 10개사 내외</t>
         </is>
       </c>
-      <c r="F563" t="inlineStr"/>
       <c r="G563" t="inlineStr">
         <is>
           <t>10개</t>
@@ -87234,7 +87186,6 @@
           <t>200만원</t>
         </is>
       </c>
-      <c r="G564" t="inlineStr"/>
       <c r="H564" t="inlineStr">
         <is>
           <t>Y</t>
@@ -87392,7 +87343,6 @@
           <t>1000만원</t>
         </is>
       </c>
-      <c r="G565" t="inlineStr"/>
       <c r="H565" t="inlineStr">
         <is>
           <t>N</t>
@@ -87488,7 +87438,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA565" t="inlineStr"/>
       <c r="AB565" t="inlineStr">
         <is>
           <t>고양산업진흥원 투자운용팀 031-962-0257, wjlee@gipa.or.kr / (운영기관) 주식회사 스타트런 070-5117-0838, kevinyoo@startrun.co.kr</t>
@@ -87546,7 +87495,6 @@
           <t>50만원</t>
         </is>
       </c>
-      <c r="G566" t="inlineStr"/>
       <c r="H566" t="inlineStr">
         <is>
           <t>Y</t>
@@ -87652,7 +87600,6 @@
           <t>(환경개선비 지원, 백년소상공인 문의) 소상공인시장진흥공단 042-363-7905, 7906 (위생컨설팅, 식품안심업소 지정 문의) 한국식품안전관리인증 1599-1102 (시스템 문의) 소상공인24 1644-5302</t>
         </is>
       </c>
-      <c r="AC566" t="inlineStr"/>
       <c r="AD566" t="inlineStr">
         <is>
           <t>042-363-7905</t>
@@ -87695,7 +87642,6 @@
           <t>○ 지원 규모 : 5개사</t>
         </is>
       </c>
-      <c r="F567" t="inlineStr"/>
       <c r="G567" t="inlineStr">
         <is>
           <t>5개</t>
@@ -87853,7 +87799,6 @@
           <t>□ (모집규모) 총 30개사 내외 ※ 양조 20개사 / 유관 10개사 내외</t>
         </is>
       </c>
-      <c r="F568" t="inlineStr"/>
       <c r="G568" t="inlineStr">
         <is>
           <t>30개</t>
@@ -88011,8 +87956,6 @@
           <t>□ 지원내용: 성주군 관내 중소기업 수출 역량 강화 및 판로 확대 지원</t>
         </is>
       </c>
-      <c r="F569" t="inlineStr"/>
-      <c r="G569" t="inlineStr"/>
       <c r="H569" t="inlineStr">
         <is>
           <t>Y</t>
@@ -88165,8 +88108,6 @@
           <t>3 지원내용</t>
         </is>
       </c>
-      <c r="F570" t="inlineStr"/>
-      <c r="G570" t="inlineStr"/>
       <c r="H570" t="inlineStr">
         <is>
           <t>Y</t>
@@ -88319,7 +88260,6 @@
           <t>○ (지원규모) 10개사 내외 지원 ※ BEF 사업 5개사, 부산경제진흥원 자체 사업 5개사</t>
         </is>
       </c>
-      <c r="F571" t="inlineStr"/>
       <c r="G571" t="inlineStr">
         <is>
           <t>10개</t>
@@ -88420,7 +88360,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA571" t="inlineStr"/>
       <c r="AB571" t="inlineStr">
         <is>
           <t>부산경제진흥원 기업지원단 051-600-1737, whruddyd1234@bepa.kr</t>
@@ -88578,7 +88517,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA572" t="inlineStr"/>
       <c r="AB572" t="inlineStr">
         <is>
           <t>전북테크노파크 기업지원단 지역균형사업팀 063-219-2123, shjung@jbtp.or.kr</t>
@@ -88636,7 +88574,6 @@
           <t>15억원</t>
         </is>
       </c>
-      <c r="G573" t="inlineStr"/>
       <c r="H573" t="inlineStr">
         <is>
           <t>N</t>
@@ -88732,7 +88669,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA573" t="inlineStr"/>
       <c r="AB573" t="inlineStr">
         <is>
           <t>경북자동차임베디드연구원 054-339-0051, khkim@givet.re.kr</t>
@@ -88890,7 +88826,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA574" t="inlineStr"/>
       <c r="AB574" t="inlineStr">
         <is>
           <t>모두의경제사회적협동조합 기획조정실 055-286-7971, mdpc@moducoop.com</t>
@@ -88943,7 +88878,6 @@
           <t>❍ 지원규모 : 남동구 소재 중소(제조)업체 15개사</t>
         </is>
       </c>
-      <c r="F575" t="inlineStr"/>
       <c r="G575" t="inlineStr">
         <is>
           <t>15개</t>
@@ -89044,7 +88978,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA575" t="inlineStr"/>
       <c r="AB575" t="inlineStr">
         <is>
           <t>인천상공회의소 국제통상실 032-810-2832, hjs@incham.net</t>
@@ -89102,7 +89035,6 @@
           <t>10만원</t>
         </is>
       </c>
-      <c r="G576" t="inlineStr"/>
       <c r="H576" t="inlineStr">
         <is>
           <t>Y</t>
@@ -89198,7 +89130,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA576" t="inlineStr"/>
       <c r="AB576" t="inlineStr">
         <is>
           <t>한국생산성본부 대전세종충청지역본부 042-489-6056, ykkim@kpc.or.kr / 한국생산성본부 AI 전환센터 02-398-7667, ykkim@kpc.or.kr</t>
@@ -89251,8 +89182,6 @@
           <t>&lt;모집공고&gt;&lt;▶&gt;&lt;신청서류  적정성 검토&gt;&lt;▶&gt;&lt;선정위원회  개최&gt;&lt;▶&gt;&lt;최종 선정  및 선정제품 통보&gt;</t>
         </is>
       </c>
-      <c r="F577" t="inlineStr"/>
-      <c r="G577" t="inlineStr"/>
       <c r="H577" t="inlineStr">
         <is>
           <t>N</t>
@@ -89358,7 +89287,6 @@
           <t>제주특별자치도경제통상진흥원 유통혁신센터 064-805-3352</t>
         </is>
       </c>
-      <c r="AC577" t="inlineStr"/>
       <c r="AD577" t="inlineStr">
         <is>
           <t>064-805-3352</t>
@@ -89407,7 +89335,6 @@
           <t>20억원</t>
         </is>
       </c>
-      <c r="G578" t="inlineStr"/>
       <c r="H578" t="inlineStr">
         <is>
           <t>Y</t>
@@ -89513,7 +89440,6 @@
           <t>충청북도기업진흥원 기업지원부 043-230-9751, 9729</t>
         </is>
       </c>
-      <c r="AC578" t="inlineStr"/>
       <c r="AD578" t="inlineStr">
         <is>
           <t>043-230-9751</t>
@@ -89561,7 +89487,6 @@
           <t>20백만원</t>
         </is>
       </c>
-      <c r="G579" t="inlineStr"/>
       <c r="H579" t="inlineStr">
         <is>
           <t>Y</t>
@@ -89667,7 +89592,6 @@
           <t>경기도경제과학진흥원 동부거점센터 (광주시, 여주시, 양평군) 031-830-8566 (하남시, 이천시) 031-830-8568</t>
         </is>
       </c>
-      <c r="AC579" t="inlineStr"/>
       <c r="AD579" t="inlineStr">
         <is>
           <t>031-830-8566</t>
@@ -89825,7 +89749,6 @@
           <t>전북특별자치도경제통상진흥원 마케팅팀 063-711-2075</t>
         </is>
       </c>
-      <c r="AC580" t="inlineStr"/>
       <c r="AD580" t="inlineStr">
         <is>
           <t>063-711-2075</t>
@@ -89868,8 +89791,6 @@
           <t>□ 지원내용</t>
         </is>
       </c>
-      <c r="F581" t="inlineStr"/>
-      <c r="G581" t="inlineStr"/>
       <c r="H581" t="inlineStr">
         <is>
           <t>Y</t>
@@ -90027,7 +89948,6 @@
           <t>360만원</t>
         </is>
       </c>
-      <c r="G582" t="inlineStr"/>
       <c r="H582" t="inlineStr">
         <is>
           <t>N</t>
@@ -90123,7 +90043,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA582" t="inlineStr"/>
       <c r="AB582" t="inlineStr">
         <is>
           <t>울산경제일자리진흥원 고용창출팀 052-283-7204, dsdszzz@ubpi.or.kr</t>
@@ -90181,7 +90100,6 @@
           <t>20백만원</t>
         </is>
       </c>
-      <c r="G583" t="inlineStr"/>
       <c r="H583" t="inlineStr">
         <is>
           <t>Y</t>
@@ -90334,7 +90252,6 @@
           <t>❍ 모집 규모 : 관내 소상공인 50개사 내외</t>
         </is>
       </c>
-      <c r="F584" t="inlineStr"/>
       <c r="G584" t="inlineStr">
         <is>
           <t>50개</t>
@@ -90435,13 +90352,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AA584" t="inlineStr"/>
       <c r="AB584" t="inlineStr">
         <is>
           <t>광주경제진흥상생일자리재단 소상공인디지털전환실 062-960-2675</t>
         </is>
       </c>
-      <c r="AC584" t="inlineStr"/>
       <c r="AD584" t="inlineStr">
         <is>
           <t>062-960-2675</t>
@@ -90651,7 +90566,6 @@
           <t>10백만원</t>
         </is>
       </c>
-      <c r="G586" t="inlineStr"/>
       <c r="H586" t="inlineStr">
         <is>
           <t>Y</t>
@@ -90775,6 +90689,9187 @@
       <c r="AF586" t="inlineStr">
         <is>
           <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125697</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>[경북] 2026년 경상북도 중소기업 인증브랜드 실라리안 추석 맞이 도청 특별 판매전 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>경상북도경제진흥원</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>이메일 접수(sillarian1997@naver.com)</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>❍ 지원내용</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="inlineStr"/>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z587" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA587" t="inlineStr">
+        <is>
+          <t>참가신청서 1부, 기타사항, ❍ 참가기업 신청 시, 목록 및 양식(첨부파일)을 반드시 확인하시고, pdf 파일로 이메일 접수 바랍니다., 할 수 있습니다., ❍ 전체 추진 일정은 변경될 수 있습니다., 하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="AB587" t="inlineStr">
+        <is>
+          <t>실라리안 담당자 053-243-8581</t>
+        </is>
+      </c>
+      <c r="AC587" t="inlineStr">
+        <is>
+          <t>sillarian1997@naver.com</t>
+        </is>
+      </c>
+      <c r="AD587" t="inlineStr">
+        <is>
+          <t>053-243-8581</t>
+        </is>
+      </c>
+      <c r="AE587" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF587" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125807</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>[전북] 진안군 2026년 사회적경제기업 컨설팅 지원사업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>진안사회적경제지원센터</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>2026-08-21 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>이메일 접수 (jacooplab@daum.net)
+※ 신청 시 담당자 연락처 필수 기재</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>확인 필요 (원문 참고)</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr"/>
+      <c r="G588" t="inlineStr"/>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z588" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA588" t="inlineStr"/>
+      <c r="AB588" t="inlineStr">
+        <is>
+          <t>진안사회적경제지원센터 063-432-9751</t>
+        </is>
+      </c>
+      <c r="AC588" t="inlineStr"/>
+      <c r="AD588" t="inlineStr">
+        <is>
+          <t>063-432-9751</t>
+        </is>
+      </c>
+      <c r="AE588" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF588" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125806</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>[전남광주] 2026년 사회연대경제 서비스체험 페어 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>전남사회적경제통합지원센터</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>상시 접수</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>이메일 접수 (sdcenter@jnsec.kr)</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>1인 20000원, 10인 200000원)</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>200000원</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr"/>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z589" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA589" t="inlineStr">
+        <is>
+          <t>※압축파일로 이메일 제출, 항목, 목록, • 참가신청서 [서식 1], • 기업 및 개인정보 제공·활용 동의서, 필수, • (예비)사회적기업, (예비)마을기업 인증/지정서</t>
+        </is>
+      </c>
+      <c r="AB589" t="inlineStr">
+        <is>
+          <t>전남사회적경제통합지원센터 061-741-9943, sdcenter@jnsec.kr</t>
+        </is>
+      </c>
+      <c r="AC589" t="inlineStr">
+        <is>
+          <t>sdcenter@jnsec.kr</t>
+        </is>
+      </c>
+      <c r="AD589" t="inlineStr">
+        <is>
+          <t>061-741-9943</t>
+        </is>
+      </c>
+      <c r="AE589" t="inlineStr">
+        <is>
+          <t>사회적기업</t>
+        </is>
+      </c>
+      <c r="AF589" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125805</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026년 농식품 중소기업 기술보호 컨설팅 지원사업 참여기업 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>농림식품기술기획평가원</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>온라인 접수(상생누리플랫폼)</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>❍ 접수결과 지원규모 초과시 ①농식품 R&amp;D 수행기업(평가원 소관 R&amp;D)</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr"/>
+      <c r="G590" t="inlineStr"/>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z590" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA590" t="inlineStr">
+        <is>
+          <t>참여 신청서(별첨1), 기업(개인) 정보활용 동의서(별첨2), Ⅱ. 선정방법, 인증기술 및, 《 컨설팅 지원사업 추진 세부절차 》, 구분 수행내용, 신청, 업체선정 ✔ 지원규모(7개사)</t>
+        </is>
+      </c>
+      <c r="AB590" t="inlineStr">
+        <is>
+          <t>농림식품기술기획평가원 기획조정실 061-338-9718, ksh5360@ipet.re.kr</t>
+        </is>
+      </c>
+      <c r="AC590" t="inlineStr">
+        <is>
+          <t>ksh5360@ipet.re.kr</t>
+        </is>
+      </c>
+      <c r="AD590" t="inlineStr">
+        <is>
+          <t>061-338-9718</t>
+        </is>
+      </c>
+      <c r="AE590" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF590" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125804</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>[전북] 진안군 2026년 하반기 착한가격업소 신규 모집 공고</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>모집 마감시까지</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>방문, 이메일 접수
+- 접수처 : 진안군 진안읍 진무로 702-30, 진안군 농촌활력과
+- 이메일 : wjdtjs3595@korea.kr</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>지방세를 3회 이상 및 100만원 이상 체납하고 있는 업소(신청일)</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr"/>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z591" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA591" t="inlineStr"/>
+      <c r="AB591" t="inlineStr">
+        <is>
+          <t>진안군 농촌활력과 민생경제팀 063-430-8055</t>
+        </is>
+      </c>
+      <c r="AC591" t="inlineStr">
+        <is>
+          <t>wjdtjs3595@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD591" t="inlineStr">
+        <is>
+          <t>063-430-8055</t>
+        </is>
+      </c>
+      <c r="AE591" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF591" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125803</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026년 농식품 중소기업 ESG 경영 도입 및 국제표준 인증 취득 지원사업 참여기업 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>농림식품기술기획평가원</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>2026-08-06 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>온라인 접수 (상생누리플랫폼)</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>❍ 접수결과 지원규모 초과시 ①농식품 R&amp;D 수행기업(평가원 소관 R&amp;D)</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr"/>
+      <c r="G592" t="inlineStr"/>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z592" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA592" t="inlineStr">
+        <is>
+          <t>참여 신청서(별첨1), 기업(개인) 정보활용 동의서(별첨2), Ⅱ. 선정방법, 인증기술 및, 《 컨설팅 지원사업 추진 세부절차 》, 구분 수행내용, 신청, 업체선정 ✔ 지원규모(12개사)를 고려</t>
+        </is>
+      </c>
+      <c r="AB592" t="inlineStr">
+        <is>
+          <t>농림식품기술기획평가원 기획조정실 061-338-9718, ksh5360@ipet.re.kr</t>
+        </is>
+      </c>
+      <c r="AC592" t="inlineStr">
+        <is>
+          <t>ksh5360@ipet.re.kr</t>
+        </is>
+      </c>
+      <c r="AD592" t="inlineStr">
+        <is>
+          <t>061-338-9718</t>
+        </is>
+      </c>
+      <c r="AE592" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF592" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125802</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>[전북] 정읍시 2026년 지역특화형비자 외국인 고용 우수기업 지원사업 참여기업 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>방문 또는 이메일 접수
+- 접수처 : 정읍시청 일자리경제과
+- 이메일 : osw2443@korea.kr
+※ 이메일 접수 시 담당자에게 수신 여부 확인 필요</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>(모집규모)</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr"/>
+      <c r="G593" t="inlineStr"/>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q593" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S593" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z593" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA593" t="inlineStr">
+        <is>
+          <t>※ 붙임 서식 참고, 기본서류, 기업소개서(리플릿, 카다로그 등 서식 자율) 1부 【붙임 2】, 기업 정관 1부, 손익계산서) 각 1부, 공인회계사 확인필 또는 홈택스 발급서류), 심사 방법</t>
+        </is>
+      </c>
+      <c r="AB593" t="inlineStr">
+        <is>
+          <t>정읍시 일자리경제과 일자리정책팀 063-539-5605</t>
+        </is>
+      </c>
+      <c r="AC593" t="inlineStr">
+        <is>
+          <t>osw2443@korea.kr</t>
+        </is>
+      </c>
+      <c r="AD593" t="inlineStr">
+        <is>
+          <t>063-539-5605</t>
+        </is>
+      </c>
+      <c r="AE593" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF593" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125801</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>[전북] 정읍시 2026년 하반기 중소기업 환경개선사업 공고</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>기초자치단체</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>2026-08-14 ~ 2026-09-04</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>방문 접수
+- 접수처 : 정읍시청 미래산업과 기업지원팀</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>원대상 선정기업에 한하여 총사업비(부가세포함)가 5백만원 이상인 사업은</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>5백만원</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr"/>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z594" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA594" t="inlineStr"/>
+      <c r="AB594" t="inlineStr">
+        <is>
+          <t>정읍시 미래산업과 기업지원팀 063-539-5663</t>
+        </is>
+      </c>
+      <c r="AC594" t="inlineStr"/>
+      <c r="AD594" t="inlineStr">
+        <is>
+          <t>063-539-5663</t>
+        </is>
+      </c>
+      <c r="AE594" t="inlineStr">
+        <is>
+          <t>중소기업</t>
+        </is>
+      </c>
+      <c r="AF594" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200Detail.do?pblancId=PBLN_000000000125800</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 5차 전북벤처산업발전협의회 벤처기업육성 지원사업 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>한국방산혁신기업협회</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>2026-08-07 ~ 2026-08-27</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>이메일 또는 방문 접수
+- 접수처 : 전북 전주시 덕진구 유상로 67, 스마트배움터 2층 JVADA (사)전북벤처산업발전협의회 
+- 이메일 : jc@jvada.or.kr</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>※총사업비 기준 최대 80%이내, 최대 100만원 이내</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr"/>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J595" 